--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -189,13 +189,10 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -214,20 +211,11 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -279,9 +267,6 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -568,861 +553,982 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="11" customWidth="1" style="23" min="1" max="1"/>
-    <col width="20" customWidth="1" style="23" min="2" max="2"/>
-    <col width="12" customWidth="1" style="23" min="3" max="3"/>
-    <col width="9" customWidth="1" style="23" min="4" max="5"/>
-    <col width="12" customWidth="1" style="23" min="6" max="6"/>
-    <col width="14" customWidth="1" style="23" min="7" max="7"/>
-    <col width="16" customWidth="1" style="23" min="8" max="8"/>
-    <col width="15" customWidth="1" style="23" min="9" max="9"/>
-    <col width="14" customWidth="1" style="23" min="10" max="10"/>
-    <col width="12" customWidth="1" style="23" min="11" max="11"/>
+    <col width="11" customWidth="1" style="19" min="1" max="1"/>
+    <col width="18" customWidth="1" style="19" min="2" max="2"/>
+    <col width="11" customWidth="1" style="19" min="3" max="3"/>
+    <col width="8" customWidth="1" style="19" min="4" max="4"/>
+    <col width="9" customWidth="1" style="19" min="5" max="5"/>
+    <col width="14" customWidth="1" style="19" min="6" max="6"/>
+    <col width="13" customWidth="1" style="19" min="7" max="7"/>
+    <col width="15" customWidth="1" style="19" min="8" max="8"/>
+    <col width="13" customWidth="1" style="19" min="9" max="9"/>
+    <col width="15" customWidth="1" style="19" min="10" max="10"/>
+    <col width="13" customWidth="1" style="19" min="11" max="11"/>
+    <col width="12" customWidth="1" style="19" min="12" max="12"/>
+    <col width="11" customWidth="1" style="19" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="24">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="20">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Эталон ПВЗ Uzum — справочник (источник правды для не-дневных параметров)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="24">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>Синие — редактируемые входы. Заказы/выручка — на листах ниже, накапливаются из узум.xlsx через build_data.py.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="23.25" customHeight="1" s="24">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="20">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Синие — редактируемые входы. OPEX = Аренда + ЗП (месячные, сум). Заказы/выручка — на листах ниже, накапливаются из узум.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23.85" customHeight="1" s="20">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Код</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>AKA</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Сегмент</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Комиссия</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
-        <is>
-          <t>Опекс, $/мес</t>
-        </is>
-      </c>
-      <c r="G4" s="27" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Аренда, сум/мес</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>ЗП, сум/мес</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>Затраты на УК, $/мес</t>
         </is>
       </c>
-      <c r="H4" s="27" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>Разное, сум/мес</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t>Гарантия, сум/мес</t>
         </is>
       </c>
-      <c r="I4" s="27" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t>Прогноз 1-го мес, зак/день</t>
         </is>
       </c>
-      <c r="J4" s="27" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t>Яндекс-пик, зак/день</t>
         </is>
       </c>
-      <c r="K4" s="27" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t>Старт</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="28" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="20">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-290</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Буз-1</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" s="31" t="n">
-        <v>1327.87</v>
-      </c>
-      <c r="G5" s="32" t="n">
+      <c r="F5" s="27" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H5" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H5" s="32" t="n">
+      <c r="I5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I5" s="29" t="n">
+      <c r="K5" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="L5" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="K5" s="33" t="inlineStr">
+      <c r="M5" s="28" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="28" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="20">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-291</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Бабур</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F6" s="31" t="n">
-        <v>1524.59</v>
-      </c>
-      <c r="G6" s="32" t="n">
+      <c r="F6" s="27" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H6" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="I6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="K6" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="L6" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="K6" s="33" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="28" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="20">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-294</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Шастри</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F7" s="31" t="n">
-        <v>1622.95</v>
-      </c>
-      <c r="G7" s="32" t="n">
+      <c r="F7" s="27" t="n">
+        <v>11909091</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H7" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H7" s="32" t="n">
+      <c r="I7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I7" s="29" t="n">
+      <c r="K7" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="L7" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="K7" s="33" t="inlineStr">
+      <c r="M7" s="28" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="28" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="20">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-292</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F8" s="31" t="n">
-        <v>1131.15</v>
-      </c>
-      <c r="G8" s="32" t="n">
+      <c r="F8" s="27" t="n">
+        <v>3647160</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H8" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="I8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="K8" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="L8" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="K8" s="33" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="28" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="20">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>FRАЛМ-9</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Алмалык Амир Т</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Алмалык</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F9" s="31" t="n">
-        <v>1032.79</v>
-      </c>
-      <c r="G9" s="32" t="n">
+      <c r="F9" s="27" t="n">
+        <v>4431000</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="H9" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H9" s="32" t="n">
+      <c r="I9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I9" s="29" t="n">
+      <c r="K9" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="L9" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="K9" s="33" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="28" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="20">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-289</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Афросиаб</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F10" s="31" t="n">
-        <v>1524.59</v>
-      </c>
-      <c r="G10" s="32" t="n">
+      <c r="F10" s="27" t="n">
+        <v>10420455</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H10" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H10" s="32" t="n">
+      <c r="I10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I10" s="29" t="n">
+      <c r="K10" s="25" t="n">
         <v>58</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="L10" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="K10" s="33" t="inlineStr">
+      <c r="M10" s="28" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" s="28" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="20">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-293</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Кургантепа</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F11" s="31" t="n">
-        <v>1327.87</v>
-      </c>
-      <c r="G11" s="32" t="n">
+      <c r="F11" s="27" t="n">
+        <v>7112000</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H11" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H11" s="32" t="n">
+      <c r="I11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I11" s="29" t="n">
+      <c r="K11" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="J11" s="29" t="n">
+      <c r="L11" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="K11" s="33" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" s="28" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="20">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-319</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Баку</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F12" s="31" t="n">
-        <v>1229.51</v>
-      </c>
-      <c r="G12" s="32" t="n">
+      <c r="F12" s="27" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H12" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H12" s="32" t="n">
+      <c r="I12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I12" s="29" t="n">
+      <c r="K12" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="J12" s="29" t="n">
+      <c r="L12" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="K12" s="33" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" s="28" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="20">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>FRБХР-30</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Бухара</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Бухара</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F13" s="31" t="n">
-        <v>1131.15</v>
-      </c>
-      <c r="G13" s="32" t="n">
+      <c r="F13" s="27" t="n">
+        <v>5818182</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="H13" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="I13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I13" s="29" t="n">
+      <c r="K13" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="J13" s="29" t="n">
+      <c r="L13" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="K13" s="33" t="inlineStr">
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" s="28" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="20">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>FRГАЗ-4</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Газалкент</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Газалкент</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F14" s="31" t="n">
-        <v>934.4299999999999</v>
-      </c>
-      <c r="G14" s="32" t="n">
+      <c r="F14" s="27" t="n">
+        <v>2954545</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>7440000</v>
+      </c>
+      <c r="H14" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="I14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I14" s="29" t="n">
+      <c r="K14" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="L14" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="K14" s="33" t="inlineStr">
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="24">
-      <c r="A15" s="28" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="20">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-308</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Янгиюнусабад</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F15" s="31" t="n">
-        <v>1327.87</v>
-      </c>
-      <c r="G15" s="32" t="n">
+      <c r="F15" s="27" t="n">
+        <v>7386364</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H15" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H15" s="32" t="n">
+      <c r="I15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I15" s="29" t="n">
+      <c r="K15" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="L15" s="25" t="n">
         <v>65</v>
       </c>
-      <c r="K15" s="33" t="inlineStr">
+      <c r="M15" s="28" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="24">
-      <c r="A16" s="28" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="20">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>FRБУК-2</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Бука</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Бука</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F16" s="31" t="n">
-        <v>934.4299999999999</v>
-      </c>
-      <c r="G16" s="32" t="n">
+      <c r="F16" s="27" t="n">
+        <v>2954545</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>7440000</v>
+      </c>
+      <c r="H16" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H16" s="32" t="n">
+      <c r="I16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I16" s="29" t="n">
+      <c r="K16" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="J16" s="29" t="n">
+      <c r="L16" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="K16" s="33" t="inlineStr">
+      <c r="M16" s="28" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" s="28" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="20">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>FRСМК-52</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Рудаки</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Самарканд</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F17" s="31" t="n">
-        <v>1278.69</v>
-      </c>
-      <c r="G17" s="32" t="n">
+      <c r="F17" s="27" t="n">
+        <v>7329545</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="H17" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H17" s="32" t="n">
+      <c r="I17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I17" s="29" t="n">
+      <c r="K17" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="L17" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="K17" s="33" t="inlineStr">
+      <c r="M17" s="28" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="24">
-      <c r="A18" s="28" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="20">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>FRАЛМ-10</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Алмалык Мустакилик</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Алмалык</t>
         </is>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F18" s="31" t="n">
-        <v>934.4299999999999</v>
-      </c>
-      <c r="G18" s="32" t="n">
+      <c r="F18" s="27" t="n">
+        <v>3409091</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="H18" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H18" s="32" t="n">
+      <c r="I18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I18" s="29" t="n">
+      <c r="K18" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="J18" s="29" t="n">
+      <c r="L18" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="K18" s="33" t="inlineStr">
+      <c r="M18" s="28" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="24">
-      <c r="A19" s="28" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="20">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>FRПСК-2</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Пскент</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Пскент</t>
         </is>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F19" s="31" t="n">
-        <v>1032.79</v>
-      </c>
-      <c r="G19" s="32" t="n">
+      <c r="F19" s="27" t="n">
+        <v>4435000</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>7440000</v>
+      </c>
+      <c r="H19" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H19" s="32" t="n">
+      <c r="I19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I19" s="29" t="n">
+      <c r="K19" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="J19" s="29" t="n">
+      <c r="L19" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="K19" s="33" t="inlineStr">
+      <c r="M19" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="24">
-      <c r="A20" s="28" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="20">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>FRТАШ-307</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Крестик</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Ташкент</t>
         </is>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="F20" s="31" t="n">
-        <v>1229.51</v>
-      </c>
-      <c r="G20" s="32" t="n">
+      <c r="F20" s="27" t="n">
+        <v>7216000</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>9920000</v>
+      </c>
+      <c r="H20" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H20" s="32" t="n">
+      <c r="I20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="27" t="n">
         <v>17400000</v>
       </c>
-      <c r="I20" s="29" t="n">
+      <c r="K20" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="J20" s="29" t="n">
+      <c r="L20" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K20" s="33" t="inlineStr">
+      <c r="M20" s="28" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="24">
-      <c r="A21" s="28" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="20">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>FRМРГ-8</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Маргилан</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>Маргилан</t>
         </is>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F21" s="31" t="n">
-        <v>934.4299999999999</v>
-      </c>
-      <c r="G21" s="32" t="n">
+      <c r="F21" s="27" t="n">
+        <v>2912000</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="H21" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H21" s="32" t="n">
+      <c r="I21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="27" t="n">
         <v>11400000</v>
       </c>
-      <c r="I21" s="29" t="n">
+      <c r="K21" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="J21" s="29" t="n">
+      <c r="L21" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="K21" s="33" t="inlineStr">
+      <c r="M21" s="28" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="24">
-      <c r="A22" s="28" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="20">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>FRСМК-53</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Андижанская</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Самарканд</t>
         </is>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F22" s="31" t="n">
-        <v>1180.33</v>
-      </c>
-      <c r="G22" s="32" t="n">
+      <c r="F22" s="27" t="n">
+        <v>5864000</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>8680000</v>
+      </c>
+      <c r="H22" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="H22" s="32" t="n">
+      <c r="I22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="27" t="n">
         <v>14000000</v>
       </c>
-      <c r="I22" s="29" t="n">
+      <c r="K22" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="J22" s="29" t="n">
+      <c r="L22" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="K22" s="33" t="inlineStr">
+      <c r="M22" s="28" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -1444,29 +1550,29 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="11" customWidth="1" style="23" min="1" max="1"/>
-    <col width="20" customWidth="1" style="23" min="2" max="2"/>
-    <col width="13" customWidth="1" style="23" min="3" max="6"/>
-    <col width="13" customWidth="1" style="24" min="4" max="4"/>
-    <col width="13" customWidth="1" style="24" min="5" max="5"/>
-    <col width="13" customWidth="1" style="24" min="6" max="6"/>
+    <col width="11" customWidth="1" style="19" min="1" max="1"/>
+    <col width="20" customWidth="1" style="19" min="2" max="2"/>
+    <col width="13" customWidth="1" style="19" min="3" max="6"/>
+    <col width="13" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13" customWidth="1" style="20" min="5" max="5"/>
+    <col width="13" customWidth="1" style="20" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="24">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="20">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Средние заказы в день по неделям (накопительно)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="24">
-      <c r="A2" s="35" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="20">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
         </is>
       </c>
     </row>
-    <row r="3" hidden="1" ht="15" customHeight="1" s="24">
+    <row r="3" hidden="1" ht="15" customHeight="1" s="20">
       <c r="C3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
@@ -1488,510 +1594,510 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="36" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="20">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Код</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>AKA</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>11.05–17.05*</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>18.05–24.05</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>25.05–31.05</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06*</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="37" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="20">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Дней с данными</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr"/>
-      <c r="C5" s="39" t="n">
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="39" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="F5" s="34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="20">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-290</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Буз-1</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="36" t="n">
         <v>37.86</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="36" t="n">
         <v>39.57</v>
       </c>
-      <c r="F6" s="41" t="n">
-        <v>55.5</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="F6" s="36" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="20">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-291</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Бабур</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="36" t="n">
         <v>33.4</v>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="36" t="n">
         <v>41.14</v>
       </c>
-      <c r="E7" s="41" t="n">
+      <c r="E7" s="36" t="n">
         <v>36.43</v>
       </c>
-      <c r="F7" s="41" t="n">
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="F7" s="36" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="20">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-292</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="36" t="n">
         <v>18.6</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="36" t="n">
         <v>21.57</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="36" t="n">
         <v>26.14</v>
       </c>
-      <c r="F8" s="41" t="n">
-        <v>30.75</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="F8" s="36" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="20">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-294</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Шастри</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="20">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-289</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Афросиаб</t>
         </is>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C10" s="36" t="n">
         <v>4.4</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D10" s="36" t="n">
         <v>17.86</v>
       </c>
-      <c r="E9" s="41" t="n">
+      <c r="E10" s="36" t="n">
         <v>20.86</v>
       </c>
-      <c r="F9" s="41" t="n">
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="F10" s="36" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="20">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-293</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Кургантепа</t>
         </is>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C11" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D11" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E11" s="36" t="n">
         <v>17.71</v>
       </c>
-      <c r="F10" s="41" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>FRТАШ-294</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>Шастри</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="D11" s="41" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="E11" s="41" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>22.75</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="F11" s="36" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="20">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-319</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Баку</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="F12" s="36" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="20">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-9</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Амир Т</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="20">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>FRБХР-30</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Бухара</t>
         </is>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C14" s="36" t="n">
         <v>13.8</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D14" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="E12" s="41" t="n">
+      <c r="E14" s="36" t="n">
         <v>15.43</v>
       </c>
-      <c r="F12" s="41" t="n">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" s="40" t="inlineStr">
-        <is>
-          <t>FRАЛМ-9</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>Алмалык Амир Т</t>
-        </is>
-      </c>
-      <c r="C13" s="41" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="D13" s="41" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="E13" s="41" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="F13" s="41" t="n">
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="F14" s="36" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="20">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>FRГАЗ-4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Газалкент</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="20">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-10</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Мустакилик</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="20">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-308</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Янгиюнусабад</t>
         </is>
       </c>
-      <c r="C14" s="41" t="n">
+      <c r="C17" s="36" t="n">
         <v>10.8</v>
       </c>
-      <c r="D14" s="41" t="n">
+      <c r="D17" s="36" t="n">
         <v>13.57</v>
       </c>
-      <c r="E14" s="41" t="n">
+      <c r="E17" s="36" t="n">
         <v>12.57</v>
       </c>
-      <c r="F14" s="41" t="n">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="24">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>FRГАЗ-4</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>Газалкент</t>
-        </is>
-      </c>
-      <c r="C15" s="41" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D15" s="41" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="E15" s="41" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="F15" s="41" t="n">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="24">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="F17" s="36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="20">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-307</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Крестик</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D18" s="36" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="20">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>FRБУК-2</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Бука</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="F19" s="36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="20">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>FRСМК-52</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Рудаки</t>
         </is>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C20" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D20" s="36" t="n">
         <v>10.43</v>
       </c>
-      <c r="E16" s="41" t="n">
+      <c r="E20" s="36" t="n">
         <v>11.14</v>
       </c>
-      <c r="F16" s="41" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>FRТАШ-319</t>
-        </is>
-      </c>
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>Баку</t>
-        </is>
-      </c>
-      <c r="C17" s="41" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="D17" s="41" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="E17" s="41" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="F17" s="41" t="n">
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="24">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>FRАЛМ-10</t>
-        </is>
-      </c>
-      <c r="B18" s="40" t="inlineStr">
-        <is>
-          <t>Алмалык Мустакилик</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D18" s="41" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="E18" s="41" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="F18" s="41" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="24">
-      <c r="A19" s="40" t="inlineStr">
-        <is>
-          <t>FRБУК-2</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>Бука</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="n">
+      <c r="F20" s="36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="20">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>FRПСК-2</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Пскент</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E21" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="D19" s="41" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="E19" s="41" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="F19" s="41" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="24">
-      <c r="A20" s="40" t="inlineStr">
-        <is>
-          <t>FRПСК-2</t>
-        </is>
-      </c>
-      <c r="B20" s="40" t="inlineStr">
-        <is>
-          <t>Пскент</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="n">
+      <c r="F21" s="36" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="20">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>FRМРГ-8</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Маргилан</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="41" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E20" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="41" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="24">
-      <c r="A21" s="40" t="inlineStr">
-        <is>
-          <t>FRТАШ-307</t>
-        </is>
-      </c>
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>Крестик</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D21" s="41" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="E21" s="41" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F21" s="41" t="n">
+      <c r="D22" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F22" s="36" t="n">
         <v>8.5</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="24">
-      <c r="A22" s="40" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="20">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>FRСМК-53</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Андижанская</t>
         </is>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C23" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="41" t="n">
+      <c r="D23" s="36" t="n">
         <v>0.14</v>
       </c>
-      <c r="E22" s="41" t="n">
+      <c r="E23" s="36" t="n">
         <v>2.86</v>
       </c>
-      <c r="F22" s="41" t="n">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="24">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>FRМРГ-8</t>
-        </is>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>Маргилан</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="41" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="F23" s="41" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="24">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="F23" s="36" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="20">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>В среднем на ПВЗ</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr"/>
-      <c r="C24" s="44">
+      <c r="B24" s="38" t="inlineStr"/>
+      <c r="C24" s="39">
         <f>AVERAGE(C6:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="39">
         <f>AVERAGE(D6:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="39">
         <f>AVERAGE(E6:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="39">
         <f>AVERAGE(F6:F23)</f>
         <v/>
       </c>
@@ -2012,29 +2118,29 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="11" customWidth="1" style="23" min="1" max="1"/>
-    <col width="20" customWidth="1" style="23" min="2" max="2"/>
-    <col width="13" customWidth="1" style="23" min="3" max="6"/>
-    <col width="13" customWidth="1" style="24" min="4" max="4"/>
-    <col width="13" customWidth="1" style="24" min="5" max="5"/>
-    <col width="13" customWidth="1" style="24" min="6" max="6"/>
+    <col width="11" customWidth="1" style="19" min="1" max="1"/>
+    <col width="20" customWidth="1" style="19" min="2" max="2"/>
+    <col width="13" customWidth="1" style="19" min="3" max="6"/>
+    <col width="13" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13" customWidth="1" style="20" min="5" max="5"/>
+    <col width="13" customWidth="1" style="20" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="24">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="20">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Сумма выручки (объём) по неделям, сум (накопительно)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="24">
-      <c r="A2" s="35" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="20">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
         </is>
       </c>
     </row>
-    <row r="3" hidden="1" ht="15" customHeight="1" s="24">
+    <row r="3" hidden="1" ht="15" customHeight="1" s="20">
       <c r="C3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
@@ -2056,510 +2162,510 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="36" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="20">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Код</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>AKA</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>11.05–17.05*</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>18.05–24.05</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>25.05–31.05</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06*</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="37" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="20">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Дней с данными</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr"/>
-      <c r="C5" s="39" t="n">
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="39" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="F5" s="34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="20">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-290</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Буз-1</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n">
+      <c r="C6" s="40" t="n">
         <v>26572309</v>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="40" t="n">
         <v>54415488</v>
       </c>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="40" t="n">
         <v>46859038</v>
       </c>
-      <c r="F6" s="45" t="n">
-        <v>31785581</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="F6" s="40" t="n">
+        <v>22088856</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="20">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-291</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Бабур</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="40" t="n">
         <v>25945431</v>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="40" t="n">
         <v>37459210</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="40" t="n">
         <v>48992678</v>
       </c>
-      <c r="F7" s="45" t="n">
-        <v>35581023</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="F7" s="40" t="n">
+        <v>7192321</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="20">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-292</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="40" t="n">
         <v>14023998</v>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="40" t="n">
         <v>23623555</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="40" t="n">
         <v>37049808</v>
       </c>
-      <c r="F8" s="45" t="n">
-        <v>25462608</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="F8" s="40" t="n">
+        <v>15343237</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="20">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-294</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Шастри</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>11787061</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>33489630</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>34406847</v>
+      </c>
+      <c r="F9" s="40" t="n">
+        <v>4614543</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="20">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-289</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Афросиаб</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C10" s="40" t="n">
         <v>3579870</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D10" s="40" t="n">
         <v>26016508</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E10" s="40" t="n">
         <v>28967720</v>
       </c>
-      <c r="F9" s="45" t="n">
-        <v>21236946</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="F10" s="40" t="n">
+        <v>8017702</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="20">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-293</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Кургантепа</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n">
+      <c r="C11" s="40" t="n">
         <v>9063650</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D11" s="40" t="n">
         <v>19435779</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E11" s="40" t="n">
         <v>20382320</v>
       </c>
-      <c r="F10" s="45" t="n">
-        <v>10697485</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>FRТАШ-294</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>Шастри</t>
-        </is>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>11787061</v>
-      </c>
-      <c r="D11" s="45" t="n">
-        <v>33489630</v>
-      </c>
-      <c r="E11" s="45" t="n">
-        <v>34406847</v>
-      </c>
-      <c r="F11" s="45" t="n">
-        <v>15532201</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="F11" s="40" t="n">
+        <v>3952124</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="20">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-319</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Баку</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>11237754</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>29303296</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>17092421</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <v>7508366</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="20">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-9</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Амир Т</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>13421812</v>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>19296100</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>32898025</v>
+      </c>
+      <c r="F13" s="40" t="n">
+        <v>6157955</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="20">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>FRБХР-30</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Бухара</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C14" s="40" t="n">
         <v>10462042</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D14" s="40" t="n">
         <v>24242808</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E14" s="40" t="n">
         <v>20176647</v>
       </c>
-      <c r="F12" s="45" t="n">
-        <v>8986966</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" s="40" t="inlineStr">
-        <is>
-          <t>FRАЛМ-9</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>Алмалык Амир Т</t>
-        </is>
-      </c>
-      <c r="C13" s="45" t="n">
-        <v>13421812</v>
-      </c>
-      <c r="D13" s="45" t="n">
-        <v>19296100</v>
-      </c>
-      <c r="E13" s="45" t="n">
-        <v>32898025</v>
-      </c>
-      <c r="F13" s="45" t="n">
-        <v>12540076</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="F14" s="40" t="n">
+        <v>3643570</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="20">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>FRГАЗ-4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Газалкент</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>6139086</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>14744333</v>
+      </c>
+      <c r="E15" s="40" t="n">
+        <v>18390296</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <v>6589707</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="20">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-10</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Мустакилик</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>6011315</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>10213590</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>10032796</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>5098524</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="20">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>FRТАШ-308</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Янгиюнусабад</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n">
+      <c r="C17" s="40" t="n">
         <v>7434617</v>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D17" s="40" t="n">
         <v>11541808</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E17" s="40" t="n">
         <v>11589026</v>
       </c>
-      <c r="F14" s="45" t="n">
-        <v>13830368</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="24">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>FRГАЗ-4</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>Газалкент</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="n">
-        <v>6139086</v>
-      </c>
-      <c r="D15" s="45" t="n">
-        <v>14744333</v>
-      </c>
-      <c r="E15" s="45" t="n">
-        <v>18390296</v>
-      </c>
-      <c r="F15" s="45" t="n">
-        <v>11768949</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="24">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="F17" s="40" t="n">
+        <v>3737498</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="20">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-307</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Крестик</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>2876909</v>
+      </c>
+      <c r="D18" s="40" t="n">
+        <v>6793378</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>3855907</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>2500720</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="20">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>FRБУК-2</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Бука</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>6458596</v>
+      </c>
+      <c r="D19" s="40" t="n">
+        <v>16321651</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>12911381</v>
+      </c>
+      <c r="F19" s="40" t="n">
+        <v>2821800</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="20">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>FRСМК-52</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Рудаки</t>
         </is>
       </c>
-      <c r="C16" s="45" t="n">
+      <c r="C20" s="40" t="n">
         <v>6460094</v>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="D20" s="40" t="n">
         <v>14908071</v>
       </c>
-      <c r="E16" s="45" t="n">
+      <c r="E20" s="40" t="n">
         <v>20904887</v>
       </c>
-      <c r="F16" s="45" t="n">
-        <v>7784127</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>FRТАШ-319</t>
-        </is>
-      </c>
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>Баку</t>
-        </is>
-      </c>
-      <c r="C17" s="45" t="n">
-        <v>11237754</v>
-      </c>
-      <c r="D17" s="45" t="n">
-        <v>29303296</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <v>17092421</v>
-      </c>
-      <c r="F17" s="45" t="n">
-        <v>10612356</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="24">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>FRАЛМ-10</t>
-        </is>
-      </c>
-      <c r="B18" s="40" t="inlineStr">
-        <is>
-          <t>Алмалык Мустакилик</t>
-        </is>
-      </c>
-      <c r="C18" s="45" t="n">
-        <v>6011315</v>
-      </c>
-      <c r="D18" s="45" t="n">
-        <v>10213590</v>
-      </c>
-      <c r="E18" s="45" t="n">
-        <v>10032796</v>
-      </c>
-      <c r="F18" s="45" t="n">
-        <v>12192687</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="24">
-      <c r="A19" s="40" t="inlineStr">
-        <is>
-          <t>FRБУК-2</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>Бука</t>
-        </is>
-      </c>
-      <c r="C19" s="45" t="n">
-        <v>6458596</v>
-      </c>
-      <c r="D19" s="45" t="n">
-        <v>16321651</v>
-      </c>
-      <c r="E19" s="45" t="n">
-        <v>12911381</v>
-      </c>
-      <c r="F19" s="45" t="n">
-        <v>8820297</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="24">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="F20" s="40" t="n">
+        <v>3500535</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="20">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>FRПСК-2</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Пскент</t>
         </is>
       </c>
-      <c r="C20" s="45" t="n">
+      <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D21" s="40" t="n">
         <v>1357510</v>
       </c>
-      <c r="E20" s="45" t="n">
+      <c r="E21" s="40" t="n">
         <v>9736256</v>
       </c>
-      <c r="F20" s="45" t="n">
-        <v>5155323</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="24">
-      <c r="A21" s="40" t="inlineStr">
-        <is>
-          <t>FRТАШ-307</t>
-        </is>
-      </c>
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>Крестик</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="n">
-        <v>2876909</v>
-      </c>
-      <c r="D21" s="45" t="n">
-        <v>6793378</v>
-      </c>
-      <c r="E21" s="45" t="n">
-        <v>3855907</v>
-      </c>
-      <c r="F21" s="45" t="n">
-        <v>4450940</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="24">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="F21" s="40" t="n">
+        <v>2131223</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="20">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>FRМРГ-8</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Маргилан</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="40" t="n">
+        <v>1377990</v>
+      </c>
+      <c r="E22" s="40" t="n">
+        <v>3465270</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <v>3033290</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="20">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>FRСМК-53</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Андижанская</t>
         </is>
       </c>
-      <c r="C22" s="45" t="n">
+      <c r="C23" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="45" t="n">
+      <c r="D23" s="40" t="n">
         <v>363900</v>
       </c>
-      <c r="E22" s="45" t="n">
+      <c r="E23" s="40" t="n">
         <v>3477490</v>
       </c>
-      <c r="F22" s="45" t="n">
-        <v>3735640</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="24">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>FRМРГ-8</t>
-        </is>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>Маргилан</t>
-        </is>
-      </c>
-      <c r="C23" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="45" t="n">
-        <v>1377990</v>
-      </c>
-      <c r="E23" s="45" t="n">
-        <v>3465270</v>
-      </c>
-      <c r="F23" s="45" t="n">
-        <v>3454610</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="24">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="F23" s="40" t="n">
+        <v>2293470</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="20">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>В среднем на ПВЗ</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr"/>
-      <c r="C24" s="46">
+      <c r="B24" s="38" t="inlineStr"/>
+      <c r="C24" s="41">
         <f>AVERAGE(C6:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="41">
         <f>AVERAGE(D6:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="41">
         <f>AVERAGE(E6:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="46">
+      <c r="F24" s="41">
         <f>AVERAGE(F6:F23)</f>
         <v/>
       </c>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Сатори_факт" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1573,22 +1574,22 @@
       </c>
     </row>
     <row r="3" hidden="1" ht="15" customHeight="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -2141,22 +2142,22 @@
       </c>
     </row>
     <row r="3" hidden="1" ht="15" customHeight="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -2675,4 +2676,354 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="20" min="1" max="1"/>
+    <col width="22" customWidth="1" style="20" min="2" max="2"/>
+    <col width="15" customWidth="1" style="20" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Факт по отчётам «Сатори» (агентское вознаграждение Uzum), сум — накопительно по месяцам</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Доход ПВЗ = фикс. вознаграждение (гарантия, прорейчено) + п.1.8 + компенсация п.5.2.1. Закрытые месяцы не переписываются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1" s="20">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>AKA</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>май 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Дней в месяце</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-290</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Буз-1</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>14619948</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-291</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Бабур</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>14598348</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-294</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Шастри</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>23504800</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-292</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>14593548</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-9</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Амир Т</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>11291523</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-289</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Афросиаб</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>10117626</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-293</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Кургантепа</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>11234206</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-319</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Баку</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>14598348</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>FRБХР-30</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Бухара</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>14003600</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>FRГАЗ-4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Газалкент</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>14001200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-308</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Янгиюнусабад</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>17401200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>FRБУК-2</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Бука</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>12193548</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-52</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Рудаки</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>12645161</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-10</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Мустакилик</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>11744335</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>FRПСК-2</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>Пскент</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="n">
+        <v>5422955</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-307</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Крестик</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="n">
+        <v>23501200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>FRМРГ-8</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Маргилан</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="n">
+        <v>5148387</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-53</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Андижанская</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="n">
+        <v>4967742</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>ИТОГО по сети</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr"/>
+      <c r="C24" s="41">
+        <f>SUM(C6:C23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1574,22 +1574,22 @@
       </c>
     </row>
     <row r="3" hidden="1" ht="15" customHeight="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -1644,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
@@ -1668,7 +1668,7 @@
         <v>39.57</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>54.5</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
@@ -1692,7 +1692,7 @@
         <v>36.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>34</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
@@ -1716,7 +1716,7 @@
         <v>26.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>32.5</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
@@ -1740,79 +1740,79 @@
         <v>28.29</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>25</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>17.86</v>
+        <v>13</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>20.86</v>
+        <v>17.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>20.5</v>
+        <v>26.17</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>13</v>
+        <v>17.86</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>17.71</v>
+        <v>20.86</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>19.5</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>14.8</v>
+        <v>10.8</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>19.43</v>
+        <v>13.57</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>15.71</v>
+        <v>12.57</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>18.5</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
@@ -1836,7 +1836,7 @@
         <v>20.86</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
@@ -1860,7 +1860,7 @@
         <v>15.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>15</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
@@ -1884,79 +1884,79 @@
         <v>14.57</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>7.2</v>
+        <v>14.8</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>12.5</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>13.57</v>
+        <v>10.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>12.57</v>
+        <v>11.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>12</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>5.14</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>5.29</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>10</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="20">
@@ -1980,103 +1980,103 @@
         <v>11.29</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>9</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>10.43</v>
+        <v>1.86</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11.14</v>
+        <v>7</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>9</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="20">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>1.86</v>
+        <v>5.14</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>7</v>
+        <v>5.29</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>8.5</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="20">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0.14</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>3.86</v>
+        <v>2.86</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>8.5</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="20">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0.14</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>2.86</v>
+        <v>3.86</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="20">
@@ -2142,22 +2142,22 @@
       </c>
     </row>
     <row r="3" hidden="1" ht="15" customHeight="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -2212,7 +2212,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
@@ -2236,7 +2236,7 @@
         <v>46859038</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>22088856</v>
+        <v>48579042</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
@@ -2260,7 +2260,7 @@
         <v>48992678</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>7192321</v>
+        <v>53854155</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
@@ -2284,7 +2284,7 @@
         <v>37049808</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>15343237</v>
+        <v>40451915</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
@@ -2308,79 +2308,79 @@
         <v>34406847</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>4614543</v>
+        <v>30921846</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>3579870</v>
+        <v>9063650</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>26016508</v>
+        <v>19435779</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>28967720</v>
+        <v>20382320</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>8017702</v>
+        <v>19881940</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9063650</v>
+        <v>3579870</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>19435779</v>
+        <v>26016508</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>20382320</v>
+        <v>28967720</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>3952124</v>
+        <v>32817499</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>11237754</v>
+        <v>7434617</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>29303296</v>
+        <v>11541808</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>17092421</v>
+        <v>11589026</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>7508366</v>
+        <v>18761766</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
@@ -2404,7 +2404,7 @@
         <v>32898025</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>6157955</v>
+        <v>17321896</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
@@ -2428,7 +2428,7 @@
         <v>20176647</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>3643570</v>
+        <v>11784346</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
@@ -2452,79 +2452,79 @@
         <v>18390296</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>6589707</v>
+        <v>16425734</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>6011315</v>
+        <v>11237754</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>10213590</v>
+        <v>29303296</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10032796</v>
+        <v>17092421</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>5098524</v>
+        <v>17761925</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>7434617</v>
+        <v>6460094</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>11541808</v>
+        <v>14908071</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11589026</v>
+        <v>20904887</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>3737498</v>
+        <v>11751567</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>2876909</v>
+        <v>6011315</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>6793378</v>
+        <v>10213590</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>3855907</v>
+        <v>10032796</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>2500720</v>
+        <v>18597957</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="20">
@@ -2548,103 +2548,103 @@
         <v>12911381</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>2821800</v>
+        <v>14145441</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6460094</v>
+        <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>14908071</v>
+        <v>1357510</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>20904887</v>
+        <v>9736256</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>3500535</v>
+        <v>17092703</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="20">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>0</v>
+        <v>2876909</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>1357510</v>
+        <v>6793378</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>9736256</v>
+        <v>3855907</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>2131223</v>
+        <v>6798330</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="20">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>1377990</v>
+        <v>363900</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>3465270</v>
+        <v>3477490</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>3033290</v>
+        <v>5756798</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="20">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>363900</v>
+        <v>1377990</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>3477490</v>
+        <v>3465270</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>2293470</v>
+        <v>4096000</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="20">
@@ -2707,7 +2707,7 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Сатори_факт" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сатори_факт" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дни_по_неделям" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -190,7 +191,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -299,6 +300,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1623,7 +1630,7 @@
       </c>
       <c r="F4" s="31" t="inlineStr">
         <is>
-          <t>01.06–07.06*</t>
+          <t>01.06–07.06</t>
         </is>
       </c>
     </row>
@@ -1644,55 +1651,55 @@
         <v>7</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>30</v>
+        <v>33.4</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>37.86</v>
+        <v>41.14</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>39.57</v>
+        <v>36.43</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>53.67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>33.4</v>
+        <v>30</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>41.14</v>
+        <v>37.86</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>36.43</v>
+        <v>39.57</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>50.5</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
@@ -1716,7 +1723,7 @@
         <v>26.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>33.33</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
@@ -1740,7 +1747,7 @@
         <v>28.29</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.33</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
@@ -1764,7 +1771,7 @@
         <v>17.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.17</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
@@ -1788,7 +1795,7 @@
         <v>20.86</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>24.83</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
@@ -1812,7 +1819,7 @@
         <v>12.57</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>17.33</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
@@ -1836,7 +1843,7 @@
         <v>20.86</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
@@ -1860,7 +1867,7 @@
         <v>15.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.83</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
@@ -1884,7 +1891,7 @@
         <v>14.57</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>15.83</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
@@ -1908,79 +1915,79 @@
         <v>15.71</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>15.67</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="20">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>12.57</v>
+        <v>10.43</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.29</v>
+        <v>11.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>12.67</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
@@ -2004,55 +2011,55 @@
         <v>7</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>9.83</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="20">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>5.14</v>
+        <v>0.14</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>5.29</v>
+        <v>2.86</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>8.17</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="20">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0.14</v>
+        <v>5.14</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>2.86</v>
+        <v>5.29</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>7.33</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="20">
@@ -2076,7 +2083,7 @@
         <v>3.86</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="20">
@@ -2191,7 +2198,7 @@
       </c>
       <c r="F4" s="31" t="inlineStr">
         <is>
-          <t>01.06–07.06*</t>
+          <t>01.06–07.06</t>
         </is>
       </c>
     </row>
@@ -2212,55 +2219,55 @@
         <v>7</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
-        <v>26572309</v>
+        <v>25945431</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>54415488</v>
+        <v>37459210</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>46859038</v>
+        <v>48992678</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>48579042</v>
+        <v>64308195</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>25945431</v>
+        <v>26572309</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>37459210</v>
+        <v>54415488</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>48992678</v>
+        <v>46859038</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>53854155</v>
+        <v>52194797</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="20">
@@ -2284,7 +2291,7 @@
         <v>37049808</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>40451915</v>
+        <v>48937774</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
@@ -2308,7 +2315,7 @@
         <v>34406847</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30921846</v>
+        <v>37161831</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
@@ -2332,7 +2339,7 @@
         <v>20382320</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>19881940</v>
+        <v>23759937</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
@@ -2356,7 +2363,7 @@
         <v>28967720</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>32817499</v>
+        <v>37959389</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
@@ -2380,7 +2387,7 @@
         <v>11589026</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18761766</v>
+        <v>20628257</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
@@ -2404,7 +2411,7 @@
         <v>32898025</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>17321896</v>
+        <v>20322786</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
@@ -2428,7 +2435,7 @@
         <v>20176647</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>11784346</v>
+        <v>18937286</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
@@ -2452,7 +2459,7 @@
         <v>18390296</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>16425734</v>
+        <v>19525644</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
@@ -2476,79 +2483,79 @@
         <v>17092421</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>17761925</v>
+        <v>18898662</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="20">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>11751567</v>
+        <v>23828037</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6011315</v>
+        <v>6458596</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>10213590</v>
+        <v>16321651</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10032796</v>
+        <v>12911381</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>18597957</v>
+        <v>18213851</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="20">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6458596</v>
+        <v>6460094</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>16321651</v>
+        <v>14908071</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>12911381</v>
+        <v>20904887</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14145441</v>
+        <v>14174417</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
@@ -2572,55 +2579,55 @@
         <v>9736256</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>17092703</v>
+        <v>18439963</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="20">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>2876909</v>
+        <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>6793378</v>
+        <v>363900</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>3855907</v>
+        <v>3477490</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>6798330</v>
+        <v>6698688</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="20">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>2876909</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>363900</v>
+        <v>6793378</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>3477490</v>
+        <v>3855907</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>5756798</v>
+        <v>7337990</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="20">
@@ -2644,7 +2651,7 @@
         <v>3465270</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>4096000</v>
+        <v>4464440</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="20">
@@ -3026,4 +3033,570 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="20" min="1" max="1"/>
+    <col width="20" customWidth="1" style="20" min="2" max="2"/>
+    <col width="13" customWidth="1" style="20" min="3" max="3"/>
+    <col width="13" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13" customWidth="1" style="20" min="5" max="5"/>
+    <col width="13" customWidth="1" style="20" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Дней с данными по каждому ПВЗ за неделю (накопительно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1" s="20">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>AKA</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>11.05–17.05*</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>18.05–24.05</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>25.05–31.05</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>01.06–07.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Дней с данными</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-291</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Бабур</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-290</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Буз-1</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-292</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-294</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Шастри</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-293</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Кургантепа</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-289</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Афросиаб</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-308</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Янгиюнусабад</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-9</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Амир Т</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>FRБХР-30</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Бухара</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>FRГАЗ-4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Газалкент</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-319</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Баку</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-10</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Мустакилик</t>
+        </is>
+      </c>
+      <c r="C17" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>FRБУК-2</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Бука</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-52</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Рудаки</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>FRПСК-2</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>Пскент</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-53</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Андижанская</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-307</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Крестик</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>FRМРГ-8</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Маргилан</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>В среднем на ПВЗ</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr"/>
+      <c r="C24" s="43">
+        <f>AVERAGE(C6:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="43">
+        <f>AVERAGE(D6:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="43">
+        <f>AVERAGE(E6:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="43">
+        <f>AVERAGE(F6:F23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы_по_неделям" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сатори_факт" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сатори_факт" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы_по_неделям" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём_по_неделям" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дни_по_неделям" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -1551,1142 +1551,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="11" customWidth="1" style="19" min="1" max="1"/>
-    <col width="20" customWidth="1" style="19" min="2" max="2"/>
-    <col width="13" customWidth="1" style="19" min="3" max="6"/>
-    <col width="13" customWidth="1" style="20" min="4" max="4"/>
-    <col width="13" customWidth="1" style="20" min="5" max="5"/>
-    <col width="13" customWidth="1" style="20" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="20">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>Средние заказы в день по неделям (накопительно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="20">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1" ht="15" customHeight="1" s="20">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>AKA</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>11.05–17.05*</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>18.05–24.05</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>25.05–31.05</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>01.06–07.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="20">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t>Дней с данными</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr"/>
-      <c r="C5" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="20">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-291</t>
-        </is>
-      </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>Бабур</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>36.43</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-290</t>
-        </is>
-      </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>Буз-1</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" s="36" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="E7" s="36" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="F7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-292</t>
-        </is>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Спутник</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>26.14</v>
-      </c>
-      <c r="F8" s="36" t="n">
-        <v>35.57</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="20">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-294</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>Шастри</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="E9" s="36" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="F9" s="36" t="n">
-        <v>28.71</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-293</t>
-        </is>
-      </c>
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>Кургантепа</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>26.57</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-289</t>
-        </is>
-      </c>
-      <c r="B11" s="35" t="inlineStr">
-        <is>
-          <t>Афросиаб</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>24.86</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-308</t>
-        </is>
-      </c>
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>Янгиюнусабад</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>17.57</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="20">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>FRАЛМ-9</t>
-        </is>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>Алмалык Амир Т</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>17.14</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="20">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>FRБХР-30</t>
-        </is>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>Бухара</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="D14" s="36" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="F14" s="36" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="20">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>FRГАЗ-4</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Газалкент</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>16.71</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="20">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-319</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Баку</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>14.86</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="20">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>FRАЛМ-10</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>Алмалык Мустакилик</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D17" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>14.14</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="20">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>FRБУК-2</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>Бука</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" s="36" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>13.43</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="20">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>FRСМК-52</t>
-        </is>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>Рудаки</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D19" s="36" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="E19" s="36" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>13.43</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>FRПСК-2</t>
-        </is>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>Пскент</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E20" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>9.289999999999999</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="20">
-      <c r="A21" s="35" t="inlineStr">
-        <is>
-          <t>FRСМК-53</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>Андижанская</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E21" s="36" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>8.43</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="20">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-307</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>Крестик</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="E22" s="36" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F22" s="36" t="n">
-        <v>7.86</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="20">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>FRМРГ-8</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>Маргилан</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="F23" s="36" t="n">
-        <v>5.86</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="20">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>В среднем на ПВЗ</t>
-        </is>
-      </c>
-      <c r="B24" s="38" t="inlineStr"/>
-      <c r="C24" s="39">
-        <f>AVERAGE(C6:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="39">
-        <f>AVERAGE(D6:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="39">
-        <f>AVERAGE(E6:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="39">
-        <f>AVERAGE(F6:F23)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="11" customWidth="1" style="19" min="1" max="1"/>
-    <col width="20" customWidth="1" style="19" min="2" max="2"/>
-    <col width="13" customWidth="1" style="19" min="3" max="6"/>
-    <col width="13" customWidth="1" style="20" min="4" max="4"/>
-    <col width="13" customWidth="1" style="20" min="5" max="5"/>
-    <col width="13" customWidth="1" style="20" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="20">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>Сумма выручки (объём) по неделям, сум (накопительно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="20">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1" ht="15" customHeight="1" s="20">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>AKA</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>11.05–17.05*</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>18.05–24.05</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>25.05–31.05</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>01.06–07.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="20">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t>Дней с данными</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr"/>
-      <c r="C5" s="34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="34" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="20">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-291</t>
-        </is>
-      </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>Бабур</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="n">
-        <v>25945431</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>37459210</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <v>48992678</v>
-      </c>
-      <c r="F6" s="40" t="n">
-        <v>64308195</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-290</t>
-        </is>
-      </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>Буз-1</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="n">
-        <v>26572309</v>
-      </c>
-      <c r="D7" s="40" t="n">
-        <v>54415488</v>
-      </c>
-      <c r="E7" s="40" t="n">
-        <v>46859038</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <v>52194797</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-292</t>
-        </is>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Спутник</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="n">
-        <v>14023998</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>23623555</v>
-      </c>
-      <c r="E8" s="40" t="n">
-        <v>37049808</v>
-      </c>
-      <c r="F8" s="40" t="n">
-        <v>48937774</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="20">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-294</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>Шастри</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="n">
-        <v>11787061</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <v>33489630</v>
-      </c>
-      <c r="E9" s="40" t="n">
-        <v>34406847</v>
-      </c>
-      <c r="F9" s="40" t="n">
-        <v>37161831</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-293</t>
-        </is>
-      </c>
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>Кургантепа</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="n">
-        <v>9063650</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>19435779</v>
-      </c>
-      <c r="E10" s="40" t="n">
-        <v>20382320</v>
-      </c>
-      <c r="F10" s="40" t="n">
-        <v>23759937</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-289</t>
-        </is>
-      </c>
-      <c r="B11" s="35" t="inlineStr">
-        <is>
-          <t>Афросиаб</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="n">
-        <v>3579870</v>
-      </c>
-      <c r="D11" s="40" t="n">
-        <v>26016508</v>
-      </c>
-      <c r="E11" s="40" t="n">
-        <v>28967720</v>
-      </c>
-      <c r="F11" s="40" t="n">
-        <v>37959389</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-308</t>
-        </is>
-      </c>
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>Янгиюнусабад</t>
-        </is>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>7434617</v>
-      </c>
-      <c r="D12" s="40" t="n">
-        <v>11541808</v>
-      </c>
-      <c r="E12" s="40" t="n">
-        <v>11589026</v>
-      </c>
-      <c r="F12" s="40" t="n">
-        <v>20628257</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="20">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>FRАЛМ-9</t>
-        </is>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>Алмалык Амир Т</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="n">
-        <v>13421812</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>19296100</v>
-      </c>
-      <c r="E13" s="40" t="n">
-        <v>32898025</v>
-      </c>
-      <c r="F13" s="40" t="n">
-        <v>20322786</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="20">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>FRБХР-30</t>
-        </is>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>Бухара</t>
-        </is>
-      </c>
-      <c r="C14" s="40" t="n">
-        <v>10462042</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>24242808</v>
-      </c>
-      <c r="E14" s="40" t="n">
-        <v>20176647</v>
-      </c>
-      <c r="F14" s="40" t="n">
-        <v>18937286</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="20">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>FRГАЗ-4</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Газалкент</t>
-        </is>
-      </c>
-      <c r="C15" s="40" t="n">
-        <v>6139086</v>
-      </c>
-      <c r="D15" s="40" t="n">
-        <v>14744333</v>
-      </c>
-      <c r="E15" s="40" t="n">
-        <v>18390296</v>
-      </c>
-      <c r="F15" s="40" t="n">
-        <v>19525644</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="20">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-319</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Баку</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="n">
-        <v>11237754</v>
-      </c>
-      <c r="D16" s="40" t="n">
-        <v>29303296</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>17092421</v>
-      </c>
-      <c r="F16" s="40" t="n">
-        <v>18898662</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="20">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>FRАЛМ-10</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>Алмалык Мустакилик</t>
-        </is>
-      </c>
-      <c r="C17" s="40" t="n">
-        <v>6011315</v>
-      </c>
-      <c r="D17" s="40" t="n">
-        <v>10213590</v>
-      </c>
-      <c r="E17" s="40" t="n">
-        <v>10032796</v>
-      </c>
-      <c r="F17" s="40" t="n">
-        <v>23828037</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="20">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>FRБУК-2</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>Бука</t>
-        </is>
-      </c>
-      <c r="C18" s="40" t="n">
-        <v>6458596</v>
-      </c>
-      <c r="D18" s="40" t="n">
-        <v>16321651</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <v>12911381</v>
-      </c>
-      <c r="F18" s="40" t="n">
-        <v>18213851</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="20">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>FRСМК-52</t>
-        </is>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>Рудаки</t>
-        </is>
-      </c>
-      <c r="C19" s="40" t="n">
-        <v>6460094</v>
-      </c>
-      <c r="D19" s="40" t="n">
-        <v>14908071</v>
-      </c>
-      <c r="E19" s="40" t="n">
-        <v>20904887</v>
-      </c>
-      <c r="F19" s="40" t="n">
-        <v>14174417</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>FRПСК-2</t>
-        </is>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>Пскент</t>
-        </is>
-      </c>
-      <c r="C20" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="40" t="n">
-        <v>1357510</v>
-      </c>
-      <c r="E20" s="40" t="n">
-        <v>9736256</v>
-      </c>
-      <c r="F20" s="40" t="n">
-        <v>18439963</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="20">
-      <c r="A21" s="35" t="inlineStr">
-        <is>
-          <t>FRСМК-53</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>Андижанская</t>
-        </is>
-      </c>
-      <c r="C21" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="40" t="n">
-        <v>363900</v>
-      </c>
-      <c r="E21" s="40" t="n">
-        <v>3477490</v>
-      </c>
-      <c r="F21" s="40" t="n">
-        <v>6698688</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="20">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>FRТАШ-307</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>Крестик</t>
-        </is>
-      </c>
-      <c r="C22" s="40" t="n">
-        <v>2876909</v>
-      </c>
-      <c r="D22" s="40" t="n">
-        <v>6793378</v>
-      </c>
-      <c r="E22" s="40" t="n">
-        <v>3855907</v>
-      </c>
-      <c r="F22" s="40" t="n">
-        <v>7337990</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="20">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>FRМРГ-8</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>Маргилан</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="40" t="n">
-        <v>1377990</v>
-      </c>
-      <c r="E23" s="40" t="n">
-        <v>3465270</v>
-      </c>
-      <c r="F23" s="40" t="n">
-        <v>4464440</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="20">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>В среднем на ПВЗ</t>
-        </is>
-      </c>
-      <c r="B24" s="38" t="inlineStr"/>
-      <c r="C24" s="41">
-        <f>AVERAGE(C6:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="41">
-        <f>AVERAGE(D6:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="41">
-        <f>AVERAGE(E6:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="41">
-        <f>AVERAGE(F6:F23)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3027,6 +1891,1138 @@
       <c r="B24" s="38" t="inlineStr"/>
       <c r="C24" s="41">
         <f>SUM(C6:C23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="20" min="1" max="1"/>
+    <col width="20" customWidth="1" style="20" min="2" max="2"/>
+    <col width="13" customWidth="1" style="20" min="3" max="3"/>
+    <col width="13" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13" customWidth="1" style="20" min="5" max="5"/>
+    <col width="13" customWidth="1" style="20" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Средние заказы в день по неделям (накопительно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1" s="20">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>AKA</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>11.05–17.05*</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>18.05–24.05</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>25.05–31.05</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>01.06–07.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Дней с данными</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-291</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Бабур</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-290</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Буз-1</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>51.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-292</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>35.57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-294</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Шастри</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>28.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-293</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Кургантепа</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>26.57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-289</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Афросиаб</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>24.86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-308</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Янгиюнусабад</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F12" s="36" t="n">
+        <v>17.57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-9</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Амир Т</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>17.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>FRБХР-30</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Бухара</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="F14" s="36" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>FRГАЗ-4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Газалкент</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>16.71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-319</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Баку</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>14.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-10</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Мустакилик</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D17" s="36" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>FRБУК-2</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Бука</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="36" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>13.43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-52</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Рудаки</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="F19" s="36" t="n">
+        <v>13.43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>FRПСК-2</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>Пскент</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E20" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="36" t="n">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-53</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Андижанская</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-307</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Крестик</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>FRМРГ-8</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Маргилан</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>В среднем на ПВЗ</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr"/>
+      <c r="C24" s="39">
+        <f>AVERAGE(C6:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="39">
+        <f>AVERAGE(D6:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="39">
+        <f>AVERAGE(E6:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="39">
+        <f>AVERAGE(F6:F23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="20" min="1" max="1"/>
+    <col width="20" customWidth="1" style="20" min="2" max="2"/>
+    <col width="13" customWidth="1" style="20" min="3" max="3"/>
+    <col width="13" customWidth="1" style="20" min="4" max="4"/>
+    <col width="13" customWidth="1" style="20" min="5" max="5"/>
+    <col width="13" customWidth="1" style="20" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Сумма выручки (объём) по неделям, сум (накопительно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Накопительный архив: полные недели не меняются, последняя неполная — обновляется. Звёздочка = неполная неделя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1" s="20">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>AKA</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>11.05–17.05*</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>18.05–24.05</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>25.05–31.05</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>01.06–07.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Дней с данными</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-291</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Бабур</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>25945431</v>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>37459210</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <v>48992678</v>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>64308195</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-290</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Буз-1</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n">
+        <v>26572309</v>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>54415488</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>46859038</v>
+      </c>
+      <c r="F7" s="40" t="n">
+        <v>52194797</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-292</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>14023998</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>23623555</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>37049808</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>48937774</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-294</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Шастри</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>11787061</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>33489630</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>34406847</v>
+      </c>
+      <c r="F9" s="40" t="n">
+        <v>37161831</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-293</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Кургантепа</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="n">
+        <v>9063650</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>19435779</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>20382320</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>23759937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-289</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Афросиаб</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>3579870</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>26016508</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>28967720</v>
+      </c>
+      <c r="F11" s="40" t="n">
+        <v>37959389</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-308</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Янгиюнусабад</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="n">
+        <v>7434617</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>11541808</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>11589026</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <v>20628257</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-9</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Амир Т</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n">
+        <v>13421812</v>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>19296100</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>32898025</v>
+      </c>
+      <c r="F13" s="40" t="n">
+        <v>20322786</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>FRБХР-30</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Бухара</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>10462042</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>24242808</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>20176647</v>
+      </c>
+      <c r="F14" s="40" t="n">
+        <v>18937286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>FRГАЗ-4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Газалкент</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>6139086</v>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>14744333</v>
+      </c>
+      <c r="E15" s="40" t="n">
+        <v>18390296</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <v>19525644</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-319</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Баку</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>11237754</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>29303296</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>17092421</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>18898662</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>FRАЛМ-10</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Алмалык Мустакилик</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="n">
+        <v>6011315</v>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>10213590</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>10032796</v>
+      </c>
+      <c r="F17" s="40" t="n">
+        <v>23828037</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>FRБУК-2</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Бука</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="n">
+        <v>6458596</v>
+      </c>
+      <c r="D18" s="40" t="n">
+        <v>16321651</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>12911381</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>18213851</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-52</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Рудаки</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="n">
+        <v>6460094</v>
+      </c>
+      <c r="D19" s="40" t="n">
+        <v>14908071</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>20904887</v>
+      </c>
+      <c r="F19" s="40" t="n">
+        <v>14174417</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>FRПСК-2</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>Пскент</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="40" t="n">
+        <v>1357510</v>
+      </c>
+      <c r="E20" s="40" t="n">
+        <v>9736256</v>
+      </c>
+      <c r="F20" s="40" t="n">
+        <v>18439963</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>FRСМК-53</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Андижанская</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="40" t="n">
+        <v>363900</v>
+      </c>
+      <c r="E21" s="40" t="n">
+        <v>3477490</v>
+      </c>
+      <c r="F21" s="40" t="n">
+        <v>6698688</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>FRТАШ-307</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Крестик</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="n">
+        <v>2876909</v>
+      </c>
+      <c r="D22" s="40" t="n">
+        <v>6793378</v>
+      </c>
+      <c r="E22" s="40" t="n">
+        <v>3855907</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <v>7337990</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>FRМРГ-8</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Маргилан</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="40" t="n">
+        <v>1377990</v>
+      </c>
+      <c r="E23" s="40" t="n">
+        <v>3465270</v>
+      </c>
+      <c r="F23" s="40" t="n">
+        <v>4464440</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>В среднем на ПВЗ</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr"/>
+      <c r="C24" s="41">
+        <f>AVERAGE(C6:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="41">
+        <f>AVERAGE(D6:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="41">
+        <f>AVERAGE(E6:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="41">
+        <f>AVERAGE(F6:F23)</f>
         <v/>
       </c>
     </row>
@@ -3272,7 +3268,7 @@
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="42" t="n">
         <v>7</v>
@@ -3488,10 +3484,10 @@
         </is>
       </c>
       <c r="C20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="D20" s="42" t="n">
-        <v>7</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -3512,10 +3508,10 @@
         </is>
       </c>
       <c r="C21" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>7</v>
@@ -3560,7 +3556,7 @@
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
         <v>7</v>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1914,6 +1914,7 @@
     <col width="13" customWidth="1" style="20" min="4" max="4"/>
     <col width="13" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
+    <col width="13" customWidth="1" style="20" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1951,6 +1952,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -1981,6 +1987,11 @@
       <c r="F4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>08.06–14.06*</t>
         </is>
       </c>
     </row>
@@ -2003,6 +2014,9 @@
       <c r="F5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="G5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2027,6 +2041,9 @@
       <c r="F6" s="36" t="n">
         <v>53</v>
       </c>
+      <c r="G6" s="36" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2051,6 +2068,9 @@
       <c r="F7" s="36" t="n">
         <v>51.43</v>
       </c>
+      <c r="G7" s="36" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2075,6 +2095,9 @@
       <c r="F8" s="36" t="n">
         <v>35.57</v>
       </c>
+      <c r="G8" s="36" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -2099,6 +2122,9 @@
       <c r="F9" s="36" t="n">
         <v>28.71</v>
       </c>
+      <c r="G9" s="36" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -2123,6 +2149,9 @@
       <c r="F10" s="36" t="n">
         <v>26.57</v>
       </c>
+      <c r="G10" s="36" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -2147,173 +2176,197 @@
       <c r="F11" s="36" t="n">
         <v>24.86</v>
       </c>
+      <c r="G11" s="36" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>10.8</v>
+        <v>7.2</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>13.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.57</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>17.57</v>
+        <v>14.14</v>
+      </c>
+      <c r="G12" s="36" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>13.4</v>
+        <v>9.6</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>16.57</v>
+        <v>13.29</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>20.86</v>
+        <v>14.57</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17.14</v>
+        <v>16.71</v>
+      </c>
+      <c r="G13" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>21.71</v>
+        <v>13.57</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>15.43</v>
+        <v>12.57</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>17</v>
+        <v>17.57</v>
+      </c>
+      <c r="G14" s="36" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>13.29</v>
+        <v>12.57</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>14.57</v>
+        <v>11.29</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>16.71</v>
+        <v>13.43</v>
+      </c>
+      <c r="G15" s="36" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>14.8</v>
+        <v>13.4</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>15.71</v>
+        <v>20.86</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.86</v>
+        <v>17.14</v>
+      </c>
+      <c r="G16" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>7.2</v>
+        <v>14.8</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.71</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>14.14</v>
+        <v>14.86</v>
+      </c>
+      <c r="G17" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>12.57</v>
+        <v>21.71</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11.29</v>
+        <v>15.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.43</v>
+        <v>17</v>
+      </c>
+      <c r="G18" s="36" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2339,101 +2392,116 @@
       <c r="F19" s="36" t="n">
         <v>13.43</v>
       </c>
+      <c r="G19" s="36" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>2.6</v>
+        <v>0.25</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>7</v>
+        <v>2.86</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8.43</v>
+      </c>
+      <c r="G20" s="36" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0.25</v>
+        <v>2.6</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>2.86</v>
+        <v>7</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>8.43</v>
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>5.14</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>5.29</v>
+        <v>3.86</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>7.86</v>
+        <v>5.86</v>
+      </c>
+      <c r="G22" s="36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="D23" s="36" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>2</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="F23" s="36" t="n">
-        <v>5.86</v>
       </c>
     </row>
     <row r="24">
@@ -2457,6 +2525,10 @@
       </c>
       <c r="F24" s="39">
         <f>AVERAGE(F6:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="39">
+        <f>AVERAGE(G6:G23)</f>
         <v/>
       </c>
     </row>
@@ -2471,7 +2543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2480,6 +2552,7 @@
     <col width="13" customWidth="1" style="20" min="4" max="4"/>
     <col width="13" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
+    <col width="13" customWidth="1" style="20" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2517,6 +2590,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2547,6 +2625,11 @@
       <c r="F4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>08.06–14.06*</t>
         </is>
       </c>
     </row>
@@ -2569,6 +2652,9 @@
       <c r="F5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="G5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2593,6 +2679,9 @@
       <c r="F6" s="40" t="n">
         <v>64308195</v>
       </c>
+      <c r="G6" s="40" t="n">
+        <v>12733834</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2617,6 +2706,9 @@
       <c r="F7" s="40" t="n">
         <v>52194797</v>
       </c>
+      <c r="G7" s="40" t="n">
+        <v>11870686</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2641,6 +2733,9 @@
       <c r="F8" s="40" t="n">
         <v>48937774</v>
       </c>
+      <c r="G8" s="40" t="n">
+        <v>8996930</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -2665,6 +2760,9 @@
       <c r="F9" s="40" t="n">
         <v>37161831</v>
       </c>
+      <c r="G9" s="40" t="n">
+        <v>4538440</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -2689,6 +2787,9 @@
       <c r="F10" s="40" t="n">
         <v>23759937</v>
       </c>
+      <c r="G10" s="40" t="n">
+        <v>5677190</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -2713,173 +2814,197 @@
       <c r="F11" s="40" t="n">
         <v>37959389</v>
       </c>
+      <c r="G11" s="40" t="n">
+        <v>5645596</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>7434617</v>
+        <v>6011315</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>11541808</v>
+        <v>10213590</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>11589026</v>
+        <v>10032796</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>20628257</v>
+        <v>23828037</v>
+      </c>
+      <c r="G12" s="40" t="n">
+        <v>6409560</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>13421812</v>
+        <v>6139086</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>19296100</v>
+        <v>14744333</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>32898025</v>
+        <v>18390296</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>20322786</v>
+        <v>19525644</v>
+      </c>
+      <c r="G13" s="40" t="n">
+        <v>3737250</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>10462042</v>
+        <v>7434617</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>24242808</v>
+        <v>11541808</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>20176647</v>
+        <v>11589026</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>18937286</v>
+        <v>20628257</v>
+      </c>
+      <c r="G14" s="40" t="n">
+        <v>1866491</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>6139086</v>
+        <v>6458596</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>14744333</v>
+        <v>16321651</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>18390296</v>
+        <v>12911381</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>19525644</v>
+        <v>18213851</v>
+      </c>
+      <c r="G15" s="40" t="n">
+        <v>1807552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>11237754</v>
+        <v>13421812</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>29303296</v>
+        <v>19296100</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>17092421</v>
+        <v>32898025</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18898662</v>
+        <v>20322786</v>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>1421720</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>6011315</v>
+        <v>11237754</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>10213590</v>
+        <v>29303296</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10032796</v>
+        <v>17092421</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>23828037</v>
+        <v>18898662</v>
+      </c>
+      <c r="G17" s="40" t="n">
+        <v>2122384</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6458596</v>
+        <v>10462042</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>16321651</v>
+        <v>24242808</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>12911381</v>
+        <v>20176647</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>18213851</v>
+        <v>18937286</v>
+      </c>
+      <c r="G18" s="40" t="n">
+        <v>2589400</v>
       </c>
     </row>
     <row r="19">
@@ -2905,101 +3030,116 @@
       <c r="F19" s="40" t="n">
         <v>14174417</v>
       </c>
+      <c r="G19" s="40" t="n">
+        <v>2274090</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>1357510</v>
+        <v>363900</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>9736256</v>
+        <v>3477490</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>18439963</v>
+        <v>6698688</v>
+      </c>
+      <c r="G20" s="40" t="n">
+        <v>2340920</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>363900</v>
+        <v>1357510</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>3477490</v>
+        <v>9736256</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>6698688</v>
+        <v>18439963</v>
+      </c>
+      <c r="G21" s="40" t="n">
+        <v>491910</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>2876909</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>6793378</v>
+        <v>1377990</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>3855907</v>
+        <v>3465270</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>7337990</v>
+        <v>4464440</v>
+      </c>
+      <c r="G22" s="40" t="n">
+        <v>4980680</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>2876909</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>1377990</v>
+        <v>6793378</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>3465270</v>
+        <v>3855907</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>4464440</v>
+        <v>7337990</v>
+      </c>
+      <c r="G23" s="40" t="n">
+        <v>207910</v>
       </c>
     </row>
     <row r="24">
@@ -3023,6 +3163,10 @@
       </c>
       <c r="F24" s="41">
         <f>AVERAGE(F6:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="41">
+        <f>AVERAGE(G6:G23)</f>
         <v/>
       </c>
     </row>
@@ -3037,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3046,6 +3190,7 @@
     <col width="13" customWidth="1" style="20" min="4" max="4"/>
     <col width="13" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
+    <col width="13" customWidth="1" style="20" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3083,6 +3228,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3113,6 +3263,11 @@
       <c r="F4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>08.06–14.06*</t>
         </is>
       </c>
     </row>
@@ -3135,6 +3290,9 @@
       <c r="F5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="G5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -3159,6 +3317,9 @@
       <c r="F6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -3183,6 +3344,9 @@
       <c r="F7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -3207,6 +3371,9 @@
       <c r="F8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G8" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -3231,6 +3398,9 @@
       <c r="F9" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G9" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -3255,6 +3425,9 @@
       <c r="F10" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G10" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -3279,16 +3452,19 @@
       <c r="F11" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G11" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
@@ -3303,16 +3479,19 @@
       <c r="F12" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G12" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3327,16 +3506,19 @@
       <c r="F13" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G13" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
@@ -3351,16 +3533,19 @@
       <c r="F14" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G14" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -3375,16 +3560,19 @@
       <c r="F15" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G15" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3399,16 +3587,19 @@
       <c r="F16" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G16" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
@@ -3423,16 +3614,19 @@
       <c r="F17" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G17" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3447,6 +3641,9 @@
       <c r="F18" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G18" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
@@ -3471,68 +3668,77 @@
       <c r="F19" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="G19" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="G20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
         <v>7</v>
@@ -3542,21 +3748,24 @@
       </c>
       <c r="F22" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="G22" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" s="42" t="n">
         <v>7</v>
@@ -3566,6 +3775,9 @@
       </c>
       <c r="F23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -3591,6 +3803,10 @@
         <f>AVERAGE(F6:F23)</f>
         <v/>
       </c>
+      <c r="G24" s="43">
+        <f>AVERAGE(G6:G23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2042,7 +2042,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -2069,7 +2069,7 @@
         <v>51.43</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -2096,142 +2096,142 @@
         <v>35.57</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>37</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>18.8</v>
+        <v>5.5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>26.57</v>
+        <v>17.86</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>28.29</v>
+        <v>20.86</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>28.71</v>
+        <v>24.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>8</v>
+        <v>18.8</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>13</v>
+        <v>26.57</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>17.71</v>
+        <v>28.29</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.57</v>
+        <v>28.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>17.86</v>
+        <v>13</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>20.86</v>
+        <v>17.71</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>24.86</v>
+        <v>26.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>26</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>7.2</v>
+        <v>13.4</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>16.57</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>20.86</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>14.14</v>
+        <v>17.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>22</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>14.57</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.71</v>
+        <v>14.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -2258,7 +2258,7 @@
         <v>17.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>19</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="15">
@@ -2285,34 +2285,34 @@
         <v>13.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>16.57</v>
+        <v>21.71</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>20.86</v>
+        <v>15.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>17.14</v>
+        <v>17</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -2339,88 +2339,88 @@
         <v>14.86</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>16</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>21.71</v>
+        <v>13.29</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>15.43</v>
+        <v>14.57</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>17</v>
+        <v>16.71</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>14</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>10.43</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.14</v>
+        <v>2.86</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>8.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>14</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0.25</v>
+        <v>10.43</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>2.86</v>
+        <v>11.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>8.43</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -2447,7 +2447,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>10</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="22">
@@ -2474,7 +2474,7 @@
         <v>5.86</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="23">
@@ -2501,7 +2501,7 @@
         <v>7.86</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>2</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="24">
@@ -2653,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2680,7 +2680,7 @@
         <v>64308195</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>12733834</v>
+        <v>29173014</v>
       </c>
     </row>
     <row r="7">
@@ -2707,7 +2707,7 @@
         <v>52194797</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>11870686</v>
+        <v>31189340</v>
       </c>
     </row>
     <row r="8">
@@ -2734,142 +2734,142 @@
         <v>48937774</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>8996930</v>
+        <v>25021030</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>11787061</v>
+        <v>3579870</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>33489630</v>
+        <v>26016508</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>34406847</v>
+        <v>28967720</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>37161831</v>
+        <v>37959389</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>4538440</v>
+        <v>20167263</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9063650</v>
+        <v>11787061</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>19435779</v>
+        <v>33489630</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>20382320</v>
+        <v>34406847</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>23759937</v>
+        <v>37161831</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>5677190</v>
+        <v>11579824</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>3579870</v>
+        <v>9063650</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>26016508</v>
+        <v>19435779</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>28967720</v>
+        <v>20382320</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>37959389</v>
+        <v>23759937</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>5645596</v>
+        <v>16411118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>6011315</v>
+        <v>13421812</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>10213590</v>
+        <v>19296100</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>10032796</v>
+        <v>32898025</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>23828037</v>
+        <v>20322786</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>6409560</v>
+        <v>14234181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>6139086</v>
+        <v>6011315</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>14744333</v>
+        <v>10213590</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>18390296</v>
+        <v>10032796</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>19525644</v>
+        <v>23828037</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>3737250</v>
+        <v>22340500</v>
       </c>
     </row>
     <row r="14">
@@ -2896,7 +2896,7 @@
         <v>20628257</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>1866491</v>
+        <v>7602741</v>
       </c>
     </row>
     <row r="15">
@@ -2923,34 +2923,34 @@
         <v>18213851</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>1807552</v>
+        <v>8786876</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>13421812</v>
+        <v>10462042</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>19296100</v>
+        <v>24242808</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>32898025</v>
+        <v>20176647</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>20322786</v>
+        <v>18937286</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>1421720</v>
+        <v>7992670</v>
       </c>
     </row>
     <row r="17">
@@ -2977,88 +2977,88 @@
         <v>18898662</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>2122384</v>
+        <v>6622614</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>10462042</v>
+        <v>6139086</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>24242808</v>
+        <v>14744333</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>20176647</v>
+        <v>18390296</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>18937286</v>
+        <v>19525644</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>2589400</v>
+        <v>7061536</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6460094</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>14908071</v>
+        <v>363900</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>20904887</v>
+        <v>3477490</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14174417</v>
+        <v>6698688</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>2274090</v>
+        <v>6132968</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>0</v>
+        <v>6460094</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>363900</v>
+        <v>14908071</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>3477490</v>
+        <v>20904887</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>6698688</v>
+        <v>14174417</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>2340920</v>
+        <v>5800193</v>
       </c>
     </row>
     <row r="21">
@@ -3085,7 +3085,7 @@
         <v>18439963</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>491910</v>
+        <v>3475570</v>
       </c>
     </row>
     <row r="22">
@@ -3112,7 +3112,7 @@
         <v>4464440</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4980680</v>
+        <v>7713840</v>
       </c>
     </row>
     <row r="23">
@@ -3139,7 +3139,7 @@
         <v>7337990</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>207910</v>
+        <v>2995030</v>
       </c>
     </row>
     <row r="24">
@@ -3291,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3318,7 +3318,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3345,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3372,22 +3372,22 @@
         <v>7</v>
       </c>
       <c r="G8" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="42" t="n">
         <v>7</v>
@@ -3399,18 +3399,18 @@
         <v>7</v>
       </c>
       <c r="G9" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -3426,22 +3426,22 @@
         <v>7</v>
       </c>
       <c r="G10" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="42" t="n">
         <v>7</v>
@@ -3453,18 +3453,18 @@
         <v>7</v>
       </c>
       <c r="G11" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
@@ -3480,18 +3480,18 @@
         <v>7</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3507,7 +3507,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3534,7 +3534,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3561,18 +3561,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3588,7 +3588,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3615,18 +3615,18 @@
         <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3642,25 +3642,25 @@
         <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -3669,25 +3669,25 @@
         <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -3723,7 +3723,7 @@
         <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -3750,7 +3750,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3777,7 +3777,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2042,7 +2042,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>70</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2069,7 +2069,7 @@
         <v>51.43</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -2096,7 +2096,7 @@
         <v>35.57</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>42.33</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="9">
@@ -2123,7 +2123,7 @@
         <v>24.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="10">
@@ -2150,7 +2150,7 @@
         <v>28.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="11">
@@ -2177,7 +2177,7 @@
         <v>26.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>27.67</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="12">
@@ -2204,34 +2204,34 @@
         <v>17.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21.33</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>7.2</v>
+        <v>13.8</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>21.71</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>14.14</v>
+        <v>17</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="14">
@@ -2258,7 +2258,7 @@
         <v>17.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>19.67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2285,142 +2285,142 @@
         <v>13.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>18.33</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>13.8</v>
+        <v>11</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>21.71</v>
+        <v>10.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>15.43</v>
+        <v>11.14</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>17</v>
+        <v>13.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>19.43</v>
+        <v>0.25</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>15.71</v>
+        <v>2.86</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>14.86</v>
+        <v>8.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>16.67</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>9.6</v>
+        <v>14.8</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>13.29</v>
+        <v>19.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>14.57</v>
+        <v>15.71</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>16.71</v>
+        <v>14.86</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>16.67</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0.25</v>
+        <v>13.29</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>2.86</v>
+        <v>14.57</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>8.43</v>
+        <v>16.71</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>16.33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>14.14</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="21">
@@ -2447,61 +2447,61 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8.67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>5.14</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>3.86</v>
+        <v>5.29</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>5.86</v>
+        <v>7.86</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>5.67</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>5.14</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>5.29</v>
+        <v>3.86</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>7.86</v>
+        <v>5.86</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="24">
@@ -2653,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2680,7 +2680,7 @@
         <v>64308195</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>29173014</v>
+        <v>55073197</v>
       </c>
     </row>
     <row r="7">
@@ -2707,7 +2707,7 @@
         <v>52194797</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>31189340</v>
+        <v>50923303</v>
       </c>
     </row>
     <row r="8">
@@ -2734,7 +2734,7 @@
         <v>48937774</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>25021030</v>
+        <v>35293812</v>
       </c>
     </row>
     <row r="9">
@@ -2761,7 +2761,7 @@
         <v>37959389</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>20167263</v>
+        <v>41863865</v>
       </c>
     </row>
     <row r="10">
@@ -2788,7 +2788,7 @@
         <v>37161831</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>11579824</v>
+        <v>22196230</v>
       </c>
     </row>
     <row r="11">
@@ -2815,7 +2815,7 @@
         <v>23759937</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>16411118</v>
+        <v>25110890</v>
       </c>
     </row>
     <row r="12">
@@ -2842,34 +2842,34 @@
         <v>20322786</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>14234181</v>
+        <v>19796801</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>6011315</v>
+        <v>10462042</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10213590</v>
+        <v>24242808</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>10032796</v>
+        <v>20176647</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>23828037</v>
+        <v>18937286</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>22340500</v>
+        <v>17981890</v>
       </c>
     </row>
     <row r="14">
@@ -2896,7 +2896,7 @@
         <v>20628257</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>7602741</v>
+        <v>13354222</v>
       </c>
     </row>
     <row r="15">
@@ -2923,142 +2923,142 @@
         <v>18213851</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>8786876</v>
+        <v>13944866</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>10462042</v>
+        <v>6460094</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>24242808</v>
+        <v>14908071</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>20176647</v>
+        <v>20904887</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18937286</v>
+        <v>14174417</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>7992670</v>
+        <v>8657838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>11237754</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>29303296</v>
+        <v>363900</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>17092421</v>
+        <v>3477490</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>18898662</v>
+        <v>6698688</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>6622614</v>
+        <v>12556479</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6139086</v>
+        <v>11237754</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>14744333</v>
+        <v>29303296</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>18390296</v>
+        <v>17092421</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>19525644</v>
+        <v>18898662</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>7061536</v>
+        <v>13533485</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>6139086</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>363900</v>
+        <v>14744333</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>3477490</v>
+        <v>18390296</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>6698688</v>
+        <v>19525644</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>6132968</v>
+        <v>16499646</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>14174417</v>
+        <v>23828037</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>5800193</v>
+        <v>27547637</v>
       </c>
     </row>
     <row r="21">
@@ -3085,61 +3085,61 @@
         <v>18439963</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>3475570</v>
+        <v>6898300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>2876909</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>1377990</v>
+        <v>6793378</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>3465270</v>
+        <v>3855907</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>4464440</v>
+        <v>7337990</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>7713840</v>
+        <v>6773650</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>2876909</v>
+        <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>6793378</v>
+        <v>1377990</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>3855907</v>
+        <v>3465270</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>7337990</v>
+        <v>4464440</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>2995030</v>
+        <v>11083170</v>
       </c>
     </row>
     <row r="24">
@@ -3291,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3318,7 +3318,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3345,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3372,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3399,7 +3399,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -3426,7 +3426,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -3453,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3480,18 +3480,18 @@
         <v>7</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3507,7 +3507,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3534,7 +3534,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -3561,18 +3561,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3588,45 +3588,45 @@
         <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="D17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3642,25 +3642,25 @@
         <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -3669,18 +3669,18 @@
         <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -3723,22 +3723,22 @@
         <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" s="42" t="n">
         <v>7</v>
@@ -3750,34 +3750,34 @@
         <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="D23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2042,7 +2042,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>70.59999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2069,7 +2069,7 @@
         <v>51.43</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -2096,7 +2096,7 @@
         <v>35.57</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>41.2</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="9">
@@ -2123,7 +2123,7 @@
         <v>24.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>40.8</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="10">
@@ -2150,7 +2150,7 @@
         <v>28.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="11">
@@ -2177,7 +2177,7 @@
         <v>26.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -2204,61 +2204,61 @@
         <v>17.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>21.71</v>
+        <v>13.57</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>15.43</v>
+        <v>12.57</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17</v>
+        <v>17.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>13.57</v>
+        <v>13.29</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.57</v>
+        <v>14.57</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>19</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="15">
@@ -2285,34 +2285,34 @@
         <v>13.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>11</v>
+        <v>13.8</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>10.43</v>
+        <v>21.71</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.14</v>
+        <v>15.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.43</v>
+        <v>17</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>18</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="17">
@@ -2339,58 +2339,58 @@
         <v>8.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>14.8</v>
+        <v>11</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>19.43</v>
+        <v>10.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>15.71</v>
+        <v>11.14</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.86</v>
+        <v>13.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>17.2</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>9.6</v>
+        <v>14.8</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>13.29</v>
+        <v>19.43</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>14.57</v>
+        <v>15.71</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>16.71</v>
+        <v>14.86</v>
       </c>
       <c r="G19" s="36" t="n">
         <v>17</v>
@@ -2420,7 +2420,7 @@
         <v>14.14</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="21">
@@ -2447,7 +2447,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -2474,7 +2474,7 @@
         <v>7.86</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>7.4</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="23">
@@ -2501,7 +2501,7 @@
         <v>5.86</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="24">
@@ -2653,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2680,7 +2680,7 @@
         <v>64308195</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>55073197</v>
+        <v>65087663</v>
       </c>
     </row>
     <row r="7">
@@ -2707,7 +2707,7 @@
         <v>52194797</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>50923303</v>
+        <v>57873348</v>
       </c>
     </row>
     <row r="8">
@@ -2734,7 +2734,7 @@
         <v>48937774</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>35293812</v>
+        <v>41565641</v>
       </c>
     </row>
     <row r="9">
@@ -2761,7 +2761,7 @@
         <v>37959389</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>41863865</v>
+        <v>46554513</v>
       </c>
     </row>
     <row r="10">
@@ -2788,7 +2788,7 @@
         <v>37161831</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>22196230</v>
+        <v>27213732</v>
       </c>
     </row>
     <row r="11">
@@ -2815,7 +2815,7 @@
         <v>23759937</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>25110890</v>
+        <v>31046231</v>
       </c>
     </row>
     <row r="12">
@@ -2842,61 +2842,61 @@
         <v>20322786</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>19796801</v>
+        <v>21888151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>10462042</v>
+        <v>7434617</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>24242808</v>
+        <v>11541808</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>20176647</v>
+        <v>11589026</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>18937286</v>
+        <v>20628257</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>17981890</v>
+        <v>15632412</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>7434617</v>
+        <v>6139086</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11541808</v>
+        <v>14744333</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11589026</v>
+        <v>18390296</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>20628257</v>
+        <v>19525644</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>13354222</v>
+        <v>20851516</v>
       </c>
     </row>
     <row r="15">
@@ -2923,34 +2923,34 @@
         <v>18213851</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>13944866</v>
+        <v>14596046</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>6460094</v>
+        <v>10462042</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>14908071</v>
+        <v>24242808</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>20904887</v>
+        <v>20176647</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14174417</v>
+        <v>18937286</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>8657838</v>
+        <v>19155820</v>
       </c>
     </row>
     <row r="17">
@@ -2977,61 +2977,61 @@
         <v>6698688</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>12556479</v>
+        <v>13408409</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>11237754</v>
+        <v>6460094</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>29303296</v>
+        <v>14908071</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>17092421</v>
+        <v>20904887</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>18898662</v>
+        <v>14174417</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>13533485</v>
+        <v>16785388</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6139086</v>
+        <v>11237754</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>14744333</v>
+        <v>29303296</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>18390296</v>
+        <v>17092421</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>19525644</v>
+        <v>18898662</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16499646</v>
+        <v>14913875</v>
       </c>
     </row>
     <row r="20">
@@ -3058,7 +3058,7 @@
         <v>23828037</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>27547637</v>
+        <v>30454877</v>
       </c>
     </row>
     <row r="21">
@@ -3085,7 +3085,7 @@
         <v>18439963</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>6898300</v>
+        <v>10230050</v>
       </c>
     </row>
     <row r="22">
@@ -3112,7 +3112,7 @@
         <v>7337990</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>6773650</v>
+        <v>8309290</v>
       </c>
     </row>
     <row r="23">
@@ -3139,7 +3139,7 @@
         <v>4464440</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>11083170</v>
+        <v>11676470</v>
       </c>
     </row>
     <row r="24">
@@ -3291,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3318,7 +3318,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3345,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -3372,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -3399,7 +3399,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -3426,7 +3426,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -3453,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3480,18 +3480,18 @@
         <v>7</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3507,18 +3507,18 @@
         <v>7</v>
       </c>
       <c r="G13" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
@@ -3534,7 +3534,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -3561,18 +3561,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3588,7 +3588,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3615,18 +3615,18 @@
         <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3642,18 +3642,18 @@
         <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3669,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -3723,7 +3723,7 @@
         <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -3750,7 +3750,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -3777,7 +3777,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
-          <t>08.06–14.06*</t>
+          <t>08.06–14.06</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2042,7 +2042,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>68</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="7">
@@ -2069,7 +2069,7 @@
         <v>51.43</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>57</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="8">
@@ -2096,7 +2096,7 @@
         <v>35.57</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>42.33</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="9">
@@ -2123,61 +2123,61 @@
         <v>24.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>37.5</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>18.8</v>
+        <v>8</v>
       </c>
       <c r="D10" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="F10" s="36" t="n">
         <v>26.57</v>
       </c>
-      <c r="E10" s="36" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>28.71</v>
-      </c>
       <c r="G10" s="36" t="n">
-        <v>31.5</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>8</v>
+        <v>18.8</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>13</v>
+        <v>26.57</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>17.71</v>
+        <v>28.29</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.57</v>
+        <v>28.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>30</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="12">
@@ -2204,115 +2204,115 @@
         <v>17.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>20.5</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>13.57</v>
+        <v>13.29</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.57</v>
+        <v>14.57</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>18.5</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>13.29</v>
+        <v>12.57</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>14.57</v>
+        <v>11.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.71</v>
+        <v>13.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>18.33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>12.57</v>
+        <v>21.71</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11.29</v>
+        <v>15.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.43</v>
+        <v>17</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>18</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>21.71</v>
+        <v>13.57</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>15.43</v>
+        <v>12.57</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>17</v>
+        <v>17.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>17.67</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="17">
@@ -2339,34 +2339,34 @@
         <v>8.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>17.5</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.43</v>
+        <v>14.14</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="19">
@@ -2393,34 +2393,34 @@
         <v>14.86</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>17</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>14.14</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>16.5</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="21">
@@ -2447,7 +2447,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>11</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="22">
@@ -2474,7 +2474,7 @@
         <v>7.86</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>7.67</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="23">
@@ -2501,7 +2501,7 @@
         <v>5.86</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>5.33</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="24">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
-          <t>08.06–14.06*</t>
+          <t>08.06–14.06</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2680,7 +2680,7 @@
         <v>64308195</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>65087663</v>
+        <v>79272397</v>
       </c>
     </row>
     <row r="7">
@@ -2707,7 +2707,7 @@
         <v>52194797</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>57873348</v>
+        <v>71643667</v>
       </c>
     </row>
     <row r="8">
@@ -2734,7 +2734,7 @@
         <v>48937774</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>41565641</v>
+        <v>45181151</v>
       </c>
     </row>
     <row r="9">
@@ -2761,61 +2761,61 @@
         <v>37959389</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>46554513</v>
+        <v>50657103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>11787061</v>
+        <v>9063650</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>33489630</v>
+        <v>19435779</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>34406847</v>
+        <v>20382320</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>37161831</v>
+        <v>23759937</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>27213732</v>
+        <v>43854730</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9063650</v>
+        <v>11787061</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>19435779</v>
+        <v>33489630</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>20382320</v>
+        <v>34406847</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>23759937</v>
+        <v>37161831</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>31046231</v>
+        <v>31826353</v>
       </c>
     </row>
     <row r="12">
@@ -2842,115 +2842,115 @@
         <v>20322786</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>21888151</v>
+        <v>26950241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>7434617</v>
+        <v>6139086</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>11541808</v>
+        <v>14744333</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>11589026</v>
+        <v>18390296</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>20628257</v>
+        <v>19525644</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>15632412</v>
+        <v>30942866</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>6139086</v>
+        <v>6458596</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>14744333</v>
+        <v>16321651</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>18390296</v>
+        <v>12911381</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>19525644</v>
+        <v>18213851</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20851516</v>
+        <v>17644316</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>6458596</v>
+        <v>10462042</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>16321651</v>
+        <v>24242808</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>12911381</v>
+        <v>20176647</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>18213851</v>
+        <v>18937286</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>14596046</v>
+        <v>21999340</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>10462042</v>
+        <v>7434617</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>24242808</v>
+        <v>11541808</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>20176647</v>
+        <v>11589026</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18937286</v>
+        <v>20628257</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>19155820</v>
+        <v>19325665</v>
       </c>
     </row>
     <row r="17">
@@ -2977,34 +2977,34 @@
         <v>6698688</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>13408409</v>
+        <v>14305166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>14174417</v>
+        <v>23828037</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>16785388</v>
+        <v>33387187</v>
       </c>
     </row>
     <row r="19">
@@ -3031,34 +3031,34 @@
         <v>18898662</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>14913875</v>
+        <v>16270790</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6011315</v>
+        <v>6460094</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>10213590</v>
+        <v>14908071</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10032796</v>
+        <v>20904887</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>23828037</v>
+        <v>14174417</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>30454877</v>
+        <v>21360428</v>
       </c>
     </row>
     <row r="21">
@@ -3085,7 +3085,7 @@
         <v>18439963</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10230050</v>
+        <v>12820644</v>
       </c>
     </row>
     <row r="22">
@@ -3112,7 +3112,7 @@
         <v>7337990</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>8309290</v>
+        <v>9843920</v>
       </c>
     </row>
     <row r="23">
@@ -3139,7 +3139,7 @@
         <v>4464440</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>11676470</v>
+        <v>11771640</v>
       </c>
     </row>
     <row r="24">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
-          <t>08.06–14.06*</t>
+          <t>08.06–14.06</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3318,7 +3318,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -3345,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3372,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3399,18 +3399,18 @@
         <v>7</v>
       </c>
       <c r="G9" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -3426,18 +3426,18 @@
         <v>7</v>
       </c>
       <c r="G10" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
@@ -3453,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3480,18 +3480,18 @@
         <v>7</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3507,18 +3507,18 @@
         <v>7</v>
       </c>
       <c r="G13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
@@ -3534,18 +3534,18 @@
         <v>7</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -3561,18 +3561,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3588,7 +3588,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3615,18 +3615,18 @@
         <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3642,7 +3642,7 @@
         <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -3669,18 +3669,18 @@
         <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -3723,7 +3723,7 @@
         <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -3750,7 +3750,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -3777,7 +3777,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1915,6 +1915,7 @@
     <col width="13" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
+    <col width="13" customWidth="1" style="20" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1957,6 +1958,11 @@
           <t>2026-06-08</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -1992,6 +1998,11 @@
       <c r="G4" s="31" t="inlineStr">
         <is>
           <t>08.06–14.06</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>15.06–21.06*</t>
         </is>
       </c>
     </row>
@@ -2017,410 +2028,458 @@
       <c r="G5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="H5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>33.4</v>
+        <v>30</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>41.14</v>
+        <v>37.86</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>36.43</v>
+        <v>39.57</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>53</v>
+        <v>51.43</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>67.86</v>
+        <v>58.43</v>
+      </c>
+      <c r="H6" s="36" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>30</v>
+        <v>33.4</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>37.86</v>
+        <v>41.14</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>39.57</v>
+        <v>36.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>51.43</v>
+        <v>53</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>58.43</v>
+        <v>67.86</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>18.6</v>
+        <v>5.5</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>21.57</v>
+        <v>17.86</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>26.14</v>
+        <v>20.86</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>35.57</v>
+        <v>24.86</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>39.71</v>
+        <v>36.43</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5.5</v>
+        <v>18.6</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>17.86</v>
+        <v>21.57</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>20.86</v>
+        <v>26.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>24.86</v>
+        <v>35.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>36.43</v>
+        <v>39.71</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>8</v>
+        <v>10.8</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>13</v>
+        <v>13.57</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>17.71</v>
+        <v>12.57</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.57</v>
+        <v>17.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>32.29</v>
+        <v>18.57</v>
+      </c>
+      <c r="H10" s="36" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>18.8</v>
+        <v>8</v>
       </c>
       <c r="D11" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="F11" s="36" t="n">
         <v>26.57</v>
       </c>
-      <c r="E11" s="36" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>28.71</v>
-      </c>
       <c r="G11" s="36" t="n">
-        <v>31.43</v>
+        <v>32.29</v>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>13.4</v>
+        <v>18.8</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>16.57</v>
+        <v>26.57</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>20.86</v>
+        <v>28.29</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>17.14</v>
+        <v>28.71</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>20.57</v>
+        <v>31.43</v>
+      </c>
+      <c r="H12" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>9.6</v>
+        <v>13.4</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>13.29</v>
+        <v>16.57</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>14.57</v>
+        <v>20.86</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>19.71</v>
+        <v>20.57</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>12.57</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>2.86</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.43</v>
+        <v>8.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>19</v>
+        <v>17.57</v>
+      </c>
+      <c r="H14" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>21.71</v>
+        <v>19.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>15.43</v>
+        <v>15.71</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>17</v>
+        <v>14.86</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>18.71</v>
+        <v>16.57</v>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>13.57</v>
+        <v>12.57</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.57</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>17.57</v>
+        <v>13.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>18.57</v>
+        <v>19</v>
+      </c>
+      <c r="H16" s="36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.25</v>
+        <v>13.29</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>2.86</v>
+        <v>14.57</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.43</v>
+        <v>16.71</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>17.57</v>
+        <v>19.71</v>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>7.2</v>
+        <v>13.8</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>21.71</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>17.14</v>
+        <v>18.71</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>14.8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>19.43</v>
+        <v>10.43</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>15.71</v>
+        <v>11.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.86</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>16.57</v>
+        <v>16.43</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>14.14</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>16.43</v>
+        <v>17.14</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2449,6 +2508,9 @@
       <c r="G21" s="36" t="n">
         <v>12.57</v>
       </c>
+      <c r="H21" s="36" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -2476,6 +2538,9 @@
       <c r="G22" s="36" t="n">
         <v>7.14</v>
       </c>
+      <c r="H22" s="36" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -2502,6 +2567,9 @@
       </c>
       <c r="G23" s="36" t="n">
         <v>4.86</v>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2529,6 +2597,10 @@
       </c>
       <c r="G24" s="39">
         <f>AVERAGE(G6:G23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="39">
+        <f>AVERAGE(H6:H23)</f>
         <v/>
       </c>
     </row>
@@ -2543,7 +2615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2553,6 +2625,7 @@
     <col width="13" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
+    <col width="13" customWidth="1" style="20" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2595,6 +2668,11 @@
           <t>2026-06-08</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2630,6 +2708,11 @@
       <c r="G4" s="31" t="inlineStr">
         <is>
           <t>08.06–14.06</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>15.06–21.06*</t>
         </is>
       </c>
     </row>
@@ -2655,410 +2738,458 @@
       <c r="G5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="H5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
-        <v>25945431</v>
+        <v>26572309</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>37459210</v>
+        <v>54415488</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>48992678</v>
+        <v>46859038</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>64308195</v>
+        <v>52194797</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>79272397</v>
+        <v>71643667</v>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>10502977</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>26572309</v>
+        <v>25945431</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>54415488</v>
+        <v>37459210</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>46859038</v>
+        <v>48992678</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>52194797</v>
+        <v>64308195</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>71643667</v>
+        <v>79272397</v>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>7251330</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>14023998</v>
+        <v>3579870</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>23623555</v>
+        <v>26016508</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>37049808</v>
+        <v>28967720</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>48937774</v>
+        <v>37959389</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>45181151</v>
+        <v>50657103</v>
+      </c>
+      <c r="H8" s="40" t="n">
+        <v>10881600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>3579870</v>
+        <v>14023998</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>26016508</v>
+        <v>23623555</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>28967720</v>
+        <v>37049808</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>37959389</v>
+        <v>48937774</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>50657103</v>
+        <v>45181151</v>
+      </c>
+      <c r="H9" s="40" t="n">
+        <v>5905477</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9063650</v>
+        <v>7434617</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>19435779</v>
+        <v>11541808</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>20382320</v>
+        <v>11589026</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>23759937</v>
+        <v>20628257</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>43854730</v>
+        <v>19325665</v>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>4771552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>11787061</v>
+        <v>9063650</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>33489630</v>
+        <v>19435779</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>34406847</v>
+        <v>20382320</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>37161831</v>
+        <v>23759937</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>31826353</v>
+        <v>43854730</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>6002990</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>13421812</v>
+        <v>11787061</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>19296100</v>
+        <v>33489630</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>32898025</v>
+        <v>34406847</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>20322786</v>
+        <v>37161831</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>26950241</v>
+        <v>31826353</v>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>3461124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>6139086</v>
+        <v>13421812</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>14744333</v>
+        <v>19296100</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>18390296</v>
+        <v>32898025</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>19525644</v>
+        <v>20322786</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>30942866</v>
+        <v>26950241</v>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>3499340</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>6458596</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>16321651</v>
+        <v>363900</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>12911381</v>
+        <v>3477490</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>18213851</v>
+        <v>6698688</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>17644316</v>
+        <v>14305166</v>
+      </c>
+      <c r="H14" s="40" t="n">
+        <v>883790</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>10462042</v>
+        <v>11237754</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>24242808</v>
+        <v>29303296</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>20176647</v>
+        <v>17092421</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>18937286</v>
+        <v>18898662</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>21999340</v>
+        <v>16270790</v>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>8251918</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>7434617</v>
+        <v>6458596</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11541808</v>
+        <v>16321651</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11589026</v>
+        <v>12911381</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>20628257</v>
+        <v>18213851</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>19325665</v>
+        <v>17644316</v>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>2310347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>6139086</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>363900</v>
+        <v>14744333</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>3477490</v>
+        <v>18390296</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>6698688</v>
+        <v>19525644</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>14305166</v>
+        <v>30942866</v>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>4037150</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6011315</v>
+        <v>10462042</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>10213590</v>
+        <v>24242808</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10032796</v>
+        <v>20176647</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>23828037</v>
+        <v>18937286</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>33387187</v>
+        <v>21999340</v>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>5824810</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>11237754</v>
+        <v>6460094</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>29303296</v>
+        <v>14908071</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>17092421</v>
+        <v>20904887</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>18898662</v>
+        <v>14174417</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16270790</v>
+        <v>21360428</v>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>1492380</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>14174417</v>
+        <v>23828037</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>21360428</v>
+        <v>33387187</v>
+      </c>
+      <c r="H20" s="40" t="n">
+        <v>3408589</v>
       </c>
     </row>
     <row r="21">
@@ -3087,6 +3218,9 @@
       <c r="G21" s="40" t="n">
         <v>12820644</v>
       </c>
+      <c r="H21" s="40" t="n">
+        <v>849350</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -3114,6 +3248,9 @@
       <c r="G22" s="40" t="n">
         <v>9843920</v>
       </c>
+      <c r="H22" s="40" t="n">
+        <v>652900</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -3140,6 +3277,9 @@
       </c>
       <c r="G23" s="40" t="n">
         <v>11771640</v>
+      </c>
+      <c r="H23" s="40" t="n">
+        <v>2341200</v>
       </c>
     </row>
     <row r="24">
@@ -3167,6 +3307,10 @@
       </c>
       <c r="G24" s="41">
         <f>AVERAGE(G6:G23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="41">
+        <f>AVERAGE(H6:H23)</f>
         <v/>
       </c>
     </row>
@@ -3181,7 +3325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3191,6 +3335,7 @@
     <col width="13" customWidth="1" style="20" min="5" max="5"/>
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
+    <col width="13" customWidth="1" style="20" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3233,6 +3378,11 @@
           <t>2026-06-08</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3268,6 +3418,11 @@
       <c r="G4" s="31" t="inlineStr">
         <is>
           <t>08.06–14.06</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>15.06–21.06*</t>
         </is>
       </c>
     </row>
@@ -3293,16 +3448,19 @@
       <c r="G5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="H5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -3320,16 +3478,19 @@
       <c r="G6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
@@ -3347,20 +3508,23 @@
       <c r="G7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="42" t="n">
         <v>7</v>
@@ -3373,21 +3537,24 @@
       </c>
       <c r="G8" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="42" t="n">
         <v>7</v>
@@ -3400,17 +3567,20 @@
       </c>
       <c r="G9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -3428,16 +3598,19 @@
       <c r="G10" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H10" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
@@ -3455,16 +3628,19 @@
       <c r="G11" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H11" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
@@ -3482,16 +3658,19 @@
       <c r="G12" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H12" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3509,23 +3688,26 @@
       <c r="G13" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H13" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -3535,17 +3717,20 @@
       </c>
       <c r="G14" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -3563,16 +3748,19 @@
       <c r="G15" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H15" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3590,23 +3778,26 @@
       <c r="G16" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H16" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -3616,17 +3807,20 @@
       </c>
       <c r="G17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3644,16 +3838,19 @@
       <c r="G18" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H18" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3671,16 +3868,19 @@
       <c r="G19" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H19" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3698,6 +3898,9 @@
       <c r="G20" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H20" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -3725,6 +3928,9 @@
       <c r="G21" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H21" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -3752,6 +3958,9 @@
       <c r="G22" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="H22" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -3778,6 +3987,9 @@
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -3807,6 +4019,10 @@
         <f>AVERAGE(G6:G23)</f>
         <v/>
       </c>
+      <c r="H24" s="43">
+        <f>AVERAGE(H6:H23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2029,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2059,7 +2059,7 @@
         <v>58.43</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>71</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="7">
@@ -2089,67 +2089,67 @@
         <v>67.86</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>46</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>5.5</v>
+        <v>18.6</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>17.86</v>
+        <v>21.57</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>20.86</v>
+        <v>26.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>24.86</v>
+        <v>35.57</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>36.43</v>
+        <v>39.71</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>18.6</v>
+        <v>5.5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>21.57</v>
+        <v>17.86</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>26.14</v>
+        <v>20.86</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>35.57</v>
+        <v>24.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>39.71</v>
+        <v>36.43</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>42</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="10">
@@ -2179,37 +2179,37 @@
         <v>18.57</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>13</v>
+        <v>0.25</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>17.71</v>
+        <v>2.86</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.57</v>
+        <v>8.43</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>32.29</v>
+        <v>17.57</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -2239,7 +2239,7 @@
         <v>31.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="13">
@@ -2269,217 +2269,217 @@
         <v>20.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>0.25</v>
+        <v>21.71</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>2.86</v>
+        <v>15.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>8.43</v>
+        <v>17</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>17.57</v>
+        <v>18.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>14.8</v>
+        <v>8</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>19.43</v>
+        <v>13</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>15.71</v>
+        <v>17.71</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.86</v>
+        <v>26.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>16.57</v>
+        <v>32.29</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>7</v>
+        <v>14.8</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>12.57</v>
+        <v>19.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>15.71</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.43</v>
+        <v>14.86</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>19</v>
+        <v>16.57</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>13.29</v>
+        <v>12.57</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>14.57</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>16.71</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>19.71</v>
+        <v>19</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>24</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>21.71</v>
+        <v>13.29</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>15.43</v>
+        <v>14.57</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>17</v>
+        <v>16.71</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>18.71</v>
+        <v>19.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>14.14</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>16.43</v>
+        <v>17.14</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>14.14</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>17.14</v>
+        <v>16.43</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2509,7 +2509,7 @@
         <v>12.57</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2539,7 +2539,7 @@
         <v>7.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="23">
@@ -2569,7 +2569,7 @@
         <v>4.86</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="24">
@@ -2739,7 +2739,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2769,7 +2769,7 @@
         <v>71643667</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>10502977</v>
+        <v>18038326</v>
       </c>
     </row>
     <row r="7">
@@ -2799,67 +2799,67 @@
         <v>79272397</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>7251330</v>
+        <v>16475600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>3579870</v>
+        <v>14023998</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>26016508</v>
+        <v>23623555</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>28967720</v>
+        <v>37049808</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>37959389</v>
+        <v>48937774</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>50657103</v>
+        <v>45181151</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>10881600</v>
+        <v>11185856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>14023998</v>
+        <v>3579870</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>23623555</v>
+        <v>26016508</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>37049808</v>
+        <v>28967720</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>48937774</v>
+        <v>37959389</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>45181151</v>
+        <v>50657103</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>5905477</v>
+        <v>14123691</v>
       </c>
     </row>
     <row r="10">
@@ -2889,37 +2889,37 @@
         <v>19325665</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>4771552</v>
+        <v>8426079</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9063650</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>19435779</v>
+        <v>363900</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>20382320</v>
+        <v>3477490</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>23759937</v>
+        <v>6698688</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>43854730</v>
+        <v>14305166</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>6002990</v>
+        <v>7229759</v>
       </c>
     </row>
     <row r="12">
@@ -2949,7 +2949,7 @@
         <v>31826353</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>3461124</v>
+        <v>7156564</v>
       </c>
     </row>
     <row r="13">
@@ -2979,217 +2979,217 @@
         <v>26950241</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>3499340</v>
+        <v>7033230</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>10462042</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>363900</v>
+        <v>24242808</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>3477490</v>
+        <v>20176647</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>6698688</v>
+        <v>18937286</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>14305166</v>
+        <v>21999340</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>883790</v>
+        <v>8538730</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>11237754</v>
+        <v>9063650</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>29303296</v>
+        <v>19435779</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>17092421</v>
+        <v>20382320</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>18898662</v>
+        <v>23759937</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>16270790</v>
+        <v>43854730</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>8251918</v>
+        <v>8027280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>6458596</v>
+        <v>11237754</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>16321651</v>
+        <v>29303296</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>12911381</v>
+        <v>17092421</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18213851</v>
+        <v>18898662</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17644316</v>
+        <v>16270790</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>2310347</v>
+        <v>11085278</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>6139086</v>
+        <v>6458596</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>14744333</v>
+        <v>16321651</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>18390296</v>
+        <v>12911381</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>19525644</v>
+        <v>18213851</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>30942866</v>
+        <v>17644316</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>4037150</v>
+        <v>7692709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>10462042</v>
+        <v>6139086</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>24242808</v>
+        <v>14744333</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>20176647</v>
+        <v>18390296</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>18937286</v>
+        <v>19525644</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>21999340</v>
+        <v>30942866</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>5824810</v>
+        <v>6238010</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14174417</v>
+        <v>23828037</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>21360428</v>
+        <v>33387187</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>1492380</v>
+        <v>6569109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6011315</v>
+        <v>6460094</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>10213590</v>
+        <v>14908071</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10032796</v>
+        <v>20904887</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>23828037</v>
+        <v>14174417</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>33387187</v>
+        <v>21360428</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>3408589</v>
+        <v>2749400</v>
       </c>
     </row>
     <row r="21">
@@ -3219,7 +3219,7 @@
         <v>12820644</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>849350</v>
+        <v>4696510</v>
       </c>
     </row>
     <row r="22">
@@ -3249,7 +3249,7 @@
         <v>9843920</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>652900</v>
+        <v>1722180</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3279,7 @@
         <v>11771640</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>2341200</v>
+        <v>2752900</v>
       </c>
     </row>
     <row r="24">
@@ -3449,7 +3449,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="H6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3509,22 +3509,22 @@
         <v>7</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="42" t="n">
         <v>7</v>
@@ -3539,22 +3539,22 @@
         <v>7</v>
       </c>
       <c r="H8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="42" t="n">
         <v>7</v>
@@ -3569,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3599,25 +3599,25 @@
         <v>7</v>
       </c>
       <c r="H10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>7</v>
@@ -3629,7 +3629,7 @@
         <v>7</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -3659,7 +3659,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3689,25 +3689,25 @@
         <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -3719,18 +3719,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -3749,18 +3749,18 @@
         <v>7</v>
       </c>
       <c r="H15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3779,18 +3779,18 @@
         <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
@@ -3809,18 +3809,18 @@
         <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3839,18 +3839,18 @@
         <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3869,18 +3869,18 @@
         <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3899,7 +3899,7 @@
         <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -3929,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -3959,7 +3959,7 @@
         <v>7</v>
       </c>
       <c r="H22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -3989,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2029,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2059,7 +2059,7 @@
         <v>58.43</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>65.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -2089,7 +2089,7 @@
         <v>67.86</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>50.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -2119,7 +2119,7 @@
         <v>39.71</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>43</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="9">
@@ -2149,187 +2149,187 @@
         <v>36.43</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>33.5</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>10.8</v>
+        <v>18.8</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>13.57</v>
+        <v>26.57</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>12.57</v>
+        <v>28.29</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>17.57</v>
+        <v>28.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>18.57</v>
+        <v>31.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>30</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0.25</v>
+        <v>16.57</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>2.86</v>
+        <v>20.86</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>8.43</v>
+        <v>17.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>17.57</v>
+        <v>20.57</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>28</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>26.57</v>
+        <v>0.25</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>28.29</v>
+        <v>2.86</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>28.71</v>
+        <v>8.43</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>31.43</v>
+        <v>17.57</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>27.5</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>13.4</v>
+        <v>10.8</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>16.57</v>
+        <v>13.57</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>20.86</v>
+        <v>12.57</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>20.57</v>
+        <v>18.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>27</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>13.8</v>
+        <v>8</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>21.71</v>
+        <v>13</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>15.43</v>
+        <v>17.71</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>17</v>
+        <v>26.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>18.71</v>
+        <v>32.29</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>26</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>8</v>
+        <v>13.8</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>13</v>
+        <v>21.71</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>17.71</v>
+        <v>15.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>26.57</v>
+        <v>17</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>32.29</v>
+        <v>18.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>25.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -2359,7 +2359,7 @@
         <v>16.57</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>22</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="17">
@@ -2389,97 +2389,97 @@
         <v>19</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>14.57</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>16.71</v>
+        <v>14.14</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>19.71</v>
+        <v>17.14</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.14</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>17.14</v>
+        <v>16.43</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>19</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>10.43</v>
+        <v>13.29</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11.14</v>
+        <v>14.57</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>16.71</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>16.43</v>
+        <v>19.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>18</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="21">
@@ -2509,7 +2509,7 @@
         <v>12.57</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="22">
@@ -2539,7 +2539,7 @@
         <v>7.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>9.5</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="23">
@@ -2569,7 +2569,7 @@
         <v>4.86</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="24">
@@ -2739,7 +2739,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2769,7 +2769,7 @@
         <v>71643667</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>18038326</v>
+        <v>26739221</v>
       </c>
     </row>
     <row r="7">
@@ -2799,7 +2799,7 @@
         <v>79272397</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>16475600</v>
+        <v>31476248</v>
       </c>
     </row>
     <row r="8">
@@ -2829,7 +2829,7 @@
         <v>45181151</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>11185856</v>
+        <v>18568965</v>
       </c>
     </row>
     <row r="9">
@@ -2859,187 +2859,187 @@
         <v>50657103</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>14123691</v>
+        <v>23804609</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>7434617</v>
+        <v>11787061</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>11541808</v>
+        <v>33489630</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>11589026</v>
+        <v>34406847</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>20628257</v>
+        <v>37161831</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>19325665</v>
+        <v>31826353</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>8426079</v>
+        <v>14575283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>13421812</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>363900</v>
+        <v>19296100</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>3477490</v>
+        <v>32898025</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>6698688</v>
+        <v>20322786</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>14305166</v>
+        <v>26950241</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>7229759</v>
+        <v>14737880</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>11787061</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>33489630</v>
+        <v>363900</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>34406847</v>
+        <v>3477490</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>37161831</v>
+        <v>6698688</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>31826353</v>
+        <v>14305166</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>7156564</v>
+        <v>9306759</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>13421812</v>
+        <v>7434617</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>19296100</v>
+        <v>11541808</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>32898025</v>
+        <v>11589026</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>20322786</v>
+        <v>20628257</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>26950241</v>
+        <v>19325665</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>7033230</v>
+        <v>11869319</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>10462042</v>
+        <v>9063650</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>24242808</v>
+        <v>19435779</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>20176647</v>
+        <v>20382320</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>18937286</v>
+        <v>23759937</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>21999340</v>
+        <v>43854730</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>8538730</v>
+        <v>9976580</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>9063650</v>
+        <v>10462042</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>19435779</v>
+        <v>24242808</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>20382320</v>
+        <v>20176647</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>23759937</v>
+        <v>18937286</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>43854730</v>
+        <v>21999340</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>8027280</v>
+        <v>12965122</v>
       </c>
     </row>
     <row r="16">
@@ -3069,7 +3069,7 @@
         <v>16270790</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>11085278</v>
+        <v>15695913</v>
       </c>
     </row>
     <row r="17">
@@ -3099,97 +3099,97 @@
         <v>17644316</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>7692709</v>
+        <v>11191865</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6139086</v>
+        <v>6011315</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>14744333</v>
+        <v>10213590</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>18390296</v>
+        <v>10032796</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>19525644</v>
+        <v>23828037</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>30942866</v>
+        <v>33387187</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>6238010</v>
+        <v>10090902</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6011315</v>
+        <v>6460094</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>10213590</v>
+        <v>14908071</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10032796</v>
+        <v>20904887</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>23828037</v>
+        <v>14174417</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>33387187</v>
+        <v>21360428</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>6569109</v>
+        <v>4655230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6460094</v>
+        <v>6139086</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>14908071</v>
+        <v>14744333</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>20904887</v>
+        <v>18390296</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>14174417</v>
+        <v>19525644</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>21360428</v>
+        <v>30942866</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>2749400</v>
+        <v>7834650</v>
       </c>
     </row>
     <row r="21">
@@ -3219,7 +3219,7 @@
         <v>12820644</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>4696510</v>
+        <v>7829320</v>
       </c>
     </row>
     <row r="22">
@@ -3249,7 +3249,7 @@
         <v>9843920</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>1722180</v>
+        <v>2560250</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3279,7 @@
         <v>11771640</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>2752900</v>
+        <v>2826080</v>
       </c>
     </row>
     <row r="24">
@@ -3449,7 +3449,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="H6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3509,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3539,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3569,18 +3569,18 @@
         <v>7</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -3599,25 +3599,25 @@
         <v>7</v>
       </c>
       <c r="H10" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>7</v>
@@ -3629,25 +3629,25 @@
         <v>7</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -3659,18 +3659,18 @@
         <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3689,18 +3689,18 @@
         <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
@@ -3719,18 +3719,18 @@
         <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -3749,7 +3749,7 @@
         <v>7</v>
       </c>
       <c r="H15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3779,7 +3779,7 @@
         <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3809,18 +3809,18 @@
         <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3839,18 +3839,18 @@
         <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3869,18 +3869,18 @@
         <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3899,7 +3899,7 @@
         <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -3929,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -3959,7 +3959,7 @@
         <v>7</v>
       </c>
       <c r="H22" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3989,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2029,67 +2029,67 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>30</v>
+        <v>33.4</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>37.86</v>
+        <v>41.14</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>39.57</v>
+        <v>36.43</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>51.43</v>
+        <v>53</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>58.43</v>
+        <v>67.86</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>60</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>33.4</v>
+        <v>30</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>41.14</v>
+        <v>37.86</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>36.43</v>
+        <v>39.57</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>53</v>
+        <v>51.43</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>67.86</v>
+        <v>58.43</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="8">
@@ -2119,7 +2119,7 @@
         <v>39.71</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>44.67</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="9">
@@ -2149,7 +2149,7 @@
         <v>36.43</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>36.67</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="10">
@@ -2179,127 +2179,127 @@
         <v>31.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>31.67</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>13.4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>16.57</v>
+        <v>13</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>20.86</v>
+        <v>17.71</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>17.14</v>
+        <v>26.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>20.57</v>
+        <v>32.29</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>28.67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0.25</v>
+        <v>13.57</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>2.86</v>
+        <v>12.57</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>8.43</v>
+        <v>17.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>17.57</v>
+        <v>18.57</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>28.67</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>13.57</v>
+        <v>16.57</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.57</v>
+        <v>20.86</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>18.57</v>
+        <v>20.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>26.67</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>13</v>
+        <v>0.25</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>17.71</v>
+        <v>2.86</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>26.57</v>
+        <v>8.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>32.29</v>
+        <v>17.57</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>23.33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -2329,67 +2329,67 @@
         <v>18.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>14.8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>19.43</v>
+        <v>12.57</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>15.71</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.86</v>
+        <v>13.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>16.57</v>
+        <v>19</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>22.33</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>7</v>
+        <v>14.8</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>12.57</v>
+        <v>19.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>15.71</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>14.86</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>19</v>
+        <v>16.57</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>19</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="18">
@@ -2419,7 +2419,7 @@
         <v>17.14</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>18</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="19">
@@ -2449,7 +2449,7 @@
         <v>16.43</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>17.33</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="20">
@@ -2479,7 +2479,7 @@
         <v>19.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>16.67</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="21">
@@ -2509,7 +2509,7 @@
         <v>12.57</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>11.67</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="22">
@@ -2539,7 +2539,7 @@
         <v>7.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>9.67</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="23">
@@ -2569,7 +2569,7 @@
         <v>4.86</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2739,67 +2739,67 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
-        <v>26572309</v>
+        <v>25945431</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>54415488</v>
+        <v>37459210</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>46859038</v>
+        <v>48992678</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>52194797</v>
+        <v>64308195</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>71643667</v>
+        <v>79272397</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>26739221</v>
+        <v>43870123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>25945431</v>
+        <v>26572309</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>37459210</v>
+        <v>54415488</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>48992678</v>
+        <v>46859038</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>64308195</v>
+        <v>52194797</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>79272397</v>
+        <v>71643667</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>31476248</v>
+        <v>34396596</v>
       </c>
     </row>
     <row r="8">
@@ -2829,7 +2829,7 @@
         <v>45181151</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>18568965</v>
+        <v>24487725</v>
       </c>
     </row>
     <row r="9">
@@ -2859,7 +2859,7 @@
         <v>50657103</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>23804609</v>
+        <v>32432649</v>
       </c>
     </row>
     <row r="10">
@@ -2889,127 +2889,127 @@
         <v>31826353</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>14575283</v>
+        <v>24418428</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>13421812</v>
+        <v>9063650</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>19296100</v>
+        <v>19435779</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>32898025</v>
+        <v>20382320</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>20322786</v>
+        <v>23759937</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>26950241</v>
+        <v>43854730</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>14737880</v>
+        <v>17672591</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>7434617</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>363900</v>
+        <v>11541808</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>3477490</v>
+        <v>11589026</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>6698688</v>
+        <v>20628257</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>14305166</v>
+        <v>19325665</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>9306759</v>
+        <v>14828189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>7434617</v>
+        <v>13421812</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>11541808</v>
+        <v>19296100</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>11589026</v>
+        <v>32898025</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>20628257</v>
+        <v>20322786</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>19325665</v>
+        <v>26950241</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>11869319</v>
+        <v>16833400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>9063650</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>19435779</v>
+        <v>363900</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>20382320</v>
+        <v>3477490</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>23759937</v>
+        <v>6698688</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>43854730</v>
+        <v>14305166</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>9976580</v>
+        <v>9751489</v>
       </c>
     </row>
     <row r="15">
@@ -3039,67 +3039,67 @@
         <v>21999340</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>12965122</v>
+        <v>17472822</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>11237754</v>
+        <v>6458596</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>29303296</v>
+        <v>16321651</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>17092421</v>
+        <v>12911381</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18898662</v>
+        <v>18213851</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>16270790</v>
+        <v>17644316</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>15695913</v>
+        <v>14012005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>6458596</v>
+        <v>11237754</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>16321651</v>
+        <v>29303296</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>12911381</v>
+        <v>17092421</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>18213851</v>
+        <v>18898662</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>17644316</v>
+        <v>16270790</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>11191865</v>
+        <v>17452136</v>
       </c>
     </row>
     <row r="18">
@@ -3129,7 +3129,7 @@
         <v>33387187</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>10090902</v>
+        <v>13770652</v>
       </c>
     </row>
     <row r="19">
@@ -3159,7 +3159,7 @@
         <v>21360428</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>4655230</v>
+        <v>5830040</v>
       </c>
     </row>
     <row r="20">
@@ -3189,7 +3189,7 @@
         <v>30942866</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>7834650</v>
+        <v>11968520</v>
       </c>
     </row>
     <row r="21">
@@ -3219,7 +3219,7 @@
         <v>12820644</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>7829320</v>
+        <v>10383580</v>
       </c>
     </row>
     <row r="22">
@@ -3249,7 +3249,7 @@
         <v>9843920</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>2560250</v>
+        <v>3315640</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3279,7 @@
         <v>11771640</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>2826080</v>
+        <v>2925070</v>
       </c>
     </row>
     <row r="24">
@@ -3449,18 +3449,18 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -3479,18 +3479,18 @@
         <v>7</v>
       </c>
       <c r="H6" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
@@ -3509,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3539,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3569,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3599,18 +3599,18 @@
         <v>7</v>
       </c>
       <c r="H10" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
@@ -3629,48 +3629,48 @@
         <v>7</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
         <v>4</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3689,25 +3689,25 @@
         <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -3719,7 +3719,7 @@
         <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -3749,18 +3749,18 @@
         <v>7</v>
       </c>
       <c r="H15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3779,18 +3779,18 @@
         <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
@@ -3809,7 +3809,7 @@
         <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3839,7 +3839,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3869,7 +3869,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -3899,7 +3899,7 @@
         <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -3929,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -3959,7 +3959,7 @@
         <v>7</v>
       </c>
       <c r="H22" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -3989,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2029,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2059,7 +2059,7 @@
         <v>67.86</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>65.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2089,7 +2089,7 @@
         <v>58.43</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>60.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="8">
@@ -2119,7 +2119,7 @@
         <v>39.71</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>43.75</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="9">
@@ -2149,7 +2149,7 @@
         <v>36.43</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38.25</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="10">
@@ -2179,7 +2179,7 @@
         <v>31.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -2209,127 +2209,127 @@
         <v>32.29</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>13.57</v>
+        <v>16.57</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.57</v>
+        <v>20.86</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>18.57</v>
+        <v>20.57</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>25.5</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>16.57</v>
+        <v>21.71</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>20.86</v>
+        <v>15.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17.14</v>
+        <v>17</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>20.57</v>
+        <v>18.71</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>25.25</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>0.25</v>
+        <v>13.57</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>2.86</v>
+        <v>12.57</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>8.43</v>
+        <v>17.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>17.57</v>
+        <v>18.57</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>25</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>21.71</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>15.43</v>
+        <v>2.86</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>17</v>
+        <v>8.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>18.71</v>
+        <v>17.57</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>23.25</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="16">
@@ -2359,7 +2359,7 @@
         <v>19</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>22.25</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="17">
@@ -2389,67 +2389,67 @@
         <v>16.57</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>20.25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.14</v>
+        <v>13.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>17.14</v>
+        <v>16.43</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17.75</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>14.14</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>16.43</v>
+        <v>17.14</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="20">
@@ -2479,7 +2479,7 @@
         <v>19.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="21">
@@ -2509,7 +2509,7 @@
         <v>12.57</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>12.25</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="22">
@@ -2539,7 +2539,7 @@
         <v>7.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -2569,7 +2569,7 @@
         <v>4.86</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2739,7 +2739,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2769,7 +2769,7 @@
         <v>79272397</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>43870123</v>
+        <v>54403313</v>
       </c>
     </row>
     <row r="7">
@@ -2799,7 +2799,7 @@
         <v>71643667</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>34396596</v>
+        <v>42982493</v>
       </c>
     </row>
     <row r="8">
@@ -2829,7 +2829,7 @@
         <v>45181151</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>24487725</v>
+        <v>31487294</v>
       </c>
     </row>
     <row r="9">
@@ -2859,7 +2859,7 @@
         <v>50657103</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>32432649</v>
+        <v>37819439</v>
       </c>
     </row>
     <row r="10">
@@ -2889,7 +2889,7 @@
         <v>31826353</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>24418428</v>
+        <v>27922528</v>
       </c>
     </row>
     <row r="11">
@@ -2919,127 +2919,127 @@
         <v>43854730</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>17672591</v>
+        <v>22046036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>7434617</v>
+        <v>13421812</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>11541808</v>
+        <v>19296100</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>11589026</v>
+        <v>32898025</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>20628257</v>
+        <v>20322786</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>19325665</v>
+        <v>26950241</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>14828189</v>
+        <v>21463940</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>13421812</v>
+        <v>10462042</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>19296100</v>
+        <v>24242808</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>32898025</v>
+        <v>20176647</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>20322786</v>
+        <v>18937286</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>26950241</v>
+        <v>21999340</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>16833400</v>
+        <v>20673362</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>7434617</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>363900</v>
+        <v>11541808</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>3477490</v>
+        <v>11589026</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>6698688</v>
+        <v>20628257</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>14305166</v>
+        <v>19325665</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>9751489</v>
+        <v>16596029</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>10462042</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>24242808</v>
+        <v>363900</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>20176647</v>
+        <v>3477490</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>18937286</v>
+        <v>6698688</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>21999340</v>
+        <v>14305166</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17472822</v>
+        <v>10599879</v>
       </c>
     </row>
     <row r="16">
@@ -3069,7 +3069,7 @@
         <v>17644316</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14012005</v>
+        <v>15303725</v>
       </c>
     </row>
     <row r="17">
@@ -3099,67 +3099,67 @@
         <v>16270790</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17452136</v>
+        <v>23502206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6011315</v>
+        <v>6460094</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>10213590</v>
+        <v>14908071</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10032796</v>
+        <v>20904887</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>23828037</v>
+        <v>14174417</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>33387187</v>
+        <v>21360428</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>13770652</v>
+        <v>9451574</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14174417</v>
+        <v>23828037</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>21360428</v>
+        <v>33387187</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>5830040</v>
+        <v>16828919</v>
       </c>
     </row>
     <row r="20">
@@ -3189,7 +3189,7 @@
         <v>30942866</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>11968520</v>
+        <v>16047450</v>
       </c>
     </row>
     <row r="21">
@@ -3219,7 +3219,7 @@
         <v>12820644</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>10383580</v>
+        <v>12417660</v>
       </c>
     </row>
     <row r="22">
@@ -3249,7 +3249,7 @@
         <v>9843920</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>3315640</v>
+        <v>3938970</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3279,7 @@
         <v>11771640</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>2925070</v>
+        <v>3386950</v>
       </c>
     </row>
     <row r="24">
@@ -3449,7 +3449,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="H6" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3509,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3539,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3569,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -3599,7 +3599,7 @@
         <v>7</v>
       </c>
       <c r="H10" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -3629,18 +3629,18 @@
         <v>7</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
@@ -3659,18 +3659,18 @@
         <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3689,25 +3689,25 @@
         <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -3719,37 +3719,37 @@
         <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -3779,7 +3779,7 @@
         <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3809,18 +3809,18 @@
         <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3839,18 +3839,18 @@
         <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3869,7 +3869,7 @@
         <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -3899,7 +3899,7 @@
         <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -3929,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -3959,7 +3959,7 @@
         <v>7</v>
       </c>
       <c r="H22" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3989,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2029,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2059,7 +2059,7 @@
         <v>67.86</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>68</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="7">
@@ -2089,7 +2089,7 @@
         <v>58.43</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>62.6</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="8">
@@ -2119,7 +2119,7 @@
         <v>39.71</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>44.6</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="9">
@@ -2149,67 +2149,67 @@
         <v>36.43</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>37.6</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>18.8</v>
+        <v>8</v>
       </c>
       <c r="D10" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="F10" s="36" t="n">
         <v>26.57</v>
       </c>
-      <c r="E10" s="36" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>28.71</v>
-      </c>
       <c r="G10" s="36" t="n">
-        <v>31.43</v>
+        <v>32.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>32</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>8</v>
+        <v>18.8</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>13</v>
+        <v>26.57</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>17.71</v>
+        <v>28.29</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.57</v>
+        <v>28.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>32.29</v>
+        <v>31.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>29.8</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="12">
@@ -2239,7 +2239,7 @@
         <v>20.57</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>24.4</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="13">
@@ -2269,7 +2269,7 @@
         <v>18.71</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>24.2</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="14">
@@ -2299,7 +2299,7 @@
         <v>18.57</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="15">
@@ -2329,7 +2329,7 @@
         <v>17.57</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>22.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -2359,7 +2359,7 @@
         <v>19</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>20.8</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="17">
@@ -2389,97 +2389,97 @@
         <v>16.57</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>19</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>10.43</v>
+        <v>13.29</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11.14</v>
+        <v>14.57</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.43</v>
+        <v>16.71</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>16.43</v>
+        <v>19.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.14</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>17.14</v>
+        <v>16.43</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>14.57</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>16.71</v>
+        <v>14.14</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>19.71</v>
+        <v>17.14</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>16.4</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="21">
@@ -2509,7 +2509,7 @@
         <v>12.57</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>11.6</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="22">
@@ -2539,7 +2539,7 @@
         <v>7.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="23">
@@ -2569,7 +2569,7 @@
         <v>4.86</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24">
@@ -2739,7 +2739,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2769,7 +2769,7 @@
         <v>79272397</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>54403313</v>
+        <v>59190916</v>
       </c>
     </row>
     <row r="7">
@@ -2799,7 +2799,7 @@
         <v>71643667</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>42982493</v>
+        <v>72569185</v>
       </c>
     </row>
     <row r="8">
@@ -2829,7 +2829,7 @@
         <v>45181151</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>31487294</v>
+        <v>37635828</v>
       </c>
     </row>
     <row r="9">
@@ -2859,67 +2859,67 @@
         <v>50657103</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>37819439</v>
+        <v>41648329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>11787061</v>
+        <v>9063650</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>33489630</v>
+        <v>19435779</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>34406847</v>
+        <v>20382320</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>37161831</v>
+        <v>23759937</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>31826353</v>
+        <v>43854730</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>27922528</v>
+        <v>31152950</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9063650</v>
+        <v>11787061</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>19435779</v>
+        <v>33489630</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>20382320</v>
+        <v>34406847</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>23759937</v>
+        <v>37161831</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>43854730</v>
+        <v>31826353</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22046036</v>
+        <v>33637818</v>
       </c>
     </row>
     <row r="12">
@@ -2949,7 +2949,7 @@
         <v>26950241</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>21463940</v>
+        <v>24961140</v>
       </c>
     </row>
     <row r="13">
@@ -2979,7 +2979,7 @@
         <v>21999340</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>20673362</v>
+        <v>25696380</v>
       </c>
     </row>
     <row r="14">
@@ -3009,7 +3009,7 @@
         <v>19325665</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>16596029</v>
+        <v>20576609</v>
       </c>
     </row>
     <row r="15">
@@ -3039,7 +3039,7 @@
         <v>14305166</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>10599879</v>
+        <v>11846559</v>
       </c>
     </row>
     <row r="16">
@@ -3069,7 +3069,7 @@
         <v>17644316</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>15303725</v>
+        <v>16790555</v>
       </c>
     </row>
     <row r="17">
@@ -3099,97 +3099,97 @@
         <v>16270790</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>23502206</v>
+        <v>26544973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6460094</v>
+        <v>6139086</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>14908071</v>
+        <v>14744333</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>20904887</v>
+        <v>18390296</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>14174417</v>
+        <v>19525644</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>21360428</v>
+        <v>30942866</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>9451574</v>
+        <v>19831440</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6011315</v>
+        <v>6460094</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>10213590</v>
+        <v>14908071</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10032796</v>
+        <v>20904887</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>23828037</v>
+        <v>14174417</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>33387187</v>
+        <v>21360428</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>16828919</v>
+        <v>10797694</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6139086</v>
+        <v>6011315</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>14744333</v>
+        <v>10213590</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>18390296</v>
+        <v>10032796</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>19525644</v>
+        <v>23828037</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>30942866</v>
+        <v>33387187</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>16047450</v>
+        <v>20906719</v>
       </c>
     </row>
     <row r="21">
@@ -3219,7 +3219,7 @@
         <v>12820644</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>12417660</v>
+        <v>13238560</v>
       </c>
     </row>
     <row r="22">
@@ -3249,7 +3249,7 @@
         <v>9843920</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>3938970</v>
+        <v>4725250</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3279,7 @@
         <v>11771640</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>3386950</v>
+        <v>3756760</v>
       </c>
     </row>
     <row r="24">
@@ -3449,7 +3449,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="H6" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3509,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -3539,7 +3539,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -3569,18 +3569,18 @@
         <v>7</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -3599,18 +3599,18 @@
         <v>7</v>
       </c>
       <c r="H10" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
@@ -3629,7 +3629,7 @@
         <v>7</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3659,7 +3659,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3689,7 +3689,7 @@
         <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -3719,7 +3719,7 @@
         <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -3749,7 +3749,7 @@
         <v>7</v>
       </c>
       <c r="H15" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -3779,7 +3779,7 @@
         <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3809,18 +3809,18 @@
         <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3839,18 +3839,18 @@
         <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3869,18 +3869,18 @@
         <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3899,7 +3899,7 @@
         <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -3929,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -3959,7 +3959,7 @@
         <v>7</v>
       </c>
       <c r="H22" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -3989,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1916,6 +1916,7 @@
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
     <col width="13" customWidth="1" style="20" min="8" max="8"/>
+    <col width="13" customWidth="1" style="20" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1963,6 +1964,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2002,7 +2008,12 @@
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>15.06–21.06*</t>
+          <t>15.06–21.06</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>22.06–28.06*</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2040,10 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2059,307 +2073,340 @@
         <v>67.86</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>63.5</v>
+        <v>60.86</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>30</v>
+        <v>5.5</v>
       </c>
       <c r="D7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="H7" s="36" t="n">
         <v>37.86</v>
       </c>
-      <c r="E7" s="36" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="F7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="G7" s="36" t="n">
-        <v>58.43</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>61.67</v>
+      <c r="I7" s="36" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>18.6</v>
+        <v>30</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>21.57</v>
+        <v>37.86</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>26.14</v>
+        <v>39.57</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>35.57</v>
+        <v>51.43</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>39.71</v>
+        <v>58.43</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>43.5</v>
+        <v>62.86</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>17.86</v>
+        <v>0.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>20.86</v>
+        <v>2.86</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>24.86</v>
+        <v>8.43</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>36.43</v>
+        <v>17.57</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>36.17</v>
+        <v>20.43</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>8</v>
+        <v>18.6</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>13</v>
+        <v>21.57</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>17.71</v>
+        <v>26.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.57</v>
+        <v>35.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>32.29</v>
+        <v>39.71</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>32.83</v>
+        <v>41.43</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>18.8</v>
+        <v>8</v>
       </c>
       <c r="D11" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="F11" s="36" t="n">
         <v>26.57</v>
       </c>
-      <c r="E11" s="36" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>28.71</v>
-      </c>
       <c r="G11" s="36" t="n">
-        <v>31.43</v>
+        <v>32.29</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>31.17</v>
+        <v>31.29</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>13.4</v>
+        <v>7</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>16.57</v>
+        <v>12.57</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>20.86</v>
+        <v>11.29</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>17.14</v>
+        <v>13.43</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>20.57</v>
+        <v>19</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>23.67</v>
+        <v>21.14</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>13.8</v>
+        <v>11</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>21.71</v>
+        <v>10.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>15.43</v>
+        <v>11.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>17</v>
+        <v>13.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>18.71</v>
+        <v>16.43</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>23.67</v>
+        <v>15.57</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>10.8</v>
+        <v>18.8</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>13.57</v>
+        <v>26.57</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.57</v>
+        <v>28.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>17.57</v>
+        <v>28.71</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>18.57</v>
+        <v>31.43</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>22.5</v>
+        <v>33</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>0.25</v>
+        <v>13.29</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>2.86</v>
+        <v>14.57</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>8.43</v>
+        <v>16.71</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>17.57</v>
+        <v>19.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>20</v>
+        <v>17.43</v>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>7</v>
+        <v>13.8</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>12.57</v>
+        <v>21.71</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>15.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.43</v>
+        <v>17</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>19</v>
+        <v>18.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>19.67</v>
+        <v>23</v>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2389,97 +2436,109 @@
         <v>16.57</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>19.33</v>
+        <v>19.71</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>13.29</v>
+        <v>13.57</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>14.57</v>
+        <v>12.57</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>16.71</v>
+        <v>17.57</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>19.71</v>
+        <v>18.57</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>10.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>14.14</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>16.43</v>
+        <v>17.14</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>16.5</v>
+        <v>16</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>7.2</v>
+        <v>13.4</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>16.57</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>20.86</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>14.14</v>
+        <v>17.14</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>17.14</v>
+        <v>20.57</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>16.17</v>
+        <v>21.57</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2509,7 +2568,10 @@
         <v>12.57</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>10.67</v>
+        <v>11.57</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2539,7 +2601,10 @@
         <v>7.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
+      </c>
+      <c r="I22" s="36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -2569,7 +2634,10 @@
         <v>4.86</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
+      </c>
+      <c r="I23" s="36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2601,6 +2669,10 @@
       </c>
       <c r="H24" s="39">
         <f>AVERAGE(H6:H23)</f>
+        <v/>
+      </c>
+      <c r="I24" s="39">
+        <f>AVERAGE(I6:I23)</f>
         <v/>
       </c>
     </row>
@@ -2615,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2626,6 +2698,7 @@
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
     <col width="13" customWidth="1" style="20" min="8" max="8"/>
+    <col width="13" customWidth="1" style="20" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2673,6 +2746,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2712,7 +2790,12 @@
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>15.06–21.06*</t>
+          <t>15.06–21.06</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>22.06–28.06*</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2822,10 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2769,307 +2855,340 @@
         <v>79272397</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>59190916</v>
+        <v>65286326</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>9924048</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>26572309</v>
+        <v>3579870</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>54415488</v>
+        <v>26016508</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>46859038</v>
+        <v>28967720</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>52194797</v>
+        <v>37959389</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>71643667</v>
+        <v>50657103</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>72569185</v>
+        <v>51071479</v>
+      </c>
+      <c r="I7" s="40" t="n">
+        <v>14176282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>14023998</v>
+        <v>26572309</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>23623555</v>
+        <v>54415488</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>37049808</v>
+        <v>46859038</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>48937774</v>
+        <v>52194797</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>45181151</v>
+        <v>71643667</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>37635828</v>
+        <v>85106488</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>9007657</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>3579870</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>26016508</v>
+        <v>363900</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>28967720</v>
+        <v>3477490</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>37959389</v>
+        <v>6698688</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>50657103</v>
+        <v>14305166</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>41648329</v>
+        <v>13436059</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>1527710</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9063650</v>
+        <v>14023998</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>19435779</v>
+        <v>23623555</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>20382320</v>
+        <v>37049808</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>23759937</v>
+        <v>48937774</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>43854730</v>
+        <v>45181151</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>31152950</v>
+        <v>41840209</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>6430123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>11787061</v>
+        <v>9063650</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>33489630</v>
+        <v>19435779</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>34406847</v>
+        <v>20382320</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>37161831</v>
+        <v>23759937</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>31826353</v>
+        <v>43854730</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>33637818</v>
+        <v>39943773</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>7358473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>13421812</v>
+        <v>6458596</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>19296100</v>
+        <v>16321651</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>32898025</v>
+        <v>12911381</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>20322786</v>
+        <v>18213851</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>26950241</v>
+        <v>17644316</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>24961140</v>
+        <v>20445615</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>2461577</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>10462042</v>
+        <v>6460094</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>24242808</v>
+        <v>14908071</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>20176647</v>
+        <v>20904887</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>18937286</v>
+        <v>14174417</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>21999340</v>
+        <v>21360428</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>25696380</v>
+        <v>14219534</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>3552356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>7434617</v>
+        <v>11787061</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11541808</v>
+        <v>33489630</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11589026</v>
+        <v>34406847</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>20628257</v>
+        <v>37161831</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>19325665</v>
+        <v>31826353</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>20576609</v>
+        <v>42562578</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>3032931</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>6139086</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>363900</v>
+        <v>14744333</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>3477490</v>
+        <v>18390296</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>6698688</v>
+        <v>19525644</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>14305166</v>
+        <v>30942866</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>11846559</v>
+        <v>24505921</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>6786916</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>6458596</v>
+        <v>10462042</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>16321651</v>
+        <v>24242808</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>12911381</v>
+        <v>20176647</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18213851</v>
+        <v>18937286</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17644316</v>
+        <v>21999340</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>16790555</v>
+        <v>27825060</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>4164590</v>
       </c>
     </row>
     <row r="17">
@@ -3099,97 +3218,109 @@
         <v>16270790</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>26544973</v>
+        <v>31755885</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>5776870</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>6139086</v>
+        <v>7434617</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>14744333</v>
+        <v>11541808</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>18390296</v>
+        <v>11589026</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>19525644</v>
+        <v>20628257</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>30942866</v>
+        <v>19325665</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19831440</v>
+        <v>21624119</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>3184411</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6460094</v>
+        <v>6011315</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>14908071</v>
+        <v>10213590</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>20904887</v>
+        <v>10032796</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14174417</v>
+        <v>23828037</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>21360428</v>
+        <v>33387187</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>10797694</v>
+        <v>23074719</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>5338500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>6011315</v>
+        <v>13421812</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>10213590</v>
+        <v>19296100</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10032796</v>
+        <v>32898025</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>23828037</v>
+        <v>20322786</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>33387187</v>
+        <v>26950241</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>20906719</v>
+        <v>25897560</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>1445133</v>
       </c>
     </row>
     <row r="21">
@@ -3219,7 +3350,10 @@
         <v>12820644</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>13238560</v>
+        <v>19371310</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>1161730</v>
       </c>
     </row>
     <row r="22">
@@ -3249,7 +3383,10 @@
         <v>9843920</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>4725250</v>
+        <v>4991190</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>865560</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3416,10 @@
         <v>11771640</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>3756760</v>
+        <v>3834910</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>263320</v>
       </c>
     </row>
     <row r="24">
@@ -3311,6 +3451,10 @@
       </c>
       <c r="H24" s="41">
         <f>AVERAGE(H6:H23)</f>
+        <v/>
+      </c>
+      <c r="I24" s="41">
+        <f>AVERAGE(I6:I23)</f>
         <v/>
       </c>
     </row>
@@ -3325,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3336,6 +3480,7 @@
     <col width="13" customWidth="1" style="20" min="6" max="6"/>
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
     <col width="13" customWidth="1" style="20" min="8" max="8"/>
+    <col width="13" customWidth="1" style="20" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3383,6 +3528,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3422,7 +3572,12 @@
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>15.06–21.06*</t>
+          <t>15.06–21.06</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>22.06–28.06*</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3604,10 @@
         <v>7</v>
       </c>
       <c r="H5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3479,22 +3637,25 @@
         <v>7</v>
       </c>
       <c r="H6" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I6" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="42" t="n">
         <v>7</v>
@@ -3509,18 +3670,21 @@
         <v>7</v>
       </c>
       <c r="H7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I7" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
@@ -3539,26 +3703,29 @@
         <v>7</v>
       </c>
       <c r="H8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
       </c>
@@ -3569,18 +3736,21 @@
         <v>7</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
@@ -3599,18 +3769,21 @@
         <v>7</v>
       </c>
       <c r="H10" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
@@ -3629,18 +3802,21 @@
         <v>7</v>
       </c>
       <c r="H11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
@@ -3659,18 +3835,21 @@
         <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -3689,18 +3868,21 @@
         <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
@@ -3719,25 +3901,28 @@
         <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -3749,18 +3934,21 @@
         <v>7</v>
       </c>
       <c r="H15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -3779,7 +3967,10 @@
         <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3809,18 +4000,21 @@
         <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -3839,18 +4033,21 @@
         <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -3869,18 +4066,21 @@
         <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -3899,7 +4099,10 @@
         <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3929,7 +4132,10 @@
         <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -3959,7 +4165,10 @@
         <v>7</v>
       </c>
       <c r="H22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I22" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -3989,7 +4198,10 @@
         <v>7</v>
       </c>
       <c r="H23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4023,6 +4235,10 @@
         <f>AVERAGE(H6:H23)</f>
         <v/>
       </c>
+      <c r="I24" s="43">
+        <f>AVERAGE(I6:I23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1917,6 +1917,8 @@
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
     <col width="13" customWidth="1" style="20" min="8" max="8"/>
     <col width="13" customWidth="1" style="20" min="9" max="9"/>
+    <col width="13" customWidth="1" style="20" min="10" max="10"/>
+    <col width="13" customWidth="1" style="20" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1936,35 +1938,45 @@
     <row r="3" hidden="1" s="20">
       <c r="C3" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
@@ -1983,35 +1995,45 @@
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>11.05–17.05*</t>
+          <t>27.04–03.05*</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
+          <t>04.05–10.05</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>11.05–17.05</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
           <t>18.05–24.05</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>25.05–31.05</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>08.06–14.06</t>
         </is>
       </c>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>15.06–21.06</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t>22.06–28.06*</t>
         </is>
@@ -2025,7 +2047,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr"/>
       <c r="C5" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="34" t="n">
         <v>7</v>
@@ -2043,7 +2065,13 @@
         <v>7</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2058,157 +2086,187 @@
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="D6" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="F6" s="36" t="n">
         <v>41.14</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="G6" s="36" t="n">
         <v>36.43</v>
       </c>
-      <c r="F6" s="36" t="n">
-        <v>53</v>
-      </c>
-      <c r="G6" s="36" t="n">
-        <v>67.86</v>
-      </c>
       <c r="H6" s="36" t="n">
-        <v>60.86</v>
+        <v>52.71</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>71</v>
+        <v>67.43000000000001</v>
+      </c>
+      <c r="J6" s="36" t="n">
+        <v>61.14</v>
+      </c>
+      <c r="K6" s="36" t="n">
+        <v>70.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>17.86</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>20.86</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>24.86</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>36.43</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>37.86</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>63</v>
+      </c>
+      <c r="K7" s="36" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>37.86</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>39.57</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>51.43</v>
+        <v>17.86</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>58.43</v>
+        <v>22.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>62.86</v>
+        <v>24.86</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>60</v>
+        <v>36.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
+        <v>38</v>
+      </c>
+      <c r="K8" s="36" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0.25</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>2.86</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>8.43</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>17.57</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>20.43</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>36</v>
+        <v>39.71</v>
+      </c>
+      <c r="J9" s="36" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="K9" s="36" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>18.6</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>21.57</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>26.14</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>35.57</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>39.71</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>41.43</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="J10" s="36" t="n">
         <v>33</v>
+      </c>
+      <c r="K10" s="36" t="n">
+        <v>31.5</v>
       </c>
     </row>
     <row r="11">
@@ -2223,157 +2281,187 @@
         </is>
       </c>
       <c r="C11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>17.71</v>
-      </c>
       <c r="F11" s="36" t="n">
-        <v>26.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="I11" s="36" t="n">
         <v>32.29</v>
       </c>
-      <c r="H11" s="36" t="n">
+      <c r="J11" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="I11" s="36" t="n">
-        <v>30</v>
+      <c r="K11" s="36" t="n">
+        <v>30.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>12.57</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.43</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19</v>
+        <v>3.33</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>21.14</v>
+        <v>11.71</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>29</v>
+        <v>17.57</v>
+      </c>
+      <c r="J12" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E13" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="36" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>11.14</v>
-      </c>
       <c r="F13" s="36" t="n">
-        <v>13.43</v>
+        <v>14.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.43</v>
+        <v>11.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>15.57</v>
+        <v>18</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>29</v>
+        <v>19.14</v>
+      </c>
+      <c r="J13" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" s="36" t="n">
+        <v>26.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>26.57</v>
+        <v>6.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>28.29</v>
+        <v>11.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>28.71</v>
+        <v>10.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>31.43</v>
+        <v>11.14</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>33</v>
+        <v>13.86</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="J14" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <v>24.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>13.29</v>
+        <v>1.67</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>14.57</v>
+        <v>12.14</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>16.71</v>
+        <v>16.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>19.71</v>
+        <v>21</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17.43</v>
+        <v>20.29</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>25</v>
+        <v>28.57</v>
+      </c>
+      <c r="J15" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="K15" s="36" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -2388,91 +2476,109 @@
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>13.8</v>
+        <v>2</v>
       </c>
       <c r="D16" s="36" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="F16" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="E16" s="36" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>17</v>
-      </c>
       <c r="G16" s="36" t="n">
-        <v>18.71</v>
+        <v>16.57</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>23</v>
+        <v>21.29</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>21</v>
+        <v>21.14</v>
+      </c>
+      <c r="J16" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K16" s="36" t="n">
+        <v>20.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>19.43</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>15.71</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>14.86</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>16.57</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>19.71</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="J17" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K17" s="36" t="n">
+        <v>20.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>13.57</v>
+        <v>9.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>12.57</v>
+        <v>12.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>17.57</v>
+        <v>13.29</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>18.57</v>
+        <v>14.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>20</v>
+        <v>19.71</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <v>18.5</v>
       </c>
     </row>
     <row r="19">
@@ -2487,58 +2593,70 @@
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F19" s="36" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="G19" s="36" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="F19" s="36" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="G19" s="36" t="n">
+      <c r="H19" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="I19" s="36" t="n">
         <v>17.14</v>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="J19" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="K19" s="36" t="n">
         <v>16</v>
-      </c>
-      <c r="I19" s="36" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>16.57</v>
+        <v>7</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>20.86</v>
+        <v>16</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>17.14</v>
+        <v>19.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>20.57</v>
+        <v>15.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>21.57</v>
+        <v>14.86</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>9</v>
+        <v>16.71</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2556,22 +2674,28 @@
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>12.57</v>
+        <v>8</v>
       </c>
       <c r="H21" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J21" s="36" t="n">
         <v>11.57</v>
       </c>
-      <c r="I21" s="36" t="n">
-        <v>8</v>
+      <c r="K21" s="36" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="22">
@@ -2586,25 +2710,31 @@
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="36" t="n">
         <v>5.14</v>
       </c>
-      <c r="E22" s="36" t="n">
+      <c r="G22" s="36" t="n">
         <v>5.29</v>
       </c>
-      <c r="F22" s="36" t="n">
+      <c r="H22" s="36" t="n">
         <v>7.86</v>
       </c>
-      <c r="G22" s="36" t="n">
+      <c r="I22" s="36" t="n">
         <v>7.14</v>
       </c>
-      <c r="H22" s="36" t="n">
+      <c r="J22" s="36" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="I22" s="36" t="n">
-        <v>6</v>
+      <c r="K22" s="36" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="23">
@@ -2622,22 +2752,28 @@
         <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>5.86</v>
+        <v>2.8</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4.86</v>
+        <v>4</v>
       </c>
       <c r="H23" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="36" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="J23" s="36" t="n">
         <v>3.43</v>
       </c>
-      <c r="I23" s="36" t="n">
-        <v>4</v>
+      <c r="K23" s="36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2673,6 +2809,14 @@
       </c>
       <c r="I24" s="39">
         <f>AVERAGE(I6:I23)</f>
+        <v/>
+      </c>
+      <c r="J24" s="39">
+        <f>AVERAGE(J6:J23)</f>
+        <v/>
+      </c>
+      <c r="K24" s="39">
+        <f>AVERAGE(K6:K23)</f>
         <v/>
       </c>
     </row>
@@ -2687,7 +2831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2699,6 +2843,8 @@
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
     <col width="13" customWidth="1" style="20" min="8" max="8"/>
     <col width="13" customWidth="1" style="20" min="9" max="9"/>
+    <col width="13" customWidth="1" style="20" min="10" max="10"/>
+    <col width="13" customWidth="1" style="20" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2718,35 +2864,45 @@
     <row r="3" hidden="1" s="20">
       <c r="C3" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
@@ -2765,35 +2921,45 @@
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>11.05–17.05*</t>
+          <t>27.04–03.05*</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
+          <t>04.05–10.05</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>11.05–17.05</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
           <t>18.05–24.05</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>25.05–31.05</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>08.06–14.06</t>
         </is>
       </c>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>15.06–21.06</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t>22.06–28.06*</t>
         </is>
@@ -2807,7 +2973,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr"/>
       <c r="C5" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="34" t="n">
         <v>7</v>
@@ -2825,7 +2991,13 @@
         <v>7</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2840,157 +3012,187 @@
         </is>
       </c>
       <c r="C6" s="40" t="n">
-        <v>25945431</v>
+        <v>0</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>37459210</v>
+        <v>8596643</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>48992678</v>
+        <v>30622284</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>64308195</v>
+        <v>33277426</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>79272397</v>
+        <v>40259616</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>65286326</v>
+        <v>54390985</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>9924048</v>
+        <v>72727058</v>
+      </c>
+      <c r="J6" s="40" t="n">
+        <v>61910106</v>
+      </c>
+      <c r="K6" s="40" t="n">
+        <v>21335915</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>3579870</v>
+        <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>26016508</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>28967720</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>37959389</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>50657103</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51071479</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>14176282</v>
+        <v>61835892</v>
+      </c>
+      <c r="J7" s="40" t="n">
+        <v>80551167</v>
+      </c>
+      <c r="K7" s="40" t="n">
+        <v>17345857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>26572309</v>
+        <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>54415488</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>46859038</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>52194797</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>71643667</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>85106488</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>9007657</v>
+        <v>42977335</v>
+      </c>
+      <c r="J8" s="40" t="n">
+        <v>44364359</v>
+      </c>
+      <c r="K8" s="40" t="n">
+        <v>18116377</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>363900</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>3477490</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>6698688</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>14305166</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>13436059</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>1527710</v>
+        <v>41788221</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <v>36755638</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>10215678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>14023998</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>23623555</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>37049808</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>48937774</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>45181151</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>41840209</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>6430123</v>
+        <v>31069118</v>
+      </c>
+      <c r="J10" s="40" t="n">
+        <v>40525338</v>
+      </c>
+      <c r="K10" s="40" t="n">
+        <v>9426451</v>
       </c>
     </row>
     <row r="11">
@@ -3005,157 +3207,187 @@
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9063650</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>19435779</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>20382320</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>23759937</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>43854730</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>39943773</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>7358473</v>
+        <v>37715520</v>
+      </c>
+      <c r="J11" s="40" t="n">
+        <v>35926824</v>
+      </c>
+      <c r="K11" s="40" t="n">
+        <v>11405237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>6458596</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>16321651</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>12911381</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18213851</v>
+        <v>363900</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>17644316</v>
+        <v>3736700</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>20445615</v>
+        <v>17796776</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>2461577</v>
+        <v>42724228</v>
+      </c>
+      <c r="J12" s="40" t="n">
+        <v>33036620</v>
+      </c>
+      <c r="K12" s="40" t="n">
+        <v>13874880</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>6460094</v>
+        <v>530238</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>14908071</v>
+        <v>8544625</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>20904887</v>
+        <v>8387478</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>14174417</v>
+        <v>10570508</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>21360428</v>
+        <v>11896580</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>14219534</v>
+        <v>19614352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>3552356</v>
+        <v>20966317</v>
+      </c>
+      <c r="J13" s="40" t="n">
+        <v>20073400</v>
+      </c>
+      <c r="K13" s="40" t="n">
+        <v>8338293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>11787061</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>33489630</v>
+        <v>5092853</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>34406847</v>
+        <v>11100161</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>37161831</v>
+        <v>14612055</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>31826353</v>
+        <v>20638987</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>42562578</v>
+        <v>14061352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>3032931</v>
+        <v>31599148</v>
+      </c>
+      <c r="J14" s="40" t="n">
+        <v>18747614</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <v>9509784</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>6139086</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>14744333</v>
+        <v>536260</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>18390296</v>
+        <v>14403556</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>19525644</v>
+        <v>16216832</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>30942866</v>
+        <v>32622053</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>24505921</v>
+        <v>23929705</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>6786916</v>
+        <v>37214538</v>
+      </c>
+      <c r="J15" s="40" t="n">
+        <v>25375430</v>
+      </c>
+      <c r="K15" s="40" t="n">
+        <v>8179353</v>
       </c>
     </row>
     <row r="16">
@@ -3170,91 +3402,109 @@
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>10462042</v>
+        <v>251520</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>24242808</v>
+        <v>10351067</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>20176647</v>
+        <v>21091580</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>18937286</v>
+        <v>24243567</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>21999340</v>
+        <v>16381412</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>27825060</v>
+        <v>21591272</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>4164590</v>
+        <v>21904190</v>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>25438080</v>
+      </c>
+      <c r="K16" s="40" t="n">
+        <v>9307840</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>11237754</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>29303296</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>17092421</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>18898662</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16270790</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>31755885</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>5776870</v>
+        <v>30845816</v>
+      </c>
+      <c r="J17" s="40" t="n">
+        <v>45285935</v>
+      </c>
+      <c r="K17" s="40" t="n">
+        <v>7221887</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>7434617</v>
+        <v>475871</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>11541808</v>
+        <v>11884771</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>11589026</v>
+        <v>10651216</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>20628257</v>
+        <v>13882033</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>19325665</v>
+        <v>17812948</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>21624119</v>
+        <v>17331854</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>3184411</v>
+        <v>26294756</v>
+      </c>
+      <c r="J18" s="40" t="n">
+        <v>24196222</v>
+      </c>
+      <c r="K18" s="40" t="n">
+        <v>8113550</v>
       </c>
     </row>
     <row r="19">
@@ -3269,58 +3519,70 @@
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>6011315</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>10213590</v>
+        <v>3249588</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10032796</v>
+        <v>7305524</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>23828037</v>
+        <v>9575225</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>33387187</v>
+        <v>9264589</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>23074719</v>
+        <v>20692424</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>5338500</v>
+        <v>27565767</v>
+      </c>
+      <c r="J19" s="40" t="n">
+        <v>19138015</v>
+      </c>
+      <c r="K19" s="40" t="n">
+        <v>10522793</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>13421812</v>
+        <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>19296100</v>
+        <v>6239584</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>32898025</v>
+        <v>13803407</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>20322786</v>
+        <v>28572076</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>26950241</v>
+        <v>15282581</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>25897560</v>
+        <v>16594572</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>1445133</v>
+        <v>15223898</v>
+      </c>
+      <c r="J20" s="40" t="n">
+        <v>27696695</v>
+      </c>
+      <c r="K20" s="40" t="n">
+        <v>6077148</v>
       </c>
     </row>
     <row r="21">
@@ -3338,22 +3600,28 @@
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>1357510</v>
+        <v>0</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>9736256</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>18439963</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>12820644</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19371310</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>1161730</v>
+        <v>13536614</v>
+      </c>
+      <c r="J21" s="40" t="n">
+        <v>22187720</v>
+      </c>
+      <c r="K21" s="40" t="n">
+        <v>2506280</v>
       </c>
     </row>
     <row r="22">
@@ -3368,25 +3636,31 @@
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>2876909</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>6793378</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>3855907</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>7337990</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>9843920</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>4991190</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>865560</v>
+        <v>10141286</v>
+      </c>
+      <c r="J22" s="40" t="n">
+        <v>6393871</v>
+      </c>
+      <c r="K22" s="40" t="n">
+        <v>1444426</v>
       </c>
     </row>
     <row r="23">
@@ -3404,22 +3678,28 @@
         <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>1377990</v>
+        <v>0</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>3465270</v>
+        <v>0</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>4464440</v>
+        <v>1339100</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>11771640</v>
+        <v>5579340</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>3834910</v>
+        <v>9518200</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>263320</v>
+        <v>11747640</v>
+      </c>
+      <c r="J23" s="40" t="n">
+        <v>3885270</v>
+      </c>
+      <c r="K23" s="40" t="n">
+        <v>2836600</v>
       </c>
     </row>
     <row r="24">
@@ -3455,6 +3735,14 @@
       </c>
       <c r="I24" s="41">
         <f>AVERAGE(I6:I23)</f>
+        <v/>
+      </c>
+      <c r="J24" s="41">
+        <f>AVERAGE(J6:J23)</f>
+        <v/>
+      </c>
+      <c r="K24" s="41">
+        <f>AVERAGE(K6:K23)</f>
         <v/>
       </c>
     </row>
@@ -3469,7 +3757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3481,6 +3769,8 @@
     <col width="13" customWidth="1" style="20" min="7" max="7"/>
     <col width="13" customWidth="1" style="20" min="8" max="8"/>
     <col width="13" customWidth="1" style="20" min="9" max="9"/>
+    <col width="13" customWidth="1" style="20" min="10" max="10"/>
+    <col width="13" customWidth="1" style="20" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3500,35 +3790,45 @@
     <row r="3" hidden="1" s="20">
       <c r="C3" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
@@ -3547,35 +3847,45 @@
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>11.05–17.05*</t>
+          <t>27.04–03.05*</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
+          <t>04.05–10.05</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>11.05–17.05</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
           <t>18.05–24.05</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>25.05–31.05</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="H4" s="31" t="inlineStr">
         <is>
           <t>01.06–07.06</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t>08.06–14.06</t>
         </is>
       </c>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="J4" s="31" t="inlineStr">
         <is>
           <t>15.06–21.06</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t>22.06–28.06*</t>
         </is>
@@ -3589,7 +3899,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr"/>
       <c r="C5" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="34" t="n">
         <v>7</v>
@@ -3607,7 +3917,13 @@
         <v>7</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3622,10 +3938,10 @@
         </is>
       </c>
       <c r="C6" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>7</v>
@@ -3640,26 +3956,32 @@
         <v>7</v>
       </c>
       <c r="I6" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J6" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="E7" s="42" t="n">
         <v>7</v>
       </c>
@@ -3673,28 +3995,34 @@
         <v>7</v>
       </c>
       <c r="I7" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J7" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -3706,18 +4034,24 @@
         <v>7</v>
       </c>
       <c r="I8" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
@@ -3739,22 +4073,28 @@
         <v>7</v>
       </c>
       <c r="I9" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
         <v>7</v>
@@ -3772,7 +4112,13 @@
         <v>7</v>
       </c>
       <c r="I10" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3787,14 +4133,14 @@
         </is>
       </c>
       <c r="C11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
       </c>
@@ -3805,55 +4151,67 @@
         <v>7</v>
       </c>
       <c r="I11" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="42" t="n">
         <v>7</v>
       </c>
       <c r="I12" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="42" t="n">
         <v>7</v>
@@ -3871,25 +4229,31 @@
         <v>7</v>
       </c>
       <c r="I13" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -3904,25 +4268,31 @@
         <v>7</v>
       </c>
       <c r="I14" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -3937,7 +4307,13 @@
         <v>7</v>
       </c>
       <c r="I15" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -3952,7 +4328,7 @@
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="42" t="n">
         <v>7</v>
@@ -3970,26 +4346,32 @@
         <v>7</v>
       </c>
       <c r="I16" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
       </c>
@@ -4003,22 +4385,28 @@
         <v>7</v>
       </c>
       <c r="I17" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
         <v>7</v>
@@ -4036,7 +4424,13 @@
         <v>7</v>
       </c>
       <c r="I18" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4051,10 +4445,10 @@
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4069,25 +4463,31 @@
         <v>7</v>
       </c>
       <c r="I19" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -4102,7 +4502,13 @@
         <v>7</v>
       </c>
       <c r="I20" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4120,13 +4526,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -4135,7 +4541,13 @@
         <v>7</v>
       </c>
       <c r="I21" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4150,7 +4562,7 @@
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
         <v>7</v>
@@ -4168,7 +4580,13 @@
         <v>7</v>
       </c>
       <c r="I22" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4186,13 +4604,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -4201,7 +4619,13 @@
         <v>7</v>
       </c>
       <c r="I23" s="42" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4239,6 +4663,14 @@
         <f>AVERAGE(I6:I23)</f>
         <v/>
       </c>
+      <c r="J24" s="43">
+        <f>AVERAGE(J6:J23)</f>
+        <v/>
+      </c>
+      <c r="K24" s="43">
+        <f>AVERAGE(K6:K23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2110,163 +2110,163 @@
         <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>70.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
+      <c r="K7" s="36" t="n">
         <v>63</v>
-      </c>
-      <c r="K7" s="36" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>0</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>3.33</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38</v>
+        <v>11.71</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>39.71</v>
+        <v>17.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>41.71</v>
+        <v>20.43</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>31.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -2305,163 +2305,163 @@
         <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>14.43</v>
+        <v>10.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.86</v>
+        <v>11.14</v>
       </c>
       <c r="H13" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I13" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I13" s="36" t="n">
-        <v>19.14</v>
-      </c>
       <c r="J13" s="36" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>6.67</v>
+        <v>14.29</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>19.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10.57</v>
+        <v>26.71</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.14</v>
+        <v>28.14</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>13.86</v>
+        <v>28.57</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>18</v>
+        <v>31.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>1.67</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>16.57</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>21</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>20.29</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>28.57</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>24.14</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -2500,85 +2500,85 @@
         <v>23.29</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>16</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>19.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>15.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>14.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>16.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>19.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>12.43</v>
+        <v>11</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.29</v>
+        <v>14.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>14.71</v>
+        <v>11.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19.71</v>
+        <v>19.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>17.71</v>
+        <v>21</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -2617,46 +2617,46 @@
         <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>16</v>
+        <v>12.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>15.86</v>
+        <v>21</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.86</v>
+        <v>20.29</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>16.71</v>
+        <v>28.57</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>19.71</v>
+        <v>24.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2695,7 +2695,7 @@
         <v>11.57</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2734,7 +2734,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -2773,7 +2773,7 @@
         <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3036,163 +3036,163 @@
         <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>21335915</v>
+        <v>10252510</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>17345857</v>
+        <v>12775217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>18116377</v>
+        <v>7873947</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>0</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>363900</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>3736700</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>17796776</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>42724228</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>33036620</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>10215678</v>
+        <v>6761090</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>9426451</v>
+        <v>6544823</v>
       </c>
     </row>
     <row r="11">
@@ -3231,163 +3231,163 @@
         <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>11405237</v>
+        <v>6790717</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>13874880</v>
+        <v>5811987</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>8544625</v>
+        <v>5092853</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8387478</v>
+        <v>11100161</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>10570508</v>
+        <v>14612055</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>11896580</v>
+        <v>20638987</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>19614352</v>
+        <v>14061352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>20966317</v>
+        <v>31599148</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>20073400</v>
+        <v>18747614</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>8338293</v>
+        <v>3221436</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>5092853</v>
+        <v>15808893</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11100161</v>
+        <v>14209578</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>14612055</v>
+        <v>30449860</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20638987</v>
+        <v>32603120</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>14061352</v>
+        <v>35552907</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31599148</v>
+        <v>31069118</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>18747614</v>
+        <v>40525338</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>9509784</v>
+        <v>2815731</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>536260</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>14403556</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>16216832</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>32622053</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>23929705</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>37214538</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>25375430</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>8179353</v>
+        <v>6347070</v>
       </c>
     </row>
     <row r="16">
@@ -3426,85 +3426,85 @@
         <v>25438080</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>9307840</v>
+        <v>4130030</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>6239584</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>13803407</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>28572076</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>15282581</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>16594572</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>15223898</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>27696695</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>7221887</v>
+        <v>4581428</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>475871</v>
+        <v>530238</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>11884771</v>
+        <v>8544625</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10651216</v>
+        <v>8387478</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>13882033</v>
+        <v>10570508</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>17812948</v>
+        <v>11896580</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17331854</v>
+        <v>19614352</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>26294756</v>
+        <v>20966317</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>24196222</v>
+        <v>20073400</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>8113550</v>
+        <v>3492403</v>
       </c>
     </row>
     <row r="19">
@@ -3543,46 +3543,46 @@
         <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>10522793</v>
+        <v>5086863</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>6239584</v>
+        <v>536260</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>13803407</v>
+        <v>14403556</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>28572076</v>
+        <v>16216832</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>15282581</v>
+        <v>32622053</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>16594572</v>
+        <v>23929705</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>15223898</v>
+        <v>37214538</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>27696695</v>
+        <v>25375430</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>6077148</v>
+        <v>2557033</v>
       </c>
     </row>
     <row r="21">
@@ -3621,7 +3621,7 @@
         <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>2506280</v>
+        <v>1418810</v>
       </c>
     </row>
     <row r="22">
@@ -3660,7 +3660,7 @@
         <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>1444426</v>
+        <v>903056</v>
       </c>
     </row>
     <row r="23">
@@ -3699,7 +3699,7 @@
         <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>2836600</v>
+        <v>248320</v>
       </c>
     </row>
     <row r="24">
@@ -3923,7 +3923,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3962,28 +3962,28 @@
         <v>7</v>
       </c>
       <c r="K6" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -4001,28 +4001,28 @@
         <v>7</v>
       </c>
       <c r="K7" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4040,34 +4040,34 @@
         <v>7</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F9" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G9" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="42" t="n">
         <v>7</v>
@@ -4079,25 +4079,25 @@
         <v>7</v>
       </c>
       <c r="K9" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -4118,7 +4118,7 @@
         <v>7</v>
       </c>
       <c r="K10" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4157,34 +4157,34 @@
         <v>7</v>
       </c>
       <c r="K11" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
         <v>7</v>
@@ -4196,25 +4196,25 @@
         <v>7</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4235,25 +4235,25 @@
         <v>7</v>
       </c>
       <c r="K13" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4274,25 +4274,25 @@
         <v>7</v>
       </c>
       <c r="K14" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -4313,7 +4313,7 @@
         <v>7</v>
       </c>
       <c r="K15" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4352,25 +4352,25 @@
         <v>7</v>
       </c>
       <c r="K16" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4391,18 +4391,18 @@
         <v>7</v>
       </c>
       <c r="K17" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -4430,7 +4430,7 @@
         <v>7</v>
       </c>
       <c r="K18" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4469,25 +4469,25 @@
         <v>7</v>
       </c>
       <c r="K19" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -4508,7 +4508,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4547,7 +4547,7 @@
         <v>7</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4586,7 +4586,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4625,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2110,163 +2110,163 @@
         <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>72</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K8" s="36" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>0</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>0.5</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>3.33</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>11.71</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>17.57</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>20.43</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="11">
@@ -2305,163 +2305,163 @@
         <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.43</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>12.71</v>
+        <v>3.33</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>14.43</v>
+        <v>11.71</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>19</v>
+        <v>17.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>21.14</v>
+        <v>20.43</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>29</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>14.29</v>
+        <v>6.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>19.14</v>
+        <v>11.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>26.71</v>
+        <v>10.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>28.14</v>
+        <v>11.14</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>28.57</v>
+        <v>13.86</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>31.57</v>
+        <v>18</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>1.67</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>12.14</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>16.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>21</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>20.29</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.71</v>
+        <v>28.57</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>17.71</v>
+        <v>24.14</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -2500,85 +2500,85 @@
         <v>23.29</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>16</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>19.43</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>15.86</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.86</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>16.71</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="19">
@@ -2617,46 +2617,46 @@
         <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>12.14</v>
+        <v>16</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>16.57</v>
+        <v>19.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>21</v>
+        <v>15.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>20.29</v>
+        <v>14.86</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>28.57</v>
+        <v>16.71</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>24.14</v>
+        <v>19.71</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2695,7 +2695,7 @@
         <v>11.57</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="22">
@@ -2734,7 +2734,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="23">
@@ -2773,7 +2773,7 @@
         <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3036,163 +3036,163 @@
         <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>10252510</v>
+        <v>21335915</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>12775217</v>
+        <v>17345857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>7873947</v>
+        <v>18116377</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>0</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>363900</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>3736700</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>17796776</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>42724228</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>33036620</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>6761090</v>
+        <v>10215678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>6544823</v>
+        <v>9426451</v>
       </c>
     </row>
     <row r="11">
@@ -3231,163 +3231,163 @@
         <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>6790717</v>
+        <v>11405237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>21387685</v>
+        <v>363900</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>16050448</v>
+        <v>3736700</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>21568794</v>
+        <v>17796776</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>30845816</v>
+        <v>42724228</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>45285935</v>
+        <v>33036620</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>5811987</v>
+        <v>13874880</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>3221436</v>
+        <v>8338293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>15808893</v>
+        <v>5092853</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14209578</v>
+        <v>11100161</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>30449860</v>
+        <v>14612055</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32603120</v>
+        <v>20638987</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>35552907</v>
+        <v>14061352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31069118</v>
+        <v>31599148</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>40525338</v>
+        <v>18747614</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>2815731</v>
+        <v>9509784</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>536260</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>14403556</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>16216832</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>32622053</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>23929705</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>37214538</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>25375430</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>6347070</v>
+        <v>8179353</v>
       </c>
     </row>
     <row r="16">
@@ -3426,85 +3426,85 @@
         <v>25438080</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>4130030</v>
+        <v>9307840</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>6239584</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>13803407</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>28572076</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>15282581</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>16594572</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>15223898</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>27696695</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>4581428</v>
+        <v>7221887</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>3492403</v>
+        <v>8113550</v>
       </c>
     </row>
     <row r="19">
@@ -3543,46 +3543,46 @@
         <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>5086863</v>
+        <v>10522793</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>536260</v>
+        <v>6239584</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>14403556</v>
+        <v>13803407</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>16216832</v>
+        <v>28572076</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>32622053</v>
+        <v>15282581</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>23929705</v>
+        <v>16594572</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>37214538</v>
+        <v>15223898</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>25375430</v>
+        <v>27696695</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>2557033</v>
+        <v>6077148</v>
       </c>
     </row>
     <row r="21">
@@ -3621,7 +3621,7 @@
         <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>1418810</v>
+        <v>2506280</v>
       </c>
     </row>
     <row r="22">
@@ -3660,7 +3660,7 @@
         <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>903056</v>
+        <v>1444426</v>
       </c>
     </row>
     <row r="23">
@@ -3699,7 +3699,7 @@
         <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>248320</v>
+        <v>2836600</v>
       </c>
     </row>
     <row r="24">
@@ -3923,7 +3923,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3962,28 +3962,28 @@
         <v>7</v>
       </c>
       <c r="K6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -4001,28 +4001,28 @@
         <v>7</v>
       </c>
       <c r="K7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4040,64 +4040,64 @@
         <v>7</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -4118,7 +4118,7 @@
         <v>7</v>
       </c>
       <c r="K10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4157,34 +4157,34 @@
         <v>7</v>
       </c>
       <c r="K11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="42" t="n">
         <v>7</v>
@@ -4196,25 +4196,25 @@
         <v>7</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4235,25 +4235,25 @@
         <v>7</v>
       </c>
       <c r="K13" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4274,46 +4274,46 @@
         <v>7</v>
       </c>
       <c r="K14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4352,25 +4352,25 @@
         <v>7</v>
       </c>
       <c r="K16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4391,18 +4391,18 @@
         <v>7</v>
       </c>
       <c r="K17" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -4430,7 +4430,7 @@
         <v>7</v>
       </c>
       <c r="K18" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4469,25 +4469,25 @@
         <v>7</v>
       </c>
       <c r="K19" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -4508,7 +4508,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4547,7 +4547,7 @@
         <v>7</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4586,7 +4586,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4625,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2110,7 +2110,7 @@
         <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>70.5</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="7">
@@ -2149,7 +2149,7 @@
         <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="8">
@@ -2188,85 +2188,85 @@
         <v>38</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>45</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>32</v>
+        <v>34.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>31.5</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="11">
@@ -2305,163 +2305,163 @@
         <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>20.43</v>
+        <v>21</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>28</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>14.43</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.86</v>
+        <v>3.33</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>18</v>
+        <v>11.71</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>19.14</v>
+        <v>17.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>6.67</v>
+        <v>1.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>12.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10.57</v>
+        <v>16.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.14</v>
+        <v>21</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>13.86</v>
+        <v>20.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>18</v>
+        <v>28.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>18</v>
+        <v>24.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.14</v>
+        <v>11.29</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>16.57</v>
+        <v>10.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>21</v>
+        <v>11.14</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>20.29</v>
+        <v>13.86</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>28.57</v>
+        <v>18</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>24.14</v>
+        <v>18</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -2500,85 +2500,85 @@
         <v>23.29</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>9.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>12.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>13.29</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>14.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>17</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>19.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>17.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>20.5</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.43</v>
+        <v>3</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>12.43</v>
+        <v>7.14</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.29</v>
+        <v>13.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>14.71</v>
+        <v>12.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17</v>
+        <v>14.43</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19.71</v>
+        <v>19</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>17.71</v>
+        <v>21.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.5</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="19">
@@ -2617,7 +2617,7 @@
         <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>16</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="20">
@@ -2656,7 +2656,7 @@
         <v>19.71</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>15</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="21">
@@ -2695,7 +2695,7 @@
         <v>11.57</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2734,7 +2734,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="23">
@@ -2773,7 +2773,7 @@
         <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="24">
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3036,7 +3036,7 @@
         <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>21335915</v>
+        <v>28240015</v>
       </c>
     </row>
     <row r="7">
@@ -3075,7 +3075,7 @@
         <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>17345857</v>
+        <v>25253667</v>
       </c>
     </row>
     <row r="8">
@@ -3114,85 +3114,85 @@
         <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>18116377</v>
+        <v>26811687</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>10215678</v>
+        <v>16586091</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>9426451</v>
+        <v>15627338</v>
       </c>
     </row>
     <row r="11">
@@ -3231,163 +3231,163 @@
         <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>11405237</v>
+        <v>21025509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>13874880</v>
+        <v>14561963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>10570508</v>
+        <v>363900</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>11896580</v>
+        <v>3736700</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>19614352</v>
+        <v>17796776</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>20966317</v>
+        <v>42724228</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>20073400</v>
+        <v>33036620</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>8338293</v>
+        <v>16247420</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>5092853</v>
+        <v>536260</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11100161</v>
+        <v>14403556</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>14612055</v>
+        <v>16216832</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20638987</v>
+        <v>32622053</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>14061352</v>
+        <v>23929705</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31599148</v>
+        <v>37214538</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>18747614</v>
+        <v>25375430</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>9509784</v>
+        <v>11555843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>536260</v>
+        <v>5092853</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>14403556</v>
+        <v>11100161</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>16216832</v>
+        <v>14612055</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>32622053</v>
+        <v>20638987</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>23929705</v>
+        <v>14061352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>37214538</v>
+        <v>31599148</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>25375430</v>
+        <v>18747614</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>8179353</v>
+        <v>12187453</v>
       </c>
     </row>
     <row r="16">
@@ -3426,85 +3426,85 @@
         <v>25438080</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>9307840</v>
+        <v>14033790</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>11884771</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>10651216</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>13882033</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>17812948</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>17331854</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>26294756</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>24196222</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>7221887</v>
+        <v>10425114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>11884771</v>
+        <v>3337146</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10651216</v>
+        <v>10420206</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>13882033</v>
+        <v>21387685</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>17812948</v>
+        <v>16050448</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17331854</v>
+        <v>21568794</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>26294756</v>
+        <v>30845816</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>24196222</v>
+        <v>45285935</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>8113550</v>
+        <v>8855797</v>
       </c>
     </row>
     <row r="19">
@@ -3543,7 +3543,7 @@
         <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>10522793</v>
+        <v>12762899</v>
       </c>
     </row>
     <row r="20">
@@ -3582,7 +3582,7 @@
         <v>27696695</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>6077148</v>
+        <v>9055658</v>
       </c>
     </row>
     <row r="21">
@@ -3621,7 +3621,7 @@
         <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>2506280</v>
+        <v>7448670</v>
       </c>
     </row>
     <row r="22">
@@ -3660,7 +3660,7 @@
         <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>1444426</v>
+        <v>1567896</v>
       </c>
     </row>
     <row r="23">
@@ -3699,7 +3699,7 @@
         <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>2836600</v>
+        <v>3407650</v>
       </c>
     </row>
     <row r="24">
@@ -3923,7 +3923,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3962,7 +3962,7 @@
         <v>7</v>
       </c>
       <c r="K6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4001,7 +4001,7 @@
         <v>7</v>
       </c>
       <c r="K7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4040,25 +4040,25 @@
         <v>7</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4079,46 +4079,46 @@
         <v>7</v>
       </c>
       <c r="K9" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4157,34 +4157,34 @@
         <v>7</v>
       </c>
       <c r="K11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="42" t="n">
         <v>7</v>
@@ -4196,34 +4196,34 @@
         <v>7</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G13" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="42" t="n">
         <v>7</v>
@@ -4235,25 +4235,25 @@
         <v>7</v>
       </c>
       <c r="K13" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4274,46 +4274,46 @@
         <v>7</v>
       </c>
       <c r="K14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4352,25 +4352,25 @@
         <v>7</v>
       </c>
       <c r="K16" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4391,25 +4391,25 @@
         <v>7</v>
       </c>
       <c r="K17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -4430,7 +4430,7 @@
         <v>7</v>
       </c>
       <c r="K18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -4469,7 +4469,7 @@
         <v>7</v>
       </c>
       <c r="K19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -4508,7 +4508,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -4547,7 +4547,7 @@
         <v>7</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4586,7 +4586,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4625,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2110,7 +2110,7 @@
         <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -2149,7 +2149,7 @@
         <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>56.67</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="8">
@@ -2188,238 +2188,238 @@
         <v>38</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>45.67</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.67</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>8</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>13.14</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>19.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>26.43</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>32.29</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>31.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>32.33</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>19.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>26.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>28.14</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>28.57</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>31.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>31</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>11</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>14.43</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>11.86</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>18</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>19.14</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>21</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>28.33</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>20.43</v>
+        <v>21</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.14</v>
+        <v>0</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.57</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>21</v>
+        <v>3.33</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>20.29</v>
+        <v>11.71</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>28.57</v>
+        <v>17.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>24.14</v>
+        <v>20.43</v>
       </c>
       <c r="K14" s="36" t="n">
         <v>26</v>
@@ -2428,118 +2428,118 @@
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>6.67</v>
+        <v>8.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11.29</v>
+        <v>13.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>10.57</v>
+        <v>21.71</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.14</v>
+        <v>16.57</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>13.86</v>
+        <v>21.29</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>18</v>
+        <v>21.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>18</v>
+        <v>23.29</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>8.43</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>13.43</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>21.71</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>16.57</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>21.29</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>21.14</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>23.29</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9.43</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.29</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>14.71</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>17</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>19.33</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="18">
@@ -2578,85 +2578,85 @@
         <v>21.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>19.33</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3.33</v>
+        <v>7</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>6.43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14</v>
+        <v>14.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.14</v>
+        <v>16.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>16.14</v>
+        <v>19.71</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.33</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>15.33</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="21">
@@ -2695,7 +2695,7 @@
         <v>11.57</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="22">
@@ -2734,7 +2734,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="23">
@@ -2773,7 +2773,7 @@
         <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>3.67</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="24">
@@ -2997,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3036,7 +3036,7 @@
         <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>28240015</v>
+        <v>34539745</v>
       </c>
     </row>
     <row r="7">
@@ -3075,7 +3075,7 @@
         <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>25253667</v>
+        <v>36847463</v>
       </c>
     </row>
     <row r="8">
@@ -3114,358 +3114,358 @@
         <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>26811687</v>
+        <v>30017443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>16586091</v>
+        <v>21852620</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>8972650</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>18100396</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>23988817</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>22409732</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>37715520</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>35926824</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>15627338</v>
+        <v>28217739</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>14209578</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>30449860</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>32603120</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>35552907</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>31069118</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>40525338</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>21025509</v>
+        <v>25491531</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>8544625</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8387478</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>10570508</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>11896580</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>19614352</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>20966317</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>20073400</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>14561963</v>
+        <v>15880723</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>16247420</v>
+        <v>16615323</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14403556</v>
+        <v>0</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>16216832</v>
+        <v>363900</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32622053</v>
+        <v>3736700</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>23929705</v>
+        <v>17796776</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37214538</v>
+        <v>42724228</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25375430</v>
+        <v>33036620</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>11555843</v>
+        <v>20005270</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>5092853</v>
+        <v>10351067</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>11100161</v>
+        <v>21091580</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>14612055</v>
+        <v>24243567</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>20638987</v>
+        <v>16381412</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>14061352</v>
+        <v>21591272</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>31599148</v>
+        <v>21904190</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>18747614</v>
+        <v>25438080</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>12187453</v>
+        <v>16136530</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>251520</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>10351067</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>21091580</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>24243567</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>16381412</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>21591272</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>21904190</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>25438080</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>14033790</v>
+        <v>12911964</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>11884771</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10651216</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>13882033</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>17812948</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17331854</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>26294756</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>24196222</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>10425114</v>
+        <v>13807713</v>
       </c>
     </row>
     <row r="18">
@@ -3504,85 +3504,85 @@
         <v>45285935</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>8855797</v>
+        <v>11911525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3249588</v>
+        <v>6239584</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>7305524</v>
+        <v>13803407</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>9575225</v>
+        <v>28572076</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>9264589</v>
+        <v>15282581</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>20692424</v>
+        <v>16594572</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>27565767</v>
+        <v>15223898</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>19138015</v>
+        <v>27696695</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>12762899</v>
+        <v>11471288</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>9055658</v>
+        <v>15767049</v>
       </c>
     </row>
     <row r="21">
@@ -3621,7 +3621,7 @@
         <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>7448670</v>
+        <v>8119110</v>
       </c>
     </row>
     <row r="22">
@@ -3660,7 +3660,7 @@
         <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>1567896</v>
+        <v>2083676</v>
       </c>
     </row>
     <row r="23">
@@ -3699,7 +3699,7 @@
         <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>3407650</v>
+        <v>4619390</v>
       </c>
     </row>
     <row r="24">
@@ -3923,7 +3923,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3962,7 +3962,7 @@
         <v>7</v>
       </c>
       <c r="K6" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4001,7 +4001,7 @@
         <v>7</v>
       </c>
       <c r="K7" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4040,25 +4040,25 @@
         <v>7</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4079,67 +4079,67 @@
         <v>7</v>
       </c>
       <c r="K9" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="42" t="n">
         <v>4</v>
-      </c>
-      <c r="E10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4157,25 +4157,25 @@
         <v>7</v>
       </c>
       <c r="K11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4196,34 +4196,34 @@
         <v>7</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F13" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="42" t="n">
         <v>7</v>
@@ -4235,34 +4235,34 @@
         <v>7</v>
       </c>
       <c r="K13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F14" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="42" t="n">
         <v>7</v>
@@ -4274,25 +4274,25 @@
         <v>7</v>
       </c>
       <c r="K14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -4313,22 +4313,22 @@
         <v>7</v>
       </c>
       <c r="K15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
         <v>7</v>
@@ -4352,25 +4352,25 @@
         <v>7</v>
       </c>
       <c r="K16" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4391,7 +4391,7 @@
         <v>7</v>
       </c>
       <c r="K17" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -4430,25 +4430,25 @@
         <v>7</v>
       </c>
       <c r="K18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4469,46 +4469,46 @@
         <v>7</v>
       </c>
       <c r="K19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="42" t="n">
         <v>4</v>
-      </c>
-      <c r="E20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -4547,7 +4547,7 @@
         <v>7</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -4586,7 +4586,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -4625,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1919,6 +1919,7 @@
     <col width="13" customWidth="1" style="20" min="9" max="9"/>
     <col width="13" customWidth="1" style="20" min="10" max="10"/>
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
+    <col width="13" customWidth="1" style="20" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1981,6 +1982,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2035,7 +2041,12 @@
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
-          <t>22.06–28.06*</t>
+          <t>22.06–28.06</t>
+        </is>
+      </c>
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>29.06–05.07*</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2082,10 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2110,7 +2124,10 @@
         <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>64</v>
+        <v>66.14</v>
+      </c>
+      <c r="L6" s="36" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -2149,280 +2166,304 @@
         <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>55.75</v>
+        <v>55.43</v>
+      </c>
+      <c r="L7" s="36" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>41.25</v>
+        <v>34.86</v>
+      </c>
+      <c r="L8" s="36" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>7.33</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>17.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>22.14</v>
       </c>
       <c r="H9" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J9" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="I9" s="36" t="n">
-        <v>39.71</v>
-      </c>
-      <c r="J9" s="36" t="n">
-        <v>41.71</v>
-      </c>
       <c r="K9" s="36" t="n">
-        <v>34.75</v>
+        <v>43.86</v>
+      </c>
+      <c r="L9" s="36" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>31.29</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>33.75</v>
+        <v>35.14</v>
+      </c>
+      <c r="L10" s="36" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.25</v>
+        <v>33.57</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>9.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.29</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>14.71</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>17</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>19.71</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>17.71</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>26.5</v>
+        <v>19.57</v>
+      </c>
+      <c r="L12" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>14.43</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.86</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>18</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>19.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>21</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>26.5</v>
+        <v>27.57</v>
+      </c>
+      <c r="L13" s="36" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>26</v>
+        <v>16.86</v>
+      </c>
+      <c r="L14" s="36" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -2461,280 +2502,304 @@
         <v>23.29</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>21.75</v>
+        <v>22.43</v>
+      </c>
+      <c r="L15" s="36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>3.33</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>11.71</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>17.57</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>20.43</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>20</v>
+        <v>21.71</v>
+      </c>
+      <c r="L16" s="36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>19.75</v>
+        <v>23.43</v>
+      </c>
+      <c r="L17" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L18" s="36" t="n">
         <v>19</v>
-      </c>
-      <c r="J18" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>18.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>16</v>
+        <v>7.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>19.43</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>15.86</v>
+        <v>12.71</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.86</v>
+        <v>14.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>16.71</v>
+        <v>19</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>16.75</v>
+        <v>18.57</v>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14</v>
+        <v>9.43</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.14</v>
+        <v>12.71</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>16.14</v>
+        <v>11.57</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>16.25</v>
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L20" s="36" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>5.14</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>5.29</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>7.86</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>7.14</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.75</v>
+        <v>7.14</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>6.67</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>4</v>
+        <v>11.29</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>5.14</v>
+        <v>10.57</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>5.29</v>
+        <v>11.14</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>13.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>18</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>18</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>4.75</v>
+        <v>17.43</v>
+      </c>
+      <c r="L22" s="36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2773,7 +2838,10 @@
         <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>4.75</v>
+        <v>5.86</v>
+      </c>
+      <c r="L23" s="36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2817,6 +2885,10 @@
       </c>
       <c r="K24" s="39">
         <f>AVERAGE(K6:K23)</f>
+        <v/>
+      </c>
+      <c r="L24" s="39">
+        <f>AVERAGE(L6:L23)</f>
         <v/>
       </c>
     </row>
@@ -2831,7 +2903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2845,6 +2917,7 @@
     <col width="13" customWidth="1" style="20" min="9" max="9"/>
     <col width="13" customWidth="1" style="20" min="10" max="10"/>
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
+    <col width="13" customWidth="1" style="20" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2907,6 +2980,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2961,7 +3039,12 @@
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
-          <t>22.06–28.06*</t>
+          <t>22.06–28.06</t>
+        </is>
+      </c>
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>29.06–05.07*</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3080,10 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3036,7 +3122,10 @@
         <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>34539745</v>
+        <v>72409127</v>
+      </c>
+      <c r="L6" s="40" t="n">
+        <v>11208198</v>
       </c>
     </row>
     <row r="7">
@@ -3075,280 +3164,304 @@
         <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>36847463</v>
+        <v>61490143</v>
+      </c>
+      <c r="L7" s="40" t="n">
+        <v>6289820</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>30017443</v>
+        <v>42402722</v>
+      </c>
+      <c r="L8" s="40" t="n">
+        <v>6008100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>2886450</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>22932586</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>24764259</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>32268886</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>42977335</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>44364359</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>21852620</v>
+        <v>53225819</v>
+      </c>
+      <c r="L9" s="40" t="n">
+        <v>8680215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>28217739</v>
+        <v>43259404</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>8403591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>25491531</v>
+        <v>39462393</v>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>4461158</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>11884771</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>10651216</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>13882033</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>17812948</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>17331854</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>26294756</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>24196222</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>15880723</v>
+        <v>22122847</v>
+      </c>
+      <c r="L12" s="40" t="n">
+        <v>2744908</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>8544625</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8387478</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>10570508</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>11896580</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>19614352</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>20966317</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>20073400</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>16615323</v>
+        <v>31500087</v>
+      </c>
+      <c r="L13" s="40" t="n">
+        <v>3402441</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>20005270</v>
+        <v>17717888</v>
+      </c>
+      <c r="L14" s="40" t="n">
+        <v>2864170</v>
       </c>
     </row>
     <row r="15">
@@ -3387,280 +3500,304 @@
         <v>25438080</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>16136530</v>
+        <v>24614280</v>
+      </c>
+      <c r="L15" s="40" t="n">
+        <v>4826630</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>0</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>0</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>363900</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>3736700</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>17796776</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>42724228</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>33036620</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>12911964</v>
+        <v>29649130</v>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>2760060</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>13807713</v>
+        <v>23801493</v>
+      </c>
+      <c r="L17" s="40" t="n">
+        <v>2242110</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>11911525</v>
+        <v>24912292</v>
+      </c>
+      <c r="L18" s="40" t="n">
+        <v>1979210</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>6239584</v>
+        <v>3337146</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>13803407</v>
+        <v>10420206</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>28572076</v>
+        <v>21387685</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>15282581</v>
+        <v>16050448</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>16594572</v>
+        <v>21568794</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>15223898</v>
+        <v>30845816</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>27696695</v>
+        <v>45285935</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>11471288</v>
+        <v>28941455</v>
+      </c>
+      <c r="L19" s="40" t="n">
+        <v>3140950</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>9575225</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>9264589</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>20692424</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>27565767</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>19138015</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>15767049</v>
+        <v>11732010</v>
+      </c>
+      <c r="L20" s="40" t="n">
+        <v>1285590</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>6991878</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>4060163</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>7685466</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>10141286</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>6393871</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>8119110</v>
+        <v>4534503</v>
+      </c>
+      <c r="L21" s="40" t="n">
+        <v>2941730</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>5092853</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>11100161</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>14612055</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>20638987</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>14061352</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>31599148</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>18747614</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>2083676</v>
+        <v>19576415</v>
+      </c>
+      <c r="L22" s="40" t="n">
+        <v>894961</v>
       </c>
     </row>
     <row r="23">
@@ -3699,7 +3836,10 @@
         <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>4619390</v>
+        <v>8765870</v>
+      </c>
+      <c r="L23" s="40" t="n">
+        <v>786100</v>
       </c>
     </row>
     <row r="24">
@@ -3743,6 +3883,10 @@
       </c>
       <c r="K24" s="41">
         <f>AVERAGE(K6:K23)</f>
+        <v/>
+      </c>
+      <c r="L24" s="41">
+        <f>AVERAGE(L6:L23)</f>
         <v/>
       </c>
     </row>
@@ -3757,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3771,6 +3915,7 @@
     <col width="13" customWidth="1" style="20" min="9" max="9"/>
     <col width="13" customWidth="1" style="20" min="10" max="10"/>
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
+    <col width="13" customWidth="1" style="20" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3833,6 +3978,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3887,7 +4037,12 @@
       </c>
       <c r="K4" s="31" t="inlineStr">
         <is>
-          <t>22.06–28.06*</t>
+          <t>22.06–28.06</t>
+        </is>
+      </c>
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>29.06–05.07*</t>
         </is>
       </c>
     </row>
@@ -3923,7 +4078,10 @@
         <v>7</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3962,7 +4120,10 @@
         <v>7</v>
       </c>
       <c r="K6" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L6" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4001,28 +4162,31 @@
         <v>7</v>
       </c>
       <c r="K7" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L7" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4040,28 +4204,31 @@
         <v>7</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>7</v>
@@ -4079,28 +4246,31 @@
         <v>7</v>
       </c>
       <c r="K9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4118,28 +4288,31 @@
         <v>7</v>
       </c>
       <c r="K10" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4157,25 +4330,28 @@
         <v>7</v>
       </c>
       <c r="K11" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4196,25 +4372,28 @@
         <v>7</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4235,34 +4414,37 @@
         <v>7</v>
       </c>
       <c r="K13" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="42" t="n">
         <v>7</v>
@@ -4274,7 +4456,10 @@
         <v>7</v>
       </c>
       <c r="K14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4313,34 +4498,37 @@
         <v>7</v>
       </c>
       <c r="K15" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G16" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="42" t="n">
         <v>7</v>
@@ -4352,25 +4540,28 @@
         <v>7</v>
       </c>
       <c r="K16" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4391,25 +4582,28 @@
         <v>7</v>
       </c>
       <c r="K17" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -4430,25 +4624,28 @@
         <v>7</v>
       </c>
       <c r="K18" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4469,31 +4666,34 @@
         <v>7</v>
       </c>
       <c r="K19" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -4508,31 +4708,34 @@
         <v>7</v>
       </c>
       <c r="K20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -4547,25 +4750,28 @@
         <v>7</v>
       </c>
       <c r="K21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>7</v>
@@ -4586,7 +4792,10 @@
         <v>7</v>
       </c>
       <c r="K22" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L22" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4625,7 +4834,10 @@
         <v>7</v>
       </c>
       <c r="K23" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="L23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4671,6 +4883,10 @@
         <f>AVERAGE(K6:K23)</f>
         <v/>
       </c>
+      <c r="L24" s="43">
+        <f>AVERAGE(L6:L23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2085,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2127,301 +2127,301 @@
         <v>66.14</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>70</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>58</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>14.29</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>19.14</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>26.71</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>28.57</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>31.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>34.86</v>
+        <v>55.43</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>51</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>8</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>13.14</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>19.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>26.43</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>32.29</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>31.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>33.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>38</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>18.71</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>21.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>30.29</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>38</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>39.71</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>41.71</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>35.14</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>9.43</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.43</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.29</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>14.71</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>17</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>19.71</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>17.71</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>19.57</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G13" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G13" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>29</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="14">
@@ -2463,343 +2463,343 @@
         <v>16.86</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>29</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>8.43</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>13.43</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>21.71</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>16.57</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>21.29</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>21.14</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>23.29</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>22.43</v>
+        <v>19.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>25</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>20.43</v>
+        <v>21</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>21.71</v>
+        <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>25</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="G17" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H17" s="36" t="n">
         <v>14.43</v>
       </c>
-      <c r="G17" s="36" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="H17" s="36" t="n">
-        <v>18</v>
-      </c>
       <c r="I17" s="36" t="n">
-        <v>19.14</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>23.43</v>
+        <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>21</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E18" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>19</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>18</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>11.29</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>3.25</v>
+        <v>10.57</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>8</v>
+        <v>11.14</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>9.43</v>
+        <v>13.86</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>12.71</v>
+        <v>18</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>11.57</v>
+        <v>18</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>17.43</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>11</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>5.14</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>5.29</v>
+        <v>8</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>7.86</v>
+        <v>9.43</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>7.14</v>
+        <v>12.71</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>11.57</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>7.14</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>6.67</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>11.29</v>
+        <v>4</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>10.57</v>
+        <v>5.14</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>11.14</v>
+        <v>5.29</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>13.86</v>
+        <v>7.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>18</v>
+        <v>7.14</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>18</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>17.43</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="23">
@@ -2841,7 +2841,7 @@
         <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="24">
@@ -3083,7 +3083,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3125,301 +3125,301 @@
         <v>72409127</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>11208198</v>
+        <v>32601628</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>6289820</v>
+        <v>23231604</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>15808893</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>14209578</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>30449860</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32603120</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>35552907</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>31069118</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>40525338</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>42402722</v>
+        <v>61490143</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>6008100</v>
+        <v>20836611</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>8680215</v>
+        <v>22099520</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>8972650</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>18100396</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>23988817</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>22409732</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>37715520</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>35926824</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>39462393</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>8403591</v>
+        <v>19532985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>3771593</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>17664217</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>21748722</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>38313932</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>49313727</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>41788221</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>36755638</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>43259404</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>4461158</v>
+        <v>21106816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>11884771</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>10651216</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>13882033</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>17812948</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>17331854</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>26294756</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>24196222</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>22122847</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>2744908</v>
+        <v>12249931</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>3402441</v>
+        <v>11824520</v>
       </c>
     </row>
     <row r="14">
@@ -3461,343 +3461,343 @@
         <v>17717888</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>2864170</v>
+        <v>10939580</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>251520</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>10351067</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>21091580</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>24243567</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>16381412</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>21591272</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>21904190</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>25438080</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24614280</v>
+        <v>22122847</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>4826630</v>
+        <v>10143909</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>29649130</v>
+        <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>2760060</v>
+        <v>6512999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>8544625</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>8387478</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>10570508</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>11896580</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>19614352</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>20966317</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>20073400</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>23801493</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>2242110</v>
+        <v>9782060</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>1979210</v>
+        <v>7081920</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>3140950</v>
+        <v>5588810</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>11100161</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1324510</v>
+        <v>14612055</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>10311989</v>
+        <v>20638987</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19934535</v>
+        <v>14061352</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>13536614</v>
+        <v>31599148</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>22187720</v>
+        <v>18747614</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>11732010</v>
+        <v>19576415</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>1285590</v>
+        <v>5202362</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>6991878</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>4060163</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>7685466</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>10141286</v>
+        <v>13536614</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>6393871</v>
+        <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>4534503</v>
+        <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>2941730</v>
+        <v>5152040</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>5092853</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>11100161</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>14612055</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>20638987</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>14061352</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>31599148</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>18747614</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>19576415</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>894961</v>
+        <v>4323010</v>
       </c>
     </row>
     <row r="23">
@@ -3839,7 +3839,7 @@
         <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>786100</v>
+        <v>1733170</v>
       </c>
     </row>
     <row r="24">
@@ -4081,7 +4081,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4123,28 +4123,28 @@
         <v>7</v>
       </c>
       <c r="L6" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -4165,112 +4165,112 @@
         <v>7</v>
       </c>
       <c r="L7" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4291,28 +4291,28 @@
         <v>7</v>
       </c>
       <c r="L10" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4333,25 +4333,25 @@
         <v>7</v>
       </c>
       <c r="L11" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4375,49 +4375,49 @@
         <v>7</v>
       </c>
       <c r="L12" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4459,22 +4459,22 @@
         <v>7</v>
       </c>
       <c r="L14" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>7</v>
@@ -4501,34 +4501,34 @@
         <v>7</v>
       </c>
       <c r="L15" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
         <v>7</v>
@@ -4543,25 +4543,25 @@
         <v>7</v>
       </c>
       <c r="L16" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4585,67 +4585,67 @@
         <v>7</v>
       </c>
       <c r="L17" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4669,31 +4669,31 @@
         <v>7</v>
       </c>
       <c r="L19" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -4711,67 +4711,67 @@
         <v>7</v>
       </c>
       <c r="L20" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>7</v>
@@ -4795,7 +4795,7 @@
         <v>7</v>
       </c>
       <c r="L22" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4837,7 +4837,7 @@
         <v>7</v>
       </c>
       <c r="L23" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2085,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2127,217 +2127,217 @@
         <v>66.14</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>72.33</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>53.33</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K8" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>52.67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>40</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>33.57</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>34.33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>18.71</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>30.29</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>38</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>39.71</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>41.71</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>35.14</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>34</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="12">
@@ -2379,133 +2379,133 @@
         <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>29</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>7</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>16</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>19.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>15.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>14.86</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>16.71</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>19.71</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>16.86</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>26.67</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>7</v>
+        <v>9.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>16</v>
+        <v>12.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>19.43</v>
+        <v>13.29</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>15.86</v>
+        <v>14.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>14.86</v>
+        <v>17</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>16.71</v>
+        <v>19.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>19.71</v>
+        <v>17.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>16.86</v>
+        <v>19.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>26.33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>8.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>13.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>21.71</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>16.57</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>21.29</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>17.71</v>
+        <v>23.29</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>22.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>20.67</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="16">
@@ -2547,175 +2547,175 @@
         <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>17.67</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>17.33</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>6.43</v>
+        <v>11.29</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.14</v>
+        <v>18</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>16.14</v>
+        <v>18</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>17.43</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15.33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>13.33</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="21">
@@ -2757,7 +2757,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>9.33</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="22">
@@ -2799,7 +2799,7 @@
         <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>9.33</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="23">
@@ -2841,7 +2841,7 @@
         <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>4.33</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="24">
@@ -3083,7 +3083,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3125,217 +3125,217 @@
         <v>72409127</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>32601628</v>
+        <v>62062925</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>23231604</v>
+        <v>55620338</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>20836611</v>
+        <v>45027717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>22099520</v>
+        <v>62931875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>39462393</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>19532985</v>
+        <v>37037706</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>17664217</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>21748722</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>38313932</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>49313727</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>41788221</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>36755638</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>43259404</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>21106816</v>
+        <v>38346642</v>
       </c>
     </row>
     <row r="12">
@@ -3377,133 +3377,133 @@
         <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>12249931</v>
+        <v>25655097</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>6239584</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>13803407</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>28572076</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>15282581</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>16594572</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>15223898</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>27696695</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>17717888</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>11824520</v>
+        <v>21992980</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>6239584</v>
+        <v>11884771</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>13803407</v>
+        <v>10651216</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>28572076</v>
+        <v>13882033</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>15282581</v>
+        <v>17812948</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>16594572</v>
+        <v>17331854</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>15223898</v>
+        <v>26294756</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>27696695</v>
+        <v>24196222</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>17717888</v>
+        <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>10939580</v>
+        <v>25634845</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>251520</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>10351067</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>21091580</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>24243567</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>16381412</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>21591272</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>21904190</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>25438080</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>24614280</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>10143909</v>
+        <v>26410442</v>
       </c>
     </row>
     <row r="16">
@@ -3545,175 +3545,175 @@
         <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>6512999</v>
+        <v>25135951</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>9782060</v>
+        <v>17129374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>7081920</v>
+        <v>19039500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3249588</v>
+        <v>5092853</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>7305524</v>
+        <v>11100161</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>9575225</v>
+        <v>14612055</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>9264589</v>
+        <v>20638987</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>20692424</v>
+        <v>14061352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>27565767</v>
+        <v>31599148</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>19138015</v>
+        <v>18747614</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>24912292</v>
+        <v>19576415</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>5588810</v>
+        <v>12277818</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>5202362</v>
+        <v>11877910</v>
       </c>
     </row>
     <row r="21">
@@ -3755,7 +3755,7 @@
         <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>5152040</v>
+        <v>18944550</v>
       </c>
     </row>
     <row r="22">
@@ -3797,7 +3797,7 @@
         <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4323010</v>
+        <v>7437150</v>
       </c>
     </row>
     <row r="23">
@@ -3839,7 +3839,7 @@
         <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>1733170</v>
+        <v>3817600</v>
       </c>
     </row>
     <row r="24">
@@ -4081,7 +4081,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -4123,28 +4123,28 @@
         <v>7</v>
       </c>
       <c r="L6" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -4165,28 +4165,28 @@
         <v>7</v>
       </c>
       <c r="L7" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4207,25 +4207,25 @@
         <v>7</v>
       </c>
       <c r="L8" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4249,28 +4249,28 @@
         <v>7</v>
       </c>
       <c r="L9" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4291,28 +4291,28 @@
         <v>7</v>
       </c>
       <c r="L10" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4333,7 +4333,7 @@
         <v>7</v>
       </c>
       <c r="L11" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -4375,25 +4375,25 @@
         <v>7</v>
       </c>
       <c r="L12" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4417,25 +4417,25 @@
         <v>7</v>
       </c>
       <c r="L13" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4459,22 +4459,22 @@
         <v>7</v>
       </c>
       <c r="L14" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>7</v>
@@ -4501,7 +4501,7 @@
         <v>7</v>
       </c>
       <c r="L15" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4543,25 +4543,25 @@
         <v>7</v>
       </c>
       <c r="L16" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4585,67 +4585,67 @@
         <v>7</v>
       </c>
       <c r="L17" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="n">
         <v>6</v>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4669,35 +4669,35 @@
         <v>7</v>
       </c>
       <c r="L19" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>7</v>
       </c>
       <c r="L20" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -4753,7 +4753,7 @@
         <v>7</v>
       </c>
       <c r="L21" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -4795,7 +4795,7 @@
         <v>7</v>
       </c>
       <c r="L22" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -4837,7 +4837,7 @@
         <v>7</v>
       </c>
       <c r="L23" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1555,12 +1555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="20" min="1" max="1"/>
     <col width="22" customWidth="1" style="20" min="2" max="2"/>
     <col width="15" customWidth="1" style="20" min="3" max="3"/>
+    <col width="15" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1578,9 +1579,14 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -1598,6 +1604,11 @@
       <c r="C4" s="31" t="inlineStr">
         <is>
           <t>май 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>июнь 2026</t>
         </is>
       </c>
     </row>
@@ -1611,6 +1622,9 @@
       <c r="C5" s="34" t="n">
         <v>31</v>
       </c>
+      <c r="D5" s="34" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -1626,6 +1640,9 @@
       <c r="C6" s="40" t="n">
         <v>14619948</v>
       </c>
+      <c r="D6" s="40" t="n">
+        <v>23574400</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -1641,6 +1658,9 @@
       <c r="C7" s="40" t="n">
         <v>14598348</v>
       </c>
+      <c r="D7" s="40" t="n">
+        <v>17460000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -1656,6 +1676,9 @@
       <c r="C8" s="40" t="n">
         <v>23504800</v>
       </c>
+      <c r="D8" s="40" t="n">
+        <v>17427600</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -1671,6 +1694,9 @@
       <c r="C9" s="40" t="n">
         <v>14593548</v>
       </c>
+      <c r="D9" s="40" t="n">
+        <v>17428800</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -1686,6 +1712,9 @@
       <c r="C10" s="40" t="n">
         <v>11291523</v>
       </c>
+      <c r="D10" s="40" t="n">
+        <v>14007200</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -1701,6 +1730,9 @@
       <c r="C11" s="40" t="n">
         <v>10117626</v>
       </c>
+      <c r="D11" s="40" t="n">
+        <v>17409600</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
@@ -1716,6 +1748,9 @@
       <c r="C12" s="40" t="n">
         <v>11234206</v>
       </c>
+      <c r="D12" s="40" t="n">
+        <v>17426400</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
@@ -1731,6 +1766,9 @@
       <c r="C13" s="40" t="n">
         <v>14598348</v>
       </c>
+      <c r="D13" s="40" t="n">
+        <v>17424000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -1746,6 +1784,9 @@
       <c r="C14" s="40" t="n">
         <v>14003600</v>
       </c>
+      <c r="D14" s="40" t="n">
+        <v>20109600</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -1761,6 +1802,9 @@
       <c r="C15" s="40" t="n">
         <v>14001200</v>
       </c>
+      <c r="D15" s="40" t="n">
+        <v>14012000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -1776,6 +1820,9 @@
       <c r="C16" s="40" t="n">
         <v>17401200</v>
       </c>
+      <c r="D16" s="40" t="n">
+        <v>17404800</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
@@ -1791,6 +1838,9 @@
       <c r="C17" s="40" t="n">
         <v>12193548</v>
       </c>
+      <c r="D17" s="40" t="n">
+        <v>14009600</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -1806,6 +1856,9 @@
       <c r="C18" s="40" t="n">
         <v>12645161</v>
       </c>
+      <c r="D18" s="40" t="n">
+        <v>14025200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
@@ -1821,6 +1874,9 @@
       <c r="C19" s="40" t="n">
         <v>11744335</v>
       </c>
+      <c r="D19" s="40" t="n">
+        <v>14021600</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
@@ -1836,6 +1892,9 @@
       <c r="C20" s="40" t="n">
         <v>5422955</v>
       </c>
+      <c r="D20" s="40" t="n">
+        <v>14008400</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -1851,6 +1910,9 @@
       <c r="C21" s="40" t="n">
         <v>23501200</v>
       </c>
+      <c r="D21" s="40" t="n">
+        <v>17406000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -1866,6 +1928,9 @@
       <c r="C22" s="40" t="n">
         <v>5148387</v>
       </c>
+      <c r="D22" s="40" t="n">
+        <v>11400000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -1880,6 +1945,9 @@
       </c>
       <c r="C23" s="40" t="n">
         <v>4967742</v>
+      </c>
+      <c r="D23" s="40" t="n">
+        <v>14000000</v>
       </c>
     </row>
     <row r="24">
@@ -1891,6 +1959,10 @@
       <c r="B24" s="38" t="inlineStr"/>
       <c r="C24" s="41">
         <f>SUM(C6:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="41">
+        <f>SUM(D6:D23)</f>
         <v/>
       </c>
     </row>
@@ -1937,52 +2009,52 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -2935,52 +3007,52 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -3933,52 +4005,52 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1579,12 +1579,12 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -2009,52 +2009,52 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>29.06–05.07*</t>
+          <t>29.06–05.07</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2199,7 +2199,7 @@
         <v>66.14</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>72.67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -2241,7 +2241,7 @@
         <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>65.5</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2283,88 +2283,88 @@
         <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>52</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>35.14</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41.17</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
         <v>41</v>
@@ -2409,7 +2409,7 @@
         <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>37.67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -2451,7 +2451,7 @@
         <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.83</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="13">
@@ -2493,7 +2493,7 @@
         <v>16.86</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>25.83</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="14">
@@ -2535,7 +2535,7 @@
         <v>19.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="15">
@@ -2577,7 +2577,7 @@
         <v>22.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>22.5</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="16">
@@ -2619,91 +2619,91 @@
         <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>20.33</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>6.43</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.17</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="19">
@@ -2745,7 +2745,7 @@
         <v>17.43</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="20">
@@ -2787,7 +2787,7 @@
         <v>21.71</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2829,7 +2829,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>12.33</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="22">
@@ -2871,7 +2871,7 @@
         <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>9.17</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2913,7 +2913,7 @@
         <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="24">
@@ -3007,52 +3007,52 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>29.06–05.07*</t>
+          <t>29.06–05.07</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3197,7 +3197,7 @@
         <v>72409127</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>62062925</v>
+        <v>72256071</v>
       </c>
     </row>
     <row r="7">
@@ -3239,7 +3239,7 @@
         <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>55620338</v>
+        <v>68619843</v>
       </c>
     </row>
     <row r="8">
@@ -3281,91 +3281,91 @@
         <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>45027717</v>
+        <v>51621207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>43259404</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>62931875</v>
+        <v>42012092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>37037706</v>
+        <v>68694825</v>
       </c>
     </row>
     <row r="11">
@@ -3407,7 +3407,7 @@
         <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>38346642</v>
+        <v>51983942</v>
       </c>
     </row>
     <row r="12">
@@ -3449,7 +3449,7 @@
         <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>25655097</v>
+        <v>28078687</v>
       </c>
     </row>
     <row r="13">
@@ -3491,7 +3491,7 @@
         <v>17717888</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>21992980</v>
+        <v>24163432</v>
       </c>
     </row>
     <row r="14">
@@ -3533,7 +3533,7 @@
         <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>25634845</v>
+        <v>31914115</v>
       </c>
     </row>
     <row r="15">
@@ -3575,7 +3575,7 @@
         <v>24614280</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>26410442</v>
+        <v>28889771</v>
       </c>
     </row>
     <row r="16">
@@ -3617,91 +3617,91 @@
         <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>25135951</v>
+        <v>27940611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>17129374</v>
+        <v>21801828</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19039500</v>
+        <v>19068954</v>
       </c>
     </row>
     <row r="19">
@@ -3743,7 +3743,7 @@
         <v>19576415</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>12277818</v>
+        <v>14226838</v>
       </c>
     </row>
     <row r="20">
@@ -3785,7 +3785,7 @@
         <v>29649130</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>11877910</v>
+        <v>13949368</v>
       </c>
     </row>
     <row r="21">
@@ -3827,7 +3827,7 @@
         <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>18944550</v>
+        <v>21143100</v>
       </c>
     </row>
     <row r="22">
@@ -3869,7 +3869,7 @@
         <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7437150</v>
+        <v>7579040</v>
       </c>
     </row>
     <row r="23">
@@ -3911,7 +3911,7 @@
         <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>3817600</v>
+        <v>4571680</v>
       </c>
     </row>
     <row r="24">
@@ -4005,52 +4005,52 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>29.06–05.07*</t>
+          <t>29.06–05.07</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4195,7 +4195,7 @@
         <v>7</v>
       </c>
       <c r="L6" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4237,7 +4237,7 @@
         <v>7</v>
       </c>
       <c r="L7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -4279,25 +4279,25 @@
         <v>7</v>
       </c>
       <c r="L8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4321,25 +4321,25 @@
         <v>7</v>
       </c>
       <c r="L9" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -4363,7 +4363,7 @@
         <v>7</v>
       </c>
       <c r="L10" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -4405,7 +4405,7 @@
         <v>7</v>
       </c>
       <c r="L11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -4447,7 +4447,7 @@
         <v>7</v>
       </c>
       <c r="L12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -4489,7 +4489,7 @@
         <v>7</v>
       </c>
       <c r="L13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -4531,7 +4531,7 @@
         <v>7</v>
       </c>
       <c r="L14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -4573,7 +4573,7 @@
         <v>7</v>
       </c>
       <c r="L15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4615,25 +4615,25 @@
         <v>7</v>
       </c>
       <c r="L16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4657,25 +4657,25 @@
         <v>7</v>
       </c>
       <c r="L17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -4699,7 +4699,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -4741,7 +4741,7 @@
         <v>7</v>
       </c>
       <c r="L19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -4783,7 +4783,7 @@
         <v>7</v>
       </c>
       <c r="L20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -4825,7 +4825,7 @@
         <v>7</v>
       </c>
       <c r="L21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -4867,7 +4867,7 @@
         <v>7</v>
       </c>
       <c r="L22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -4909,7 +4909,7 @@
         <v>7</v>
       </c>
       <c r="L23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1977,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1992,6 +1992,7 @@
     <col width="13" customWidth="1" style="20" min="10" max="10"/>
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
+    <col width="13" customWidth="1" style="20" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2059,6 +2060,11 @@
           <t>2026-06-29</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2119,6 +2125,11 @@
       <c r="L4" s="31" t="inlineStr">
         <is>
           <t>29.06–05.07</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>06.07–12.07*</t>
         </is>
       </c>
     </row>
@@ -2159,6 +2170,9 @@
       <c r="L5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="M5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2201,6 +2215,9 @@
       <c r="L6" s="36" t="n">
         <v>72</v>
       </c>
+      <c r="M6" s="36" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2243,16 +2260,19 @@
       <c r="L7" s="36" t="n">
         <v>69.56999999999999</v>
       </c>
+      <c r="M7" s="36" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
@@ -2262,531 +2282,570 @@
         <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>13.14</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>19.43</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>26.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>32.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>31.29</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>33.57</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>40</v>
+      </c>
+      <c r="M8" s="36" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41.29</v>
+        <v>41</v>
+      </c>
+      <c r="M9" s="36" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>7.33</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>17.86</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>22.14</v>
       </c>
       <c r="H10" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J10" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="I10" s="36" t="n">
-        <v>39.71</v>
-      </c>
-      <c r="J10" s="36" t="n">
-        <v>41.71</v>
-      </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>43.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41</v>
+        <v>50.14</v>
+      </c>
+      <c r="M10" s="36" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>19.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>26.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>28.14</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>28.57</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>31.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>34.86</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>41.29</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F12" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G12" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G12" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>22.43</v>
+      </c>
+      <c r="M12" s="36" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>7</v>
+        <v>9.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>16</v>
+        <v>12.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>19.43</v>
+        <v>13.29</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>15.86</v>
+        <v>14.71</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>14.86</v>
+        <v>17</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>16.71</v>
+        <v>19.71</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>19.71</v>
+        <v>17.71</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>16.86</v>
+        <v>19.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>24.86</v>
+        <v>24.14</v>
+      </c>
+      <c r="M13" s="36" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.43</v>
+        <v>1.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.43</v>
+        <v>12.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.29</v>
+        <v>16.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>14.71</v>
+        <v>21</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>17</v>
+        <v>20.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.71</v>
+        <v>28.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>17.71</v>
+        <v>24.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>19.57</v>
+        <v>27.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.14</v>
+        <v>28.14</v>
+      </c>
+      <c r="M14" s="36" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>13.43</v>
+        <v>0</v>
       </c>
       <c r="F15" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="J15" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="K15" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="G15" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="H15" s="36" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="I15" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="J15" s="36" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="K15" s="36" t="n">
-        <v>22.43</v>
-      </c>
       <c r="L15" s="36" t="n">
-        <v>22.43</v>
+        <v>15</v>
+      </c>
+      <c r="M15" s="36" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.43</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.86</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I16" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="36" t="n">
-        <v>19.14</v>
-      </c>
       <c r="J16" s="36" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>23.43</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>20.43</v>
+        <v>15.29</v>
+      </c>
+      <c r="M16" s="36" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>16.14</v>
+      </c>
+      <c r="M17" s="36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>6.43</v>
+        <v>11</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>14.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>19.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>21</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
+      </c>
+      <c r="M18" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>6.67</v>
+        <v>3</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.29</v>
+        <v>7.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>10.57</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>11.14</v>
+        <v>12.71</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>13.86</v>
+        <v>14.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>18</v>
+        <v>21.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>17.43</v>
+        <v>18.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15.29</v>
+        <v>16.57</v>
+      </c>
+      <c r="M19" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L20" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="M20" s="36" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2831,6 +2890,9 @@
       <c r="L21" s="36" t="n">
         <v>11.86</v>
       </c>
+      <c r="M21" s="36" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -2873,6 +2935,9 @@
       <c r="L22" s="36" t="n">
         <v>8.289999999999999</v>
       </c>
+      <c r="M22" s="36" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -2914,6 +2979,9 @@
       </c>
       <c r="L23" s="36" t="n">
         <v>5.71</v>
+      </c>
+      <c r="M23" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2961,6 +3029,10 @@
       </c>
       <c r="L24" s="39">
         <f>AVERAGE(L6:L23)</f>
+        <v/>
+      </c>
+      <c r="M24" s="39">
+        <f>AVERAGE(M6:M23)</f>
         <v/>
       </c>
     </row>
@@ -2975,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2990,6 +3062,7 @@
     <col width="13" customWidth="1" style="20" min="10" max="10"/>
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
+    <col width="13" customWidth="1" style="20" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3057,6 +3130,11 @@
           <t>2026-06-29</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3117,6 +3195,11 @@
       <c r="L4" s="31" t="inlineStr">
         <is>
           <t>29.06–05.07</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>06.07–12.07*</t>
         </is>
       </c>
     </row>
@@ -3157,6 +3240,9 @@
       <c r="L5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="M5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -3199,6 +3285,9 @@
       <c r="L6" s="40" t="n">
         <v>72256071</v>
       </c>
+      <c r="M6" s="40" t="n">
+        <v>17883229</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -3241,16 +3330,19 @@
       <c r="L7" s="40" t="n">
         <v>68619843</v>
       </c>
+      <c r="M7" s="40" t="n">
+        <v>10146282</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
@@ -3260,532 +3352,571 @@
         <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>8972650</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>18100396</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>23988817</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>22409732</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>37715520</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>35926824</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>39462393</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>51983942</v>
+      </c>
+      <c r="M8" s="40" t="n">
+        <v>19457588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>42012092</v>
+        <v>68694825</v>
+      </c>
+      <c r="M9" s="40" t="n">
+        <v>8799765</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>2886450</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>22932586</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>24764259</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>32268886</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>42977335</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>44364359</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>53225819</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>68694825</v>
+        <v>51621207</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>7347366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>14209578</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>30449860</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>32603120</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>35552907</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>31069118</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>40525338</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>42402722</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>42012092</v>
+      </c>
+      <c r="M11" s="40" t="n">
+        <v>13103781</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>28889771</v>
+      </c>
+      <c r="M12" s="40" t="n">
+        <v>10129220</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>6239584</v>
+        <v>11884771</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>13803407</v>
+        <v>10651216</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>28572076</v>
+        <v>13882033</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>15282581</v>
+        <v>17812948</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>16594572</v>
+        <v>17331854</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>15223898</v>
+        <v>26294756</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>27696695</v>
+        <v>24196222</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>17717888</v>
+        <v>22122847</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>24163432</v>
+        <v>31914115</v>
+      </c>
+      <c r="M13" s="40" t="n">
+        <v>4971291</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11884771</v>
+        <v>536260</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>10651216</v>
+        <v>14403556</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>13882033</v>
+        <v>16216832</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>17812948</v>
+        <v>32622053</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>17331854</v>
+        <v>23929705</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>26294756</v>
+        <v>37214538</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>24196222</v>
+        <v>25375430</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>22122847</v>
+        <v>31500087</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>31914115</v>
+        <v>28078687</v>
+      </c>
+      <c r="M14" s="40" t="n">
+        <v>5131540</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>10351067</v>
+        <v>0</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>21091580</v>
+        <v>0</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>24243567</v>
+        <v>363900</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>16381412</v>
+        <v>3736700</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>21591272</v>
+        <v>17796776</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>21904190</v>
+        <v>42724228</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>25438080</v>
+        <v>33036620</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24614280</v>
+        <v>29649130</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>28889771</v>
+        <v>13949368</v>
+      </c>
+      <c r="M15" s="40" t="n">
+        <v>4874150</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>8544625</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>8387478</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10570508</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>11896580</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19614352</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>20966317</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>20073400</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>23801493</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>27940611</v>
+        <v>14226838</v>
+      </c>
+      <c r="M16" s="40" t="n">
+        <v>4393985</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>19068954</v>
+      </c>
+      <c r="M17" s="40" t="n">
+        <v>3400570</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>8544625</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>8387478</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>10570508</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>11896580</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>19614352</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>20966317</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>20073400</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>23801493</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>27940611</v>
+      </c>
+      <c r="M18" s="40" t="n">
+        <v>2734970</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>5092853</v>
+        <v>3337146</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>11100161</v>
+        <v>10420206</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14612055</v>
+        <v>21387685</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>20638987</v>
+        <v>16050448</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>14061352</v>
+        <v>21568794</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>31599148</v>
+        <v>30845816</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>18747614</v>
+        <v>45285935</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>19576415</v>
+        <v>28941455</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>14226838</v>
+        <v>21801828</v>
+      </c>
+      <c r="M19" s="40" t="n">
+        <v>1899230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
+      </c>
+      <c r="M20" s="40" t="n">
+        <v>2645320</v>
       </c>
     </row>
     <row r="21">
@@ -3829,6 +3960,9 @@
       <c r="L21" s="40" t="n">
         <v>21143100</v>
       </c>
+      <c r="M21" s="40" t="n">
+        <v>369200</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -3871,6 +4005,9 @@
       <c r="L22" s="40" t="n">
         <v>7579040</v>
       </c>
+      <c r="M22" s="40" t="n">
+        <v>131200</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -3912,6 +4049,9 @@
       </c>
       <c r="L23" s="40" t="n">
         <v>4571680</v>
+      </c>
+      <c r="M23" s="40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3959,6 +4099,10 @@
       </c>
       <c r="L24" s="41">
         <f>AVERAGE(L6:L23)</f>
+        <v/>
+      </c>
+      <c r="M24" s="41">
+        <f>AVERAGE(M6:M23)</f>
         <v/>
       </c>
     </row>
@@ -3973,7 +4117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3988,6 +4132,7 @@
     <col width="13" customWidth="1" style="20" min="10" max="10"/>
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
+    <col width="13" customWidth="1" style="20" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4055,6 +4200,11 @@
           <t>2026-06-29</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4115,6 +4265,11 @@
       <c r="L4" s="31" t="inlineStr">
         <is>
           <t>29.06–05.07</t>
+        </is>
+      </c>
+      <c r="M4" s="31" t="inlineStr">
+        <is>
+          <t>06.07–12.07*</t>
         </is>
       </c>
     </row>
@@ -4155,6 +4310,9 @@
       <c r="L5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="M5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4197,6 +4355,9 @@
       <c r="L6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="M6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -4239,16 +4400,19 @@
       <c r="L7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="M7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
@@ -4258,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4280,24 +4444,27 @@
       </c>
       <c r="L8" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4322,27 +4489,30 @@
       </c>
       <c r="L9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4364,27 +4534,30 @@
       </c>
       <c r="L10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4406,24 +4579,27 @@
       </c>
       <c r="L11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4448,24 +4624,27 @@
       </c>
       <c r="L12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4490,24 +4669,27 @@
       </c>
       <c r="L13" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4532,66 +4714,72 @@
       </c>
       <c r="L14" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -4616,24 +4804,27 @@
       </c>
       <c r="L16" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -4658,24 +4849,27 @@
       </c>
       <c r="L17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -4700,24 +4894,27 @@
       </c>
       <c r="L18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4742,33 +4939,36 @@
       </c>
       <c r="L19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -4784,6 +4984,9 @@
       </c>
       <c r="L20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4827,6 +5030,9 @@
       <c r="L21" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="M21" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -4869,6 +5075,9 @@
       <c r="L22" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="M22" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -4910,6 +5119,9 @@
       </c>
       <c r="L23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="M23" s="42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4959,6 +5171,10 @@
         <f>AVERAGE(L6:L23)</f>
         <v/>
       </c>
+      <c r="M24" s="43">
+        <f>AVERAGE(M6:M23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2216,7 +2216,7 @@
         <v>72</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>76</v>
+        <v>78.67</v>
       </c>
     </row>
     <row r="7">
@@ -2261,18 +2261,18 @@
         <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>73</v>
+        <v>65.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
@@ -2282,31 +2282,31 @@
         <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>13.14</v>
+        <v>17.86</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>19.43</v>
+        <v>22.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>26.43</v>
+        <v>24.86</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>32.29</v>
+        <v>36.57</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>31.29</v>
+        <v>38</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>33.57</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>40</v>
+        <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>52</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="9">
@@ -2351,97 +2351,97 @@
         <v>41</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>51</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>50.14</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>48</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -2486,7 +2486,7 @@
         <v>22.43</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>35</v>
+        <v>34.67</v>
       </c>
     </row>
     <row r="13">
@@ -2531,7 +2531,7 @@
         <v>24.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>33</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="14">
@@ -2576,49 +2576,49 @@
         <v>28.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K15" s="36" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="L15" s="36" t="n">
         <v>20.43</v>
-      </c>
-      <c r="K15" s="36" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="L15" s="36" t="n">
-        <v>15</v>
       </c>
       <c r="M15" s="36" t="n">
         <v>27</v>
@@ -2627,226 +2627,226 @@
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>26</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>6.43</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.14</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G18" s="36" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="E18" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>11.86</v>
-      </c>
       <c r="H18" s="36" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19.14</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>21</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>23.43</v>
+        <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>7.14</v>
+        <v>16</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>19.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>12.71</v>
+        <v>15.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.43</v>
+        <v>14.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19</v>
+        <v>16.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21.14</v>
+        <v>19.71</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>16.57</v>
+        <v>24.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>16</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>16</v>
+        <v>7.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>19.43</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>15.86</v>
+        <v>12.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.86</v>
+        <v>14.43</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>16.71</v>
+        <v>19</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>24.86</v>
+        <v>16.57</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>15</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="21">
@@ -2891,7 +2891,7 @@
         <v>11.86</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2936,7 +2936,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -2981,7 +2981,7 @@
         <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3241,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3286,7 +3286,7 @@
         <v>72256071</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>17883229</v>
+        <v>43407209</v>
       </c>
     </row>
     <row r="7">
@@ -3331,18 +3331,18 @@
         <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>10146282</v>
+        <v>30122536</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
@@ -3352,31 +3352,31 @@
         <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>8972650</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>18100396</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>23988817</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>22409732</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>37715520</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>35926824</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>39462393</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51983942</v>
+        <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>19457588</v>
+        <v>24321352</v>
       </c>
     </row>
     <row r="9">
@@ -3421,97 +3421,97 @@
         <v>68694825</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>8799765</v>
+        <v>21908161</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51621207</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>7347366</v>
+        <v>34623369</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>13103781</v>
+        <v>30692748</v>
       </c>
     </row>
     <row r="12">
@@ -3556,7 +3556,7 @@
         <v>28889771</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>10129220</v>
+        <v>19350740</v>
       </c>
     </row>
     <row r="13">
@@ -3601,7 +3601,7 @@
         <v>31914115</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>4971291</v>
+        <v>14769011</v>
       </c>
     </row>
     <row r="14">
@@ -3646,277 +3646,277 @@
         <v>28078687</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>5131540</v>
+        <v>17697660</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>29649130</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>13949368</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>4874150</v>
+        <v>13958966</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>14226838</v>
+        <v>13949368</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>4393985</v>
+        <v>9334940</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>19068954</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>3400570</v>
+        <v>14197945</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>8544625</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>8387478</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>10570508</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>11896580</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19614352</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>20966317</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>20073400</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>23801493</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>27940611</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>2734970</v>
+        <v>11625960</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3337146</v>
+        <v>6239584</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10420206</v>
+        <v>13803407</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>21387685</v>
+        <v>28572076</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16050448</v>
+        <v>15282581</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>21568794</v>
+        <v>16594572</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>30845816</v>
+        <v>15223898</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>45285935</v>
+        <v>27696695</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>28941455</v>
+        <v>17717888</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21801828</v>
+        <v>24163432</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>1899230</v>
+        <v>8673587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>6239584</v>
+        <v>3337146</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>13803407</v>
+        <v>10420206</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>28572076</v>
+        <v>21387685</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>15282581</v>
+        <v>16050448</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>16594572</v>
+        <v>21568794</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>15223898</v>
+        <v>30845816</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>27696695</v>
+        <v>45285935</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>17717888</v>
+        <v>28941455</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>24163432</v>
+        <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>2645320</v>
+        <v>9046220</v>
       </c>
     </row>
     <row r="21">
@@ -3961,7 +3961,7 @@
         <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>369200</v>
+        <v>3650850</v>
       </c>
     </row>
     <row r="22">
@@ -4006,7 +4006,7 @@
         <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>131200</v>
+        <v>3469666</v>
       </c>
     </row>
     <row r="23">
@@ -4051,7 +4051,7 @@
         <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>0</v>
+        <v>1271050</v>
       </c>
     </row>
     <row r="24">
@@ -4311,7 +4311,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4356,7 +4356,7 @@
         <v>7</v>
       </c>
       <c r="M6" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4401,18 +4401,18 @@
         <v>7</v>
       </c>
       <c r="M7" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4446,7 +4446,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4491,97 +4491,97 @@
         <v>7</v>
       </c>
       <c r="M9" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4626,7 +4626,7 @@
         <v>7</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4671,7 +4671,7 @@
         <v>7</v>
       </c>
       <c r="M13" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4716,34 +4716,34 @@
         <v>7</v>
       </c>
       <c r="M14" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F15" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="42" t="n">
         <v>7</v>
@@ -4761,35 +4761,35 @@
         <v>7</v>
       </c>
       <c r="M15" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H16" s="42" t="n">
         <v>7</v>
       </c>
@@ -4806,70 +4806,70 @@
         <v>7</v>
       </c>
       <c r="M16" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -4896,25 +4896,25 @@
         <v>7</v>
       </c>
       <c r="M18" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4941,25 +4941,25 @@
         <v>7</v>
       </c>
       <c r="M19" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -4986,7 +4986,7 @@
         <v>7</v>
       </c>
       <c r="M20" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="M21" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -5076,7 +5076,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5121,7 +5121,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2216,7 +2216,7 @@
         <v>72</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>78.67</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2261,7 +2261,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>65.67</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2306,7 +2306,7 @@
         <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59.67</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="9">
@@ -2351,7 +2351,7 @@
         <v>41</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>48.33</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="10">
@@ -2396,7 +2396,7 @@
         <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>43.33</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="11">
@@ -2441,7 +2441,7 @@
         <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -2486,7 +2486,7 @@
         <v>22.43</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>34.67</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="13">
@@ -2531,7 +2531,7 @@
         <v>24.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>32.33</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="14">
@@ -2576,7 +2576,7 @@
         <v>28.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>30</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="15">
@@ -2621,97 +2621,97 @@
         <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>0</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>0.5</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>3.33</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>11.71</v>
+        <v>13.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.57</v>
+        <v>18</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>20.43</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>21.71</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>23.33</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="18">
@@ -2756,7 +2756,7 @@
         <v>16.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>22.67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -2801,7 +2801,7 @@
         <v>24.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>18.33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -2846,7 +2846,7 @@
         <v>16.57</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>17.33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2891,7 +2891,7 @@
         <v>11.86</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="22">
@@ -2936,7 +2936,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="23">
@@ -2981,7 +2981,7 @@
         <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="24">
@@ -3241,7 +3241,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3286,7 +3286,7 @@
         <v>72256071</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>43407209</v>
+        <v>60181985</v>
       </c>
     </row>
     <row r="7">
@@ -3331,7 +3331,7 @@
         <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>30122536</v>
+        <v>50857766</v>
       </c>
     </row>
     <row r="8">
@@ -3376,7 +3376,7 @@
         <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>24321352</v>
+        <v>44918717</v>
       </c>
     </row>
     <row r="9">
@@ -3421,7 +3421,7 @@
         <v>68694825</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>21908161</v>
+        <v>36471034</v>
       </c>
     </row>
     <row r="10">
@@ -3466,7 +3466,7 @@
         <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>34623369</v>
+        <v>47350679</v>
       </c>
     </row>
     <row r="11">
@@ -3511,7 +3511,7 @@
         <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>30692748</v>
+        <v>47123184</v>
       </c>
     </row>
     <row r="12">
@@ -3556,7 +3556,7 @@
         <v>28889771</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>19350740</v>
+        <v>38730240</v>
       </c>
     </row>
     <row r="13">
@@ -3601,7 +3601,7 @@
         <v>31914115</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>14769011</v>
+        <v>23564616</v>
       </c>
     </row>
     <row r="14">
@@ -3646,7 +3646,7 @@
         <v>28078687</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>17697660</v>
+        <v>25747970</v>
       </c>
     </row>
     <row r="15">
@@ -3691,97 +3691,97 @@
         <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>13958966</v>
+        <v>21302859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>0</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>363900</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>3736700</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17796776</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>42724228</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>33036620</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>29649130</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>13949368</v>
+        <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>9334940</v>
+        <v>18624157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>14197945</v>
+        <v>18287923</v>
       </c>
     </row>
     <row r="18">
@@ -3826,7 +3826,7 @@
         <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>11625960</v>
+        <v>17979931</v>
       </c>
     </row>
     <row r="19">
@@ -3871,7 +3871,7 @@
         <v>24163432</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>8673587</v>
+        <v>15830679</v>
       </c>
     </row>
     <row r="20">
@@ -3916,7 +3916,7 @@
         <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>9046220</v>
+        <v>13949360</v>
       </c>
     </row>
     <row r="21">
@@ -3961,7 +3961,7 @@
         <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>3650850</v>
+        <v>9723300</v>
       </c>
     </row>
     <row r="22">
@@ -4006,7 +4006,7 @@
         <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>3469666</v>
+        <v>7940806</v>
       </c>
     </row>
     <row r="23">
@@ -4051,7 +4051,7 @@
         <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>1271050</v>
+        <v>3142340</v>
       </c>
     </row>
     <row r="24">
@@ -4311,7 +4311,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4356,7 +4356,7 @@
         <v>7</v>
       </c>
       <c r="M6" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -4401,7 +4401,7 @@
         <v>7</v>
       </c>
       <c r="M7" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4446,7 +4446,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -4491,7 +4491,7 @@
         <v>7</v>
       </c>
       <c r="M9" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -4536,7 +4536,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -4581,7 +4581,7 @@
         <v>7</v>
       </c>
       <c r="M11" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -4626,7 +4626,7 @@
         <v>7</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -4671,7 +4671,7 @@
         <v>7</v>
       </c>
       <c r="M13" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -4716,7 +4716,7 @@
         <v>7</v>
       </c>
       <c r="M14" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -4761,34 +4761,34 @@
         <v>7</v>
       </c>
       <c r="M15" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="42" t="n">
         <v>7</v>
@@ -4806,35 +4806,35 @@
         <v>7</v>
       </c>
       <c r="M16" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>7</v>
       </c>
       <c r="M17" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -4896,7 +4896,7 @@
         <v>7</v>
       </c>
       <c r="M18" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -4941,7 +4941,7 @@
         <v>7</v>
       </c>
       <c r="M19" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -4986,7 +4986,7 @@
         <v>7</v>
       </c>
       <c r="M20" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="M21" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -5076,7 +5076,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -5121,7 +5121,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2129,7 +2129,7 @@
       </c>
       <c r="M4" s="31" t="inlineStr">
         <is>
-          <t>06.07–12.07*</t>
+          <t>06.07–12.07</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2216,7 +2216,7 @@
         <v>72</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>73.59999999999999</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2261,7 +2261,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>65.40000000000001</v>
+        <v>66.43000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2306,7 +2306,7 @@
         <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>62.6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -2351,232 +2351,232 @@
         <v>41</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>43.2</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>19.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>26.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>28.14</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>28.57</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>31.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>34.86</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>41.29</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>43</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>30.6</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9.43</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.43</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>13.29</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>14.71</v>
+        <v>16.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>17</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>17.71</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>19.57</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>29.4</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.67</v>
+        <v>9.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.57</v>
+        <v>13.29</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>21</v>
+        <v>14.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>20.29</v>
+        <v>17</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>28.57</v>
+        <v>19.71</v>
       </c>
       <c r="J14" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="L14" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="K14" s="36" t="n">
+      <c r="M14" s="36" t="n">
         <v>27.57</v>
-      </c>
-      <c r="L14" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="M14" s="36" t="n">
-        <v>28.8</v>
       </c>
     </row>
     <row r="15">
@@ -2621,7 +2621,7 @@
         <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>26.4</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="16">
@@ -2666,142 +2666,142 @@
         <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.6</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15</v>
+        <v>24.86</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>24.6</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E18" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>24</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>23</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="20">
@@ -2846,7 +2846,7 @@
         <v>16.57</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>15</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="21">
@@ -2891,7 +2891,7 @@
         <v>11.86</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.6</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2936,7 +2936,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.4</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2981,7 +2981,7 @@
         <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="M4" s="31" t="inlineStr">
         <is>
-          <t>06.07–12.07*</t>
+          <t>06.07–12.07</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3286,7 +3286,7 @@
         <v>72256071</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>60181985</v>
+        <v>82753547</v>
       </c>
     </row>
     <row r="7">
@@ -3331,7 +3331,7 @@
         <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>50857766</v>
+        <v>81742671</v>
       </c>
     </row>
     <row r="8">
@@ -3376,7 +3376,7 @@
         <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>44918717</v>
+        <v>58204066</v>
       </c>
     </row>
     <row r="9">
@@ -3421,232 +3421,232 @@
         <v>68694825</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>36471034</v>
+        <v>48824266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>47350679</v>
+        <v>58935844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>14209578</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>30449860</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>32603120</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>35552907</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>31069118</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>40525338</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>42402722</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>42012092</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>47123184</v>
+        <v>58722069</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>38730240</v>
+        <v>34472458</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>475871</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>11884771</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>10651216</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>13882033</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>17812948</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>17331854</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>26294756</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>24196222</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>22122847</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>31914115</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>23564616</v>
+        <v>44250621</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>536260</v>
+        <v>11884771</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14403556</v>
+        <v>10651216</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>16216832</v>
+        <v>13882033</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32622053</v>
+        <v>17812948</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>23929705</v>
+        <v>17331854</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37214538</v>
+        <v>26294756</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25375430</v>
+        <v>24196222</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>31500087</v>
+        <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28078687</v>
+        <v>31914115</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>25747970</v>
+        <v>32069521</v>
       </c>
     </row>
     <row r="15">
@@ -3691,7 +3691,7 @@
         <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>21302859</v>
+        <v>27893929</v>
       </c>
     </row>
     <row r="16">
@@ -3736,142 +3736,142 @@
         <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>18624157</v>
+        <v>23197145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>18287923</v>
+        <v>23623477</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>17979931</v>
+        <v>24539413</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>15830679</v>
+        <v>25387051</v>
       </c>
     </row>
     <row r="20">
@@ -3916,7 +3916,7 @@
         <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>13949360</v>
+        <v>19628570</v>
       </c>
     </row>
     <row r="21">
@@ -3961,7 +3961,7 @@
         <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>9723300</v>
+        <v>14330970</v>
       </c>
     </row>
     <row r="22">
@@ -4006,7 +4006,7 @@
         <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>7940806</v>
+        <v>9679437</v>
       </c>
     </row>
     <row r="23">
@@ -4051,7 +4051,7 @@
         <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3142340</v>
+        <v>3911995</v>
       </c>
     </row>
     <row r="24">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="M4" s="31" t="inlineStr">
         <is>
-          <t>06.07–12.07*</t>
+          <t>06.07–12.07</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4356,7 +4356,7 @@
         <v>7</v>
       </c>
       <c r="M6" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4401,7 +4401,7 @@
         <v>7</v>
       </c>
       <c r="M7" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -4446,7 +4446,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4491,28 +4491,28 @@
         <v>7</v>
       </c>
       <c r="M9" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4536,28 +4536,28 @@
         <v>7</v>
       </c>
       <c r="M10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4581,25 +4581,25 @@
         <v>7</v>
       </c>
       <c r="M11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4626,22 +4626,22 @@
         <v>7</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
         <v>7</v>
@@ -4671,25 +4671,25 @@
         <v>7</v>
       </c>
       <c r="M13" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4716,7 +4716,7 @@
         <v>7</v>
       </c>
       <c r="M14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="M15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4806,34 +4806,34 @@
         <v>7</v>
       </c>
       <c r="M16" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -4851,34 +4851,34 @@
         <v>7</v>
       </c>
       <c r="M17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -4896,25 +4896,25 @@
         <v>7</v>
       </c>
       <c r="M18" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4941,7 +4941,7 @@
         <v>7</v>
       </c>
       <c r="M19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -4986,7 +4986,7 @@
         <v>7</v>
       </c>
       <c r="M20" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -5031,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="M21" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -5076,7 +5076,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -5121,7 +5121,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1977,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1993,6 +1993,7 @@
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
+    <col width="13" customWidth="1" style="20" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2065,6 +2066,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2130,6 +2136,11 @@
       <c r="M4" s="31" t="inlineStr">
         <is>
           <t>06.07–12.07</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>13.07–19.07*</t>
         </is>
       </c>
     </row>
@@ -2173,6 +2184,9 @@
       <c r="M5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="N5" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2218,6 +2232,9 @@
       <c r="M6" s="36" t="n">
         <v>72.56999999999999</v>
       </c>
+      <c r="N6" s="36" t="n">
+        <v>85.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2263,6 +2280,9 @@
       <c r="M7" s="36" t="n">
         <v>66.43000000000001</v>
       </c>
+      <c r="N7" s="36" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2308,6 +2328,9 @@
       <c r="M8" s="36" t="n">
         <v>59</v>
       </c>
+      <c r="N8" s="36" t="n">
+        <v>55.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -2353,185 +2376,200 @@
       <c r="M9" s="36" t="n">
         <v>48</v>
       </c>
+      <c r="N9" s="36" t="n">
+        <v>46.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>33.57</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>40</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>42.43</v>
+        <v>41.43</v>
+      </c>
+      <c r="N10" s="36" t="n">
+        <v>39.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>41.43</v>
+        <v>42.43</v>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>37.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F12" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G12" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G12" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L12" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M12" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="M12" s="36" t="n">
-        <v>28.86</v>
+      <c r="N12" s="36" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>28.86</v>
+      </c>
+      <c r="N13" s="36" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -2578,6 +2616,9 @@
       <c r="M14" s="36" t="n">
         <v>27.57</v>
       </c>
+      <c r="N14" s="36" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -2623,6 +2664,9 @@
       <c r="M15" s="36" t="n">
         <v>24.57</v>
       </c>
+      <c r="N15" s="36" t="n">
+        <v>27.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -2668,275 +2712,296 @@
       <c r="M16" s="36" t="n">
         <v>24.43</v>
       </c>
+      <c r="N16" s="36" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>19.43</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>15.86</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.86</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>16.71</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>19.71</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>16.86</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>24.86</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>23.43</v>
+        <v>22.71</v>
+      </c>
+      <c r="N17" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L18" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M18" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="L18" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M18" s="36" t="n">
-        <v>22.71</v>
+      <c r="N18" s="36" t="n">
+        <v>19.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3.33</v>
+        <v>7</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>6.43</v>
+        <v>16</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14</v>
+        <v>14.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.14</v>
+        <v>16.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>16.14</v>
+        <v>19.71</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>16.14</v>
+        <v>24.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>21.71</v>
+        <v>23.43</v>
+      </c>
+      <c r="N19" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I20" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H20" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I20" s="36" t="n">
-        <v>19</v>
-      </c>
       <c r="J20" s="36" t="n">
-        <v>21.14</v>
+        <v>11.57</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>18.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>16.57</v>
+        <v>11.86</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>14.71</v>
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N20" s="36" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>5.14</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>5.29</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>7.86</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>7.14</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>7.14</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11.86</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M21" s="36" t="n">
         <v>9.710000000000001</v>
       </c>
+      <c r="N21" s="36" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>4</v>
+        <v>7.14</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>5.14</v>
+        <v>13.43</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>5.29</v>
+        <v>12.71</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>14.43</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>19</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>21.14</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>18.57</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>16.57</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>14.71</v>
+      </c>
+      <c r="N22" s="36" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -2982,6 +3047,9 @@
       </c>
       <c r="M23" s="36" t="n">
         <v>6</v>
+      </c>
+      <c r="N23" s="36" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -3033,6 +3101,10 @@
       </c>
       <c r="M24" s="39">
         <f>AVERAGE(M6:M23)</f>
+        <v/>
+      </c>
+      <c r="N24" s="39">
+        <f>AVERAGE(N6:N23)</f>
         <v/>
       </c>
     </row>
@@ -3047,7 +3119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3063,6 +3135,7 @@
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
+    <col width="13" customWidth="1" style="20" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3135,6 +3208,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3200,6 +3278,11 @@
       <c r="M4" s="31" t="inlineStr">
         <is>
           <t>06.07–12.07</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>13.07–19.07*</t>
         </is>
       </c>
     </row>
@@ -3243,6 +3326,9 @@
       <c r="M5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="N5" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -3288,6 +3374,9 @@
       <c r="M6" s="40" t="n">
         <v>82753547</v>
       </c>
+      <c r="N6" s="40" t="n">
+        <v>24552201</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -3333,6 +3422,9 @@
       <c r="M7" s="40" t="n">
         <v>81742671</v>
       </c>
+      <c r="N7" s="40" t="n">
+        <v>19414750</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -3378,6 +3470,9 @@
       <c r="M8" s="40" t="n">
         <v>58204066</v>
       </c>
+      <c r="N8" s="40" t="n">
+        <v>18402964</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -3423,185 +3518,200 @@
       <c r="M9" s="40" t="n">
         <v>48824266</v>
       </c>
+      <c r="N9" s="40" t="n">
+        <v>14699150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>39462393</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51983942</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58935844</v>
+        <v>58722069</v>
+      </c>
+      <c r="N10" s="40" t="n">
+        <v>11796996</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58722069</v>
+        <v>58935844</v>
+      </c>
+      <c r="N11" s="40" t="n">
+        <v>12239510</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>28889771</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>44250621</v>
+      </c>
+      <c r="N12" s="40" t="n">
+        <v>9676558</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>34472458</v>
+      </c>
+      <c r="N13" s="40" t="n">
+        <v>10147733</v>
       </c>
     </row>
     <row r="14">
@@ -3648,6 +3758,9 @@
       <c r="M14" s="40" t="n">
         <v>32069521</v>
       </c>
+      <c r="N14" s="40" t="n">
+        <v>11135040</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -3693,6 +3806,9 @@
       <c r="M15" s="40" t="n">
         <v>27893929</v>
       </c>
+      <c r="N15" s="40" t="n">
+        <v>7711840</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -3738,275 +3854,296 @@
       <c r="M16" s="40" t="n">
         <v>23197145</v>
       </c>
+      <c r="N16" s="40" t="n">
+        <v>6074640</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>13803407</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>28572076</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>15282581</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>16594572</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>15223898</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>27696695</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>17717888</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>24163432</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23623477</v>
+        <v>24539413</v>
+      </c>
+      <c r="N17" s="40" t="n">
+        <v>4549140</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13949368</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>24539413</v>
+        <v>25387051</v>
+      </c>
+      <c r="N18" s="40" t="n">
+        <v>5879760</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3249588</v>
+        <v>6239584</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>7305524</v>
+        <v>13803407</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>9575225</v>
+        <v>28572076</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>9264589</v>
+        <v>15282581</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>20692424</v>
+        <v>16594572</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>27565767</v>
+        <v>15223898</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>19138015</v>
+        <v>27696695</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>24912292</v>
+        <v>17717888</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>19068954</v>
+        <v>24163432</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>25387051</v>
+        <v>23623477</v>
+      </c>
+      <c r="N19" s="40" t="n">
+        <v>5294430</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
+      </c>
+      <c r="N20" s="40" t="n">
+        <v>8906100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>6991878</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>4060163</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>7685466</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>10141286</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>6393871</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>11732010</v>
+        <v>4534503</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21143100</v>
+        <v>7579040</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>14330970</v>
+        <v>9679437</v>
+      </c>
+      <c r="N21" s="40" t="n">
+        <v>1553754</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>3337146</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>10420206</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>21387685</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>16050448</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>21568794</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>30845816</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>45285935</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>28941455</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>21801828</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>19628570</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>3378860</v>
       </c>
     </row>
     <row r="23">
@@ -4052,6 +4189,9 @@
       </c>
       <c r="M23" s="40" t="n">
         <v>3911995</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>5552810</v>
       </c>
     </row>
     <row r="24">
@@ -4103,6 +4243,10 @@
       </c>
       <c r="M24" s="41">
         <f>AVERAGE(M6:M23)</f>
+        <v/>
+      </c>
+      <c r="N24" s="41">
+        <f>AVERAGE(N6:N23)</f>
         <v/>
       </c>
     </row>
@@ -4117,7 +4261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4133,6 +4277,7 @@
     <col width="13" customWidth="1" style="20" min="11" max="11"/>
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
+    <col width="13" customWidth="1" style="20" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4205,6 +4350,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4270,6 +4420,11 @@
       <c r="M4" s="31" t="inlineStr">
         <is>
           <t>06.07–12.07</t>
+        </is>
+      </c>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>13.07–19.07*</t>
         </is>
       </c>
     </row>
@@ -4313,6 +4468,9 @@
       <c r="M5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="N5" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4358,6 +4516,9 @@
       <c r="M6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N6" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -4403,6 +4564,9 @@
       <c r="M7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N7" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -4448,6 +4612,9 @@
       <c r="M8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N8" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -4493,26 +4660,29 @@
       <c r="M9" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N9" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4537,27 +4707,30 @@
       </c>
       <c r="M10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N10" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4582,24 +4755,27 @@
       </c>
       <c r="M11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N11" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4627,24 +4803,27 @@
       </c>
       <c r="M12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4672,6 +4851,9 @@
       </c>
       <c r="M13" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -4718,6 +4900,9 @@
       <c r="M14" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N14" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -4763,6 +4948,9 @@
       <c r="M15" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N15" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -4808,32 +4996,35 @@
       <c r="M16" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="N16" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -4852,69 +5043,75 @@
       </c>
       <c r="M17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -4942,30 +5139,33 @@
       </c>
       <c r="M19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N19" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -4987,30 +5187,33 @@
       </c>
       <c r="M20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N20" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -5032,24 +5235,27 @@
       </c>
       <c r="M21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N21" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>7</v>
@@ -5077,6 +5283,9 @@
       </c>
       <c r="M22" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="N22" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -5122,6 +5331,9 @@
       </c>
       <c r="M23" s="42" t="n">
         <v>6</v>
+      </c>
+      <c r="N23" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -5175,6 +5387,10 @@
         <f>AVERAGE(M6:M23)</f>
         <v/>
       </c>
+      <c r="N24" s="43">
+        <f>AVERAGE(N6:N23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2185,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2233,7 +2233,7 @@
         <v>72.56999999999999</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>85.5</v>
+        <v>90.67</v>
       </c>
     </row>
     <row r="7">
@@ -2281,7 +2281,7 @@
         <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="8">
@@ -2329,7 +2329,7 @@
         <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>55.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -2377,7 +2377,7 @@
         <v>48</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -2425,7 +2425,7 @@
         <v>41.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>39.5</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="11">
@@ -2473,7 +2473,7 @@
         <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>37.5</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="12">
@@ -2521,7 +2521,7 @@
         <v>28.14</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>36</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="13">
@@ -2569,7 +2569,7 @@
         <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>35</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>27.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>28</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="15">
@@ -2665,7 +2665,7 @@
         <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>27.5</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="16">
@@ -2713,55 +2713,55 @@
         <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15</v>
+        <v>24.86</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>22.71</v>
+        <v>23.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -2809,55 +2809,55 @@
         <v>21.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>19.43</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>15.86</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.86</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>16.71</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>19.71</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>16.86</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>24.86</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>23.43</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -2905,103 +2905,103 @@
         <v>9.710000000000001</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>13.5</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>4</v>
+        <v>7.14</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>5.14</v>
+        <v>13.43</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>5.29</v>
+        <v>12.71</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>7.86</v>
+        <v>14.43</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>7.14</v>
+        <v>19</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>21.14</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>7.14</v>
+        <v>18.57</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>16.57</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>12.5</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G22" s="36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="H22" s="36" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I22" s="36" t="n">
         <v>7.14</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="H22" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I22" s="36" t="n">
-        <v>19</v>
-      </c>
       <c r="J22" s="36" t="n">
-        <v>21.14</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>18.57</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>16.57</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>14.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>10</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="23">
@@ -3049,7 +3049,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="24">
@@ -3327,7 +3327,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3375,7 +3375,7 @@
         <v>82753547</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>24552201</v>
+        <v>41714755</v>
       </c>
     </row>
     <row r="7">
@@ -3423,7 +3423,7 @@
         <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>19414750</v>
+        <v>30134016</v>
       </c>
     </row>
     <row r="8">
@@ -3471,7 +3471,7 @@
         <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>18402964</v>
+        <v>28222893</v>
       </c>
     </row>
     <row r="9">
@@ -3519,7 +3519,7 @@
         <v>48824266</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>14699150</v>
+        <v>20488750</v>
       </c>
     </row>
     <row r="10">
@@ -3567,7 +3567,7 @@
         <v>58722069</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>11796996</v>
+        <v>16957120</v>
       </c>
     </row>
     <row r="11">
@@ -3615,7 +3615,7 @@
         <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>12239510</v>
+        <v>18040161</v>
       </c>
     </row>
     <row r="12">
@@ -3663,7 +3663,7 @@
         <v>44250621</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>9676558</v>
+        <v>13030111</v>
       </c>
     </row>
     <row r="13">
@@ -3711,7 +3711,7 @@
         <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>10147733</v>
+        <v>14524483</v>
       </c>
     </row>
     <row r="14">
@@ -3759,7 +3759,7 @@
         <v>32069521</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>11135040</v>
+        <v>13473770</v>
       </c>
     </row>
     <row r="15">
@@ -3807,7 +3807,7 @@
         <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>7711840</v>
+        <v>11762022</v>
       </c>
     </row>
     <row r="16">
@@ -3855,55 +3855,55 @@
         <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>6074640</v>
+        <v>8307815</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>24539413</v>
+        <v>23623477</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>4549140</v>
+        <v>8153965</v>
       </c>
     </row>
     <row r="18">
@@ -3951,55 +3951,55 @@
         <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>5879760</v>
+        <v>11240220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>13803407</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>28572076</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>15282581</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>16594572</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>15223898</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>27696695</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>17717888</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>24163432</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>23623477</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>5294430</v>
+        <v>6565310</v>
       </c>
     </row>
     <row r="20">
@@ -4047,103 +4047,103 @@
         <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>8906100</v>
+        <v>16667400</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>2474409</v>
+        <v>3337146</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>4696696</v>
+        <v>10420206</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>6991878</v>
+        <v>21387685</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>4060163</v>
+        <v>16050448</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>7685466</v>
+        <v>21568794</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>10141286</v>
+        <v>30845816</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>6393871</v>
+        <v>45285935</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>4534503</v>
+        <v>28941455</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>7579040</v>
+        <v>21801828</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>9679437</v>
+        <v>19628570</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>1553754</v>
+        <v>7396820</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>3337146</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>10420206</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>21387685</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>16050448</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>21568794</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>30845816</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>45285935</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>28941455</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>21801828</v>
+        <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>19628570</v>
+        <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>3378860</v>
+        <v>2818984</v>
       </c>
     </row>
     <row r="23">
@@ -4191,7 +4191,7 @@
         <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>5552810</v>
+        <v>5866900</v>
       </c>
     </row>
     <row r="24">
@@ -4469,7 +4469,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4517,7 +4517,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4565,7 +4565,7 @@
         <v>7</v>
       </c>
       <c r="N7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4613,7 +4613,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4661,7 +4661,7 @@
         <v>7</v>
       </c>
       <c r="N9" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4709,7 +4709,7 @@
         <v>7</v>
       </c>
       <c r="N10" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4757,7 +4757,7 @@
         <v>7</v>
       </c>
       <c r="N11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -4805,7 +4805,7 @@
         <v>7</v>
       </c>
       <c r="N12" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4853,7 +4853,7 @@
         <v>7</v>
       </c>
       <c r="N13" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4901,7 +4901,7 @@
         <v>7</v>
       </c>
       <c r="N14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -4949,7 +4949,7 @@
         <v>7</v>
       </c>
       <c r="N15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -4997,34 +4997,34 @@
         <v>7</v>
       </c>
       <c r="N16" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -5045,7 +5045,7 @@
         <v>7</v>
       </c>
       <c r="N17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5093,34 +5093,34 @@
         <v>7</v>
       </c>
       <c r="N18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -5141,7 +5141,7 @@
         <v>7</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -5189,73 +5189,73 @@
         <v>7</v>
       </c>
       <c r="N20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N21" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>7</v>
@@ -5285,7 +5285,7 @@
         <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5333,7 +5333,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2185,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2233,7 +2233,7 @@
         <v>72.56999999999999</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>90.67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -2281,7 +2281,7 @@
         <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>80.67</v>
+        <v>79.25</v>
       </c>
     </row>
     <row r="8">
@@ -2329,7 +2329,7 @@
         <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -2377,103 +2377,103 @@
         <v>48</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>47</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>41.43</v>
+        <v>42.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>37.67</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>37.67</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="12">
@@ -2521,55 +2521,55 @@
         <v>28.14</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>36.33</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>14.29</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>19.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.57</v>
+        <v>26.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>28.14</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>28.57</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>31.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>33</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>34.86</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.86</v>
+        <v>41.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>33.67</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>27.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>25.67</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="15">
@@ -2665,7 +2665,7 @@
         <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>25.67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -2713,151 +2713,151 @@
         <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>18</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E18" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>18</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15</v>
+        <v>24.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>23.43</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -2905,7 +2905,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>17.67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2953,7 +2953,7 @@
         <v>14.71</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>14.67</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="22">
@@ -3001,7 +3001,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>11.67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -3049,7 +3049,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="24">
@@ -3327,7 +3327,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3375,7 +3375,7 @@
         <v>82753547</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>41714755</v>
+        <v>53422329</v>
       </c>
     </row>
     <row r="7">
@@ -3423,7 +3423,7 @@
         <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>30134016</v>
+        <v>39117732</v>
       </c>
     </row>
     <row r="8">
@@ -3471,7 +3471,7 @@
         <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>28222893</v>
+        <v>40120472</v>
       </c>
     </row>
     <row r="9">
@@ -3519,103 +3519,103 @@
         <v>48824266</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>20488750</v>
+        <v>29786040</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58722069</v>
+        <v>58935844</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>16957120</v>
+        <v>22710940</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>18040161</v>
+        <v>22157473</v>
       </c>
     </row>
     <row r="12">
@@ -3663,55 +3663,55 @@
         <v>44250621</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>13030111</v>
+        <v>17474157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>15808893</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>14209578</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>30449860</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>32603120</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>35552907</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>31069118</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>40525338</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>42402722</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>42012092</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>58722069</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>14524483</v>
+        <v>20499240</v>
       </c>
     </row>
     <row r="14">
@@ -3759,7 +3759,7 @@
         <v>32069521</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>13473770</v>
+        <v>16274928</v>
       </c>
     </row>
     <row r="15">
@@ -3807,7 +3807,7 @@
         <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>11762022</v>
+        <v>13760742</v>
       </c>
     </row>
     <row r="16">
@@ -3855,151 +3855,151 @@
         <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>8307815</v>
+        <v>11156599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23623477</v>
+        <v>25387051</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>8153965</v>
+        <v>13898280</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>25387051</v>
+        <v>24539413</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>11240220</v>
+        <v>9970320</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>23623477</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>6565310</v>
+        <v>10058891</v>
       </c>
     </row>
     <row r="20">
@@ -4047,7 +4047,7 @@
         <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>16667400</v>
+        <v>21342730</v>
       </c>
     </row>
     <row r="21">
@@ -4095,7 +4095,7 @@
         <v>19628570</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>7396820</v>
+        <v>9649530</v>
       </c>
     </row>
     <row r="22">
@@ -4143,7 +4143,7 @@
         <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>2818984</v>
+        <v>3630774</v>
       </c>
     </row>
     <row r="23">
@@ -4191,7 +4191,7 @@
         <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>5866900</v>
+        <v>6741300</v>
       </c>
     </row>
     <row r="24">
@@ -4469,7 +4469,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4517,7 +4517,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4565,7 +4565,7 @@
         <v>7</v>
       </c>
       <c r="N7" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4613,7 +4613,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4661,28 +4661,28 @@
         <v>7</v>
       </c>
       <c r="N9" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4709,28 +4709,28 @@
         <v>7</v>
       </c>
       <c r="N10" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4757,7 +4757,7 @@
         <v>7</v>
       </c>
       <c r="N11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -4805,25 +4805,25 @@
         <v>7</v>
       </c>
       <c r="N12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>7</v>
       </c>
       <c r="N13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -4901,7 +4901,7 @@
         <v>7</v>
       </c>
       <c r="N14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -4949,7 +4949,7 @@
         <v>7</v>
       </c>
       <c r="N15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -4997,82 +4997,82 @@
         <v>7</v>
       </c>
       <c r="N16" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
         <v>4</v>
-      </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -5093,34 +5093,34 @@
         <v>7</v>
       </c>
       <c r="N18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -5141,7 +5141,7 @@
         <v>7</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -5189,7 +5189,7 @@
         <v>7</v>
       </c>
       <c r="N20" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -5237,7 +5237,7 @@
         <v>7</v>
       </c>
       <c r="N21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -5285,7 +5285,7 @@
         <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -5333,7 +5333,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2140,7 +2140,7 @@
       </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>13.07–19.07*</t>
+          <t>13.07–19.07</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2233,7 +2233,7 @@
         <v>72.56999999999999</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>90</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="7">
@@ -2281,7 +2281,7 @@
         <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>79.25</v>
+        <v>76.86</v>
       </c>
     </row>
     <row r="8">
@@ -2329,7 +2329,7 @@
         <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>63</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="9">
@@ -2377,439 +2377,439 @@
         <v>48</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>45.75</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>33.57</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>40</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>42.43</v>
+        <v>41.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>38.25</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>36.5</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.14</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>36.5</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>16.33</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>14.29</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>19.14</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>26.71</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="J13" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K13" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L13" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M13" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="H13" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>33</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="M13" s="36" t="n">
-        <v>41.43</v>
-      </c>
       <c r="N13" s="36" t="n">
-        <v>35.25</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.43</v>
+        <v>6.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.29</v>
+        <v>10.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>14.71</v>
+        <v>11.14</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>17</v>
+        <v>13.86</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>19.57</v>
+        <v>17.43</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.14</v>
+        <v>15.29</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>27.57</v>
+        <v>24.43</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.5</v>
+        <v>24.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>20.43</v>
+        <v>24.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.57</v>
+        <v>27.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>17.43</v>
+        <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15.29</v>
+        <v>20.43</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.43</v>
+        <v>24.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>23.25</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E17" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>20.75</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L18" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M18" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="L18" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M18" s="36" t="n">
-        <v>22.71</v>
-      </c>
       <c r="N18" s="36" t="n">
-        <v>20.25</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="19">
@@ -2857,103 +2857,103 @@
         <v>23.43</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>17</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>3.25</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>8</v>
+        <v>12.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>9.43</v>
+        <v>14.43</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>12.71</v>
+        <v>19</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>11.57</v>
+        <v>21.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>18.57</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>11.86</v>
+        <v>16.57</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>17</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I21" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H21" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I21" s="36" t="n">
+      <c r="J21" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M21" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N21" s="36" t="n">
         <v>19</v>
-      </c>
-      <c r="J21" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="M21" s="36" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <v>16.25</v>
       </c>
     </row>
     <row r="22">
@@ -3001,7 +3001,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>10</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3049,7 +3049,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.25</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="24">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>13.07–19.07*</t>
+          <t>13.07–19.07</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3375,7 +3375,7 @@
         <v>82753547</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>53422329</v>
+        <v>82566330</v>
       </c>
     </row>
     <row r="7">
@@ -3423,7 +3423,7 @@
         <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>39117732</v>
+        <v>69757179</v>
       </c>
     </row>
     <row r="8">
@@ -3471,7 +3471,7 @@
         <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>40120472</v>
+        <v>58190202</v>
       </c>
     </row>
     <row r="9">
@@ -3519,439 +3519,439 @@
         <v>48824266</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>29786040</v>
+        <v>57556194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>39462393</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51983942</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58935844</v>
+        <v>58722069</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>22710940</v>
+        <v>48135084</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>22157473</v>
+        <v>38454971</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>44250621</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>17474157</v>
+        <v>35343350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>9458306</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>15808893</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14209578</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>30449860</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32603120</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>35552907</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>31069118</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>40525338</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>42402722</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>42012092</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>58722069</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>20499240</v>
+        <v>29608597</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11884771</v>
+        <v>5092853</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>10651216</v>
+        <v>11100161</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>13882033</v>
+        <v>14612055</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>17812948</v>
+        <v>20638987</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>17331854</v>
+        <v>14061352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>26294756</v>
+        <v>31599148</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>24196222</v>
+        <v>18747614</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>22122847</v>
+        <v>19576415</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>31914115</v>
+        <v>14226838</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>32069521</v>
+        <v>23197145</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>16274928</v>
+        <v>25790711</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>22122847</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>31914115</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>32069521</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>13760742</v>
+        <v>38287475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>19576415</v>
+        <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>14226838</v>
+        <v>27940611</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23197145</v>
+        <v>27893929</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>11156599</v>
+        <v>29635773</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>25387051</v>
+        <v>24539413</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>13898280</v>
+        <v>19087217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13949368</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>24539413</v>
+        <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>9970320</v>
+        <v>21008637</v>
       </c>
     </row>
     <row r="19">
@@ -3999,103 +3999,103 @@
         <v>23623477</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>10058891</v>
+        <v>19145601</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1324510</v>
+        <v>21387685</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>10311989</v>
+        <v>16050448</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19934535</v>
+        <v>21568794</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>13536614</v>
+        <v>30845816</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>22187720</v>
+        <v>45285935</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>11732010</v>
+        <v>28941455</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21143100</v>
+        <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>14330970</v>
+        <v>19628570</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>21342730</v>
+        <v>23276090</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>9649530</v>
+        <v>38267409</v>
       </c>
     </row>
     <row r="22">
@@ -4143,7 +4143,7 @@
         <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>3630774</v>
+        <v>6102368</v>
       </c>
     </row>
     <row r="23">
@@ -4191,7 +4191,7 @@
         <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>6741300</v>
+        <v>9234090</v>
       </c>
     </row>
     <row r="24">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>13.07–19.07*</t>
+          <t>13.07–19.07</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
         <v>7</v>
       </c>
       <c r="N5" s="34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4517,7 +4517,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4565,7 +4565,7 @@
         <v>7</v>
       </c>
       <c r="N7" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -4613,7 +4613,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4661,28 +4661,28 @@
         <v>7</v>
       </c>
       <c r="N9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -4709,28 +4709,28 @@
         <v>7</v>
       </c>
       <c r="N10" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4757,25 +4757,25 @@
         <v>7</v>
       </c>
       <c r="N11" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4805,22 +4805,22 @@
         <v>7</v>
       </c>
       <c r="N12" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
         <v>7</v>
@@ -4853,25 +4853,25 @@
         <v>7</v>
       </c>
       <c r="N13" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4901,18 +4901,18 @@
         <v>7</v>
       </c>
       <c r="N14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -4949,25 +4949,25 @@
         <v>7</v>
       </c>
       <c r="N15" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -4997,34 +4997,34 @@
         <v>7</v>
       </c>
       <c r="N16" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -5045,34 +5045,34 @@
         <v>7</v>
       </c>
       <c r="N17" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -5093,7 +5093,7 @@
         <v>7</v>
       </c>
       <c r="N18" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -5141,31 +5141,31 @@
         <v>7</v>
       </c>
       <c r="N19" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -5189,31 +5189,31 @@
         <v>7</v>
       </c>
       <c r="N20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -5237,7 +5237,7 @@
         <v>7</v>
       </c>
       <c r="N21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -5285,7 +5285,7 @@
         <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -5333,7 +5333,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1977,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1994,6 +1994,7 @@
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
+    <col width="13" customWidth="1" style="20" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2071,6 +2072,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2141,6 +2147,11 @@
       <c r="N4" s="31" t="inlineStr">
         <is>
           <t>13.07–19.07</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>20.07–26.07*</t>
         </is>
       </c>
     </row>
@@ -2187,101 +2198,110 @@
       <c r="N5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="O5" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>31.14</v>
+        <v>29.43</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>41.14</v>
+        <v>38</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>36.43</v>
+        <v>41.29</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>52.71</v>
+        <v>51.43</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>67.43000000000001</v>
+        <v>58.29</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>61.14</v>
+        <v>63</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>66.14</v>
+        <v>55.43</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>72.56999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>77.86</v>
+        <v>76.86</v>
+      </c>
+      <c r="O6" s="36" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>31.14</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>38</v>
+        <v>41.14</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>41.29</v>
+        <v>36.43</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>51.43</v>
+        <v>52.71</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>58.29</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>63</v>
+        <v>61.14</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>66.14</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>77.86</v>
+      </c>
+      <c r="O7" s="36" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -2331,149 +2351,161 @@
       <c r="N8" s="36" t="n">
         <v>53.71</v>
       </c>
+      <c r="O8" s="36" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>8.43</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>13.43</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>21.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>16.57</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38</v>
+        <v>21.29</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>39.71</v>
+        <v>21.14</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>41.71</v>
+        <v>23.29</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>35.14</v>
+        <v>22.43</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41</v>
+        <v>22.43</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>48</v>
+        <v>28.14</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>49.43</v>
+        <v>31.14</v>
+      </c>
+      <c r="O9" s="36" t="n">
+        <v>40.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>41</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>41.43</v>
+        <v>48</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>46.14</v>
+        <v>49.43</v>
+      </c>
+      <c r="O10" s="36" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>12.43</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>13.29</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>14.71</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>17</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>19.71</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>17.71</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>19.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>24.14</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>27.57</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>38.57</v>
+        <v>24.43</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="12">
@@ -2523,149 +2555,161 @@
       <c r="N12" s="36" t="n">
         <v>33.14</v>
       </c>
+      <c r="O12" s="36" t="n">
+        <v>31.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>16.33</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>14.29</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>19.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>26.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>28.14</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>28.57</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>31.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>33</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>34.86</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>41.29</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>41.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>31.14</v>
+        <v>46.14</v>
+      </c>
+      <c r="O13" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>6.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>18</v>
+        <v>17.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>18</v>
+        <v>16.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>17.43</v>
+        <v>18.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>15.29</v>
+        <v>16.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>24.43</v>
+        <v>21.71</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.71</v>
+        <v>20.86</v>
+      </c>
+      <c r="O14" s="36" t="n">
+        <v>29.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>6.67</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>10.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>11.14</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>13.86</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>17.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.14</v>
+        <v>15.29</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>27.57</v>
+        <v>24.43</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.43</v>
+        <v>24.71</v>
+      </c>
+      <c r="O15" s="36" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2715,208 +2759,223 @@
       <c r="N16" s="36" t="n">
         <v>24.14</v>
       </c>
+      <c r="O16" s="36" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15</v>
+        <v>16.57</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>22.71</v>
+        <v>14.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>22.43</v>
+        <v>19.14</v>
+      </c>
+      <c r="O17" s="36" t="n">
+        <v>23.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3.33</v>
+        <v>7</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>6.43</v>
+        <v>16</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>14.86</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>16.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>19.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>24.86</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21.71</v>
+        <v>23.43</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>20.86</v>
+        <v>19.43</v>
+      </c>
+      <c r="O18" s="36" t="n">
+        <v>22.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F19" s="36" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="G19" s="36" t="n">
         <v>19.43</v>
       </c>
-      <c r="G19" s="36" t="n">
-        <v>15.86</v>
-      </c>
       <c r="H19" s="36" t="n">
-        <v>14.86</v>
+        <v>26.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>16.71</v>
+        <v>32.29</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>19.71</v>
+        <v>31.29</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>16.86</v>
+        <v>33.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>24.86</v>
+        <v>40</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>23.43</v>
+        <v>42.43</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19.43</v>
+        <v>38.57</v>
+      </c>
+      <c r="O19" s="36" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I20" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H20" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I20" s="36" t="n">
+      <c r="J20" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L20" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M20" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N20" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="J20" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K20" s="36" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="M20" s="36" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="N20" s="36" t="n">
-        <v>19.14</v>
+      <c r="O20" s="36" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
@@ -2929,127 +2988,136 @@
         <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>3.33</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>11.71</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>17.57</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>20.43</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>21.71</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11.86</v>
+        <v>15</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>22.71</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>19</v>
+        <v>22.43</v>
+      </c>
+      <c r="O21" s="36" t="n">
+        <v>18.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
+      </c>
+      <c r="O22" s="36" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
+      </c>
+      <c r="O23" s="36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -3105,6 +3173,10 @@
       </c>
       <c r="N24" s="39">
         <f>AVERAGE(N6:N23)</f>
+        <v/>
+      </c>
+      <c r="O24" s="39">
+        <f>AVERAGE(O6:O23)</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3136,6 +3208,7 @@
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
+    <col width="13" customWidth="1" style="20" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3213,6 +3286,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3283,6 +3361,11 @@
       <c r="N4" s="31" t="inlineStr">
         <is>
           <t>13.07–19.07</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>20.07–26.07*</t>
         </is>
       </c>
     </row>
@@ -3329,101 +3412,110 @@
       <c r="N5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="O5" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>8596643</v>
+        <v>6122227</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>30622284</v>
+        <v>31792625</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>33277426</v>
+        <v>49374899</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>40259616</v>
+        <v>38585414</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>54390985</v>
+        <v>51458725</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>72727058</v>
+        <v>61835892</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>61910106</v>
+        <v>80551167</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>72409127</v>
+        <v>61490143</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>72256071</v>
+        <v>68619843</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>82753547</v>
+        <v>81742671</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>82566330</v>
+        <v>69757179</v>
+      </c>
+      <c r="O6" s="40" t="n">
+        <v>17588842</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>8596643</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>30622284</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>33277426</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>40259616</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>54390985</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>72727058</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>61910106</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>72409127</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>72256071</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>82753547</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>82566330</v>
+      </c>
+      <c r="O7" s="40" t="n">
+        <v>16029470</v>
       </c>
     </row>
     <row r="8">
@@ -3473,149 +3565,161 @@
       <c r="N8" s="40" t="n">
         <v>58190202</v>
       </c>
+      <c r="O8" s="40" t="n">
+        <v>11574371</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>10351067</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>21091580</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>24243567</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>16381412</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>21591272</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>21904190</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>25438080</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>43259404</v>
+        <v>24614280</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>68694825</v>
+        <v>28889771</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>48824266</v>
+        <v>44250621</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>57556194</v>
+        <v>29608597</v>
+      </c>
+      <c r="O9" s="40" t="n">
+        <v>10057272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>68694825</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58722069</v>
+        <v>48824266</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>48135084</v>
+        <v>57556194</v>
+      </c>
+      <c r="O10" s="40" t="n">
+        <v>10460360</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>11884771</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>10651216</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>13882033</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>17812948</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>17331854</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>26294756</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>24196222</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>22122847</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>31914115</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>32069521</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>38287475</v>
+      </c>
+      <c r="O11" s="40" t="n">
+        <v>7842397</v>
       </c>
     </row>
     <row r="12">
@@ -3665,149 +3769,161 @@
       <c r="N12" s="40" t="n">
         <v>35343350</v>
       </c>
+      <c r="O12" s="40" t="n">
+        <v>14635500</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>9458306</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>15808893</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>14209578</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>30449860</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>32603120</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>35552907</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>31069118</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>40525338</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>42402722</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>42012092</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>58722069</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>48135084</v>
+      </c>
+      <c r="O13" s="40" t="n">
+        <v>11038350</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>5092853</v>
+        <v>3249588</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11100161</v>
+        <v>7305524</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>14612055</v>
+        <v>9575225</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20638987</v>
+        <v>9264589</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>14061352</v>
+        <v>20692424</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31599148</v>
+        <v>27565767</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>18747614</v>
+        <v>19138015</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>19576415</v>
+        <v>24912292</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>14226838</v>
+        <v>19068954</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>23197145</v>
+        <v>25387051</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>25790711</v>
+        <v>21008637</v>
+      </c>
+      <c r="O14" s="40" t="n">
+        <v>9849000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>5092853</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>11100161</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>14612055</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>20638987</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>14061352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>31599148</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>18747614</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>19576415</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>31914115</v>
+        <v>14226838</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>32069521</v>
+        <v>23197145</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38287475</v>
+        <v>25790711</v>
+      </c>
+      <c r="O15" s="40" t="n">
+        <v>6793654</v>
       </c>
     </row>
     <row r="16">
@@ -3857,208 +3973,223 @@
       <c r="N16" s="40" t="n">
         <v>29635773</v>
       </c>
+      <c r="O16" s="40" t="n">
+        <v>5437559</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>21801828</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>24539413</v>
+        <v>19628570</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19087217</v>
+        <v>23276090</v>
+      </c>
+      <c r="O17" s="40" t="n">
+        <v>11009344</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>6239584</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>13803407</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>28572076</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>15282581</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>16594572</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>15223898</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>27696695</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>17717888</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>24163432</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>25387051</v>
+        <v>23623477</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>21008637</v>
+        <v>19145601</v>
+      </c>
+      <c r="O18" s="40" t="n">
+        <v>6424443</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>13803407</v>
+        <v>8972650</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>28572076</v>
+        <v>18100396</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>15282581</v>
+        <v>23988817</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>16594572</v>
+        <v>22409732</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>15223898</v>
+        <v>37715520</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>27696695</v>
+        <v>35926824</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>17717888</v>
+        <v>39462393</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>24163432</v>
+        <v>51983942</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>23623477</v>
+        <v>58935844</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19145601</v>
+        <v>38454971</v>
+      </c>
+      <c r="O19" s="40" t="n">
+        <v>6872561</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>23276090</v>
+        <v>38267409</v>
+      </c>
+      <c r="O20" s="40" t="n">
+        <v>6763300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
@@ -4071,127 +4202,136 @@
         <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>363900</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>3736700</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>17796776</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>42724228</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>33036620</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>11732010</v>
+        <v>29649130</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21143100</v>
+        <v>13949368</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>14330970</v>
+        <v>24539413</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>38267409</v>
+        <v>19087217</v>
+      </c>
+      <c r="O21" s="40" t="n">
+        <v>6972480</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
+      </c>
+      <c r="O22" s="40" t="n">
+        <v>2369350</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
+      </c>
+      <c r="O23" s="40" t="n">
+        <v>248760</v>
       </c>
     </row>
     <row r="24">
@@ -4247,6 +4387,10 @@
       </c>
       <c r="N24" s="41">
         <f>AVERAGE(N6:N23)</f>
+        <v/>
+      </c>
+      <c r="O24" s="41">
+        <f>AVERAGE(O6:O23)</f>
         <v/>
       </c>
     </row>
@@ -4261,7 +4405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4278,6 +4422,7 @@
     <col width="13" customWidth="1" style="20" min="12" max="12"/>
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
+    <col width="13" customWidth="1" style="20" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4355,6 +4500,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4425,6 +4575,11 @@
       <c r="N4" s="31" t="inlineStr">
         <is>
           <t>13.07–19.07</t>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>20.07–26.07*</t>
         </is>
       </c>
     </row>
@@ -4471,16 +4626,19 @@
       <c r="N5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="O5" s="34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -4519,16 +4677,19 @@
       <c r="N6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="O6" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
@@ -4567,6 +4728,9 @@
       <c r="N7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="O7" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -4615,23 +4779,26 @@
       <c r="N8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="O8" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4662,24 +4829,27 @@
       </c>
       <c r="N9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O9" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -4710,27 +4880,30 @@
       </c>
       <c r="N10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O10" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4758,6 +4931,9 @@
       </c>
       <c r="N11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O11" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4807,20 +4983,23 @@
       <c r="N12" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="O12" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="42" t="n">
         <v>7</v>
@@ -4854,24 +5033,27 @@
       </c>
       <c r="N13" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -4902,54 +5084,60 @@
       </c>
       <c r="N14" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O14" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N15" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4999,71 +5187,77 @@
       <c r="N16" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="O16" s="42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -5094,27 +5288,30 @@
       </c>
       <c r="N18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O18" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" s="42" t="n">
         <v>7</v>
@@ -5142,30 +5339,33 @@
       </c>
       <c r="N19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O19" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -5190,17 +5390,20 @@
       </c>
       <c r="N20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O20" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
@@ -5213,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" s="42" t="n">
         <v>7</v>
@@ -5238,30 +5441,33 @@
       </c>
       <c r="N21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O21" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -5282,34 +5488,37 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O22" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -5330,10 +5539,13 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="O23" s="42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -5391,6 +5603,10 @@
         <f>AVERAGE(N6:N23)</f>
         <v/>
       </c>
+      <c r="O24" s="43">
+        <f>AVERAGE(O6:O23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2199,109 +2199,109 @@
         <v>7</v>
       </c>
       <c r="O5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>29.43</v>
+        <v>31.14</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>38</v>
+        <v>41.14</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>41.29</v>
+        <v>36.43</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>51.43</v>
+        <v>52.71</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>58.29</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>63</v>
+        <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>55.43</v>
+        <v>66.14</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>76.86</v>
+        <v>77.86</v>
       </c>
       <c r="O6" s="36" t="n">
-        <v>60</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>31.14</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>41.14</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>36.43</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>52.71</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>67.43000000000001</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>61.14</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>66.14</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>72.56999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>77.86</v>
+        <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -2352,466 +2352,466 @@
         <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>43</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>8.43</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>13.43</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.71</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>16.57</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>21.29</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>21.14</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>23.29</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>22.43</v>
+        <v>35.14</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>22.43</v>
+        <v>41</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>28.14</v>
+        <v>48</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>31.14</v>
+        <v>49.43</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>40.5</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>8.43</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>13.43</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>21.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>16.57</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>21.29</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>21.14</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>23.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>22.43</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41</v>
+        <v>22.43</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>48</v>
+        <v>28.14</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>49.43</v>
+        <v>31.14</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>38</v>
+        <v>34.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>2.5</v>
+        <v>16.33</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>9.43</v>
+        <v>14.29</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>12.43</v>
+        <v>19.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.29</v>
+        <v>26.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>14.71</v>
+        <v>28.14</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>17</v>
+        <v>28.57</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>19.71</v>
+        <v>31.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>17.71</v>
+        <v>33</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>19.57</v>
+        <v>34.86</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>24.14</v>
+        <v>41.29</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>27.57</v>
+        <v>41.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>24.43</v>
+        <v>46.14</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>32.5</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>9.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.29</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>14.71</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>17</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>19.71</v>
       </c>
       <c r="J12" s="36" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="L12" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="K12" s="36" t="n">
+      <c r="M12" s="36" t="n">
         <v>27.57</v>
       </c>
-      <c r="L12" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="M12" s="36" t="n">
-        <v>28.86</v>
-      </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>24.43</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>31.5</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>14.29</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>19.14</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>26.71</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="J13" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="K13" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="L13" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="H13" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>33</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>41.29</v>
-      </c>
       <c r="M13" s="36" t="n">
-        <v>41.43</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>46.14</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>6.43</v>
+        <v>8</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.14</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>14</v>
+        <v>26.43</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>17.14</v>
+        <v>32.29</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>16.14</v>
+        <v>31.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>18.57</v>
+        <v>33.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>16.14</v>
+        <v>40</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>21.71</v>
+        <v>42.43</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>20.86</v>
+        <v>38.57</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>29.5</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>17.43</v>
+        <v>23.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>15.29</v>
+        <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.43</v>
+        <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.71</v>
+        <v>24.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>28</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.43</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.86</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I16" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="36" t="n">
-        <v>19.14</v>
-      </c>
       <c r="J16" s="36" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>23.43</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>20.43</v>
+        <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.57</v>
+        <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.14</v>
+        <v>24.71</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>16.14</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>14.71</v>
+        <v>21.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.14</v>
+        <v>20.86</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>23.5</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="18">
@@ -2862,58 +2862,58 @@
         <v>19.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>8</v>
+        <v>7.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.14</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>19.43</v>
+        <v>12.71</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>26.43</v>
+        <v>14.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>32.29</v>
+        <v>19</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>31.29</v>
+        <v>21.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>33.57</v>
+        <v>18.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>40</v>
+        <v>16.57</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>42.43</v>
+        <v>14.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>38.57</v>
+        <v>19.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>22</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="20">
@@ -2964,7 +2964,7 @@
         <v>19</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>22</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="21">
@@ -3015,7 +3015,7 @@
         <v>22.43</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>18.5</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="22">
@@ -3066,7 +3066,7 @@
         <v>7.43</v>
       </c>
       <c r="O22" s="36" t="n">
-        <v>8</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="23">
@@ -3117,7 +3117,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="O23" s="36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3413,109 +3413,109 @@
         <v>7</v>
       </c>
       <c r="O5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>6122227</v>
+        <v>8596643</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>31792625</v>
+        <v>30622284</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>49374899</v>
+        <v>33277426</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>38585414</v>
+        <v>40259616</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>51458725</v>
+        <v>54390985</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>61835892</v>
+        <v>72727058</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>80551167</v>
+        <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>61490143</v>
+        <v>72409127</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>68619843</v>
+        <v>72256071</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>81742671</v>
+        <v>82753547</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>69757179</v>
+        <v>82566330</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>17588842</v>
+        <v>30612327</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>8596643</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>30622284</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>33277426</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>40259616</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>54390985</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>72727058</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>61910106</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>72409127</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>72256071</v>
+        <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>82753547</v>
+        <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>82566330</v>
+        <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>16029470</v>
+        <v>28585252</v>
       </c>
     </row>
     <row r="8">
@@ -3566,466 +3566,466 @@
         <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>11574371</v>
+        <v>18323741</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>10351067</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>21091580</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>24243567</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>16381412</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>21591272</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>21904190</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>25438080</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>24614280</v>
+        <v>43259404</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>28889771</v>
+        <v>68694825</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>44250621</v>
+        <v>48824266</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>29608597</v>
+        <v>57556194</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>10057272</v>
+        <v>15476802</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>10351067</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>21091580</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>24243567</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>16381412</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>21591272</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>21904190</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>25438080</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>24614280</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>68694825</v>
+        <v>28889771</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>48824266</v>
+        <v>44250621</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>57556194</v>
+        <v>29608597</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>10460360</v>
+        <v>12873512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>475871</v>
+        <v>9458306</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>11884771</v>
+        <v>15808893</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>10651216</v>
+        <v>14209578</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>13882033</v>
+        <v>30449860</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>17812948</v>
+        <v>32603120</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>17331854</v>
+        <v>35552907</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>26294756</v>
+        <v>31069118</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>24196222</v>
+        <v>40525338</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>22122847</v>
+        <v>42402722</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>31914115</v>
+        <v>42012092</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>32069521</v>
+        <v>58722069</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38287475</v>
+        <v>48135084</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>7842397</v>
+        <v>17271936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>11884771</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>10651216</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>13882033</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>17812948</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>17331854</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>26294756</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>24196222</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>22122847</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>31914115</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>32069521</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>38287475</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>14635500</v>
+        <v>15828687</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>15808893</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14209578</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>30449860</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32603120</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>35552907</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>31069118</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>40525338</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>42402722</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>42012092</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>58722069</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>48135084</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>11038350</v>
+        <v>19172470</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>7305524</v>
+        <v>8972650</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>9575225</v>
+        <v>18100396</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>9264589</v>
+        <v>23988817</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>20692424</v>
+        <v>22409732</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>27565767</v>
+        <v>37715520</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>19138015</v>
+        <v>35926824</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>24912292</v>
+        <v>39462393</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>19068954</v>
+        <v>51983942</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>25387051</v>
+        <v>58935844</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>21008637</v>
+        <v>38454971</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>9849000</v>
+        <v>18165981</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>19576415</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>14226838</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>23197145</v>
+        <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>25790711</v>
+        <v>29635773</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>6793654</v>
+        <v>9207569</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>8544625</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>8387478</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10570508</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>11896580</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19614352</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>20966317</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>20073400</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>23801493</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>27940611</v>
+        <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>27893929</v>
+        <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>29635773</v>
+        <v>25790711</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>5437559</v>
+        <v>10026304</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>19068954</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>19628570</v>
+        <v>25387051</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>23276090</v>
+        <v>21008637</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>11009344</v>
+        <v>12605990</v>
       </c>
     </row>
     <row r="18">
@@ -4076,58 +4076,58 @@
         <v>19145601</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>6424443</v>
+        <v>9908447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>8972650</v>
+        <v>10420206</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>18100396</v>
+        <v>21387685</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>23988817</v>
+        <v>16050448</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>22409732</v>
+        <v>21568794</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>37715520</v>
+        <v>30845816</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>35926824</v>
+        <v>45285935</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>39462393</v>
+        <v>28941455</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>51983942</v>
+        <v>21801828</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>58935844</v>
+        <v>19628570</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38454971</v>
+        <v>23276090</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>6872561</v>
+        <v>13650224</v>
       </c>
     </row>
     <row r="20">
@@ -4178,7 +4178,7 @@
         <v>38267409</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>6763300</v>
+        <v>18766604</v>
       </c>
     </row>
     <row r="21">
@@ -4229,7 +4229,7 @@
         <v>19087217</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>6972480</v>
+        <v>8953300</v>
       </c>
     </row>
     <row r="22">
@@ -4280,7 +4280,7 @@
         <v>9234090</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>2369350</v>
+        <v>2728810</v>
       </c>
     </row>
     <row r="23">
@@ -4331,7 +4331,7 @@
         <v>6102368</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>248760</v>
+        <v>1576570</v>
       </c>
     </row>
     <row r="24">
@@ -4627,18 +4627,18 @@
         <v>7</v>
       </c>
       <c r="O5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -4678,18 +4678,18 @@
         <v>7</v>
       </c>
       <c r="O6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
@@ -4729,7 +4729,7 @@
         <v>7</v>
       </c>
       <c r="O7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4780,25 +4780,25 @@
         <v>7</v>
       </c>
       <c r="O8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -4831,25 +4831,25 @@
         <v>7</v>
       </c>
       <c r="O9" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -4882,22 +4882,22 @@
         <v>7</v>
       </c>
       <c r="O10" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="42" t="n">
         <v>7</v>
@@ -4933,77 +4933,77 @@
         <v>7</v>
       </c>
       <c r="O11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
       </c>
@@ -5035,76 +5035,76 @@
         <v>7</v>
       </c>
       <c r="O13" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5137,25 +5137,25 @@
         <v>7</v>
       </c>
       <c r="O15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5188,25 +5188,25 @@
         <v>7</v>
       </c>
       <c r="O16" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5239,7 +5239,7 @@
         <v>7</v>
       </c>
       <c r="O17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5290,28 +5290,28 @@
         <v>7</v>
       </c>
       <c r="O18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
         <v>7</v>
@@ -5341,7 +5341,7 @@
         <v>7</v>
       </c>
       <c r="O19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -5392,7 +5392,7 @@
         <v>7</v>
       </c>
       <c r="O20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -5443,7 +5443,7 @@
         <v>7</v>
       </c>
       <c r="O21" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -5494,7 +5494,7 @@
         <v>7</v>
       </c>
       <c r="O22" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5545,7 +5545,7 @@
         <v>7</v>
       </c>
       <c r="O23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O4" s="31" t="inlineStr">
         <is>
-          <t>20.07–26.07*</t>
+          <t>20.07–26.07</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         <v>7</v>
       </c>
       <c r="O5" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2250,7 +2250,7 @@
         <v>77.86</v>
       </c>
       <c r="O6" s="36" t="n">
-        <v>65.33</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2301,7 +2301,7 @@
         <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64</v>
+        <v>64.29000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2352,7 +2352,7 @@
         <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>44.67</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="9">
@@ -2403,313 +2403,313 @@
         <v>49.43</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>42.67</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>2</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>8.43</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>13.43</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.71</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>16.57</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>21.29</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>21.14</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>23.29</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>22.43</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>22.43</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>28.14</v>
+        <v>41.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>31.14</v>
+        <v>46.14</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>34.67</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>41.43</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>46.14</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>32.33</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>9.43</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.43</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.29</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>14.71</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>17</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>19.71</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>17.71</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>19.57</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>24.14</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>27.57</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>24.43</v>
+        <v>33.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>31.33</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G13" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G13" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M13" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="M13" s="36" t="n">
-        <v>28.86</v>
-      </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>31.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>8</v>
+        <v>12.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.14</v>
+        <v>13.29</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>19.43</v>
+        <v>14.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>26.43</v>
+        <v>17</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>32.29</v>
+        <v>19.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>31.29</v>
+        <v>17.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>33.57</v>
+        <v>19.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>40</v>
+        <v>24.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>42.43</v>
+        <v>27.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>38.57</v>
+        <v>24.43</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>28.67</v>
+        <v>27.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>7</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>19.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>15.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>16.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>19.71</v>
       </c>
       <c r="K15" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L15" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="M15" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="L15" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M15" s="36" t="n">
-        <v>24.57</v>
-      </c>
       <c r="N15" s="36" t="n">
-        <v>24.14</v>
+        <v>19.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>28.67</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="16">
@@ -2760,160 +2760,160 @@
         <v>24.71</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>26</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>6.43</v>
+        <v>11</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>14.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>19.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>21</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>21.71</v>
+        <v>24.57</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>20.86</v>
+        <v>24.14</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>25.33</v>
+        <v>24.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19.43</v>
+        <v>20.86</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>25</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>12.71</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.43</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21.14</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>16.57</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>14.71</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19.14</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>23.67</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="20">
@@ -2964,157 +2964,157 @@
         <v>19</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>20.33</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>15</v>
+        <v>16.57</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>22.71</v>
+        <v>14.71</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>22.43</v>
+        <v>19.14</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>18.67</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O22" s="36" t="n">
-        <v>6.33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H23" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="O4" s="31" t="inlineStr">
         <is>
-          <t>20.07–26.07*</t>
+          <t>20.07–26.07</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
         <v>7</v>
       </c>
       <c r="O5" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3464,7 +3464,7 @@
         <v>82566330</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>30612327</v>
+        <v>96616423</v>
       </c>
     </row>
     <row r="7">
@@ -3515,7 +3515,7 @@
         <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>28585252</v>
+        <v>68198708</v>
       </c>
     </row>
     <row r="8">
@@ -3566,7 +3566,7 @@
         <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>18323741</v>
+        <v>46275213</v>
       </c>
     </row>
     <row r="9">
@@ -3617,313 +3617,313 @@
         <v>57556194</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>15476802</v>
+        <v>38323101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>251520</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>10351067</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>21091580</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>24243567</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>16381412</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>21591272</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>21904190</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>25438080</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>24614280</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>28889771</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>44250621</v>
+        <v>58722069</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>29608597</v>
+        <v>48135084</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>12873512</v>
+        <v>44293878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58722069</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>48135084</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>17271936</v>
+        <v>42939312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>11884771</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>10651216</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>13882033</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>17812948</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>17331854</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>26294756</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>24196222</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>22122847</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>31914115</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>32069521</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38287475</v>
+        <v>35343350</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>15828687</v>
+        <v>51225290</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>29608597</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>19172470</v>
+        <v>25219748</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>0</v>
+        <v>11884771</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>8972650</v>
+        <v>10651216</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>18100396</v>
+        <v>13882033</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>23988817</v>
+        <v>17812948</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>22409732</v>
+        <v>17331854</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37715520</v>
+        <v>26294756</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>35926824</v>
+        <v>24196222</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>39462393</v>
+        <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>51983942</v>
+        <v>31914115</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>58935844</v>
+        <v>32069521</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>38454971</v>
+        <v>38287475</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>18165981</v>
+        <v>28283704</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>6239584</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>13803407</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>28572076</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>15282581</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>16594572</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>15223898</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>27696695</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>17717888</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>24163432</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>23623477</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29635773</v>
+        <v>19145601</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>9207569</v>
+        <v>30157601</v>
       </c>
     </row>
     <row r="16">
@@ -3974,160 +3974,160 @@
         <v>25790711</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>10026304</v>
+        <v>27856115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>8544625</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>8387478</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>10570508</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>11896580</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>19614352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>20966317</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>20073400</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>23801493</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>19068954</v>
+        <v>27940611</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>25387051</v>
+        <v>27893929</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>21008637</v>
+        <v>29635773</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>12605990</v>
+        <v>19554230</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>23623477</v>
+        <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19145601</v>
+        <v>21008637</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>9908447</v>
+        <v>30862574</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>21387685</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16050448</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>21568794</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>30845816</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>45285935</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>28941455</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21801828</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>19628570</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>23276090</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>13650224</v>
+        <v>17139440</v>
       </c>
     </row>
     <row r="20">
@@ -4178,160 +4178,160 @@
         <v>38267409</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>18766604</v>
+        <v>46351274</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>13949368</v>
+        <v>21801828</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>24539413</v>
+        <v>19628570</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>19087217</v>
+        <v>23276090</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>8953300</v>
+        <v>27906254</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>2728810</v>
+        <v>4294070</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>1576570</v>
+        <v>5390260</v>
       </c>
     </row>
     <row r="24">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="O4" s="31" t="inlineStr">
         <is>
-          <t>20.07–26.07*</t>
+          <t>20.07–26.07</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
         <v>7</v>
       </c>
       <c r="O5" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4678,7 +4678,7 @@
         <v>7</v>
       </c>
       <c r="O6" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4729,7 +4729,7 @@
         <v>7</v>
       </c>
       <c r="O7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -4780,7 +4780,7 @@
         <v>7</v>
       </c>
       <c r="O8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -4831,22 +4831,22 @@
         <v>7</v>
       </c>
       <c r="O9" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
         <v>7</v>
@@ -4882,28 +4882,28 @@
         <v>7</v>
       </c>
       <c r="O10" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4933,25 +4933,25 @@
         <v>7</v>
       </c>
       <c r="O11" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -4984,25 +4984,25 @@
         <v>7</v>
       </c>
       <c r="O12" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -5035,28 +5035,28 @@
         <v>7</v>
       </c>
       <c r="O13" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>7</v>
@@ -5086,25 +5086,25 @@
         <v>7</v>
       </c>
       <c r="O14" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5137,7 +5137,7 @@
         <v>7</v>
       </c>
       <c r="O15" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -5188,25 +5188,25 @@
         <v>7</v>
       </c>
       <c r="O16" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5239,25 +5239,25 @@
         <v>7</v>
       </c>
       <c r="O17" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -5290,34 +5290,34 @@
         <v>7</v>
       </c>
       <c r="O18" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -5341,7 +5341,7 @@
         <v>7</v>
       </c>
       <c r="O19" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -5392,34 +5392,34 @@
         <v>7</v>
       </c>
       <c r="O20" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="42" t="n">
         <v>7</v>
@@ -5443,31 +5443,31 @@
         <v>7</v>
       </c>
       <c r="O21" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -5488,37 +5488,37 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
       </c>
       <c r="O22" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -5539,13 +5539,13 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
       </c>
       <c r="O23" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1977,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -1995,6 +1995,7 @@
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
+    <col width="13" customWidth="1" style="20" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2077,6 +2078,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2152,6 +2158,11 @@
       <c r="O4" s="31" t="inlineStr">
         <is>
           <t>20.07–26.07</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>27.07–02.08*</t>
         </is>
       </c>
     </row>
@@ -2201,6 +2212,9 @@
       <c r="O5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="P5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2252,107 +2266,116 @@
       <c r="O6" s="36" t="n">
         <v>74.56999999999999</v>
       </c>
+      <c r="P6" s="36" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>14.29</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>19.14</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>38</v>
+        <v>26.71</v>
       </c>
       <c r="G7" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
+        <v>33</v>
+      </c>
+      <c r="K7" s="36" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="L7" s="36" t="n">
         <v>41.29</v>
       </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
-      <c r="K7" s="36" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
-      </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>41.43</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>46.14</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>41.57</v>
+      </c>
+      <c r="P7" s="36" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
+      </c>
+      <c r="P8" s="36" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -2405,209 +2428,224 @@
       <c r="O9" s="36" t="n">
         <v>45.57</v>
       </c>
+      <c r="P9" s="36" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>7.33</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>17.86</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>22.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>24.86</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>36.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>43.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>50.14</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>41.43</v>
+        <v>59</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>46.14</v>
+        <v>53.71</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>41.57</v>
+        <v>46.57</v>
+      </c>
+      <c r="P10" s="36" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>23.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>22.43</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>22.43</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>28.14</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>38.57</v>
+        <v>31.14</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>34.29</v>
+        <v>30</v>
+      </c>
+      <c r="P11" s="36" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
+      </c>
+      <c r="P12" s="36" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>31.14</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30</v>
+        <v>30.71</v>
+      </c>
+      <c r="P13" s="36" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -2660,271 +2698,289 @@
       <c r="O14" s="36" t="n">
         <v>27.29</v>
       </c>
+      <c r="P14" s="36" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>7</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>19.43</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>15.86</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14.86</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>16.71</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>19.71</v>
+        <v>21</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>16.86</v>
+        <v>23.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.86</v>
+        <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>23.43</v>
+        <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>19.43</v>
+        <v>24.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>25.57</v>
+        <v>24.43</v>
+      </c>
+      <c r="P15" s="36" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>16</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10.57</v>
+        <v>19.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.14</v>
+        <v>15.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>13.86</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>18</v>
+        <v>16.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>18</v>
+        <v>19.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>17.43</v>
+        <v>16.86</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15.29</v>
+        <v>24.86</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.43</v>
+        <v>23.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.71</v>
+        <v>19.43</v>
       </c>
       <c r="O16" s="36" t="n">
         <v>25.57</v>
       </c>
+      <c r="P16" s="36" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>14.43</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.86</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I17" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I17" s="36" t="n">
-        <v>19.14</v>
-      </c>
       <c r="J17" s="36" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>23.43</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>20.43</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>24.57</v>
+        <v>24.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>24.14</v>
+        <v>24.71</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>24.43</v>
+        <v>25.57</v>
+      </c>
+      <c r="P17" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>9.43</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>12.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>11.57</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>11.86</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>20.86</v>
+        <v>19</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.86</v>
+        <v>19.57</v>
+      </c>
+      <c r="P18" s="36" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>14</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M19" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="L19" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>22.71</v>
-      </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>20.86</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>20.86</v>
+      </c>
+      <c r="P19" s="36" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
@@ -2937,34 +2993,37 @@
         <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>8</v>
+        <v>3.33</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>9.43</v>
+        <v>11.71</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>12.71</v>
+        <v>17.57</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>11.57</v>
+        <v>20.43</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>21.71</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>11.86</v>
+        <v>15</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>22.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19</v>
+        <v>22.43</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>19.57</v>
+        <v>20.14</v>
+      </c>
+      <c r="P20" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -3017,6 +3076,9 @@
       <c r="O21" s="36" t="n">
         <v>18</v>
       </c>
+      <c r="P21" s="36" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -3068,6 +3130,9 @@
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
+      <c r="P22" s="36" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -3118,6 +3183,9 @@
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
+      </c>
+      <c r="P23" s="36" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -3177,6 +3245,10 @@
       </c>
       <c r="O24" s="39">
         <f>AVERAGE(O6:O23)</f>
+        <v/>
+      </c>
+      <c r="P24" s="39">
+        <f>AVERAGE(P6:P23)</f>
         <v/>
       </c>
     </row>
@@ -3191,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3209,6 +3281,7 @@
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
+    <col width="13" customWidth="1" style="20" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3291,6 +3364,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3366,6 +3444,11 @@
       <c r="O4" s="31" t="inlineStr">
         <is>
           <t>20.07–26.07</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>27.07–02.08*</t>
         </is>
       </c>
     </row>
@@ -3415,6 +3498,9 @@
       <c r="O5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="P5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -3466,107 +3552,116 @@
       <c r="O6" s="40" t="n">
         <v>96616423</v>
       </c>
+      <c r="P6" s="40" t="n">
+        <v>8660475</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>15808893</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>14209578</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>30449860</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>32603120</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>35552907</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>31069118</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>40525338</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>42402722</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>42012092</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>58722069</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>48135084</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>44293878</v>
+      </c>
+      <c r="P7" s="40" t="n">
+        <v>9039290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
+      </c>
+      <c r="P8" s="40" t="n">
+        <v>8706990</v>
       </c>
     </row>
     <row r="9">
@@ -3619,209 +3714,224 @@
       <c r="O9" s="40" t="n">
         <v>38323101</v>
       </c>
+      <c r="P9" s="40" t="n">
+        <v>8176766</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>2886450</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>22932586</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>24764259</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>32268886</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>42977335</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>44364359</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>53225819</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>51621207</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58722069</v>
+        <v>58204066</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>48135084</v>
+        <v>58190202</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>44293878</v>
+        <v>46275213</v>
+      </c>
+      <c r="P10" s="40" t="n">
+        <v>4720092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
+      </c>
+      <c r="P11" s="40" t="n">
+        <v>6666149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
+      </c>
+      <c r="P12" s="40" t="n">
+        <v>6445850</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>51225290</v>
+      </c>
+      <c r="P13" s="40" t="n">
+        <v>8156954</v>
       </c>
     </row>
     <row r="14">
@@ -3874,271 +3984,289 @@
       <c r="O14" s="40" t="n">
         <v>28283704</v>
       </c>
+      <c r="P14" s="40" t="n">
+        <v>6017020</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>6239584</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>13803407</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>28572076</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>15282581</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>16594572</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>15223898</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>27696695</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>17717888</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>24163432</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>23623477</v>
+        <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>19145601</v>
+        <v>29635773</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30157601</v>
+        <v>19554230</v>
+      </c>
+      <c r="P15" s="40" t="n">
+        <v>3318460</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>5092853</v>
+        <v>6239584</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11100161</v>
+        <v>13803407</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14612055</v>
+        <v>28572076</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>20638987</v>
+        <v>15282581</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14061352</v>
+        <v>16594572</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>31599148</v>
+        <v>15223898</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>18747614</v>
+        <v>27696695</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>19576415</v>
+        <v>17717888</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>14226838</v>
+        <v>24163432</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23197145</v>
+        <v>23623477</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>25790711</v>
+        <v>19145601</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>27856115</v>
+        <v>30157601</v>
+      </c>
+      <c r="P16" s="40" t="n">
+        <v>3296170</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>8544625</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>8387478</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>10570508</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>11896580</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>19614352</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>20966317</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>20073400</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>23801493</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>27940611</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>27893929</v>
+        <v>23197145</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>29635773</v>
+        <v>25790711</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>19554230</v>
+        <v>27856115</v>
+      </c>
+      <c r="P17" s="40" t="n">
+        <v>1895040</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>1324510</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>10311989</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>19934535</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>13536614</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>22187720</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>11732010</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>21143100</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>25387051</v>
+        <v>14330970</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>21008637</v>
+        <v>38267409</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30862574</v>
+        <v>46351274</v>
+      </c>
+      <c r="P18" s="40" t="n">
+        <v>5450230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>9575225</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>9264589</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>20692424</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>27565767</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>24912292</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>19068954</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>25387051</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>21008637</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>30862574</v>
+      </c>
+      <c r="P19" s="40" t="n">
+        <v>3344722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
@@ -4151,34 +4279,37 @@
         <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1324510</v>
+        <v>363900</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>10311989</v>
+        <v>3736700</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19934535</v>
+        <v>17796776</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>13536614</v>
+        <v>42724228</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>22187720</v>
+        <v>33036620</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>11732010</v>
+        <v>29649130</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21143100</v>
+        <v>13949368</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>14330970</v>
+        <v>24539413</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>38267409</v>
+        <v>19087217</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>46351274</v>
+        <v>17139440</v>
+      </c>
+      <c r="P20" s="40" t="n">
+        <v>2013170</v>
       </c>
     </row>
     <row r="21">
@@ -4231,6 +4362,9 @@
       <c r="O21" s="40" t="n">
         <v>27906254</v>
       </c>
+      <c r="P21" s="40" t="n">
+        <v>3683890</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -4282,6 +4416,9 @@
       <c r="O22" s="40" t="n">
         <v>4294070</v>
       </c>
+      <c r="P22" s="40" t="n">
+        <v>1763230</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -4332,6 +4469,9 @@
       </c>
       <c r="O23" s="40" t="n">
         <v>5390260</v>
+      </c>
+      <c r="P23" s="40" t="n">
+        <v>1067540</v>
       </c>
     </row>
     <row r="24">
@@ -4391,6 +4531,10 @@
       </c>
       <c r="O24" s="41">
         <f>AVERAGE(O6:O23)</f>
+        <v/>
+      </c>
+      <c r="P24" s="41">
+        <f>AVERAGE(P6:P23)</f>
         <v/>
       </c>
     </row>
@@ -4405,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4423,6 +4567,7 @@
     <col width="13" customWidth="1" style="20" min="13" max="13"/>
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
+    <col width="13" customWidth="1" style="20" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4505,6 +4650,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4580,6 +4730,11 @@
       <c r="O4" s="31" t="inlineStr">
         <is>
           <t>20.07–26.07</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="inlineStr">
+        <is>
+          <t>27.07–02.08*</t>
         </is>
       </c>
     </row>
@@ -4629,6 +4784,9 @@
       <c r="O5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="P5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4680,23 +4838,26 @@
       <c r="O6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="P6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>7</v>
@@ -4730,27 +4891,30 @@
       </c>
       <c r="O7" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P7" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -4781,6 +4945,9 @@
       </c>
       <c r="O8" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4833,27 +5000,30 @@
       <c r="O9" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="P9" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
       </c>
@@ -4883,27 +5053,30 @@
       </c>
       <c r="O10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -4934,27 +5107,30 @@
       </c>
       <c r="O11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -4985,57 +5161,63 @@
       </c>
       <c r="O12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -5088,23 +5270,26 @@
       <c r="O14" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="P14" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5138,24 +5323,27 @@
       </c>
       <c r="O15" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5189,24 +5377,27 @@
       </c>
       <c r="O16" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5240,30 +5431,33 @@
       </c>
       <c r="O17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" s="42" t="n">
         <v>7</v>
@@ -5291,33 +5485,36 @@
       </c>
       <c r="O18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -5342,17 +5539,20 @@
       </c>
       <c r="O19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -5365,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -5393,6 +5593,9 @@
       </c>
       <c r="O20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -5445,6 +5648,9 @@
       <c r="O21" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="P21" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -5496,6 +5702,9 @@
       <c r="O22" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="P22" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -5546,6 +5755,9 @@
       </c>
       <c r="O23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="P23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -5607,6 +5819,10 @@
         <f>AVERAGE(O6:O23)</f>
         <v/>
       </c>
+      <c r="P24" s="43">
+        <f>AVERAGE(P6:P23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2213,277 +2213,277 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>31.14</v>
+        <v>29.43</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>41.14</v>
+        <v>38</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>36.43</v>
+        <v>41.29</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>52.71</v>
+        <v>51.43</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>67.43000000000001</v>
+        <v>58.29</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>61.14</v>
+        <v>63</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>66.14</v>
+        <v>55.43</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>72.56999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>77.86</v>
+        <v>76.86</v>
       </c>
       <c r="O6" s="36" t="n">
-        <v>74.56999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P6" s="36" t="n">
-        <v>66</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>14.29</v>
+        <v>10</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>19.14</v>
+        <v>31.14</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>26.71</v>
+        <v>41.14</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>28.14</v>
+        <v>36.43</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>28.57</v>
+        <v>52.71</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>31.57</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>33</v>
+        <v>61.14</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>34.86</v>
+        <v>66.14</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>41.29</v>
+        <v>72</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>41.43</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>46.14</v>
+        <v>77.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>41.57</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>66</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>14.29</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>29.43</v>
+        <v>19.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>38</v>
+        <v>26.71</v>
       </c>
       <c r="G8" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
+        <v>33</v>
+      </c>
+      <c r="K8" s="36" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="L8" s="36" t="n">
         <v>41.29</v>
       </c>
-      <c r="H8" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>63</v>
-      </c>
-      <c r="K8" s="36" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="L8" s="36" t="n">
-        <v>69.56999999999999</v>
-      </c>
       <c r="M8" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>41.43</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>76.86</v>
+        <v>46.14</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>41.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>7.33</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>17.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>22.14</v>
       </c>
       <c r="H9" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J9" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="I9" s="36" t="n">
-        <v>39.71</v>
-      </c>
-      <c r="J9" s="36" t="n">
-        <v>41.71</v>
-      </c>
       <c r="K9" s="36" t="n">
-        <v>35.14</v>
+        <v>43.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41</v>
+        <v>50.14</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>49.43</v>
+        <v>53.71</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>45.57</v>
+        <v>46.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>7.33</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>17.86</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>22.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>24.86</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>36.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>38</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>43.86</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>50.14</v>
+        <v>41</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>53.71</v>
+        <v>49.43</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>46.57</v>
+        <v>45.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -2537,115 +2537,115 @@
         <v>30</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>48</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -2699,7 +2699,7 @@
         <v>27.29</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>30</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="15">
@@ -2753,109 +2753,109 @@
         <v>24.43</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>24</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>16</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>19.43</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>15.86</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14.86</v>
+        <v>13.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>16.71</v>
+        <v>18</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>16.86</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.86</v>
+        <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>23.43</v>
+        <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>19.43</v>
+        <v>24.71</v>
       </c>
       <c r="O16" s="36" t="n">
         <v>25.57</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>16</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>19.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>15.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>14.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>16.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>19.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>16.86</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>24.86</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>24.43</v>
+        <v>23.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>24.71</v>
+        <v>19.43</v>
       </c>
       <c r="O17" s="36" t="n">
         <v>25.57</v>
@@ -2867,109 +2867,109 @@
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>3.25</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>8</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>9.43</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>12.71</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>11.57</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>11.86</v>
+        <v>16.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>21.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19</v>
+        <v>20.86</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>19.57</v>
+        <v>20.86</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14</v>
+        <v>9.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.14</v>
+        <v>12.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>16.14</v>
+        <v>11.57</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>16.14</v>
+        <v>11.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>21.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>20.86</v>
+        <v>19</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.86</v>
+        <v>19.57</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="20">
@@ -3023,7 +3023,7 @@
         <v>20.14</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="21">
@@ -3077,7 +3077,7 @@
         <v>18</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="22">
@@ -3185,7 +3185,7 @@
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="24">
@@ -3499,277 +3499,277 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>8596643</v>
+        <v>6122227</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>30622284</v>
+        <v>31792625</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>33277426</v>
+        <v>49374899</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>40259616</v>
+        <v>38585414</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>54390985</v>
+        <v>51458725</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>72727058</v>
+        <v>61835892</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>61910106</v>
+        <v>80551167</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>72409127</v>
+        <v>61490143</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>72256071</v>
+        <v>68619843</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>82753547</v>
+        <v>81742671</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>82566330</v>
+        <v>69757179</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>96616423</v>
+        <v>68198708</v>
       </c>
       <c r="P6" s="40" t="n">
-        <v>8660475</v>
+        <v>19096862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>15808893</v>
+        <v>8596643</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>14209578</v>
+        <v>30622284</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>30449860</v>
+        <v>33277426</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>32603120</v>
+        <v>40259616</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>35552907</v>
+        <v>54390985</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>31069118</v>
+        <v>72727058</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>40525338</v>
+        <v>61910106</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>42402722</v>
+        <v>72409127</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>42012092</v>
+        <v>72256071</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>58722069</v>
+        <v>82753547</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>48135084</v>
+        <v>82566330</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>44293878</v>
+        <v>96616423</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>9039290</v>
+        <v>19876994</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>6122227</v>
+        <v>15808893</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>31792625</v>
+        <v>14209578</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>49374899</v>
+        <v>30449860</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>38585414</v>
+        <v>32603120</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>51458725</v>
+        <v>35552907</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>61835892</v>
+        <v>31069118</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>80551167</v>
+        <v>40525338</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>61490143</v>
+        <v>42402722</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>68619843</v>
+        <v>42012092</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>81742671</v>
+        <v>58722069</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>69757179</v>
+        <v>48135084</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>68198708</v>
+        <v>44293878</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>8706990</v>
+        <v>14092692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>2886450</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>22932586</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>24764259</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>32268886</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>42977335</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>44364359</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>43259404</v>
+        <v>53225819</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>68694825</v>
+        <v>51621207</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>48824266</v>
+        <v>58204066</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>57556194</v>
+        <v>58190202</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>38323101</v>
+        <v>46275213</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>8176766</v>
+        <v>14083062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>2886450</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>22932586</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>24764259</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>32268886</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>42977335</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>44364359</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>53225819</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51621207</v>
+        <v>68694825</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58204066</v>
+        <v>48824266</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>58190202</v>
+        <v>57556194</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>46275213</v>
+        <v>38323101</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>4720092</v>
+        <v>11185836</v>
       </c>
     </row>
     <row r="11">
@@ -3823,115 +3823,115 @@
         <v>25219748</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>6666149</v>
+        <v>10969569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>6445850</v>
+        <v>16055419</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>8156954</v>
+        <v>11561340</v>
       </c>
     </row>
     <row r="14">
@@ -3985,7 +3985,7 @@
         <v>28283704</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>6017020</v>
+        <v>11220890</v>
       </c>
     </row>
     <row r="15">
@@ -4039,223 +4039,223 @@
         <v>19554230</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>3318460</v>
+        <v>7533790</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>6239584</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>13803407</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>28572076</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>15282581</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>16594572</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>15223898</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>27696695</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>17717888</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>24163432</v>
+        <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23623477</v>
+        <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>19145601</v>
+        <v>25790711</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30157601</v>
+        <v>27856115</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>3296170</v>
+        <v>7313850</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>6239584</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>13803407</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>28572076</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>15282581</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>16594572</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>15223898</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>27696695</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>17717888</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>24163432</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23197145</v>
+        <v>23623477</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>25790711</v>
+        <v>19145601</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27856115</v>
+        <v>30157601</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>1895040</v>
+        <v>4749920</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>1324510</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>10311989</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19934535</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>13536614</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>22187720</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>11732010</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>21143100</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>14330970</v>
+        <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>38267409</v>
+        <v>21008637</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>46351274</v>
+        <v>30862574</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>5450230</v>
+        <v>9695532</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>9575225</v>
+        <v>1324510</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>9264589</v>
+        <v>10311989</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>20692424</v>
+        <v>19934535</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>27565767</v>
+        <v>13536614</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>19138015</v>
+        <v>22187720</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>24912292</v>
+        <v>11732010</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>19068954</v>
+        <v>21143100</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>25387051</v>
+        <v>14330970</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>21008637</v>
+        <v>38267409</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>30862574</v>
+        <v>46351274</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>3344722</v>
+        <v>10842360</v>
       </c>
     </row>
     <row r="20">
@@ -4309,7 +4309,7 @@
         <v>17139440</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>2013170</v>
+        <v>3956590</v>
       </c>
     </row>
     <row r="21">
@@ -4363,7 +4363,7 @@
         <v>27906254</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>3683890</v>
+        <v>7111910</v>
       </c>
     </row>
     <row r="22">
@@ -4417,7 +4417,7 @@
         <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>1763230</v>
+        <v>3009170</v>
       </c>
     </row>
     <row r="23">
@@ -4471,7 +4471,7 @@
         <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>1067540</v>
+        <v>2000110</v>
       </c>
     </row>
     <row r="24">
@@ -4785,18 +4785,18 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -4839,25 +4839,25 @@
         <v>7</v>
       </c>
       <c r="P6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>7</v>
@@ -4893,25 +4893,25 @@
         <v>7</v>
       </c>
       <c r="P7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="42" t="n">
         <v>7</v>
@@ -4947,28 +4947,28 @@
         <v>7</v>
       </c>
       <c r="P8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>7</v>
@@ -5001,28 +5001,28 @@
         <v>7</v>
       </c>
       <c r="P9" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -5055,7 +5055,7 @@
         <v>7</v>
       </c>
       <c r="P10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5109,28 +5109,28 @@
         <v>7</v>
       </c>
       <c r="P11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -5163,28 +5163,28 @@
         <v>7</v>
       </c>
       <c r="P12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" s="42" t="n">
         <v>7</v>
@@ -5217,7 +5217,7 @@
         <v>7</v>
       </c>
       <c r="P13" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5271,7 +5271,7 @@
         <v>7</v>
       </c>
       <c r="P14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5325,25 +5325,25 @@
         <v>7</v>
       </c>
       <c r="P15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5379,25 +5379,25 @@
         <v>7</v>
       </c>
       <c r="P16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5433,31 +5433,31 @@
         <v>7</v>
       </c>
       <c r="P17" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
         <v>7</v>
@@ -5487,31 +5487,31 @@
         <v>7</v>
       </c>
       <c r="P18" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="P19" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -5595,7 +5595,7 @@
         <v>7</v>
       </c>
       <c r="P20" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -5649,7 +5649,7 @@
         <v>7</v>
       </c>
       <c r="P21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -5703,7 +5703,7 @@
         <v>7</v>
       </c>
       <c r="P22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -5757,7 +5757,7 @@
         <v>7</v>
       </c>
       <c r="P23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2213,115 +2213,115 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>29.43</v>
+        <v>31.14</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>38</v>
+        <v>41.14</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>41.29</v>
+        <v>36.43</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>51.43</v>
+        <v>52.71</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>58.29</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>63</v>
+        <v>61.14</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>55.43</v>
+        <v>66.14</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>76.86</v>
+        <v>77.86</v>
       </c>
       <c r="O6" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="P6" s="36" t="n">
-        <v>70.5</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>31.14</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>41.14</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>36.43</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>52.71</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>67.43000000000001</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>61.14</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>66.14</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>72.56999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>77.86</v>
+        <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>74.56999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>68.5</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="8">
@@ -2375,7 +2375,7 @@
         <v>41.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>59</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="9">
@@ -2429,7 +2429,7 @@
         <v>46.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>53</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="10">
@@ -2483,61 +2483,61 @@
         <v>45.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>45</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>13.43</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.71</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>16.57</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>21.29</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>21.14</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>23.29</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>22.43</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>22.43</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.14</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>31.14</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>30</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>39.5</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="12">
@@ -2591,61 +2591,61 @@
         <v>30.71</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>38</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>31.29</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>33.57</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>40</v>
+        <v>22.43</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>42.43</v>
+        <v>28.14</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>38.57</v>
+        <v>31.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>34.29</v>
+        <v>30</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>34</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="14">
@@ -2699,163 +2699,163 @@
         <v>27.29</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>33.5</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>7</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>19.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>15.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>16.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>19.71</v>
       </c>
       <c r="K15" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L15" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="M15" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="L15" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M15" s="36" t="n">
-        <v>24.57</v>
-      </c>
       <c r="N15" s="36" t="n">
-        <v>24.14</v>
+        <v>19.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>24.43</v>
+        <v>25.57</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>20.5</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>6.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>18</v>
+        <v>17.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>18</v>
+        <v>16.14</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>17.43</v>
+        <v>18.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15.29</v>
+        <v>16.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.43</v>
+        <v>21.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.71</v>
+        <v>20.86</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>25.57</v>
+        <v>20.86</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>20.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>16</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>19.43</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>15.86</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.86</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>16.71</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>16.86</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>24.86</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>23.43</v>
+        <v>24.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.43</v>
+        <v>24.71</v>
       </c>
       <c r="O17" s="36" t="n">
         <v>25.57</v>
@@ -2867,109 +2867,109 @@
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>6.43</v>
+        <v>11</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>14.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>19.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>21</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21.71</v>
+        <v>24.57</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>20.86</v>
+        <v>24.14</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>18.5</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>3.25</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>8</v>
+        <v>12.71</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>9.43</v>
+        <v>14.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>12.71</v>
+        <v>19</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>11.57</v>
+        <v>21.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>18.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>11.86</v>
+        <v>16.57</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>19.57</v>
+        <v>18</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -3023,61 +3023,61 @@
         <v>20.14</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I21" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H21" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I21" s="36" t="n">
+      <c r="J21" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M21" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N21" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="J21" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="M21" s="36" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <v>19.14</v>
-      </c>
       <c r="O21" s="36" t="n">
-        <v>18</v>
+        <v>19.57</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="22">
@@ -3131,7 +3131,7 @@
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="23">
@@ -3185,7 +3185,7 @@
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="24">
@@ -3499,115 +3499,115 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>6122227</v>
+        <v>8596643</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>31792625</v>
+        <v>30622284</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>49374899</v>
+        <v>33277426</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>38585414</v>
+        <v>40259616</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>51458725</v>
+        <v>54390985</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>61835892</v>
+        <v>72727058</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>80551167</v>
+        <v>61910106</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>61490143</v>
+        <v>72409127</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>68619843</v>
+        <v>72256071</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>81742671</v>
+        <v>82753547</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>69757179</v>
+        <v>82566330</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>68198708</v>
+        <v>96616423</v>
       </c>
       <c r="P6" s="40" t="n">
-        <v>19096862</v>
+        <v>57159305</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>8596643</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>30622284</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>33277426</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>40259616</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>54390985</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>72727058</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>61910106</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>72409127</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>72256071</v>
+        <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>82753547</v>
+        <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>82566330</v>
+        <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>96616423</v>
+        <v>68198708</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>19876994</v>
+        <v>46643500</v>
       </c>
     </row>
     <row r="8">
@@ -3661,7 +3661,7 @@
         <v>44293878</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>14092692</v>
+        <v>32276736</v>
       </c>
     </row>
     <row r="9">
@@ -3715,7 +3715,7 @@
         <v>46275213</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>14083062</v>
+        <v>36064815</v>
       </c>
     </row>
     <row r="10">
@@ -3769,61 +3769,61 @@
         <v>38323101</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>11185836</v>
+        <v>27232040</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>10351067</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>21091580</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>24243567</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>16381412</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>21591272</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>21904190</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25438080</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>24614280</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28889771</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>44250621</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>29608597</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>25219748</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>10969569</v>
+        <v>31498845</v>
       </c>
     </row>
     <row r="12">
@@ -3877,61 +3877,61 @@
         <v>51225290</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>16055419</v>
+        <v>28080678</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>11561340</v>
+        <v>23604573</v>
       </c>
     </row>
     <row r="14">
@@ -3985,277 +3985,277 @@
         <v>28283704</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>11220890</v>
+        <v>21134420</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>6239584</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>13803407</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>28572076</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>15282581</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>16594572</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>15223898</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>27696695</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>17717888</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>24163432</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>23623477</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29635773</v>
+        <v>19145601</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>19554230</v>
+        <v>30157601</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>7533790</v>
+        <v>33579791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>5092853</v>
+        <v>3249588</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11100161</v>
+        <v>7305524</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14612055</v>
+        <v>9575225</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>20638987</v>
+        <v>9264589</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14061352</v>
+        <v>20692424</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>31599148</v>
+        <v>27565767</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>18747614</v>
+        <v>19138015</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>19576415</v>
+        <v>24912292</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>14226838</v>
+        <v>19068954</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23197145</v>
+        <v>25387051</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>25790711</v>
+        <v>21008637</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>27856115</v>
+        <v>30862574</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>7313850</v>
+        <v>26102327</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>6239584</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>13803407</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>28572076</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>15282581</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>16594572</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>15223898</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>27696695</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>17717888</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>24163432</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23623477</v>
+        <v>23197145</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19145601</v>
+        <v>25790711</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>30157601</v>
+        <v>27856115</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>4749920</v>
+        <v>17385901</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>8544625</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>8387478</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>10570508</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>11896580</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>19614352</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>20966317</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>20073400</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>23801493</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>27940611</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>25387051</v>
+        <v>27893929</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>21008637</v>
+        <v>29635773</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30862574</v>
+        <v>19554230</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>9695532</v>
+        <v>14962773</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>1324510</v>
+        <v>21387685</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>10311989</v>
+        <v>16050448</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19934535</v>
+        <v>21568794</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>13536614</v>
+        <v>30845816</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>22187720</v>
+        <v>45285935</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>11732010</v>
+        <v>28941455</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21143100</v>
+        <v>21801828</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>14330970</v>
+        <v>19628570</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38267409</v>
+        <v>23276090</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>46351274</v>
+        <v>27906254</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>10842360</v>
+        <v>15915834</v>
       </c>
     </row>
     <row r="20">
@@ -4309,61 +4309,61 @@
         <v>17139440</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>3956590</v>
+        <v>8578430</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>23276090</v>
+        <v>38267409</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>27906254</v>
+        <v>46351274</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>7111910</v>
+        <v>24885940</v>
       </c>
     </row>
     <row r="22">
@@ -4417,7 +4417,7 @@
         <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>3009170</v>
+        <v>5163649</v>
       </c>
     </row>
     <row r="23">
@@ -4471,7 +4471,7 @@
         <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>2000110</v>
+        <v>3242920</v>
       </c>
     </row>
     <row r="24">
@@ -4785,18 +4785,18 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -4839,18 +4839,18 @@
         <v>7</v>
       </c>
       <c r="P6" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
@@ -4893,7 +4893,7 @@
         <v>7</v>
       </c>
       <c r="P7" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4947,7 +4947,7 @@
         <v>7</v>
       </c>
       <c r="P8" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -5001,7 +5001,7 @@
         <v>7</v>
       </c>
       <c r="P9" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -5055,28 +5055,28 @@
         <v>7</v>
       </c>
       <c r="P10" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -5109,7 +5109,7 @@
         <v>7</v>
       </c>
       <c r="P11" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -5163,61 +5163,61 @@
         <v>7</v>
       </c>
       <c r="P12" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5271,25 +5271,25 @@
         <v>7</v>
       </c>
       <c r="P14" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5325,25 +5325,25 @@
         <v>7</v>
       </c>
       <c r="P15" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5379,25 +5379,25 @@
         <v>7</v>
       </c>
       <c r="P16" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5433,25 +5433,25 @@
         <v>7</v>
       </c>
       <c r="P17" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -5487,31 +5487,31 @@
         <v>7</v>
       </c>
       <c r="P18" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -5541,7 +5541,7 @@
         <v>7</v>
       </c>
       <c r="P19" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -5595,61 +5595,61 @@
         <v>7</v>
       </c>
       <c r="P20" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P21" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="E21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P21" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -5703,7 +5703,7 @@
         <v>7</v>
       </c>
       <c r="P22" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -5757,7 +5757,7 @@
         <v>7</v>
       </c>
       <c r="P23" s="42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1555,13 +1555,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="20" min="1" max="1"/>
     <col width="22" customWidth="1" style="20" min="2" max="2"/>
     <col width="15" customWidth="1" style="20" min="3" max="3"/>
     <col width="15" customWidth="1" style="20" min="4" max="4"/>
+    <col width="15" customWidth="1" style="20" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1579,14 +1580,19 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1609,6 +1615,11 @@
       <c r="D4" s="31" t="inlineStr">
         <is>
           <t>июнь 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>июль 2026</t>
         </is>
       </c>
     </row>
@@ -1625,6 +1636,9 @@
       <c r="D5" s="34" t="n">
         <v>30</v>
       </c>
+      <c r="E5" s="34" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -1643,6 +1657,9 @@
       <c r="D6" s="40" t="n">
         <v>23574400</v>
       </c>
+      <c r="E6" s="40" t="n">
+        <v>17883525</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -1661,6 +1678,9 @@
       <c r="D7" s="40" t="n">
         <v>17460000</v>
       </c>
+      <c r="E7" s="40" t="n">
+        <v>25822436</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -1679,6 +1699,9 @@
       <c r="D8" s="40" t="n">
         <v>17427600</v>
       </c>
+      <c r="E8" s="40" t="n">
+        <v>17400000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -1697,6 +1720,9 @@
       <c r="D9" s="40" t="n">
         <v>17428800</v>
       </c>
+      <c r="E9" s="40" t="n">
+        <v>23500000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -1715,6 +1741,9 @@
       <c r="D10" s="40" t="n">
         <v>14007200</v>
       </c>
+      <c r="E10" s="40" t="n">
+        <v>20100000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -1733,6 +1762,9 @@
       <c r="D11" s="40" t="n">
         <v>17409600</v>
       </c>
+      <c r="E11" s="40" t="n">
+        <v>23500000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
@@ -1751,6 +1783,9 @@
       <c r="D12" s="40" t="n">
         <v>17426400</v>
       </c>
+      <c r="E12" s="40" t="n">
+        <v>23500000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
@@ -1769,6 +1804,9 @@
       <c r="D13" s="40" t="n">
         <v>17424000</v>
       </c>
+      <c r="E13" s="40" t="n">
+        <v>23500000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -1787,6 +1825,9 @@
       <c r="D14" s="40" t="n">
         <v>20109600</v>
       </c>
+      <c r="E14" s="40" t="n">
+        <v>14000000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -1805,6 +1846,9 @@
       <c r="D15" s="40" t="n">
         <v>14012000</v>
       </c>
+      <c r="E15" s="40" t="n">
+        <v>20100000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -1823,6 +1867,9 @@
       <c r="D16" s="40" t="n">
         <v>17404800</v>
       </c>
+      <c r="E16" s="40" t="n">
+        <v>23500000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
@@ -1841,6 +1888,9 @@
       <c r="D17" s="40" t="n">
         <v>14009600</v>
       </c>
+      <c r="E17" s="40" t="n">
+        <v>20100000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -1859,6 +1909,9 @@
       <c r="D18" s="40" t="n">
         <v>14025200</v>
       </c>
+      <c r="E18" s="40" t="n">
+        <v>20100000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
@@ -1877,6 +1930,9 @@
       <c r="D19" s="40" t="n">
         <v>14021600</v>
       </c>
+      <c r="E19" s="40" t="n">
+        <v>20100000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
@@ -1895,6 +1951,9 @@
       <c r="D20" s="40" t="n">
         <v>14008400</v>
       </c>
+      <c r="E20" s="40" t="n">
+        <v>20100000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -1913,6 +1972,9 @@
       <c r="D21" s="40" t="n">
         <v>17406000</v>
       </c>
+      <c r="E21" s="40" t="n">
+        <v>17400000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -1931,6 +1993,9 @@
       <c r="D22" s="40" t="n">
         <v>11400000</v>
       </c>
+      <c r="E22" s="40" t="n">
+        <v>17500000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -1948,6 +2013,9 @@
       </c>
       <c r="D23" s="40" t="n">
         <v>14000000</v>
+      </c>
+      <c r="E23" s="40" t="n">
+        <v>20100000</v>
       </c>
     </row>
     <row r="24">
@@ -1963,6 +2031,10 @@
       </c>
       <c r="D24" s="41">
         <f>SUM(D6:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="41">
+        <f>SUM(E6:E23)</f>
         <v/>
       </c>
     </row>
@@ -2013,72 +2085,72 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
@@ -3299,72 +3371,72 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
@@ -4585,72 +4657,72 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1580,17 +1580,17 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
@@ -2049,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2068,6 +2068,7 @@
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
+    <col width="13" customWidth="1" style="20" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2085,74 +2086,79 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2240,12 @@
       </c>
       <c r="P4" s="31" t="inlineStr">
         <is>
-          <t>27.07–02.08*</t>
+          <t>27.07–02.08</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>03.08–09.08*</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2296,10 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q5" s="34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2339,763 +2353,808 @@
         <v>74.56999999999999</v>
       </c>
       <c r="P6" s="36" t="n">
-        <v>74.40000000000001</v>
+        <v>75.43000000000001</v>
+      </c>
+      <c r="Q6" s="36" t="n">
+        <v>77.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>70.8</v>
+        <v>49.29</v>
+      </c>
+      <c r="Q7" s="36" t="n">
+        <v>69.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>14.29</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>19.14</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>26.71</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>28.57</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>31.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>34.86</v>
+        <v>55.43</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>41.29</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>41.43</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>46.14</v>
+        <v>76.86</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>41.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>55.6</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="Q8" s="36" t="n">
+        <v>63.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>50.14</v>
+        <v>41.29</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>59</v>
+        <v>41.43</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>53.71</v>
+        <v>46.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>46.57</v>
+        <v>41.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>54.4</v>
+        <v>51.86</v>
+      </c>
+      <c r="Q9" s="36" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>8</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>13.14</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>19.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>26.43</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>32.29</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>31.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>33.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>48</v>
+        <v>42.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>49.43</v>
+        <v>38.57</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>45.57</v>
+        <v>34.29</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>39.2</v>
+        <v>37.86</v>
+      </c>
+      <c r="Q10" s="36" t="n">
+        <v>49.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>18.71</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>21.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>30.29</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>38</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>39.71</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>41.71</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>35.14</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>48</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>38.57</v>
+        <v>49.43</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>34.29</v>
+        <v>45.57</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>33.8</v>
+        <v>43</v>
+      </c>
+      <c r="Q11" s="36" t="n">
+        <v>47.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F12" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G12" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G12" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L12" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M12" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="M12" s="36" t="n">
-        <v>28.86</v>
-      </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>31.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>30</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>33.2</v>
+        <v>30.43</v>
+      </c>
+      <c r="Q12" s="36" t="n">
+        <v>32.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>7</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>16</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>19.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>15.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>14.86</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>16.71</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>19.71</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>16.86</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>24.86</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>23.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>31.14</v>
+        <v>19.43</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30</v>
+        <v>25.57</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>32.4</v>
+        <v>27.43</v>
+      </c>
+      <c r="Q13" s="36" t="n">
+        <v>30.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.43</v>
+        <v>1.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.43</v>
+        <v>12.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.29</v>
+        <v>16.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>14.71</v>
+        <v>21</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>17</v>
+        <v>20.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.71</v>
+        <v>28.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>17.71</v>
+        <v>24.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>19.57</v>
+        <v>27.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.14</v>
+        <v>28.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>27.57</v>
+        <v>28.86</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.43</v>
+        <v>33.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>27.29</v>
+        <v>30.71</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>27.8</v>
+        <v>31.14</v>
+      </c>
+      <c r="Q14" s="36" t="n">
+        <v>29.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>19.43</v>
+        <v>20.86</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>25.57</v>
+        <v>20.86</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>27.2</v>
+        <v>21.86</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <v>26.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>6.43</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.14</v>
+        <v>18</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>16.14</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>18.57</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.14</v>
+        <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>21.71</v>
+        <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>20.86</v>
+        <v>24.71</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>20.86</v>
+        <v>25.57</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>25.2</v>
+        <v>19.29</v>
+      </c>
+      <c r="Q16" s="36" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>9.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>12.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>13.29</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>14.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>17</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>19.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>17.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>19.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>24.14</v>
       </c>
       <c r="M17" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="N17" s="36" t="n">
         <v>24.43</v>
       </c>
-      <c r="N17" s="36" t="n">
-        <v>24.71</v>
-      </c>
       <c r="O17" s="36" t="n">
-        <v>25.57</v>
+        <v>27.29</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>20</v>
+        <v>26.57</v>
+      </c>
+      <c r="Q17" s="36" t="n">
+        <v>25.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.43</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>11.86</v>
+        <v>3.33</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>18</v>
+        <v>11.71</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19.14</v>
+        <v>17.57</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>20.43</v>
+        <v>15</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>24.57</v>
+        <v>22.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>24.43</v>
+        <v>20.14</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>19.8</v>
+        <v>15.71</v>
+      </c>
+      <c r="Q18" s="36" t="n">
+        <v>22.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>7.14</v>
+        <v>11</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>14.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>12.71</v>
+        <v>11.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14.43</v>
+        <v>18</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21.14</v>
+        <v>21</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>16.57</v>
+        <v>20.43</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>14.71</v>
+        <v>24.57</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19.14</v>
+        <v>24.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>18</v>
+        <v>24.43</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="Q19" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>15</v>
+        <v>16.57</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>22.71</v>
+        <v>14.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>22.43</v>
+        <v>19.14</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>20.14</v>
+        <v>18</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
+      </c>
+      <c r="Q20" s="36" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -3149,7 +3208,10 @@
         <v>19.57</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>14.4</v>
+        <v>16.86</v>
+      </c>
+      <c r="Q21" s="36" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -3203,7 +3265,10 @@
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>12.6</v>
+        <v>9.710000000000001</v>
+      </c>
+      <c r="Q22" s="36" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -3257,7 +3322,10 @@
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>7.8</v>
+        <v>7.71</v>
+      </c>
+      <c r="Q23" s="36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3321,6 +3389,10 @@
       </c>
       <c r="P24" s="39">
         <f>AVERAGE(P6:P23)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="39">
+        <f>AVERAGE(Q6:Q23)</f>
         <v/>
       </c>
     </row>
@@ -3335,7 +3407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3354,6 +3426,7 @@
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
+    <col width="13" customWidth="1" style="20" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3371,74 +3444,79 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3598,12 @@
       </c>
       <c r="P4" s="31" t="inlineStr">
         <is>
-          <t>27.07–02.08*</t>
+          <t>27.07–02.08</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>03.08–09.08*</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3654,10 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q5" s="34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3625,763 +3711,808 @@
         <v>96616423</v>
       </c>
       <c r="P6" s="40" t="n">
-        <v>57159305</v>
+        <v>79977173</v>
+      </c>
+      <c r="Q6" s="40" t="n">
+        <v>35933735</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>46643500</v>
+        <v>51530060</v>
+      </c>
+      <c r="Q7" s="40" t="n">
+        <v>42921870</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>15808893</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>14209578</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>30449860</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32603120</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>35552907</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>31069118</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>40525338</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>42402722</v>
+        <v>61490143</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>42012092</v>
+        <v>68619843</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58722069</v>
+        <v>81742671</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>48135084</v>
+        <v>69757179</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>44293878</v>
+        <v>68198708</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>32276736</v>
+        <v>67906121</v>
+      </c>
+      <c r="Q8" s="40" t="n">
+        <v>33088394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>51621207</v>
+        <v>42012092</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58204066</v>
+        <v>58722069</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>58190202</v>
+        <v>48135084</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>46275213</v>
+        <v>44293878</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>36064815</v>
+        <v>41613311</v>
+      </c>
+      <c r="Q9" s="40" t="n">
+        <v>19260848</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>8972650</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>18100396</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>23988817</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>22409732</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>37715520</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>35926824</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>39462393</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>68694825</v>
+        <v>51983942</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>48824266</v>
+        <v>58935844</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>57556194</v>
+        <v>38454971</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>38323101</v>
+        <v>42939312</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>27232040</v>
+        <v>43650420</v>
+      </c>
+      <c r="Q10" s="40" t="n">
+        <v>23587042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>3771593</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>17664217</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>21748722</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>38313932</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>49313727</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>41788221</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>36755638</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>43259404</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>68694825</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>48824266</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>57556194</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>38323101</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>31498845</v>
+        <v>40276838</v>
+      </c>
+      <c r="Q11" s="40" t="n">
+        <v>19066933</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>28889771</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>44250621</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>29608597</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>25219748</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>28080678</v>
+        <v>28515437</v>
+      </c>
+      <c r="Q12" s="40" t="n">
+        <v>18963950</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>6239584</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>13803407</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>28572076</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>15282581</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>16594572</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>15223898</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>27696695</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>17717888</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>24163432</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>23623477</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>19145601</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>30157601</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>23604573</v>
+        <v>41172333</v>
+      </c>
+      <c r="Q13" s="40" t="n">
+        <v>21288956</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11884771</v>
+        <v>536260</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>10651216</v>
+        <v>14403556</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>13882033</v>
+        <v>16216832</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>17812948</v>
+        <v>32622053</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>17331854</v>
+        <v>23929705</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>26294756</v>
+        <v>37214538</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>24196222</v>
+        <v>25375430</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>22122847</v>
+        <v>31500087</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>31914115</v>
+        <v>28078687</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>32069521</v>
+        <v>34472458</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>38287475</v>
+        <v>35343350</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>28283704</v>
+        <v>51225290</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>21134420</v>
+        <v>36142612</v>
+      </c>
+      <c r="Q14" s="40" t="n">
+        <v>12941311</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>23623477</v>
+        <v>25387051</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>19145601</v>
+        <v>21008637</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30157601</v>
+        <v>30862574</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>33579791</v>
+        <v>31820447</v>
+      </c>
+      <c r="Q15" s="40" t="n">
+        <v>9398580</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3249588</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>7305524</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>9575225</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>9264589</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>20692424</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>27565767</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>19138015</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>24912292</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>19068954</v>
+        <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>25387051</v>
+        <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>21008637</v>
+        <v>25790711</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30862574</v>
+        <v>27856115</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>26102327</v>
+        <v>20981901</v>
+      </c>
+      <c r="Q16" s="40" t="n">
+        <v>9885316</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>11884771</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>10651216</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>13882033</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>17812948</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>17331854</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>26294756</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>24196222</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>22122847</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>31914115</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23197145</v>
+        <v>32069521</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>25790711</v>
+        <v>38287475</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27856115</v>
+        <v>28283704</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>17385901</v>
+        <v>27334091</v>
+      </c>
+      <c r="Q17" s="40" t="n">
+        <v>16692195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>10570508</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>11896580</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19614352</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>20966317</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>20073400</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>23801493</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>27940611</v>
+        <v>13949368</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>27893929</v>
+        <v>24539413</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>29635773</v>
+        <v>19087217</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>19554230</v>
+        <v>17139440</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>14962773</v>
+        <v>17746930</v>
+      </c>
+      <c r="Q18" s="40" t="n">
+        <v>11582350</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3337146</v>
+        <v>8544625</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10420206</v>
+        <v>8387478</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>21387685</v>
+        <v>10570508</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16050448</v>
+        <v>11896580</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>21568794</v>
+        <v>19614352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>30845816</v>
+        <v>20966317</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>45285935</v>
+        <v>20073400</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>28941455</v>
+        <v>23801493</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21801828</v>
+        <v>27940611</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>19628570</v>
+        <v>27893929</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>23276090</v>
+        <v>29635773</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>27906254</v>
+        <v>19554230</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>15915834</v>
+        <v>23848495</v>
+      </c>
+      <c r="Q19" s="40" t="n">
+        <v>12782818</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>13949368</v>
+        <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>24539413</v>
+        <v>19628570</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>19087217</v>
+        <v>23276090</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>17139440</v>
+        <v>27906254</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>8578430</v>
+        <v>20822247</v>
+      </c>
+      <c r="Q20" s="40" t="n">
+        <v>3746355</v>
       </c>
     </row>
     <row r="21">
@@ -4435,7 +4566,10 @@
         <v>46351274</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>24885940</v>
+        <v>37105387</v>
+      </c>
+      <c r="Q21" s="40" t="n">
+        <v>6106227</v>
       </c>
     </row>
     <row r="22">
@@ -4489,7 +4623,10 @@
         <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>5163649</v>
+        <v>5589419</v>
+      </c>
+      <c r="Q22" s="40" t="n">
+        <v>7767470</v>
       </c>
     </row>
     <row r="23">
@@ -4543,7 +4680,10 @@
         <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>3242920</v>
+        <v>4645370</v>
+      </c>
+      <c r="Q23" s="40" t="n">
+        <v>3020680</v>
       </c>
     </row>
     <row r="24">
@@ -4607,6 +4747,10 @@
       </c>
       <c r="P24" s="41">
         <f>AVERAGE(P6:P23)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="41">
+        <f>AVERAGE(Q6:Q23)</f>
         <v/>
       </c>
     </row>
@@ -4621,7 +4765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4640,6 +4784,7 @@
     <col width="13" customWidth="1" style="20" min="14" max="14"/>
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
+    <col width="13" customWidth="1" style="20" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4657,74 +4802,79 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4956,12 @@
       </c>
       <c r="P4" s="31" t="inlineStr">
         <is>
-          <t>27.07–02.08*</t>
+          <t>27.07–02.08</t>
+        </is>
+      </c>
+      <c r="Q4" s="31" t="inlineStr">
+        <is>
+          <t>03.08–09.08*</t>
         </is>
       </c>
     </row>
@@ -4857,7 +5012,10 @@
         <v>7</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q5" s="34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4911,28 +5069,31 @@
         <v>7</v>
       </c>
       <c r="P6" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q6" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -4965,136 +5126,145 @@
         <v>7</v>
       </c>
       <c r="P7" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q7" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P9" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -5127,28 +5297,31 @@
         <v>7</v>
       </c>
       <c r="P10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q10" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -5181,79 +5354,85 @@
         <v>7</v>
       </c>
       <c r="P11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q11" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -5289,25 +5468,28 @@
         <v>7</v>
       </c>
       <c r="P13" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -5343,25 +5525,28 @@
         <v>7</v>
       </c>
       <c r="P14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q14" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5397,79 +5582,85 @@
         <v>7</v>
       </c>
       <c r="P15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q15" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5505,34 +5696,37 @@
         <v>7</v>
       </c>
       <c r="P17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q17" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G18" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -5559,25 +5753,28 @@
         <v>7</v>
       </c>
       <c r="P18" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q18" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>7</v>
@@ -5613,34 +5810,37 @@
         <v>7</v>
       </c>
       <c r="P19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q19" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -5667,7 +5867,10 @@
         <v>7</v>
       </c>
       <c r="P20" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q20" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -5721,7 +5924,10 @@
         <v>7</v>
       </c>
       <c r="P21" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q21" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -5775,7 +5981,10 @@
         <v>7</v>
       </c>
       <c r="P22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q22" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5829,7 +6038,10 @@
         <v>7</v>
       </c>
       <c r="P23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="Q23" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5895,6 +6107,10 @@
         <f>AVERAGE(P6:P23)</f>
         <v/>
       </c>
+      <c r="Q24" s="43">
+        <f>AVERAGE(Q6:Q23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
-          <t>03.08–09.08*</t>
+          <t>03.08–09.08</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         <v>7</v>
       </c>
       <c r="Q5" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2356,121 +2356,121 @@
         <v>75.43000000000001</v>
       </c>
       <c r="Q6" s="36" t="n">
-        <v>77.33</v>
+        <v>80.56999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>49.29</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>69.67</v>
+        <v>78.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K8" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>63.33</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2527,292 +2527,292 @@
         <v>51.86</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>56</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>31.29</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>33.57</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>42.43</v>
+        <v>48</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>38.57</v>
+        <v>49.43</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>34.29</v>
+        <v>45.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>37.86</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>49.33</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>18.71</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>30.29</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>38</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>39.71</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>41.71</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>35.14</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>48</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>49.43</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>45.57</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>43</v>
+        <v>37.86</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>47.67</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.14</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="O12" s="36" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="P12" s="36" t="n">
         <v>31.14</v>
       </c>
-      <c r="O12" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P12" s="36" t="n">
-        <v>30.43</v>
-      </c>
       <c r="Q12" s="36" t="n">
-        <v>32.67</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>7</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>16</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>19.43</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>15.86</v>
+        <v>16.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>14.86</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>16.71</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>19.71</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>16.86</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>24.86</v>
+        <v>22.43</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>23.43</v>
+        <v>28.14</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>19.43</v>
+        <v>31.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>25.57</v>
+        <v>30</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>27.43</v>
+        <v>30.43</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>30.33</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.14</v>
+        <v>16</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.57</v>
+        <v>19.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>21</v>
+        <v>15.86</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>20.29</v>
+        <v>14.86</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>28.57</v>
+        <v>16.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>24.14</v>
+        <v>19.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>27.57</v>
+        <v>16.86</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>28.14</v>
+        <v>24.86</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>28.86</v>
+        <v>23.43</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>33.14</v>
+        <v>19.43</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>30.71</v>
+        <v>25.57</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>31.14</v>
+        <v>27.43</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>29.33</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="15">
@@ -2869,235 +2869,235 @@
         <v>21.86</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>26.67</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>6.67</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10.57</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.14</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>13.86</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>18</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>18</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>17.43</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15.29</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="N16" s="36" t="n">
         <v>24.43</v>
       </c>
-      <c r="N16" s="36" t="n">
-        <v>24.71</v>
-      </c>
       <c r="O16" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="P16" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q16" s="36" t="n">
         <v>25.57</v>
-      </c>
-      <c r="P16" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q16" s="36" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9.43</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.29</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>14.71</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>17</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>19.57</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>24.14</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>27.57</v>
+        <v>24.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>24.43</v>
+        <v>24.71</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>26.57</v>
+        <v>19.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>25.33</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J18" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="L18" s="36" t="n">
         <v>20.43</v>
       </c>
-      <c r="K18" s="36" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>15</v>
-      </c>
       <c r="M18" s="36" t="n">
-        <v>22.71</v>
+        <v>24.57</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>22.43</v>
+        <v>24.14</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.14</v>
+        <v>24.43</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>15.71</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>22.67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.43</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>11.86</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>18</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19.14</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>20.43</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>24.57</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>24.43</v>
+        <v>20.14</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>22</v>
+        <v>15.71</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="20">
@@ -3154,7 +3154,7 @@
         <v>15.29</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>14</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="21">
@@ -3211,121 +3211,121 @@
         <v>16.86</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>12</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
-          <t>03.08–09.08*</t>
+          <t>03.08–09.08</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>7</v>
       </c>
       <c r="Q5" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3714,121 +3714,121 @@
         <v>79977173</v>
       </c>
       <c r="Q6" s="40" t="n">
-        <v>35933735</v>
+        <v>91676410</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>51530060</v>
+        <v>67906121</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>42921870</v>
+        <v>84229530</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>33088394</v>
+        <v>85043089</v>
       </c>
     </row>
     <row r="9">
@@ -3885,292 +3885,292 @@
         <v>41613311</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>19260848</v>
+        <v>43739350</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>39462393</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51983942</v>
+        <v>68694825</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58935844</v>
+        <v>48824266</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>38454971</v>
+        <v>57556194</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>42939312</v>
+        <v>38323101</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>43650420</v>
+        <v>40276838</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>23587042</v>
+        <v>45419704</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>17664217</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>21748722</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>38313932</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>49313727</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>41788221</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>36755638</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>43259404</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>68694825</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>48824266</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>57556194</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>38323101</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>40276838</v>
+        <v>43650420</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>19066933</v>
+        <v>53954095</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>44250621</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>29608597</v>
+        <v>35343350</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>25219748</v>
+        <v>51225290</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>28515437</v>
+        <v>36142612</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>18963950</v>
+        <v>47488940</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>6239584</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>13803407</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>28572076</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>15282581</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>16594572</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>15223898</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>27696695</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>17717888</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>24163432</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>23623477</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>19145601</v>
+        <v>29608597</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>30157601</v>
+        <v>25219748</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>41172333</v>
+        <v>28515437</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>21288956</v>
+        <v>35235670</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>536260</v>
+        <v>6239584</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14403556</v>
+        <v>13803407</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>16216832</v>
+        <v>28572076</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32622053</v>
+        <v>15282581</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>23929705</v>
+        <v>16594572</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37214538</v>
+        <v>15223898</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25375430</v>
+        <v>27696695</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>31500087</v>
+        <v>17717888</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28078687</v>
+        <v>24163432</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>34472458</v>
+        <v>23623477</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>35343350</v>
+        <v>19145601</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>51225290</v>
+        <v>30157601</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>36142612</v>
+        <v>41172333</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>12941311</v>
+        <v>34303423</v>
       </c>
     </row>
     <row r="15">
@@ -4227,235 +4227,235 @@
         <v>31820447</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>9398580</v>
+        <v>31875986</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>5092853</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11100161</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14612055</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>20638987</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14061352</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>31599148</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>18747614</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>19576415</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>14226838</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23197145</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>25790711</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>27856115</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>20981901</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>9885316</v>
+        <v>36312415</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>11884771</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10651216</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>13882033</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>17812948</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17331854</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>26294756</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>24196222</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>22122847</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>31914115</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>32069521</v>
+        <v>23197145</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>38287475</v>
+        <v>25790711</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>28283704</v>
+        <v>27856115</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>27334091</v>
+        <v>20981901</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>16692195</v>
+        <v>25433123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>23801493</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13949368</v>
+        <v>27940611</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>24539413</v>
+        <v>27893929</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19087217</v>
+        <v>29635773</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>17139440</v>
+        <v>19554230</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>17746930</v>
+        <v>23848495</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>11582350</v>
+        <v>24194638</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>10570508</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>11896580</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19614352</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>20966317</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>20073400</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>23801493</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>27940611</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>27893929</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>29635773</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>19554230</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>23848495</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>12782818</v>
+        <v>21437830</v>
       </c>
     </row>
     <row r="20">
@@ -4512,7 +4512,7 @@
         <v>20822247</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>3746355</v>
+        <v>20014322</v>
       </c>
     </row>
     <row r="21">
@@ -4569,121 +4569,121 @@
         <v>37105387</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>6106227</v>
+        <v>19868191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>7767470</v>
+        <v>10400980</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>3020680</v>
+        <v>10264941</v>
       </c>
     </row>
     <row r="24">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="Q4" s="31" t="inlineStr">
         <is>
-          <t>03.08–09.08*</t>
+          <t>03.08–09.08</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
         <v>7</v>
       </c>
       <c r="Q5" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -5072,28 +5072,28 @@
         <v>7</v>
       </c>
       <c r="Q6" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -5129,28 +5129,28 @@
         <v>7</v>
       </c>
       <c r="Q7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -5186,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="Q8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -5243,28 +5243,28 @@
         <v>7</v>
       </c>
       <c r="Q9" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -5300,28 +5300,28 @@
         <v>7</v>
       </c>
       <c r="Q10" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -5357,25 +5357,25 @@
         <v>7</v>
       </c>
       <c r="Q11" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -5414,25 +5414,25 @@
         <v>7</v>
       </c>
       <c r="Q12" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -5471,25 +5471,25 @@
         <v>7</v>
       </c>
       <c r="Q13" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -5528,7 +5528,7 @@
         <v>7</v>
       </c>
       <c r="Q14" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -5585,25 +5585,25 @@
         <v>7</v>
       </c>
       <c r="Q15" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5642,25 +5642,25 @@
         <v>7</v>
       </c>
       <c r="Q16" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5699,34 +5699,34 @@
         <v>7</v>
       </c>
       <c r="Q17" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -5756,34 +5756,34 @@
         <v>7</v>
       </c>
       <c r="Q18" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -5813,7 +5813,7 @@
         <v>7</v>
       </c>
       <c r="Q19" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -5870,7 +5870,7 @@
         <v>7</v>
       </c>
       <c r="Q20" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -5927,31 +5927,31 @@
         <v>7</v>
       </c>
       <c r="Q21" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -5972,7 +5972,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -5984,31 +5984,31 @@
         <v>7</v>
       </c>
       <c r="Q22" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -6029,7 +6029,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
@@ -6041,7 +6041,7 @@
         <v>7</v>
       </c>
       <c r="Q23" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2049,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2069,6 +2069,7 @@
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
+    <col width="13" customWidth="1" style="20" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2161,6 +2162,11 @@
           <t>2026-08-03</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2246,6 +2252,11 @@
       <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>03.08–09.08</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>10.08–16.08*</t>
         </is>
       </c>
     </row>
@@ -2301,6 +2312,9 @@
       <c r="Q5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="R5" s="34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2358,6 +2372,9 @@
       <c r="Q6" s="36" t="n">
         <v>80.56999999999999</v>
       </c>
+      <c r="R6" s="36" t="n">
+        <v>89.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2415,6 +2432,9 @@
       <c r="Q7" s="36" t="n">
         <v>78.86</v>
       </c>
+      <c r="R7" s="36" t="n">
+        <v>72.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2472,233 +2492,248 @@
       <c r="Q8" s="36" t="n">
         <v>65.56999999999999</v>
       </c>
+      <c r="R8" s="36" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41.29</v>
+        <v>41</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>41.43</v>
+        <v>48</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>46.14</v>
+        <v>49.43</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>41.57</v>
+        <v>45.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>51.86</v>
+        <v>43</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>48.71</v>
+        <v>46.57</v>
+      </c>
+      <c r="R9" s="36" t="n">
+        <v>46.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>48</v>
+        <v>41.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>49.43</v>
+        <v>46.14</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>45.57</v>
+        <v>41.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>43</v>
+        <v>51.86</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>46.57</v>
+        <v>48.71</v>
+      </c>
+      <c r="R10" s="36" t="n">
+        <v>44.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
+      </c>
+      <c r="R11" s="36" t="n">
+        <v>44.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
+      </c>
+      <c r="R12" s="36" t="n">
+        <v>38.67</v>
       </c>
     </row>
     <row r="13">
@@ -2757,6 +2792,9 @@
       <c r="Q13" s="36" t="n">
         <v>31.29</v>
       </c>
+      <c r="R13" s="36" t="n">
+        <v>35.67</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -2814,290 +2852,308 @@
       <c r="Q14" s="36" t="n">
         <v>29.14</v>
       </c>
+      <c r="R14" s="36" t="n">
+        <v>26.67</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
+      </c>
+      <c r="R15" s="36" t="n">
+        <v>24.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>3.33</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>6.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>17.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>16.14</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>18.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.14</v>
+        <v>16.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>27.57</v>
+        <v>21.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.43</v>
+        <v>20.86</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>27.29</v>
+        <v>20.86</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>26.57</v>
+        <v>21.86</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>25.57</v>
+        <v>28.71</v>
+      </c>
+      <c r="R16" s="36" t="n">
+        <v>21.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>24.43</v>
+        <v>22.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>24.71</v>
+        <v>22.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>25.57</v>
+        <v>20.14</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>19.29</v>
+        <v>15.71</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>25.43</v>
+        <v>19.43</v>
+      </c>
+      <c r="R17" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.43</v>
+        <v>10.57</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>11.86</v>
+        <v>11.14</v>
       </c>
       <c r="H18" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I18" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I18" s="36" t="n">
-        <v>19.14</v>
-      </c>
       <c r="J18" s="36" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>23.43</v>
+        <v>17.43</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>20.43</v>
+        <v>15.29</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>24.57</v>
+        <v>24.43</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>24.14</v>
+        <v>24.71</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>24.43</v>
+        <v>25.57</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>22</v>
+        <v>19.29</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>23</v>
+        <v>25.43</v>
+      </c>
+      <c r="R18" s="36" t="n">
+        <v>18.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J19" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="L19" s="36" t="n">
         <v>20.43</v>
       </c>
-      <c r="K19" s="36" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>15</v>
-      </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>24.57</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>24.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>24.43</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="36" t="n">
+        <v>16.33</v>
       </c>
     </row>
     <row r="20">
@@ -3156,6 +3212,9 @@
       <c r="Q20" s="36" t="n">
         <v>15.29</v>
       </c>
+      <c r="R20" s="36" t="n">
+        <v>14.67</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -3213,119 +3272,128 @@
       <c r="Q21" s="36" t="n">
         <v>15</v>
       </c>
+      <c r="R21" s="36" t="n">
+        <v>11.67</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
+      </c>
+      <c r="R22" s="36" t="n">
+        <v>7.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H23" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>10.29</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3393,6 +3461,10 @@
       </c>
       <c r="Q24" s="39">
         <f>AVERAGE(Q6:Q23)</f>
+        <v/>
+      </c>
+      <c r="R24" s="39">
+        <f>AVERAGE(R6:R23)</f>
         <v/>
       </c>
     </row>
@@ -3407,7 +3479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3427,6 +3499,7 @@
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
+    <col width="13" customWidth="1" style="20" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3519,6 +3592,11 @@
           <t>2026-08-03</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3604,6 +3682,11 @@
       <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>03.08–09.08</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>10.08–16.08*</t>
         </is>
       </c>
     </row>
@@ -3659,6 +3742,9 @@
       <c r="Q5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="R5" s="34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -3716,6 +3802,9 @@
       <c r="Q6" s="40" t="n">
         <v>91676410</v>
       </c>
+      <c r="R6" s="40" t="n">
+        <v>38375482</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -3773,6 +3862,9 @@
       <c r="Q7" s="40" t="n">
         <v>84229530</v>
       </c>
+      <c r="R7" s="40" t="n">
+        <v>45524935</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -3830,233 +3922,248 @@
       <c r="Q8" s="40" t="n">
         <v>85043089</v>
       </c>
+      <c r="R8" s="40" t="n">
+        <v>30692633</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>42012092</v>
+        <v>68694825</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58722069</v>
+        <v>48824266</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>48135084</v>
+        <v>57556194</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>44293878</v>
+        <v>38323101</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>41613311</v>
+        <v>40276838</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>43739350</v>
+        <v>45419704</v>
+      </c>
+      <c r="R9" s="40" t="n">
+        <v>28331799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>68694825</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>48824266</v>
+        <v>58722069</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>57556194</v>
+        <v>48135084</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>38323101</v>
+        <v>44293878</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>40276838</v>
+        <v>41613311</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>45419704</v>
+        <v>43739350</v>
+      </c>
+      <c r="R10" s="40" t="n">
+        <v>25997643</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
+      </c>
+      <c r="R11" s="40" t="n">
+        <v>23009036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
+      </c>
+      <c r="R12" s="40" t="n">
+        <v>18623266</v>
       </c>
     </row>
     <row r="13">
@@ -4115,6 +4222,9 @@
       <c r="Q13" s="40" t="n">
         <v>35235670</v>
       </c>
+      <c r="R13" s="40" t="n">
+        <v>17179814</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -4172,290 +4282,308 @@
       <c r="Q14" s="40" t="n">
         <v>34303423</v>
       </c>
+      <c r="R14" s="40" t="n">
+        <v>24401064</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
+      </c>
+      <c r="R15" s="40" t="n">
+        <v>14645026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>3249588</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>7305524</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>9575225</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>9264589</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>20692424</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>27565767</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>19138015</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>24912292</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>19068954</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>25387051</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>21008637</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>30862574</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>31820447</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>31875986</v>
+      </c>
+      <c r="R16" s="40" t="n">
+        <v>16514250</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23197145</v>
+        <v>24539413</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>25790711</v>
+        <v>19087217</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27856115</v>
+        <v>17139440</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20981901</v>
+        <v>17746930</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>25433123</v>
+        <v>21437830</v>
+      </c>
+      <c r="R17" s="40" t="n">
+        <v>6339682</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>8544625</v>
+        <v>5092853</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>8387478</v>
+        <v>11100161</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>10570508</v>
+        <v>14612055</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>11896580</v>
+        <v>20638987</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19614352</v>
+        <v>14061352</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>20966317</v>
+        <v>31599148</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>20073400</v>
+        <v>18747614</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>23801493</v>
+        <v>19576415</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>27940611</v>
+        <v>14226838</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>27893929</v>
+        <v>23197145</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>29635773</v>
+        <v>25790711</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>19554230</v>
+        <v>27856115</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>23848495</v>
+        <v>20981901</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>24194638</v>
+        <v>25433123</v>
+      </c>
+      <c r="R18" s="40" t="n">
+        <v>7077251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>23801493</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>27940611</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>27893929</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>29635773</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>19554230</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>23848495</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>24194638</v>
+      </c>
+      <c r="R19" s="40" t="n">
+        <v>7272615</v>
       </c>
     </row>
     <row r="20">
@@ -4514,6 +4642,9 @@
       <c r="Q20" s="40" t="n">
         <v>20014322</v>
       </c>
+      <c r="R20" s="40" t="n">
+        <v>5192900</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -4571,119 +4702,128 @@
       <c r="Q21" s="40" t="n">
         <v>19868191</v>
       </c>
+      <c r="R21" s="40" t="n">
+        <v>4888990</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
+      </c>
+      <c r="R22" s="40" t="n">
+        <v>2695237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
+      </c>
+      <c r="R23" s="40" t="n">
+        <v>2647110</v>
       </c>
     </row>
     <row r="24">
@@ -4751,6 +4891,10 @@
       </c>
       <c r="Q24" s="41">
         <f>AVERAGE(Q6:Q23)</f>
+        <v/>
+      </c>
+      <c r="R24" s="41">
+        <f>AVERAGE(R6:R23)</f>
         <v/>
       </c>
     </row>
@@ -4765,7 +4909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4785,6 +4929,7 @@
     <col width="13" customWidth="1" style="20" min="15" max="15"/>
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
+    <col width="13" customWidth="1" style="20" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4877,6 +5022,11 @@
           <t>2026-08-03</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4962,6 +5112,11 @@
       <c r="Q4" s="31" t="inlineStr">
         <is>
           <t>03.08–09.08</t>
+        </is>
+      </c>
+      <c r="R4" s="31" t="inlineStr">
+        <is>
+          <t>10.08–16.08*</t>
         </is>
       </c>
     </row>
@@ -5017,6 +5172,9 @@
       <c r="Q5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="R5" s="34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -5074,6 +5232,9 @@
       <c r="Q6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R6" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -5131,6 +5292,9 @@
       <c r="Q7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R7" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -5188,80 +5352,86 @@
       <c r="Q8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R8" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -5301,27 +5471,30 @@
       </c>
       <c r="Q10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R10" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -5358,63 +5531,69 @@
       </c>
       <c r="Q11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R11" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -5473,6 +5652,9 @@
       <c r="Q13" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R13" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -5530,80 +5712,86 @@
       <c r="Q14" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R14" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q15" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5643,34 +5831,37 @@
       </c>
       <c r="Q16" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
       </c>
@@ -5700,24 +5891,27 @@
       </c>
       <c r="Q17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R17" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -5757,33 +5951,36 @@
       </c>
       <c r="Q18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R18" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -5814,6 +6011,9 @@
       </c>
       <c r="Q19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R19" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -5872,6 +6072,9 @@
       <c r="Q20" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R20" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -5929,29 +6132,32 @@
       <c r="Q21" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="R21" s="42" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -5972,7 +6178,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -5985,63 +6191,69 @@
       </c>
       <c r="Q22" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="R22" s="42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q23" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6111,6 +6323,10 @@
         <f>AVERAGE(Q6:Q23)</f>
         <v/>
       </c>
+      <c r="R24" s="43">
+        <f>AVERAGE(R6:R23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2313,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2373,7 +2373,7 @@
         <v>80.56999999999999</v>
       </c>
       <c r="R6" s="36" t="n">
-        <v>89.67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -2433,7 +2433,7 @@
         <v>78.86</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>72.67</v>
+        <v>77.17</v>
       </c>
     </row>
     <row r="8">
@@ -2493,247 +2493,247 @@
         <v>65.56999999999999</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>35.14</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41</v>
+        <v>41.29</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>48</v>
+        <v>41.43</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>49.43</v>
+        <v>46.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>45.57</v>
+        <v>41.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>43</v>
+        <v>51.86</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>46.57</v>
+        <v>48.71</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>46.67</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>41</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>41.43</v>
+        <v>48</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>46.14</v>
+        <v>49.43</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>41.57</v>
+        <v>45.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>51.86</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>48.71</v>
+        <v>46.57</v>
       </c>
       <c r="R10" s="36" t="n">
-        <v>44.67</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>44.33</v>
+        <v>39.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>38.67</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="13">
@@ -2793,127 +2793,127 @@
         <v>31.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>35.67</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>7</v>
+        <v>9.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>16</v>
+        <v>12.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>19.43</v>
+        <v>13.29</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>15.86</v>
+        <v>14.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>14.86</v>
+        <v>17</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>16.71</v>
+        <v>19.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>19.71</v>
+        <v>17.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>16.86</v>
+        <v>19.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.86</v>
+        <v>24.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>23.43</v>
+        <v>27.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>19.43</v>
+        <v>24.43</v>
       </c>
       <c r="O14" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="P14" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q14" s="36" t="n">
         <v>25.57</v>
       </c>
-      <c r="P14" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q14" s="36" t="n">
-        <v>29.14</v>
-      </c>
       <c r="R14" s="36" t="n">
-        <v>26.67</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>7</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>16</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>19.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>15.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="36" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="J15" s="36" t="n">
         <v>19.71</v>
       </c>
-      <c r="J15" s="36" t="n">
-        <v>17.71</v>
-      </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>16.86</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.14</v>
+        <v>24.86</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>27.57</v>
+        <v>23.43</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.43</v>
+        <v>19.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>26.57</v>
+        <v>27.43</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>25.57</v>
+        <v>29.14</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>24.67</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="16">
@@ -2973,127 +2973,127 @@
         <v>28.71</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>21.33</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>21.71</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>22.71</v>
+        <v>24.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>22.43</v>
+        <v>24.71</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.14</v>
+        <v>25.57</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.71</v>
+        <v>19.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>19.43</v>
+        <v>25.43</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>20</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>24.43</v>
+        <v>22.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>24.71</v>
+        <v>22.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>25.57</v>
+        <v>20.14</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>19.29</v>
+        <v>15.71</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>25.43</v>
+        <v>19.43</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>18.67</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="19">
@@ -3153,7 +3153,7 @@
         <v>23</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>16.33</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="20">
@@ -3213,7 +3213,7 @@
         <v>15.29</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>14.67</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="21">
@@ -3273,7 +3273,7 @@
         <v>15</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>11.67</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="22">
@@ -3333,7 +3333,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>7.67</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="23">
@@ -3393,7 +3393,7 @@
         <v>10.29</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="24">
@@ -3743,7 +3743,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3803,7 +3803,7 @@
         <v>91676410</v>
       </c>
       <c r="R6" s="40" t="n">
-        <v>38375482</v>
+        <v>72606071</v>
       </c>
     </row>
     <row r="7">
@@ -3863,7 +3863,7 @@
         <v>84229530</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>45524935</v>
+        <v>79075084</v>
       </c>
     </row>
     <row r="8">
@@ -3923,247 +3923,247 @@
         <v>85043089</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>30692633</v>
+        <v>58525703</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>43259404</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>68694825</v>
+        <v>42012092</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>48824266</v>
+        <v>58722069</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>57556194</v>
+        <v>48135084</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>38323101</v>
+        <v>44293878</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>40276838</v>
+        <v>41613311</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>45419704</v>
+        <v>43739350</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>28331799</v>
+        <v>71740410</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>68694825</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58722069</v>
+        <v>48824266</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>48135084</v>
+        <v>57556194</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>44293878</v>
+        <v>38323101</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>41613311</v>
+        <v>40276838</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>43739350</v>
+        <v>45419704</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>25997643</v>
+        <v>43567502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>23009036</v>
+        <v>32823793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>18623266</v>
+        <v>38024392</v>
       </c>
     </row>
     <row r="13">
@@ -4223,127 +4223,127 @@
         <v>35235670</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>17179814</v>
+        <v>33565709</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>6239584</v>
+        <v>11884771</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>13803407</v>
+        <v>10651216</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>28572076</v>
+        <v>13882033</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>15282581</v>
+        <v>17812948</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>16594572</v>
+        <v>17331854</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>15223898</v>
+        <v>26294756</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>27696695</v>
+        <v>24196222</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>17717888</v>
+        <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>24163432</v>
+        <v>31914115</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>23623477</v>
+        <v>32069521</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>19145601</v>
+        <v>38287475</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>30157601</v>
+        <v>28283704</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>41172333</v>
+        <v>27334091</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>34303423</v>
+        <v>36312415</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>24401064</v>
+        <v>32332541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>6239584</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>13803407</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>28572076</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>15282581</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>16594572</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>15223898</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>27696695</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>17717888</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>31914115</v>
+        <v>24163432</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>32069521</v>
+        <v>23623477</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38287475</v>
+        <v>19145601</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>28283704</v>
+        <v>30157601</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>27334091</v>
+        <v>41172333</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>36312415</v>
+        <v>34303423</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>14645026</v>
+        <v>32525879</v>
       </c>
     </row>
     <row r="16">
@@ -4403,127 +4403,127 @@
         <v>31875986</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>16514250</v>
+        <v>43419014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>24539413</v>
+        <v>23197145</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19087217</v>
+        <v>25790711</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>17139440</v>
+        <v>27856115</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>17746930</v>
+        <v>20981901</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>21437830</v>
+        <v>25433123</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>6339682</v>
+        <v>18290763</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>14226838</v>
+        <v>13949368</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>23197145</v>
+        <v>24539413</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>25790711</v>
+        <v>19087217</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>27856115</v>
+        <v>17139440</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>20981901</v>
+        <v>17746930</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>25433123</v>
+        <v>21437830</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>7077251</v>
+        <v>15259467</v>
       </c>
     </row>
     <row r="19">
@@ -4583,7 +4583,7 @@
         <v>24194638</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>7272615</v>
+        <v>17525964</v>
       </c>
     </row>
     <row r="20">
@@ -4643,7 +4643,7 @@
         <v>20014322</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>5192900</v>
+        <v>15042489</v>
       </c>
     </row>
     <row r="21">
@@ -4703,7 +4703,7 @@
         <v>19868191</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>4888990</v>
+        <v>13934800</v>
       </c>
     </row>
     <row r="22">
@@ -4763,7 +4763,7 @@
         <v>10264941</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>2695237</v>
+        <v>5499950</v>
       </c>
     </row>
     <row r="23">
@@ -4823,7 +4823,7 @@
         <v>10400980</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>2647110</v>
+        <v>5196872</v>
       </c>
     </row>
     <row r="24">
@@ -5173,7 +5173,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -5233,7 +5233,7 @@
         <v>7</v>
       </c>
       <c r="R6" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -5293,7 +5293,7 @@
         <v>7</v>
       </c>
       <c r="R7" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5353,25 +5353,25 @@
         <v>7</v>
       </c>
       <c r="R8" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -5413,25 +5413,25 @@
         <v>7</v>
       </c>
       <c r="R9" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -5473,28 +5473,28 @@
         <v>7</v>
       </c>
       <c r="R10" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -5533,28 +5533,28 @@
         <v>7</v>
       </c>
       <c r="R11" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -5593,7 +5593,7 @@
         <v>7</v>
       </c>
       <c r="R12" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -5653,25 +5653,25 @@
         <v>7</v>
       </c>
       <c r="R13" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -5713,25 +5713,25 @@
         <v>7</v>
       </c>
       <c r="R14" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5773,7 +5773,7 @@
         <v>7</v>
       </c>
       <c r="R15" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -5833,95 +5833,95 @@
         <v>7</v>
       </c>
       <c r="R16" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" s="42" t="n">
         <v>6</v>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>7</v>
       </c>
       <c r="R18" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -6013,7 +6013,7 @@
         <v>7</v>
       </c>
       <c r="R19" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -6073,7 +6073,7 @@
         <v>7</v>
       </c>
       <c r="R20" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6133,7 +6133,7 @@
         <v>7</v>
       </c>
       <c r="R21" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="R22" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -6253,7 +6253,7 @@
         <v>7</v>
       </c>
       <c r="R23" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2049,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2070,6 +2070,7 @@
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
     <col width="13" customWidth="1" style="20" min="18" max="18"/>
+    <col width="13" customWidth="1" style="20" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2167,6 +2168,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2256,7 +2262,12 @@
       </c>
       <c r="R4" s="31" t="inlineStr">
         <is>
-          <t>10.08–16.08*</t>
+          <t>10.08–16.08</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>17.08–23.08*</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2324,10 @@
         <v>7</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2373,247 +2387,262 @@
         <v>80.56999999999999</v>
       </c>
       <c r="R6" s="36" t="n">
-        <v>82</v>
+        <v>82.14</v>
+      </c>
+      <c r="S6" s="36" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>78.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>77.17</v>
+        <v>67.29000000000001</v>
+      </c>
+      <c r="S7" s="36" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>49.29</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>68.5</v>
+        <v>78.43000000000001</v>
+      </c>
+      <c r="S8" s="36" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>1.67</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>12.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>16.57</v>
       </c>
       <c r="G9" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="J9" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="K9" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="L9" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="H9" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="I9" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="J9" s="36" t="n">
-        <v>33</v>
-      </c>
-      <c r="K9" s="36" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="L9" s="36" t="n">
-        <v>41.29</v>
-      </c>
       <c r="M9" s="36" t="n">
-        <v>41.43</v>
+        <v>28.86</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>46.14</v>
+        <v>33.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>41.57</v>
+        <v>30.71</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>51.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>48.71</v>
+        <v>40.29</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>45.17</v>
+        <v>38.71</v>
+      </c>
+      <c r="S9" s="36" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>48</v>
+        <v>41.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>49.43</v>
+        <v>46.14</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>45.57</v>
+        <v>41.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>43</v>
+        <v>51.86</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>46.57</v>
+        <v>48.71</v>
       </c>
       <c r="R10" s="36" t="n">
-        <v>44.17</v>
+        <v>45.14</v>
+      </c>
+      <c r="S10" s="36" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -2673,558 +2702,588 @@
         <v>42.86</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>39.67</v>
+        <v>40.71</v>
+      </c>
+      <c r="S11" s="36" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>7.25</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>18.71</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>21.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>30.29</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>38</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>39.71</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>41.71</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>35.14</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>41</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.86</v>
+        <v>48</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>49.43</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>45.57</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>31.14</v>
+        <v>43</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>40.29</v>
+        <v>46.57</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>39.17</v>
+        <v>48.43</v>
+      </c>
+      <c r="S12" s="36" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>7</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>16</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>19.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>15.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>14.86</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>16.71</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>19.71</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>16.86</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>24.86</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>23.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>31.14</v>
+        <v>19.43</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30</v>
+        <v>25.57</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>30.43</v>
+        <v>27.43</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>31.29</v>
+        <v>29.14</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>36.67</v>
+        <v>25</v>
+      </c>
+      <c r="S13" s="36" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.43</v>
+        <v>8.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.43</v>
+        <v>13.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.29</v>
+        <v>21.71</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>14.71</v>
+        <v>16.57</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>17</v>
+        <v>21.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>17.71</v>
+        <v>23.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>19.57</v>
+        <v>22.43</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>27.57</v>
+        <v>28.14</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.43</v>
+        <v>31.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>27.29</v>
+        <v>30</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>26.57</v>
+        <v>30.43</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>25.57</v>
+        <v>31.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>27.67</v>
+        <v>36.14</v>
+      </c>
+      <c r="S14" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>19.43</v>
+        <v>20.86</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>25.57</v>
+        <v>20.86</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>27.43</v>
+        <v>21.86</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>29.14</v>
+        <v>28.71</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>25.17</v>
+        <v>24.71</v>
+      </c>
+      <c r="S15" s="36" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>24.5</v>
+        <v>29</v>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>23.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>20.43</v>
       </c>
       <c r="M17" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N17" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="O17" s="36" t="n">
         <v>24.43</v>
       </c>
-      <c r="N17" s="36" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="O17" s="36" t="n">
-        <v>25.57</v>
-      </c>
       <c r="P17" s="36" t="n">
-        <v>19.29</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>25.43</v>
+        <v>23</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>23.67</v>
+        <v>18.43</v>
+      </c>
+      <c r="S17" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>11.29</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>10.57</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>11.14</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>13.86</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>18</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>20.43</v>
+        <v>18</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>21.71</v>
+        <v>17.43</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>22.71</v>
+        <v>24.43</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>22.43</v>
+        <v>24.71</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.14</v>
+        <v>25.57</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>15.71</v>
+        <v>19.29</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>19.43</v>
+        <v>25.43</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>20.83</v>
+        <v>22.57</v>
+      </c>
+      <c r="S18" s="36" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.43</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>11.86</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>18</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19.14</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>20.43</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>24.57</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>24.43</v>
+        <v>20.14</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>22</v>
+        <v>15.71</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>23</v>
+        <v>19.43</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>18.33</v>
+        <v>20.29</v>
+      </c>
+      <c r="S19" s="36" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I20" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H20" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I20" s="36" t="n">
+      <c r="J20" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L20" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M20" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N20" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="J20" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K20" s="36" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="M20" s="36" t="n">
+      <c r="O20" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P20" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q20" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R20" s="36" t="n">
         <v>14.71</v>
       </c>
-      <c r="N20" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="O20" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="P20" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="Q20" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="R20" s="36" t="n">
-        <v>17.67</v>
+      <c r="S20" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
@@ -3237,43 +3296,46 @@
         <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>6</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>4.43</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>3.43</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11.86</v>
+        <v>5.71</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>19</v>
+        <v>7.43</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>19.57</v>
+        <v>5</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>16.86</v>
+        <v>7.71</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>15</v>
+        <v>10.29</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>15.17</v>
+        <v>7</v>
+      </c>
+      <c r="S21" s="36" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -3333,67 +3395,73 @@
         <v>9.289999999999999</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>9.83</v>
+        <v>9.289999999999999</v>
+      </c>
+      <c r="S22" s="36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>2.8</v>
+        <v>13.43</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4</v>
+        <v>12.71</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>6</v>
+        <v>14.43</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>4.43</v>
+        <v>19</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>3.43</v>
+        <v>21.14</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>5.86</v>
+        <v>18.57</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.71</v>
+        <v>16.57</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>6</v>
+        <v>14.71</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>7.43</v>
+        <v>19.14</v>
       </c>
       <c r="O23" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="P23" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="Q23" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="S23" s="36" t="n">
         <v>5</v>
-      </c>
-      <c r="P23" s="36" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="Q23" s="36" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="R23" s="36" t="n">
-        <v>6.5</v>
       </c>
     </row>
     <row r="24">
@@ -3465,6 +3533,10 @@
       </c>
       <c r="R24" s="39">
         <f>AVERAGE(R6:R23)</f>
+        <v/>
+      </c>
+      <c r="S24" s="39">
+        <f>AVERAGE(S6:S23)</f>
         <v/>
       </c>
     </row>
@@ -3479,7 +3551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3500,6 +3572,7 @@
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
     <col width="13" customWidth="1" style="20" min="18" max="18"/>
+    <col width="13" customWidth="1" style="20" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3597,6 +3670,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3686,7 +3764,12 @@
       </c>
       <c r="R4" s="31" t="inlineStr">
         <is>
-          <t>10.08–16.08*</t>
+          <t>10.08–16.08</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>17.08–23.08*</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3826,10 @@
         <v>7</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3803,247 +3889,262 @@
         <v>91676410</v>
       </c>
       <c r="R6" s="40" t="n">
-        <v>72606071</v>
+        <v>85717459</v>
+      </c>
+      <c r="S6" s="40" t="n">
+        <v>15147542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>84229530</v>
+        <v>85043089</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>79075084</v>
+        <v>67469168</v>
+      </c>
+      <c r="S7" s="40" t="n">
+        <v>11256320</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>51530060</v>
+        <v>67906121</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>85043089</v>
+        <v>84229530</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>58525703</v>
+        <v>92096471</v>
+      </c>
+      <c r="S8" s="40" t="n">
+        <v>7646273</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>536260</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>14403556</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>16216832</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>32622053</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>23929705</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>37214538</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>25375430</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>31500087</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>42012092</v>
+        <v>28078687</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58722069</v>
+        <v>34472458</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>48135084</v>
+        <v>35343350</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>44293878</v>
+        <v>51225290</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>41613311</v>
+        <v>36142612</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>43739350</v>
+        <v>47488940</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>71740410</v>
+        <v>44805002</v>
+      </c>
+      <c r="S9" s="40" t="n">
+        <v>8577530</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>68694825</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>48824266</v>
+        <v>58722069</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>57556194</v>
+        <v>48135084</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>38323101</v>
+        <v>44293878</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>40276838</v>
+        <v>41613311</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>45419704</v>
+        <v>43739350</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>43567502</v>
+        <v>78234960</v>
+      </c>
+      <c r="S10" s="40" t="n">
+        <v>5749350</v>
       </c>
     </row>
     <row r="11">
@@ -4103,558 +4204,588 @@
         <v>53954095</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>32823793</v>
+        <v>48898463</v>
+      </c>
+      <c r="S11" s="40" t="n">
+        <v>3489260</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>3771593</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>17664217</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>21748722</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>38313932</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>49313727</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>41788221</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>36755638</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>43259404</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>68694825</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>48824266</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>57556194</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>38323101</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>36142612</v>
+        <v>40276838</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>47488940</v>
+        <v>45419704</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>38024392</v>
+        <v>55923182</v>
+      </c>
+      <c r="S12" s="40" t="n">
+        <v>4116300</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>6239584</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>13803407</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>28572076</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>15282581</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>16594572</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>15223898</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>27696695</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>17717888</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>24163432</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>23623477</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>19145601</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>30157601</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>28515437</v>
+        <v>41172333</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>35235670</v>
+        <v>34303423</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>33565709</v>
+        <v>35044850</v>
+      </c>
+      <c r="S13" s="40" t="n">
+        <v>5772649</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>475871</v>
+        <v>251520</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11884771</v>
+        <v>10351067</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>10651216</v>
+        <v>21091580</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>13882033</v>
+        <v>24243567</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>17812948</v>
+        <v>16381412</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>17331854</v>
+        <v>21591272</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>26294756</v>
+        <v>21904190</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>24196222</v>
+        <v>25438080</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>22122847</v>
+        <v>24614280</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>31914115</v>
+        <v>28889771</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>32069521</v>
+        <v>44250621</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>38287475</v>
+        <v>29608597</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>28283704</v>
+        <v>25219748</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>27334091</v>
+        <v>28515437</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>36312415</v>
+        <v>35235670</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>32332541</v>
+        <v>38511490</v>
+      </c>
+      <c r="S14" s="40" t="n">
+        <v>5708487</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>23623477</v>
+        <v>25387051</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>19145601</v>
+        <v>21008637</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30157601</v>
+        <v>30862574</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>41172333</v>
+        <v>31820447</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>34303423</v>
+        <v>31875986</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>32525879</v>
+        <v>48358034</v>
+      </c>
+      <c r="S15" s="40" t="n">
+        <v>4387770</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>43419014</v>
+        <v>39333565</v>
+      </c>
+      <c r="S16" s="40" t="n">
+        <v>3363110</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>23801493</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>27940611</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23197145</v>
+        <v>27893929</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>25790711</v>
+        <v>29635773</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27856115</v>
+        <v>19554230</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20981901</v>
+        <v>23848495</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>25433123</v>
+        <v>24194638</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>18290763</v>
+        <v>20330094</v>
+      </c>
+      <c r="S17" s="40" t="n">
+        <v>1882070</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>11100161</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>14612055</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>20638987</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>14061352</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>31599148</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>18747614</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>19576415</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13949368</v>
+        <v>14226838</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>24539413</v>
+        <v>23197145</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19087217</v>
+        <v>25790711</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>17139440</v>
+        <v>27856115</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>17746930</v>
+        <v>20981901</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>21437830</v>
+        <v>25433123</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>15259467</v>
+        <v>19355230</v>
+      </c>
+      <c r="S18" s="40" t="n">
+        <v>1616530</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>10570508</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>11896580</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19614352</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>20966317</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>20073400</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>23801493</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>27940611</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>27893929</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>29635773</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>19554230</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>23848495</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>24194638</v>
+        <v>21437830</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17525964</v>
+        <v>17616397</v>
+      </c>
+      <c r="S19" s="40" t="n">
+        <v>1654860</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>23276090</v>
+        <v>38267409</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>27906254</v>
+        <v>46351274</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>20822247</v>
+        <v>37105387</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>20014322</v>
+        <v>19868191</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>15042489</v>
+        <v>15153480</v>
+      </c>
+      <c r="S20" s="40" t="n">
+        <v>2771020</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
@@ -4667,43 +4798,46 @@
         <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>1339100</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>5579340</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>9518200</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>11747640</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>3885270</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>11732010</v>
+        <v>8765870</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21143100</v>
+        <v>4571680</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>14330970</v>
+        <v>3911995</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>38267409</v>
+        <v>9234090</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>46351274</v>
+        <v>5390260</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>37105387</v>
+        <v>4645370</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>19868191</v>
+        <v>10400980</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>13934800</v>
+        <v>6123322</v>
+      </c>
+      <c r="S21" s="40" t="n">
+        <v>1690050</v>
       </c>
     </row>
     <row r="22">
@@ -4763,67 +4897,73 @@
         <v>10264941</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>5499950</v>
+        <v>6114083</v>
+      </c>
+      <c r="S22" s="40" t="n">
+        <v>548250</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1339100</v>
+        <v>21387685</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>5579340</v>
+        <v>16050448</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>9518200</v>
+        <v>21568794</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>11747640</v>
+        <v>30845816</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>3885270</v>
+        <v>45285935</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>8765870</v>
+        <v>28941455</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4571680</v>
+        <v>21801828</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3911995</v>
+        <v>19628570</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>9234090</v>
+        <v>23276090</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>5390260</v>
+        <v>27906254</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>4645370</v>
+        <v>20822247</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10400980</v>
+        <v>20014322</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>5196872</v>
+        <v>19159625</v>
+      </c>
+      <c r="S23" s="40" t="n">
+        <v>481880</v>
       </c>
     </row>
     <row r="24">
@@ -4895,6 +5035,10 @@
       </c>
       <c r="R24" s="41">
         <f>AVERAGE(R6:R23)</f>
+        <v/>
+      </c>
+      <c r="S24" s="41">
+        <f>AVERAGE(S6:S23)</f>
         <v/>
       </c>
     </row>
@@ -4909,7 +5053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4930,6 +5074,7 @@
     <col width="13" customWidth="1" style="20" min="16" max="16"/>
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
     <col width="13" customWidth="1" style="20" min="18" max="18"/>
+    <col width="13" customWidth="1" style="20" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5027,6 +5172,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -5116,7 +5266,12 @@
       </c>
       <c r="R4" s="31" t="inlineStr">
         <is>
-          <t>10.08–16.08*</t>
+          <t>10.08–16.08</t>
+        </is>
+      </c>
+      <c r="S4" s="31" t="inlineStr">
+        <is>
+          <t>17.08–23.08*</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5328,10 @@
         <v>7</v>
       </c>
       <c r="R5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S5" s="34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5233,28 +5391,31 @@
         <v>7</v>
       </c>
       <c r="R6" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S6" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -5293,28 +5454,31 @@
         <v>7</v>
       </c>
       <c r="R7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S7" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -5353,26 +5517,29 @@
         <v>7</v>
       </c>
       <c r="R8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
       </c>
@@ -5413,25 +5580,28 @@
         <v>7</v>
       </c>
       <c r="R9" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -5473,7 +5643,10 @@
         <v>7</v>
       </c>
       <c r="R10" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5533,25 +5706,28 @@
         <v>7</v>
       </c>
       <c r="R11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -5593,82 +5769,88 @@
         <v>7</v>
       </c>
       <c r="R12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>7</v>
@@ -5713,25 +5895,28 @@
         <v>7</v>
       </c>
       <c r="R14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5773,25 +5958,28 @@
         <v>7</v>
       </c>
       <c r="R15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -5833,25 +6021,28 @@
         <v>7</v>
       </c>
       <c r="R16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -5893,34 +6084,37 @@
         <v>7</v>
       </c>
       <c r="R17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -5953,34 +6147,37 @@
         <v>7</v>
       </c>
       <c r="R18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -6013,31 +6210,34 @@
         <v>7</v>
       </c>
       <c r="R19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -6073,18 +6273,21 @@
         <v>7</v>
       </c>
       <c r="R20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
@@ -6097,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -6118,7 +6321,7 @@
         <v>7</v>
       </c>
       <c r="M21" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N21" s="42" t="n">
         <v>7</v>
@@ -6133,7 +6336,10 @@
         <v>7</v>
       </c>
       <c r="R21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -6193,31 +6399,34 @@
         <v>7</v>
       </c>
       <c r="R22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S22" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -6238,7 +6447,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
@@ -6253,7 +6462,10 @@
         <v>7</v>
       </c>
       <c r="R23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="S23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6327,6 +6539,10 @@
         <f>AVERAGE(R6:R23)</f>
         <v/>
       </c>
+      <c r="S24" s="43">
+        <f>AVERAGE(S6:S23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2327,7 +2327,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2390,322 +2390,322 @@
         <v>82.14</v>
       </c>
       <c r="S6" s="36" t="n">
-        <v>116</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>49.29</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S7" s="36" t="n">
-        <v>69</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K8" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>78.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>61</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>1.67</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>12.14</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>16.57</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>21</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>20.29</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>28.57</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>24.14</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>27.57</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>28.86</v>
+        <v>41.43</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>33.14</v>
+        <v>46.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>30.71</v>
+        <v>41.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>31.14</v>
+        <v>51.86</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>40.29</v>
+        <v>48.71</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>38.71</v>
+        <v>45.14</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>41.43</v>
+        <v>42.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>46.14</v>
+        <v>38.57</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>41.57</v>
+        <v>34.29</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>51.86</v>
+        <v>37.86</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>48.71</v>
+        <v>42.86</v>
       </c>
       <c r="R10" s="36" t="n">
-        <v>45.14</v>
+        <v>40.71</v>
       </c>
       <c r="S10" s="36" t="n">
-        <v>50</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>36</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="12">
@@ -2768,259 +2768,259 @@
         <v>48.43</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>7</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>16</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>19.43</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>15.86</v>
+        <v>16.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>14.86</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>16.71</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>19.71</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>16.86</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>24.86</v>
+        <v>22.43</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>23.43</v>
+        <v>28.14</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>19.43</v>
+        <v>31.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>25.57</v>
+        <v>30</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>27.43</v>
+        <v>30.43</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>29.14</v>
+        <v>31.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>25</v>
+        <v>36.14</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>34</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>8.43</v>
+        <v>7</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>13.43</v>
+        <v>16</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>21.71</v>
+        <v>19.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>16.57</v>
+        <v>15.86</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>21.29</v>
+        <v>14.86</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>21.14</v>
+        <v>16.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>23.29</v>
+        <v>19.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>22.43</v>
+        <v>16.86</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>22.43</v>
+        <v>24.86</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>28.14</v>
+        <v>23.43</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>31.14</v>
+        <v>19.43</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>30</v>
+        <v>25.57</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>30.43</v>
+        <v>27.43</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>31.29</v>
+        <v>29.14</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>36.14</v>
+        <v>25</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>24.71</v>
+        <v>29</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>3.33</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>6.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>17.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>16.14</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>18.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.14</v>
+        <v>16.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>27.57</v>
+        <v>21.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.43</v>
+        <v>20.86</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>27.29</v>
+        <v>20.86</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>26.57</v>
+        <v>21.86</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>25.57</v>
+        <v>28.71</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>29</v>
+        <v>24.71</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>22</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="17">
@@ -3083,207 +3083,207 @@
         <v>18.43</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>20</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>24.43</v>
+        <v>22.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>24.71</v>
+        <v>22.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>25.57</v>
+        <v>20.14</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>19.29</v>
+        <v>15.71</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>25.43</v>
+        <v>19.43</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>22.57</v>
+        <v>20.29</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>18</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>11.29</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>10.57</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>11.14</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>13.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>18</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>18</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>21.71</v>
+        <v>17.43</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>24.43</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>24.71</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>25.57</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>19.29</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>25.43</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>20.29</v>
+        <v>22.57</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>3.25</v>
+        <v>13.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>8</v>
+        <v>12.71</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>9.43</v>
+        <v>14.43</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>12.71</v>
+        <v>19</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>11.57</v>
+        <v>21.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>18.57</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>11.86</v>
+        <v>16.57</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>19.57</v>
+        <v>18</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>16.86</v>
+        <v>15.29</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>14.71</v>
+        <v>18.71</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
@@ -3296,172 +3296,172 @@
         <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>6</v>
+        <v>9.43</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>4.43</v>
+        <v>12.71</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>3.43</v>
+        <v>11.57</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>5.86</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>5.71</v>
+        <v>11.86</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>7.43</v>
+        <v>19</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>5</v>
+        <v>19.57</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>7.71</v>
+        <v>16.86</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>10.29</v>
+        <v>15</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>7</v>
+        <v>14.71</v>
       </c>
       <c r="S21" s="36" t="n">
-        <v>13</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>10.29</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>7</v>
       </c>
       <c r="S22" s="36" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G23" s="36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I23" s="36" t="n">
         <v>7.14</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="H23" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I23" s="36" t="n">
-        <v>19</v>
-      </c>
       <c r="J23" s="36" t="n">
-        <v>21.14</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>18.57</v>
+        <v>7.14</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>16.57</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>14.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>19.14</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O23" s="36" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>15.29</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>15.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>18.71</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S23" s="36" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="24">
@@ -3829,7 +3829,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3892,322 +3892,322 @@
         <v>85717459</v>
       </c>
       <c r="S6" s="40" t="n">
-        <v>15147542</v>
+        <v>65469373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>51530060</v>
+        <v>67906121</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>85043089</v>
+        <v>84229530</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>67469168</v>
+        <v>92096471</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>11256320</v>
+        <v>51411977</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>84229530</v>
+        <v>85043089</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>92096471</v>
+        <v>67469168</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>7646273</v>
+        <v>46705509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>536260</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14403556</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>16216832</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32622053</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>23929705</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>37214538</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>25375430</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>31500087</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>28078687</v>
+        <v>42012092</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>34472458</v>
+        <v>58722069</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>35343350</v>
+        <v>48135084</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>51225290</v>
+        <v>44293878</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>36142612</v>
+        <v>41613311</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>47488940</v>
+        <v>43739350</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>44805002</v>
+        <v>78234960</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>8577530</v>
+        <v>31746969</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58722069</v>
+        <v>58935844</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>48135084</v>
+        <v>38454971</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>44293878</v>
+        <v>42939312</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>41613311</v>
+        <v>43650420</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>43739350</v>
+        <v>53954095</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>78234960</v>
+        <v>48898463</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>5749350</v>
+        <v>31934997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>3489260</v>
+        <v>29720732</v>
       </c>
     </row>
     <row r="12">
@@ -4270,259 +4270,259 @@
         <v>55923182</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>4116300</v>
+        <v>28919201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>6239584</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>13803407</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>28572076</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>15282581</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>16594572</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>15223898</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>27696695</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>17717888</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>24163432</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>23623477</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>19145601</v>
+        <v>29608597</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>30157601</v>
+        <v>25219748</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>41172333</v>
+        <v>28515437</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>34303423</v>
+        <v>35235670</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>35044850</v>
+        <v>38511490</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>5772649</v>
+        <v>32275557</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>10351067</v>
+        <v>6239584</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>21091580</v>
+        <v>13803407</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>24243567</v>
+        <v>28572076</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>16381412</v>
+        <v>15282581</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>21591272</v>
+        <v>16594572</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>21904190</v>
+        <v>15223898</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25438080</v>
+        <v>27696695</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>24614280</v>
+        <v>17717888</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28889771</v>
+        <v>24163432</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>44250621</v>
+        <v>23623477</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>29608597</v>
+        <v>19145601</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>25219748</v>
+        <v>30157601</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>28515437</v>
+        <v>41172333</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>35235670</v>
+        <v>34303423</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>38511490</v>
+        <v>35044850</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>5708487</v>
+        <v>23931749</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>48358034</v>
+        <v>39333565</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>4387770</v>
+        <v>21844736</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>3249588</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>7305524</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>9575225</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>9264589</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>20692424</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>27565767</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>19138015</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>24912292</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>19068954</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>25387051</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>21008637</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>30862574</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>31820447</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>31875986</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>39333565</v>
+        <v>48358034</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>3363110</v>
+        <v>22520354</v>
       </c>
     </row>
     <row r="17">
@@ -4585,207 +4585,207 @@
         <v>20330094</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>1882070</v>
+        <v>19749314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>14226838</v>
+        <v>13949368</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>23197145</v>
+        <v>24539413</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>25790711</v>
+        <v>19087217</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>27856115</v>
+        <v>17139440</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>20981901</v>
+        <v>17746930</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>25433123</v>
+        <v>21437830</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>19355230</v>
+        <v>17616397</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>1616530</v>
+        <v>15373928</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>11100161</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>14612055</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>20638987</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>14061352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>31599148</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>18747614</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>19576415</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>14226838</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>23197145</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>25790711</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>27856115</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>20981901</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>25433123</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17616397</v>
+        <v>19355230</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>1654860</v>
+        <v>18615402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1324510</v>
+        <v>21387685</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>10311989</v>
+        <v>16050448</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19934535</v>
+        <v>21568794</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>13536614</v>
+        <v>30845816</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>22187720</v>
+        <v>45285935</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>11732010</v>
+        <v>28941455</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21143100</v>
+        <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>14330970</v>
+        <v>19628570</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>38267409</v>
+        <v>23276090</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>46351274</v>
+        <v>27906254</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>37105387</v>
+        <v>20822247</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>19868191</v>
+        <v>20014322</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>15153480</v>
+        <v>19159625</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>2771020</v>
+        <v>15331216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
@@ -4798,172 +4798,172 @@
         <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1339100</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>5579340</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>9518200</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>11747640</v>
+        <v>13536614</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>3885270</v>
+        <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>8765870</v>
+        <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>4571680</v>
+        <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>3911995</v>
+        <v>14330970</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>9234090</v>
+        <v>38267409</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>5390260</v>
+        <v>46351274</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>4645370</v>
+        <v>37105387</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>10400980</v>
+        <v>19868191</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>6123322</v>
+        <v>15153480</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>1690050</v>
+        <v>12675948</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>548250</v>
+        <v>4715660</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>3337146</v>
+        <v>2474409</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>10420206</v>
+        <v>4696696</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>21387685</v>
+        <v>6991878</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>16050448</v>
+        <v>4060163</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>21568794</v>
+        <v>7685466</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>30845816</v>
+        <v>10141286</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>45285935</v>
+        <v>6393871</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>28941455</v>
+        <v>4534503</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>21801828</v>
+        <v>7579040</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>19628570</v>
+        <v>9679437</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>23276090</v>
+        <v>6102368</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>27906254</v>
+        <v>4294070</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>20822247</v>
+        <v>5589419</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>20014322</v>
+        <v>10264941</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>19159625</v>
+        <v>6114083</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>481880</v>
+        <v>8735740</v>
       </c>
     </row>
     <row r="24">
@@ -5331,7 +5331,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -5394,28 +5394,28 @@
         <v>7</v>
       </c>
       <c r="S6" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -5457,28 +5457,28 @@
         <v>7</v>
       </c>
       <c r="S7" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -5520,25 +5520,25 @@
         <v>7</v>
       </c>
       <c r="S8" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -5583,28 +5583,28 @@
         <v>7</v>
       </c>
       <c r="S9" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -5646,70 +5646,70 @@
         <v>7</v>
       </c>
       <c r="S10" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="F11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S11" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5772,25 +5772,25 @@
         <v>7</v>
       </c>
       <c r="S12" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -5835,25 +5835,25 @@
         <v>7</v>
       </c>
       <c r="S13" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -5898,25 +5898,25 @@
         <v>7</v>
       </c>
       <c r="S14" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -5961,25 +5961,25 @@
         <v>7</v>
       </c>
       <c r="S15" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -6024,7 +6024,7 @@
         <v>7</v>
       </c>
       <c r="S16" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -6087,35 +6087,35 @@
         <v>7</v>
       </c>
       <c r="S17" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
       </c>
@@ -6150,34 +6150,34 @@
         <v>7</v>
       </c>
       <c r="S18" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -6213,31 +6213,31 @@
         <v>7</v>
       </c>
       <c r="S19" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -6276,18 +6276,18 @@
         <v>7</v>
       </c>
       <c r="S20" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
@@ -6300,70 +6300,70 @@
         <v>0</v>
       </c>
       <c r="F21" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="G21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M21" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S21" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -6384,7 +6384,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -6402,70 +6402,70 @@
         <v>7</v>
       </c>
       <c r="S22" s="42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="E23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S23" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2267,7 +2267,7 @@
       </c>
       <c r="S4" s="31" t="inlineStr">
         <is>
-          <t>17.08–23.08*</t>
+          <t>17.08–23.08</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2390,7 +2390,7 @@
         <v>82.14</v>
       </c>
       <c r="S6" s="36" t="n">
-        <v>93</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2453,7 +2453,7 @@
         <v>78.43000000000001</v>
       </c>
       <c r="S7" s="36" t="n">
-        <v>65.59999999999999</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2516,7 +2516,7 @@
         <v>67.29000000000001</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>61.4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -2579,7 +2579,7 @@
         <v>45.14</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>51.4</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="10">
@@ -2642,7 +2642,7 @@
         <v>40.71</v>
       </c>
       <c r="S10" s="36" t="n">
-        <v>43.2</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="11">
@@ -2705,7 +2705,7 @@
         <v>38.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>41.2</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="12">
@@ -2768,7 +2768,7 @@
         <v>48.43</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>36.4</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="13">
@@ -2831,7 +2831,7 @@
         <v>36.14</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -2894,7 +2894,7 @@
         <v>25</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>29.8</v>
+        <v>29.57</v>
       </c>
     </row>
     <row r="15">
@@ -2957,133 +2957,133 @@
         <v>29</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>27.8</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>6.43</v>
+        <v>11</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>14.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.14</v>
+        <v>19.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>16.14</v>
+        <v>21</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>21.71</v>
+        <v>24.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>20.86</v>
+        <v>24.14</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>21.86</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>28.71</v>
+        <v>23</v>
       </c>
       <c r="R16" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S16" s="36" t="n">
         <v>24.71</v>
-      </c>
-      <c r="S16" s="36" t="n">
-        <v>26.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G17" s="36" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="E17" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="G17" s="36" t="n">
-        <v>11.86</v>
-      </c>
       <c r="H17" s="36" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19.14</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>23.43</v>
+        <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="M17" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="N17" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="O17" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="P17" s="36" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="Q17" s="36" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="R17" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="S17" s="36" t="n">
         <v>24.57</v>
-      </c>
-      <c r="N17" s="36" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="O17" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="P17" s="36" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q17" s="36" t="n">
-        <v>23</v>
-      </c>
-      <c r="R17" s="36" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="S17" s="36" t="n">
-        <v>25.4</v>
       </c>
     </row>
     <row r="18">
@@ -3146,7 +3146,7 @@
         <v>20.29</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>24.8</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="19">
@@ -3209,7 +3209,7 @@
         <v>22.57</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>21</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="20">
@@ -3272,7 +3272,7 @@
         <v>18.71</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -3335,7 +3335,7 @@
         <v>14.71</v>
       </c>
       <c r="S21" s="36" t="n">
-        <v>15.2</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="22">
@@ -3398,7 +3398,7 @@
         <v>7</v>
       </c>
       <c r="S22" s="36" t="n">
-        <v>10.6</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3461,7 +3461,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="S23" s="36" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="S4" s="31" t="inlineStr">
         <is>
-          <t>17.08–23.08*</t>
+          <t>17.08–23.08</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3892,7 +3892,7 @@
         <v>85717459</v>
       </c>
       <c r="S6" s="40" t="n">
-        <v>65469373</v>
+        <v>87147990</v>
       </c>
     </row>
     <row r="7">
@@ -3955,7 +3955,7 @@
         <v>92096471</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>51411977</v>
+        <v>78023476</v>
       </c>
     </row>
     <row r="8">
@@ -4018,7 +4018,7 @@
         <v>67469168</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>46705509</v>
+        <v>66040134</v>
       </c>
     </row>
     <row r="9">
@@ -4081,7 +4081,7 @@
         <v>78234960</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>31746969</v>
+        <v>47535640</v>
       </c>
     </row>
     <row r="10">
@@ -4144,7 +4144,7 @@
         <v>48898463</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>31934997</v>
+        <v>48011655</v>
       </c>
     </row>
     <row r="11">
@@ -4207,7 +4207,7 @@
         <v>44805002</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>29720732</v>
+        <v>43327432</v>
       </c>
     </row>
     <row r="12">
@@ -4270,7 +4270,7 @@
         <v>55923182</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>28919201</v>
+        <v>40248814</v>
       </c>
     </row>
     <row r="13">
@@ -4333,7 +4333,7 @@
         <v>38511490</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>32275557</v>
+        <v>40935998</v>
       </c>
     </row>
     <row r="14">
@@ -4396,7 +4396,7 @@
         <v>35044850</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>23931749</v>
+        <v>33519824</v>
       </c>
     </row>
     <row r="15">
@@ -4459,133 +4459,133 @@
         <v>39333565</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>21844736</v>
+        <v>28566119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3249588</v>
+        <v>8544625</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>7305524</v>
+        <v>8387478</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>9575225</v>
+        <v>10570508</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>9264589</v>
+        <v>11896580</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>20692424</v>
+        <v>19614352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>27565767</v>
+        <v>20966317</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>19138015</v>
+        <v>20073400</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>24912292</v>
+        <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>19068954</v>
+        <v>27940611</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>25387051</v>
+        <v>27893929</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>21008637</v>
+        <v>29635773</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30862574</v>
+        <v>19554230</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>31820447</v>
+        <v>23848495</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>31875986</v>
+        <v>24194638</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>48358034</v>
+        <v>20330094</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>22520354</v>
+        <v>26044199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>8544625</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>8387478</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>10570508</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>11896580</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>19614352</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>20966317</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>20073400</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>23801493</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>27940611</v>
+        <v>19068954</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>27893929</v>
+        <v>25387051</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>29635773</v>
+        <v>21008637</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>19554230</v>
+        <v>30862574</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>23848495</v>
+        <v>31820447</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>24194638</v>
+        <v>31875986</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>20330094</v>
+        <v>48358034</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>19749314</v>
+        <v>30000524</v>
       </c>
     </row>
     <row r="18">
@@ -4648,7 +4648,7 @@
         <v>17616397</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>15373928</v>
+        <v>19360848</v>
       </c>
     </row>
     <row r="19">
@@ -4711,7 +4711,7 @@
         <v>19355230</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>18615402</v>
+        <v>24713836</v>
       </c>
     </row>
     <row r="20">
@@ -4774,7 +4774,7 @@
         <v>19159625</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>15331216</v>
+        <v>22535696</v>
       </c>
     </row>
     <row r="21">
@@ -4837,7 +4837,7 @@
         <v>15153480</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>12675948</v>
+        <v>19277087</v>
       </c>
     </row>
     <row r="22">
@@ -4900,7 +4900,7 @@
         <v>6123322</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>4715660</v>
+        <v>5648770</v>
       </c>
     </row>
     <row r="23">
@@ -4963,7 +4963,7 @@
         <v>6114083</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>8735740</v>
+        <v>10758755</v>
       </c>
     </row>
     <row r="24">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="S4" s="31" t="inlineStr">
         <is>
-          <t>17.08–23.08*</t>
+          <t>17.08–23.08</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
         <v>7</v>
       </c>
       <c r="S5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -5394,7 +5394,7 @@
         <v>7</v>
       </c>
       <c r="S6" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -5457,7 +5457,7 @@
         <v>7</v>
       </c>
       <c r="S7" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -5520,7 +5520,7 @@
         <v>7</v>
       </c>
       <c r="S8" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -5583,7 +5583,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -5646,7 +5646,7 @@
         <v>7</v>
       </c>
       <c r="S10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -5709,7 +5709,7 @@
         <v>7</v>
       </c>
       <c r="S11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -5772,7 +5772,7 @@
         <v>7</v>
       </c>
       <c r="S12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -5835,7 +5835,7 @@
         <v>7</v>
       </c>
       <c r="S13" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -5898,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="S14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -5961,25 +5961,25 @@
         <v>7</v>
       </c>
       <c r="S15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -6024,25 +6024,25 @@
         <v>7</v>
       </c>
       <c r="S16" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -6087,7 +6087,7 @@
         <v>7</v>
       </c>
       <c r="S17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -6150,7 +6150,7 @@
         <v>7</v>
       </c>
       <c r="S18" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -6213,7 +6213,7 @@
         <v>7</v>
       </c>
       <c r="S19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -6276,7 +6276,7 @@
         <v>7</v>
       </c>
       <c r="S20" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -6339,7 +6339,7 @@
         <v>7</v>
       </c>
       <c r="S21" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -6402,7 +6402,7 @@
         <v>7</v>
       </c>
       <c r="S22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -6465,7 +6465,7 @@
         <v>7</v>
       </c>
       <c r="S23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2049,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2071,6 +2071,7 @@
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
     <col width="13" customWidth="1" style="20" min="18" max="18"/>
     <col width="13" customWidth="1" style="20" min="19" max="19"/>
+    <col width="13" customWidth="1" style="20" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2173,6 +2174,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2268,6 +2274,11 @@
       <c r="S4" s="31" t="inlineStr">
         <is>
           <t>17.08–23.08</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>24.08–30.08*</t>
         </is>
       </c>
     </row>
@@ -2329,572 +2340,602 @@
       <c r="S5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="T5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>31.14</v>
+        <v>29.43</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>41.14</v>
+        <v>38</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>36.43</v>
+        <v>41.29</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>52.71</v>
+        <v>51.43</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>67.43000000000001</v>
+        <v>58.29</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>61.14</v>
+        <v>63</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>66.14</v>
+        <v>55.43</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>72.56999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>77.86</v>
+        <v>76.86</v>
       </c>
       <c r="O6" s="36" t="n">
-        <v>74.56999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P6" s="36" t="n">
-        <v>75.43000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q6" s="36" t="n">
-        <v>80.56999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="R6" s="36" t="n">
-        <v>82.14</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S6" s="36" t="n">
-        <v>85.56999999999999</v>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="T6" s="36" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>31.14</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>38</v>
+        <v>41.14</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>41.29</v>
+        <v>36.43</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>51.43</v>
+        <v>52.71</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>58.29</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>63</v>
+        <v>61.14</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>66.14</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>77.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>78.86</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="S7" s="36" t="n">
-        <v>72.43000000000001</v>
+        <v>85.56999999999999</v>
+      </c>
+      <c r="T7" s="36" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>41.29</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59</v>
+        <v>41.43</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>53.71</v>
+        <v>46.14</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>46.57</v>
+        <v>41.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>49.29</v>
+        <v>51.86</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>48.71</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>45.14</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>61</v>
+        <v>50.71</v>
+      </c>
+      <c r="T8" s="36" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>7.33</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>17.86</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>22.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>24.86</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>36.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.86</v>
+        <v>43.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41.29</v>
+        <v>50.14</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>41.43</v>
+        <v>59</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>46.14</v>
+        <v>53.71</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>41.57</v>
+        <v>46.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>51.86</v>
+        <v>49.29</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>48.71</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>45.14</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>50.71</v>
+        <v>61</v>
+      </c>
+      <c r="T9" s="36" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J10" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K10" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L10" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M10" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="N10" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="O10" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P10" s="36" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="Q10" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="K10" s="36" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="L10" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="M10" s="36" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="N10" s="36" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="O10" s="36" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="P10" s="36" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="Q10" s="36" t="n">
-        <v>42.86</v>
-      </c>
       <c r="R10" s="36" t="n">
-        <v>40.71</v>
+        <v>36.14</v>
       </c>
       <c r="S10" s="36" t="n">
-        <v>45.43</v>
+        <v>31</v>
+      </c>
+      <c r="T10" s="36" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>1.67</v>
+        <v>7.25</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>12.14</v>
+        <v>18.71</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>16.57</v>
+        <v>21.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>21</v>
+        <v>30.29</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>20.29</v>
+        <v>38</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>28.57</v>
+        <v>39.71</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>24.14</v>
+        <v>41.71</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>27.57</v>
+        <v>35.14</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>28.14</v>
+        <v>41</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.86</v>
+        <v>48</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>33.14</v>
+        <v>49.43</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>30.71</v>
+        <v>45.57</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>31.14</v>
+        <v>43</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>40.29</v>
+        <v>46.57</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>38.71</v>
+        <v>48.43</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>43.14</v>
+        <v>38.29</v>
+      </c>
+      <c r="T11" s="36" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>7.25</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>18.71</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>21.57</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>30.29</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>38</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>39.71</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>41.71</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>35.14</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>41</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>48</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>49.43</v>
+        <v>33.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>45.57</v>
+        <v>30.71</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>43</v>
+        <v>31.14</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>46.57</v>
+        <v>40.29</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>48.43</v>
+        <v>38.71</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>38.29</v>
+        <v>43.14</v>
+      </c>
+      <c r="T12" s="36" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>8</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>13.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>19.43</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>26.43</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>32.29</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>31.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>33.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>40</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>42.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>31.14</v>
+        <v>38.57</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30</v>
+        <v>34.29</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>30.43</v>
+        <v>37.86</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>31.29</v>
+        <v>42.86</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>36.14</v>
+        <v>40.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>31</v>
+        <v>45.43</v>
+      </c>
+      <c r="T13" s="36" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>7</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>19.43</v>
+        <v>14.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>15.86</v>
+        <v>11.86</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>14.86</v>
+        <v>18</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>16.71</v>
+        <v>19.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>19.71</v>
+        <v>21</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>16.86</v>
+        <v>23.43</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.86</v>
+        <v>20.43</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>23.43</v>
+        <v>24.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>19.43</v>
+        <v>24.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>25.57</v>
+        <v>24.43</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>27.43</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>29.14</v>
+        <v>23</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>25</v>
+        <v>18.43</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>29.57</v>
+        <v>24.71</v>
+      </c>
+      <c r="T14" s="36" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -2959,131 +3000,140 @@
       <c r="S15" s="36" t="n">
         <v>27.71</v>
       </c>
+      <c r="T15" s="36" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>7</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.43</v>
+        <v>19.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.86</v>
+        <v>15.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>18</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.14</v>
+        <v>16.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>21</v>
+        <v>19.71</v>
       </c>
       <c r="K16" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="L16" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="M16" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="L16" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M16" s="36" t="n">
-        <v>24.57</v>
-      </c>
       <c r="N16" s="36" t="n">
-        <v>24.14</v>
+        <v>19.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>24.43</v>
+        <v>25.57</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>22</v>
+        <v>27.43</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>23</v>
+        <v>29.14</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>18.43</v>
+        <v>25</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>24.71</v>
+        <v>29.57</v>
+      </c>
+      <c r="T16" s="36" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>6.43</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.14</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>21.71</v>
+        <v>24.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>20.86</v>
+        <v>24.71</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.86</v>
+        <v>25.57</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>21.86</v>
+        <v>19.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>28.71</v>
+        <v>25.43</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>24.71</v>
+        <v>22.57</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>24.57</v>
+        <v>21.29</v>
+      </c>
+      <c r="T17" s="36" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -3148,194 +3198,206 @@
       <c r="S18" s="36" t="n">
         <v>22.29</v>
       </c>
+      <c r="T18" s="36" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>10.57</v>
+        <v>3.25</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>11.14</v>
+        <v>8</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>13.86</v>
+        <v>9.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>18</v>
+        <v>12.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>18</v>
+        <v>11.57</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>17.43</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15.29</v>
+        <v>11.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>24.43</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>24.71</v>
+        <v>19</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>25.57</v>
+        <v>19.57</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>19.29</v>
+        <v>16.86</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>25.43</v>
+        <v>15</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>22.57</v>
+        <v>14.71</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>21.29</v>
+        <v>15.86</v>
+      </c>
+      <c r="T19" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K20" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>16.57</v>
+        <v>16.14</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>14.71</v>
+        <v>21.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19.14</v>
+        <v>20.86</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>18</v>
+        <v>20.86</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>15.29</v>
+        <v>21.86</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>15.29</v>
+        <v>28.71</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>18.71</v>
+        <v>24.71</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>18</v>
+        <v>24.57</v>
+      </c>
+      <c r="T20" s="36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>13.43</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>12.71</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>14.43</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>19</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>21.14</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>18.57</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11.86</v>
+        <v>16.57</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>19.57</v>
+        <v>18</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>16.86</v>
+        <v>15.29</v>
       </c>
       <c r="Q21" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="R21" s="36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="S21" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="T21" s="36" t="n">
         <v>15</v>
-      </c>
-      <c r="R21" s="36" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="S21" s="36" t="n">
-        <v>15.86</v>
       </c>
     </row>
     <row r="22">
@@ -3400,6 +3462,9 @@
       <c r="S22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
+      <c r="T22" s="36" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -3462,6 +3527,9 @@
       </c>
       <c r="S23" s="36" t="n">
         <v>8</v>
+      </c>
+      <c r="T23" s="36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3537,6 +3605,10 @@
       </c>
       <c r="S24" s="39">
         <f>AVERAGE(S6:S23)</f>
+        <v/>
+      </c>
+      <c r="T24" s="39">
+        <f>AVERAGE(T6:T23)</f>
         <v/>
       </c>
     </row>
@@ -3551,7 +3623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3573,6 +3645,7 @@
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
     <col width="13" customWidth="1" style="20" min="18" max="18"/>
     <col width="13" customWidth="1" style="20" min="19" max="19"/>
+    <col width="13" customWidth="1" style="20" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3675,6 +3748,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -3770,6 +3848,11 @@
       <c r="S4" s="31" t="inlineStr">
         <is>
           <t>17.08–23.08</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>24.08–30.08*</t>
         </is>
       </c>
     </row>
@@ -3831,572 +3914,602 @@
       <c r="S5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="T5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>8596643</v>
+        <v>6122227</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>30622284</v>
+        <v>31792625</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>33277426</v>
+        <v>49374899</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>40259616</v>
+        <v>38585414</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>54390985</v>
+        <v>51458725</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>72727058</v>
+        <v>61835892</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>61910106</v>
+        <v>80551167</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>72409127</v>
+        <v>61490143</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>72256071</v>
+        <v>68619843</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>82753547</v>
+        <v>81742671</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>82566330</v>
+        <v>69757179</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>96616423</v>
+        <v>68198708</v>
       </c>
       <c r="P6" s="40" t="n">
-        <v>79977173</v>
+        <v>67906121</v>
       </c>
       <c r="Q6" s="40" t="n">
-        <v>91676410</v>
+        <v>84229530</v>
       </c>
       <c r="R6" s="40" t="n">
-        <v>85717459</v>
+        <v>92096471</v>
       </c>
       <c r="S6" s="40" t="n">
-        <v>87147990</v>
+        <v>78023476</v>
+      </c>
+      <c r="T6" s="40" t="n">
+        <v>12861736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>8596643</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>30622284</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>33277426</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>40259616</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>54390985</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>72727058</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>61910106</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>72409127</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>72256071</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>82753547</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>82566330</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>96616423</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>67906121</v>
+        <v>79977173</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>84229530</v>
+        <v>91676410</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>92096471</v>
+        <v>85717459</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>78023476</v>
+        <v>87147990</v>
+      </c>
+      <c r="T7" s="40" t="n">
+        <v>13476285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>42012092</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58204066</v>
+        <v>58722069</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>58190202</v>
+        <v>48135084</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>46275213</v>
+        <v>44293878</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>51530060</v>
+        <v>41613311</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>85043089</v>
+        <v>43739350</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>67469168</v>
+        <v>78234960</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>66040134</v>
+        <v>47535640</v>
+      </c>
+      <c r="T8" s="40" t="n">
+        <v>9154564</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>2886450</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>22932586</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>24764259</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>32268886</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>42977335</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>44364359</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>53225819</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>42012092</v>
+        <v>51621207</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58722069</v>
+        <v>58204066</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>48135084</v>
+        <v>58190202</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>44293878</v>
+        <v>46275213</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>41613311</v>
+        <v>51530060</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>43739350</v>
+        <v>85043089</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>78234960</v>
+        <v>67469168</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>47535640</v>
+        <v>66040134</v>
+      </c>
+      <c r="T9" s="40" t="n">
+        <v>12244680</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>43650420</v>
+        <v>28515437</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>53954095</v>
+        <v>35235670</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>48898463</v>
+        <v>38511490</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>48011655</v>
+        <v>40935998</v>
+      </c>
+      <c r="T10" s="40" t="n">
+        <v>9440810</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>536260</v>
+        <v>3771593</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14403556</v>
+        <v>17664217</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>16216832</v>
+        <v>21748722</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32622053</v>
+        <v>38313932</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>23929705</v>
+        <v>49313727</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37214538</v>
+        <v>41788221</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25375430</v>
+        <v>36755638</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>31500087</v>
+        <v>43259404</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28078687</v>
+        <v>68694825</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>34472458</v>
+        <v>48824266</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>35343350</v>
+        <v>57556194</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>51225290</v>
+        <v>38323101</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>36142612</v>
+        <v>40276838</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>47488940</v>
+        <v>45419704</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>44805002</v>
+        <v>55923182</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>43327432</v>
+        <v>40248814</v>
+      </c>
+      <c r="T11" s="40" t="n">
+        <v>7472758</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>3771593</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>17664217</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>21748722</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>38313932</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>49313727</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>41788221</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>36755638</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>43259404</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>68694825</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>48824266</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>57556194</v>
+        <v>35343350</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>38323101</v>
+        <v>51225290</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>40276838</v>
+        <v>36142612</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>45419704</v>
+        <v>47488940</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>55923182</v>
+        <v>44805002</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>40248814</v>
+        <v>43327432</v>
+      </c>
+      <c r="T12" s="40" t="n">
+        <v>4507596</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>8972650</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>18100396</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>23988817</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>22409732</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>37715520</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>35926824</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>39462393</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>51983942</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>58935844</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>38454971</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>42939312</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>28515437</v>
+        <v>43650420</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>35235670</v>
+        <v>53954095</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>38511490</v>
+        <v>48898463</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>40935998</v>
+        <v>48011655</v>
+      </c>
+      <c r="T13" s="40" t="n">
+        <v>6385500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>6239584</v>
+        <v>8544625</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>13803407</v>
+        <v>8387478</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>28572076</v>
+        <v>10570508</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>15282581</v>
+        <v>11896580</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>16594572</v>
+        <v>19614352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>15223898</v>
+        <v>20966317</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>27696695</v>
+        <v>20073400</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>17717888</v>
+        <v>23801493</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>24163432</v>
+        <v>27940611</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>23623477</v>
+        <v>27893929</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>19145601</v>
+        <v>29635773</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>30157601</v>
+        <v>19554230</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>41172333</v>
+        <v>23848495</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>34303423</v>
+        <v>24194638</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>35044850</v>
+        <v>20330094</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>33519824</v>
+        <v>26044199</v>
+      </c>
+      <c r="T14" s="40" t="n">
+        <v>3507427</v>
       </c>
     </row>
     <row r="15">
@@ -4461,131 +4574,140 @@
       <c r="S15" s="40" t="n">
         <v>28566119</v>
       </c>
+      <c r="T15" s="40" t="n">
+        <v>4447388</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>8544625</v>
+        <v>6239584</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>8387478</v>
+        <v>13803407</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10570508</v>
+        <v>28572076</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>11896580</v>
+        <v>15282581</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19614352</v>
+        <v>16594572</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>20966317</v>
+        <v>15223898</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>20073400</v>
+        <v>27696695</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>23801493</v>
+        <v>17717888</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>27940611</v>
+        <v>24163432</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>27893929</v>
+        <v>23623477</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>29635773</v>
+        <v>19145601</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>19554230</v>
+        <v>30157601</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>23848495</v>
+        <v>41172333</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>24194638</v>
+        <v>34303423</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>20330094</v>
+        <v>35044850</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>26044199</v>
+        <v>33519824</v>
+      </c>
+      <c r="T16" s="40" t="n">
+        <v>4273858</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>19068954</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>25387051</v>
+        <v>23197145</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>21008637</v>
+        <v>25790711</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>30862574</v>
+        <v>27856115</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>31820447</v>
+        <v>20981901</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>31875986</v>
+        <v>25433123</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>48358034</v>
+        <v>19355230</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>30000524</v>
+        <v>24713836</v>
+      </c>
+      <c r="T17" s="40" t="n">
+        <v>4164200</v>
       </c>
     </row>
     <row r="18">
@@ -4650,194 +4772,206 @@
       <c r="S18" s="40" t="n">
         <v>19360848</v>
       </c>
+      <c r="T18" s="40" t="n">
+        <v>3597346</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>14612055</v>
+        <v>1324510</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>20638987</v>
+        <v>10311989</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>14061352</v>
+        <v>19934535</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>31599148</v>
+        <v>13536614</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>18747614</v>
+        <v>22187720</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>19576415</v>
+        <v>11732010</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>14226838</v>
+        <v>21143100</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>23197145</v>
+        <v>14330970</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>25790711</v>
+        <v>38267409</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>27856115</v>
+        <v>46351274</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>20981901</v>
+        <v>37105387</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>25433123</v>
+        <v>19868191</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>19355230</v>
+        <v>15153480</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>24713836</v>
+        <v>19277087</v>
+      </c>
+      <c r="T19" s="40" t="n">
+        <v>1926980</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21801828</v>
+        <v>19068954</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>19628570</v>
+        <v>25387051</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>23276090</v>
+        <v>21008637</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>27906254</v>
+        <v>30862574</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>20822247</v>
+        <v>31820447</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>20014322</v>
+        <v>31875986</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>19159625</v>
+        <v>48358034</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>22535696</v>
+        <v>30000524</v>
+      </c>
+      <c r="T20" s="40" t="n">
+        <v>2471650</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>21387685</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>16050448</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>21568794</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>30845816</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>45285935</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>11732010</v>
+        <v>28941455</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21143100</v>
+        <v>21801828</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>14330970</v>
+        <v>19628570</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>38267409</v>
+        <v>23276090</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>46351274</v>
+        <v>27906254</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>37105387</v>
+        <v>20822247</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>19868191</v>
+        <v>20014322</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>15153480</v>
+        <v>19159625</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>19277087</v>
+        <v>22535696</v>
+      </c>
+      <c r="T21" s="40" t="n">
+        <v>1532130</v>
       </c>
     </row>
     <row r="22">
@@ -4902,6 +5036,9 @@
       <c r="S22" s="40" t="n">
         <v>5648770</v>
       </c>
+      <c r="T22" s="40" t="n">
+        <v>1390160</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -4964,6 +5101,9 @@
       </c>
       <c r="S23" s="40" t="n">
         <v>10758755</v>
+      </c>
+      <c r="T23" s="40" t="n">
+        <v>1680460</v>
       </c>
     </row>
     <row r="24">
@@ -5039,6 +5179,10 @@
       </c>
       <c r="S24" s="41">
         <f>AVERAGE(S6:S23)</f>
+        <v/>
+      </c>
+      <c r="T24" s="41">
+        <f>AVERAGE(T6:T23)</f>
         <v/>
       </c>
     </row>
@@ -5053,7 +5197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -5075,6 +5219,7 @@
     <col width="13" customWidth="1" style="20" min="17" max="17"/>
     <col width="13" customWidth="1" style="20" min="18" max="18"/>
     <col width="13" customWidth="1" style="20" min="19" max="19"/>
+    <col width="13" customWidth="1" style="20" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5177,6 +5322,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -5272,6 +5422,11 @@
       <c r="S4" s="31" t="inlineStr">
         <is>
           <t>17.08–23.08</t>
+        </is>
+      </c>
+      <c r="T4" s="31" t="inlineStr">
+        <is>
+          <t>24.08–30.08*</t>
         </is>
       </c>
     </row>
@@ -5333,16 +5488,19 @@
       <c r="S5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="T5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-291</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C6" s="42" t="n">
@@ -5396,16 +5554,19 @@
       <c r="S6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="T6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-291</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
@@ -5459,26 +5620,29 @@
       <c r="S7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="T7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -5521,28 +5685,31 @@
       </c>
       <c r="S8" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T8" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="F9" s="42" t="n">
         <v>7</v>
       </c>
@@ -5584,27 +5751,30 @@
       </c>
       <c r="S9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -5647,24 +5817,27 @@
       </c>
       <c r="S10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>7</v>
@@ -5710,24 +5883,27 @@
       </c>
       <c r="S11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -5773,87 +5949,93 @@
       </c>
       <c r="S12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -5899,6 +6081,9 @@
       </c>
       <c r="S14" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5963,23 +6148,26 @@
       <c r="S15" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="T15" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -6025,24 +6213,27 @@
       </c>
       <c r="S16" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -6088,6 +6279,9 @@
       </c>
       <c r="S17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -6152,29 +6346,32 @@
       <c r="S18" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="T18" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -6214,24 +6411,27 @@
       </c>
       <c r="S19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -6277,30 +6477,33 @@
       </c>
       <c r="S20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -6340,6 +6543,9 @@
       </c>
       <c r="S21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -6404,6 +6610,9 @@
       <c r="S22" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="T22" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -6466,6 +6675,9 @@
       </c>
       <c r="S23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="T23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6543,6 +6755,10 @@
         <f>AVERAGE(S6:S23)</f>
         <v/>
       </c>
+      <c r="T24" s="43">
+        <f>AVERAGE(T6:T23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2341,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="T5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2407,7 +2407,7 @@
         <v>72.43000000000001</v>
       </c>
       <c r="T6" s="36" t="n">
-        <v>87</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="7">
@@ -2473,139 +2473,139 @@
         <v>85.56999999999999</v>
       </c>
       <c r="T7" s="36" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>19.14</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>26.71</v>
+        <v>17.86</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>28.14</v>
+        <v>22.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>28.57</v>
+        <v>24.86</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>31.57</v>
+        <v>36.57</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>34.86</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>41.29</v>
+        <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>41.43</v>
+        <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>46.14</v>
+        <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>41.57</v>
+        <v>46.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>51.86</v>
+        <v>49.29</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>48.71</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>45.14</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>50.71</v>
+        <v>61</v>
       </c>
       <c r="T8" s="36" t="n">
-        <v>68</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>50.14</v>
+        <v>41.29</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>59</v>
+        <v>41.43</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>53.71</v>
+        <v>46.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>46.57</v>
+        <v>41.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>49.29</v>
+        <v>51.86</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>48.71</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>45.14</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>61</v>
+        <v>50.71</v>
       </c>
       <c r="T9" s="36" t="n">
-        <v>66</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="10">
@@ -2671,7 +2671,7 @@
         <v>31</v>
       </c>
       <c r="T10" s="36" t="n">
-        <v>51</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="11">
@@ -2737,414 +2737,414 @@
         <v>38.29</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>45.43</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>20.43</v>
+        <v>24.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>24.57</v>
+        <v>27.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.14</v>
+        <v>24.43</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>24.43</v>
+        <v>27.29</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>22</v>
+        <v>26.57</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>23</v>
+        <v>25.57</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>18.43</v>
+        <v>29</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>24.71</v>
+        <v>27.71</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>7</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>16</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>19.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>15.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="36" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="J15" s="36" t="n">
         <v>19.71</v>
       </c>
-      <c r="J15" s="36" t="n">
-        <v>17.71</v>
-      </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>16.86</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.14</v>
+        <v>24.86</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>27.57</v>
+        <v>23.43</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.43</v>
+        <v>19.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>26.57</v>
+        <v>27.43</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>25.57</v>
+        <v>29.14</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>27.71</v>
+        <v>29.57</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>34</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>16</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>19.43</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>15.86</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14.86</v>
+        <v>13.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>16.71</v>
+        <v>18</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>16.86</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.86</v>
+        <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>23.43</v>
+        <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>19.43</v>
+        <v>24.71</v>
       </c>
       <c r="O16" s="36" t="n">
         <v>25.57</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>27.43</v>
+        <v>19.29</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>29.14</v>
+        <v>25.43</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>25</v>
+        <v>22.57</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>29.57</v>
+        <v>21.29</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>32</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>23.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>20.43</v>
       </c>
       <c r="M17" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N17" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="O17" s="36" t="n">
         <v>24.43</v>
       </c>
-      <c r="N17" s="36" t="n">
+      <c r="P17" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q17" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R17" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S17" s="36" t="n">
         <v>24.71</v>
       </c>
-      <c r="O17" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P17" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q17" s="36" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="R17" s="36" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="S17" s="36" t="n">
-        <v>21.29</v>
-      </c>
       <c r="T17" s="36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
@@ -3157,60 +3157,60 @@
         <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>8</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>9.43</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>12.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>20.43</v>
+        <v>11.57</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>21.71</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L18" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M18" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N18" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O18" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P18" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q18" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="M18" s="36" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="N18" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="O18" s="36" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="P18" s="36" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="Q18" s="36" t="n">
-        <v>19.43</v>
-      </c>
       <c r="R18" s="36" t="n">
-        <v>20.29</v>
+        <v>14.71</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>22.29</v>
+        <v>15.86</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>22</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
@@ -3223,49 +3223,49 @@
         <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>8</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>9.43</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>12.71</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>11.57</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>11.86</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>19.57</v>
+        <v>20.14</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>16.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>15</v>
+        <v>19.43</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>14.71</v>
+        <v>20.29</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>15.86</v>
+        <v>22.29</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>21</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="20">
@@ -3331,7 +3331,7 @@
         <v>24.57</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>16</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="21">
@@ -3397,7 +3397,7 @@
         <v>18</v>
       </c>
       <c r="T21" s="36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -3463,7 +3463,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="T22" s="36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="23">
@@ -3529,7 +3529,7 @@
         <v>8</v>
       </c>
       <c r="T23" s="36" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="24">
@@ -3915,7 +3915,7 @@
         <v>7</v>
       </c>
       <c r="T5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3981,7 +3981,7 @@
         <v>78023476</v>
       </c>
       <c r="T6" s="40" t="n">
-        <v>12861736</v>
+        <v>25696743</v>
       </c>
     </row>
     <row r="7">
@@ -4047,139 +4047,139 @@
         <v>87147990</v>
       </c>
       <c r="T7" s="40" t="n">
-        <v>13476285</v>
+        <v>26322600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>14209578</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>30449860</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32603120</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>35552907</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>31069118</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>40525338</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>42402722</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>42012092</v>
+        <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58722069</v>
+        <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>48135084</v>
+        <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>44293878</v>
+        <v>46275213</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>41613311</v>
+        <v>51530060</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>43739350</v>
+        <v>85043089</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>78234960</v>
+        <v>67469168</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>47535640</v>
+        <v>66040134</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>9154564</v>
+        <v>26071852</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>51621207</v>
+        <v>42012092</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58204066</v>
+        <v>58722069</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>58190202</v>
+        <v>48135084</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>46275213</v>
+        <v>44293878</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>51530060</v>
+        <v>41613311</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>85043089</v>
+        <v>43739350</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>67469168</v>
+        <v>78234960</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>66040134</v>
+        <v>47535640</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>12244680</v>
+        <v>16115655</v>
       </c>
     </row>
     <row r="10">
@@ -4245,7 +4245,7 @@
         <v>40935998</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>9440810</v>
+        <v>21014437</v>
       </c>
     </row>
     <row r="11">
@@ -4311,414 +4311,414 @@
         <v>40248814</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>7472758</v>
+        <v>12989308</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>4507596</v>
+        <v>14673500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>48011655</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>6385500</v>
+        <v>12075606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>23801493</v>
+        <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>27940611</v>
+        <v>31914115</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>27893929</v>
+        <v>32069521</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>29635773</v>
+        <v>38287475</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>19554230</v>
+        <v>28283704</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>23848495</v>
+        <v>27334091</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>24194638</v>
+        <v>36312415</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>20330094</v>
+        <v>39333565</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>26044199</v>
+        <v>28566119</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>3507427</v>
+        <v>9649748</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>6239584</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>13803407</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>28572076</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>15282581</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>16594572</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>15223898</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>27696695</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>17717888</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>31914115</v>
+        <v>24163432</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>32069521</v>
+        <v>23623477</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38287475</v>
+        <v>19145601</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>28283704</v>
+        <v>30157601</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>27334091</v>
+        <v>41172333</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>36312415</v>
+        <v>34303423</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>39333565</v>
+        <v>35044850</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>28566119</v>
+        <v>33519824</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>4447388</v>
+        <v>7342752</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>6239584</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>13803407</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>28572076</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>15282581</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>16594572</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>15223898</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>27696695</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>17717888</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>24163432</v>
+        <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23623477</v>
+        <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>19145601</v>
+        <v>25790711</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30157601</v>
+        <v>27856115</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>41172333</v>
+        <v>20981901</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>34303423</v>
+        <v>25433123</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>35044850</v>
+        <v>19355230</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>33519824</v>
+        <v>24713836</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>4273858</v>
+        <v>7293082</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>23801493</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>27940611</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23197145</v>
+        <v>27893929</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>25790711</v>
+        <v>29635773</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27856115</v>
+        <v>19554230</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20981901</v>
+        <v>23848495</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>25433123</v>
+        <v>24194638</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19355230</v>
+        <v>20330094</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>24713836</v>
+        <v>26044199</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>4164200</v>
+        <v>6761840</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
@@ -4731,60 +4731,60 @@
         <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>1324510</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>10311989</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>19934535</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>13536614</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>22187720</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>11732010</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13949368</v>
+        <v>21143100</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>24539413</v>
+        <v>14330970</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19087217</v>
+        <v>38267409</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>17139440</v>
+        <v>46351274</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>17746930</v>
+        <v>37105387</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>21437830</v>
+        <v>19868191</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>17616397</v>
+        <v>15153480</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>19360848</v>
+        <v>19277087</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>3597346</v>
+        <v>9084376</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
@@ -4797,49 +4797,49 @@
         <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>1324510</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>10311989</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19934535</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>13536614</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>22187720</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>11732010</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21143100</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>14330970</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38267409</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>46351274</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>37105387</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>19868191</v>
+        <v>21437830</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>15153480</v>
+        <v>17616397</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19277087</v>
+        <v>19360848</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>1926980</v>
+        <v>6699656</v>
       </c>
     </row>
     <row r="20">
@@ -4905,7 +4905,7 @@
         <v>30000524</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>2471650</v>
+        <v>6198580</v>
       </c>
     </row>
     <row r="21">
@@ -4971,7 +4971,7 @@
         <v>22535696</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>1532130</v>
+        <v>3284950</v>
       </c>
     </row>
     <row r="22">
@@ -5037,7 +5037,7 @@
         <v>5648770</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>1390160</v>
+        <v>2313170</v>
       </c>
     </row>
     <row r="23">
@@ -5103,7 +5103,7 @@
         <v>10758755</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>1680460</v>
+        <v>2057540</v>
       </c>
     </row>
     <row r="24">
@@ -5489,7 +5489,7 @@
         <v>7</v>
       </c>
       <c r="T5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5555,7 +5555,7 @@
         <v>7</v>
       </c>
       <c r="T6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5621,29 +5621,29 @@
         <v>7</v>
       </c>
       <c r="T7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
       </c>
@@ -5687,28 +5687,28 @@
         <v>7</v>
       </c>
       <c r="T8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>7</v>
@@ -5753,7 +5753,7 @@
         <v>7</v>
       </c>
       <c r="T9" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5819,7 +5819,7 @@
         <v>7</v>
       </c>
       <c r="T10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5885,28 +5885,28 @@
         <v>7</v>
       </c>
       <c r="T11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -5951,28 +5951,28 @@
         <v>7</v>
       </c>
       <c r="T12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" s="42" t="n">
         <v>7</v>
@@ -6017,18 +6017,18 @@
         <v>7</v>
       </c>
       <c r="T13" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
@@ -6083,91 +6083,91 @@
         <v>7</v>
       </c>
       <c r="T14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -6215,25 +6215,25 @@
         <v>7</v>
       </c>
       <c r="T16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -6281,18 +6281,18 @@
         <v>7</v>
       </c>
       <c r="T17" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
@@ -6305,60 +6305,60 @@
         <v>0</v>
       </c>
       <c r="F18" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T18" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -6371,10 +6371,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -6413,7 +6413,7 @@
         <v>7</v>
       </c>
       <c r="T19" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="T20" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -6545,7 +6545,7 @@
         <v>7</v>
       </c>
       <c r="T21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -6611,7 +6611,7 @@
         <v>7</v>
       </c>
       <c r="T22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -6677,7 +6677,7 @@
         <v>7</v>
       </c>
       <c r="T23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2341,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="T5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2407,7 +2407,7 @@
         <v>72.43000000000001</v>
       </c>
       <c r="T6" s="36" t="n">
-        <v>90.5</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="7">
@@ -2473,7 +2473,7 @@
         <v>85.56999999999999</v>
       </c>
       <c r="T7" s="36" t="n">
-        <v>80</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="8">
@@ -2539,7 +2539,7 @@
         <v>61</v>
       </c>
       <c r="T8" s="36" t="n">
-        <v>65.5</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="9">
@@ -2605,205 +2605,205 @@
         <v>50.71</v>
       </c>
       <c r="T9" s="36" t="n">
-        <v>60.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30